--- a/Excel/9_Refrigerants_WIP_v02.prename.bak.xlsx
+++ b/Excel/9_Refrigerants_WIP_v02.prename.bak.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\htdocs\zneagcrc\GAF-VEERG-Functions\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A61542CE-DF03-417F-BFF6-634CD64C7B17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0B48590-F211-4EB9-A343-7920FFF4B11B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="12645" firstSheet="2" activeTab="2" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
+    <workbookView xWindow="2340" yWindow="2340" windowWidth="28800" windowHeight="15345" firstSheet="2" activeTab="6" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
   </bookViews>
   <sheets>
     <sheet name="Home" sheetId="71" r:id="rId1"/>
@@ -19,8 +19,11 @@
     <sheet name="Input - Refrigerants" sheetId="70" r:id="rId4"/>
     <sheet name="9.1.1.1-2 Refrigerant use" sheetId="69" r:id="rId5"/>
     <sheet name="Constants - Refrigerants" sheetId="110" r:id="rId6"/>
-    <sheet name="Constants - Common" sheetId="119" r:id="rId7"/>
+    <sheet name="Constants - Common" sheetId="120" r:id="rId7"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId8"/>
+  </externalReferences>
   <definedNames>
     <definedName name="Common_Equations.Common_ConvertCH4ToCO2e">_xlfn.LAMBDA(_xlpm.E_CH4,_xlpm.GWP_CH4, _xlpm.E_CH4 * _xlpm.GWP_CH4)</definedName>
     <definedName name="Common_Equations.Common_ConvertCH4ToCO2e_Arguments">_xlfn.LAMBDA(_xlfn.MAKEARRAY(2, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"ECH4","Methane emissions (t CH4)";"GWPCH4","Global warming potential for methane (t CO2-e / t CH4)"}, _xlpm.r, _xlpm.c))))</definedName>
@@ -177,6 +180,7 @@
     <definedName name="Common_SourceData.Common_SourceData_WetAndDryZones_Unit">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_WetAndDryZones_Variable">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_WetAndDryZones_Variation">_xlfn.LAMBDA(_xlfn.MAKEARRAY(3, 1, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"VARIATION OF SOURCE DATA:";"Added warm / cool temperate moist / dry - low frost and high temp classes to accommodate climate scenarios excluded by VEERG criteria.";"Fixed typo - Changed 'Fry' to 'Dry'."}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="Common_SourceData_DensityOfMethane_Data">'Constants - Common'!$D$175</definedName>
     <definedName name="CommonCropping_SourceData.CommonCropping_SourceData_FracGASFfInorganicFertiliser_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(6, 3, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Fertiliser type f","FracGASFf","Basis";"Urea-based fertilisers",0.15,"Urea";"Ammonium-based fertilisers",0.08,"Ammonium";"Nitrate-based fertilisers",0.01,"Nitrate";"Ammonium-nitrate based fertilisers",0.05,"Ammonium-nitrate";"Other fertilisers",0.11,"Other"}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="CommonCropping_SourceData.CommonCropping_SourceData_FracGASFfInorganicFertiliser_NIRReference">_xlfn.LAMBDA("IPCC 2019 Refinement Volume 4 Table 11.3 [1, p. 11]")</definedName>
     <definedName name="CommonCropping_SourceData.CommonCropping_SourceData_FracGASFfInorganicFertiliser_Source">_xlfn.LAMBDA("VEERG 2026:Table 12.2.2.9")</definedName>
@@ -2066,126 +2070,6 @@
   <dxfs count="60">
     <dxf>
       <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
@@ -3045,6 +2929,126 @@
         <patternFill patternType="none">
           <fgColor indexed="64"/>
           <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4657,6 +4661,26 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Home"/>
+      <sheetName val="Constants - Common"/>
+      <sheetName val="Acknowledgements"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
 <file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
 <rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
   <global>
@@ -4742,7 +4766,7 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{23E8EA07-16D0-4744-9285-B13305AFD092}" name="Table_SourceData_ClimateZones" displayName="Table_SourceData_ClimateZones" ref="D89:S97" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="25" xr:uid="{35F934AF-96CE-4CF5-A60B-E9B089BC81DF}" name="Table_SourceData_ClimateZones" displayName="Table_SourceData_ClimateZones" ref="D89:S97" totalsRowShown="0">
   <autoFilter ref="D89:S97" xr:uid="{5A437AE9-7724-4CF2-ACCF-291078682FB9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -4762,52 +4786,52 @@
     <filterColumn colId="15" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{AA8187F8-0042-4C0E-A158-2B1DDD89C55E}" name="Climate zone" totalsRowCellStyle="Content bold">
+    <tableColumn id="1" xr3:uid="{F4D32187-9689-4807-97E3-B4C92D417D3A}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{EAA8886F-E011-45A8-B808-0BEFAC3A35DF}" name="MAT" totalsRowDxfId="47" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{D31F47AF-2C35-45B1-BB9E-25301AF21F11}" name="MAT" totalsRowDxfId="35" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{AA7B88F7-095C-4E16-9CF8-A98235D82885}" name="MAP" totalsRowDxfId="46" totalsRowCellStyle="Content bold">
+    <tableColumn id="3" xr3:uid="{3AA65C4C-AF27-4115-8193-750D88828575}" name="MAP" totalsRowDxfId="34" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{0ECBB133-8208-4BC5-87AC-C9A17199BA63}" name="Frost days per year" totalsRowDxfId="45" totalsRowCellStyle="Content bold">
+    <tableColumn id="4" xr3:uid="{C95D7C2D-94FE-4B53-BE81-5D8690A7E23B}" name="Frost days per year" totalsRowDxfId="33" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{3D9AC821-75C8-4D27-BCEF-C2056472F642}" name="Elevation" totalsRowDxfId="44" totalsRowCellStyle="Content bold">
+    <tableColumn id="5" xr3:uid="{78B75B35-D227-4BE6-BE0B-623E34096F44}" name="Elevation" totalsRowDxfId="32" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{D643E4EB-D004-46BD-9D3C-B84163D0D6FB}" name="MAP:PET" totalsRowDxfId="43" totalsRowCellStyle="Content bold">
+    <tableColumn id="6" xr3:uid="{F2E5F8B3-348E-4E83-8B88-25C14A75B279}" name="MAP:PET" totalsRowDxfId="31" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{12A07609-F08E-4413-B6D3-C87FDF66E215}" name="Min temp" totalsRowDxfId="42" totalsRowCellStyle="Content bold">
+    <tableColumn id="7" xr3:uid="{85922B28-B16D-4DC4-A967-AE14609F23B9}" name="Min temp" totalsRowDxfId="30" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{F102AF9F-9FEA-40DD-AF28-041C1461D83E}" name="Max temp" totalsRowDxfId="41" totalsRowCellStyle="Content bold">
+    <tableColumn id="8" xr3:uid="{0235F957-3B8E-4193-9DC3-13B01DA62086}" name="Max temp" totalsRowDxfId="29" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{90A51AC4-8B22-4441-A14C-E02D0326E5F8}" name="Min rainfall" totalsRowDxfId="40" totalsRowCellStyle="Content bold">
+    <tableColumn id="9" xr3:uid="{16D7044C-C5D3-41F4-BC5E-78CF1E858FE4}" name="Min rainfall" totalsRowDxfId="28" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{3FD86231-C6F8-4A32-80AD-5D4060FD1B31}" name="Max rainfall" totalsRowDxfId="39" totalsRowCellStyle="Content bold">
+    <tableColumn id="10" xr3:uid="{74526D7A-ED68-4FA8-9F13-C17608FE4E24}" name="Max rainfall" totalsRowDxfId="27" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{73D202BF-BFCE-42FA-9D0F-2DA13C4481FC}" name="Min frost days" totalsRowDxfId="38" totalsRowCellStyle="Content bold">
+    <tableColumn id="11" xr3:uid="{6757D4E7-76CC-413F-875B-980B201E0504}" name="Min frost days" totalsRowDxfId="26" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{F3AAFA92-EA40-43BB-8481-31088FE8F2A5}" name="Max frost days" totalsRowDxfId="37" totalsRowCellStyle="Content bold">
+    <tableColumn id="15" xr3:uid="{37E37A80-AB6B-4A5C-8522-62A6ED4FC83E}" name="Max frost days" totalsRowDxfId="25" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{EFBF1273-7CCE-435E-9C54-D0FC021C2D12}" name="Min elevation" totalsRowDxfId="36" totalsRowCellStyle="Content bold">
+    <tableColumn id="12" xr3:uid="{EBB3FCD8-6E3F-43BE-A81F-9BA40DDCCF6A}" name="Min elevation" totalsRowDxfId="24" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{35C9987E-D507-47A4-9DE5-D9177126FF2D}" name="Max elevation" totalsRowDxfId="35" totalsRowCellStyle="Content bold">
+    <tableColumn id="16" xr3:uid="{BA1B1A55-157F-49A2-B423-1D6618F9C39B}" name="Max elevation" totalsRowDxfId="23" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{F27CE1D5-2216-4EDB-B3ED-8A6CCE6C7142}" name="Min MAP:PET" totalsRowDxfId="34" totalsRowCellStyle="Content bold">
+    <tableColumn id="13" xr3:uid="{FE7612EE-50DD-455B-A802-19744E0B2DC7}" name="Min MAP:PET" totalsRowDxfId="22" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{520A4B37-7DA2-48BF-AF37-03D14FA097BC}" name="Max MAP:PET" totalsRowDxfId="33" totalsRowCellStyle="Content bold">
+    <tableColumn id="17" xr3:uid="{2E5EF2DF-58FB-4100-A2D7-FB96478581BA}" name="Max MAP:PET" totalsRowDxfId="21" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4816,16 +4840,16 @@
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{5AAD80A4-98CA-4A77-AF91-D13C800FBEDB}" name="Table_SourceData_WetDryZones" displayName="Table_SourceData_WetDryZones" ref="D63:E77" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="28" xr:uid="{0426B1D2-2352-4DCB-A9F8-8C8C2346781E}" name="Table_SourceData_WetDryZones" displayName="Table_SourceData_WetDryZones" ref="D63:E77" totalsRowShown="0">
   <autoFilter ref="D63:E77" xr:uid="{3597E019-B21E-4B76-BCC8-D02D497BCFA9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{4EF58733-2135-49D9-856E-9C4907356A09}" name="Climate zone" totalsRowCellStyle="Content bold">
+    <tableColumn id="1" xr3:uid="{2ED8E2F2-C8F1-4562-9242-D5E2772AB3D4}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{F7659FA5-BEFD-4223-A8BA-0F0B54D3C77A}" name="Wet or Dry Zone" totalsRowDxfId="32" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{B7335F21-A9B1-4DEF-834C-281703478B2D}" name="Wet or Dry Zone" totalsRowDxfId="20" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4834,7 +4858,7 @@
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{B4EF9EAB-A496-4FA6-9FF3-9C2DA7DF988D}" name="Table_SourceData_TemperatureZones" displayName="Table_SourceData_TemperatureZones" ref="D109:G112" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="29" xr:uid="{CBE0606A-3CAF-4CE1-AC24-D4DC40DC05C3}" name="Table_SourceData_TemperatureZones" displayName="Table_SourceData_TemperatureZones" ref="D109:G112" totalsRowShown="0">
   <autoFilter ref="D109:G112" xr:uid="{AB16FEAB-AB03-45E1-BBD4-66D29CD412DF}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -4842,16 +4866,16 @@
     <filterColumn colId="3" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{692CCA7F-354D-4462-A5CC-B470737A3175}" name="Temperature Zone">
+    <tableColumn id="1" xr3:uid="{33C89ED6-F5EE-4D14-9CF5-6D2A36331426}" name="Temperature Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{9417D96B-90BA-4033-B9C6-FDA813678B4C}" name="MAT">
+    <tableColumn id="2" xr3:uid="{972F6417-E1A5-496F-8993-00FF64A3A141}" name="MAT">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{F61EA434-BCC2-42F2-8919-8D2C0B407D0C}" name="Min MAT">
+    <tableColumn id="3" xr3:uid="{80871890-6F44-4C09-9807-B233ED5490DA}" name="Min MAT">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{ECBB14F8-F7FB-45E5-B482-8ACA32BD90F9}" name="Max MAT">
+    <tableColumn id="4" xr3:uid="{571515C8-4435-4667-92BB-14DE15F28E8D}" name="Max MAT">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4860,7 +4884,7 @@
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{CF1750BE-922B-48E8-ADA4-66091A5A0FE9}" name="Table_SourceData_RainfallZones" displayName="Table_SourceData_RainfallZones" ref="D119:G121" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="30" xr:uid="{6D497332-DA71-4BAF-8A78-2105B6F62172}" name="Table_SourceData_RainfallZones" displayName="Table_SourceData_RainfallZones" ref="D119:G121" totalsRowShown="0">
   <autoFilter ref="D119:G121" xr:uid="{E08772F3-2E8C-40A8-B755-08A5BBDF4130}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -4868,16 +4892,16 @@
     <filterColumn colId="3" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{4F8142C1-4652-4EFB-ACD0-F33E4ADF1A95}" name="Rainfall Zone">
+    <tableColumn id="1" xr3:uid="{C9A04143-F828-4783-8D7B-F4163D569297}" name="Rainfall Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{C4EAC22C-2A06-49E0-913C-77E92F7B10F6}" name="Annual rainfall">
+    <tableColumn id="2" xr3:uid="{B813FCF0-34D7-41FE-8A86-9747C8BB585D}" name="Annual rainfall">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{433AECB9-327A-4C6E-8EE9-E1448F5E2DBE}" name="Min rainfall">
+    <tableColumn id="3" xr3:uid="{5A93C354-BCCC-45FB-B6C1-7EB5B328874F}" name="Min rainfall">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{2AA94844-B51B-405E-B9AD-53CEE3499D09}" name="Max rainfall">
+    <tableColumn id="4" xr3:uid="{EC42452E-8DC3-415B-8CA5-C25B157A6C21}" name="Max rainfall">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4886,16 +4910,16 @@
 </file>
 
 <file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{596BD446-2F05-45FD-83F3-42F2F34B5B9E}" name="Table_SourceData_LeachingZones" displayName="Table_SourceData_LeachingZones" ref="D127:E129" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="31" xr:uid="{0F8B52AA-8BEF-4584-AAE6-A9500A6D828D}" name="Table_SourceData_LeachingZones" displayName="Table_SourceData_LeachingZones" ref="D127:E129" totalsRowShown="0">
   <autoFilter ref="D127:E129" xr:uid="{A159E140-02ED-4547-B6E1-6695D8B16A11}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{3FBF0D07-67BB-436A-9984-469656A28704}" name="Leaching Zone">
+    <tableColumn id="1" xr3:uid="{BF9E0B8A-8354-47B3-B838-FC46E4FDD11D}" name="Leaching Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{EC0DCA32-396C-478E-90F8-04A7BED9BB16}" name="Leaching criteria">
+    <tableColumn id="2" xr3:uid="{84ADB0FD-89A7-4F98-92AD-A52B79C5D5B9}" name="Leaching criteria">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4904,16 +4928,16 @@
 </file>
 
 <file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{490FA27C-33C1-4662-9AFF-006C08A4211E}" name="Table_SourceData_DataScores_Scope3" displayName="Table_SourceData_DataScores_Scope3" ref="D153:E158" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="32" xr:uid="{A70A8CA7-1327-470C-AFCF-EB10104749E9}" name="Table_SourceData_DataScores_Scope3" displayName="Table_SourceData_DataScores_Scope3" ref="D153:E158" totalsRowShown="0">
   <autoFilter ref="D153:E158" xr:uid="{133D42B0-F6D2-470A-858A-37E6A7F5EC2B}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{F71770D4-9368-4676-B714-C7475FF89B62}" name="Data source">
+    <tableColumn id="1" xr3:uid="{330CF42B-2587-49FF-A553-2E6208DC544C}" name="Data source">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{0C157665-6F13-4351-A6EB-9119D273426C}" name="Data score">
+    <tableColumn id="2" xr3:uid="{DA9EF727-9C1A-4D4E-8171-9A82880367CC}" name="Data score">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4922,16 +4946,16 @@
 </file>
 
 <file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{9B5F685E-7CFD-4B01-8F98-11C78979ED5D}" name="Table_SourceData_FracWET" displayName="Table_SourceData_FracWET" ref="D134:E136" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="33" xr:uid="{9F776C67-747F-45BC-8671-66B1D124DC3C}" name="Table_SourceData_FracWET" displayName="Table_SourceData_FracWET" ref="D134:E136" totalsRowShown="0">
   <autoFilter ref="D134:E136" xr:uid="{308E99BE-FE1F-47A4-B2CA-97217277C4E9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{75BEBE37-39B4-4E59-A52E-53C1E93F718F}" name="Is in leaching zone">
+    <tableColumn id="1" xr3:uid="{04B33934-32D4-463F-9CA5-2DB963128054}" name="Is in leaching zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{C0D50F48-A838-46A3-8B4E-BD74578D5EA5}" name="FracWET" dataDxfId="31">
+    <tableColumn id="2" xr3:uid="{C4FA5E52-C277-4018-8AF0-C0FC73EDF70B}" name="FracWET" dataDxfId="19">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4940,7 +4964,7 @@
 </file>
 
 <file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{C38EC5FD-5E4F-4880-BB81-BDF89DA918CA}" name="Table_SourceData_Common_EFN2O" displayName="Table_SourceData_Common_EFN2O" ref="D186:H199" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="34" xr:uid="{D715CC72-721C-4EC5-96C1-9F3814696A48}" name="Table_SourceData_Common_EFN2O" displayName="Table_SourceData_Common_EFN2O" ref="D186:H199" totalsRowShown="0">
   <autoFilter ref="D186:H199" xr:uid="{D41FBEA4-8379-4DF7-A068-BF94D364F1A2}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -4949,19 +4973,19 @@
     <filterColumn colId="4" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{CFB3196B-0D9B-41E0-81A6-84DA7CAE04DD}" name="Production system j">
+    <tableColumn id="1" xr3:uid="{8A277B50-D0EE-4ACE-8E8B-EED9ECE40179}" name="Production system j">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{209F7857-519C-48A2-BB2E-9BCB020F651D}" name="EFN2O">
+    <tableColumn id="2" xr3:uid="{13921FCD-B117-443D-8595-AB03C4DE4C0F}" name="EFN2O">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{5DF0D2F4-5F2B-4DE6-ADC7-CD7463078EEE}" name="Production system only">
+    <tableColumn id="3" xr3:uid="{90B54C62-B4A3-4CB8-9470-7093FE328B81}" name="Production system only">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{EC04533A-568D-4D72-AC19-2C7248B47182}" name="Irrigation method">
+    <tableColumn id="4" xr3:uid="{FA768EDC-6E2D-47B9-863D-8A063CC351C1}" name="Irrigation method">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{C32F65B2-1CB1-4ABE-9FC4-BE4364E12ECE}" name="Rainfall zone">
+    <tableColumn id="5" xr3:uid="{632496A2-D38D-48EE-8760-3B64C07C0852}" name="Rainfall zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4970,16 +4994,16 @@
 </file>
 
 <file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{89729ED1-E86C-4E41-B0BE-BE545A1501D2}" name="Table_SourceData_FracWETIrrigation" displayName="Table_SourceData_FracWETIrrigation" ref="D142:E147" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="35" xr:uid="{83E7C448-A724-4445-AD75-232480A2E6BE}" name="Table_SourceData_FracWETIrrigation" displayName="Table_SourceData_FracWETIrrigation" ref="D142:E147" totalsRowShown="0">
   <autoFilter ref="D142:E147" xr:uid="{1F48CA34-50DE-46D5-B32A-BB3A1E818E37}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{058EE474-821C-46B8-B9DB-A856FC27B7A9}" name="Irrigation type i">
+    <tableColumn id="1" xr3:uid="{B7346040-DB38-49E4-A9B9-D34F265E843C}" name="Irrigation type i">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{64C441F6-07CD-4748-BEAE-C8625EB5AEF9}" name="FracWET" dataDxfId="30" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{D960657A-BD1E-45D3-825A-C3C29BB6893B}" name="FracWET" dataDxfId="18" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4988,16 +5012,16 @@
 </file>
 
 <file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{578524F2-0357-449F-ABA2-BC0D3754A4DA}" name="Table_SourceData_EFPastureRangeAndPaddock" displayName="Table_SourceData_EFPastureRangeAndPaddock" ref="D206:E208" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="36" xr:uid="{1228D111-2F00-4F48-B056-B438A3F69665}" name="Table_SourceData_EFPastureRangeAndPaddock" displayName="Table_SourceData_EFPastureRangeAndPaddock" ref="D206:E208" totalsRowShown="0">
   <autoFilter ref="D206:E208" xr:uid="{D5BE3F89-D70E-4C53-A71C-E756622DEF38}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{A9D82E06-BBC8-48FF-87E0-4E5D302CD314}" name="Climate zone">
+    <tableColumn id="1" xr3:uid="{A7591274-8B84-419F-8426-A123AEF27A2B}" name="Climate zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{6B8B8187-2CE6-4828-B655-AC0E679BD856}" name="EFPRP" dataDxfId="29" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{3B251A85-EA78-4BF5-AE28-FBBB25AE45AF}" name="EFPRP" dataDxfId="17" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5036,16 +5060,16 @@
 </file>
 
 <file path=xl/tables/table20.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="22" xr:uid="{87C71CAF-1371-452F-BE5F-BBFF68E929C1}" name="Table_SourceData_Common_MonthToSeason" displayName="Table_SourceData_Common_MonthToSeason" ref="D212:E224" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="37" xr:uid="{94DF2052-FF8A-4A05-976F-88BB68FAA76C}" name="Table_SourceData_Common_MonthToSeason" displayName="Table_SourceData_Common_MonthToSeason" ref="D212:E224" totalsRowShown="0">
   <autoFilter ref="D212:E224" xr:uid="{97796C3A-D95E-4077-AA20-A8FE4145DAAD}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{DB86F89E-F0C6-4E23-84FA-724586BBF2C0}" name="Month">
+    <tableColumn id="1" xr3:uid="{98D96C85-70B0-47BB-B6FA-37B5BBD3A0C5}" name="Month">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{E19CC679-0382-4B3E-B2BA-CA84BD9BEC57}" name="Season" dataDxfId="28" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{50CEE149-B6ED-4E47-AC7F-E706418D8D14}" name="Season" dataDxfId="16" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5054,7 +5078,7 @@
 </file>
 
 <file path=xl/tables/table21.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="26" xr:uid="{3E8C17E0-8327-49FB-920D-57E9236C3ACA}" name="Table_SourceData_Common_MCFTemperatureZone" displayName="Table_SourceData_Common_MCFTemperatureZone" ref="D231:S250" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="38" xr:uid="{9EDF6F40-482A-4F82-ABA1-1F207CA28176}" name="Table_SourceData_Common_MCFTemperatureZone" displayName="Table_SourceData_Common_MCFTemperatureZone" ref="D231:S250" totalsRowShown="0">
   <autoFilter ref="D231:S250" xr:uid="{1D72DD9B-C8FA-48F4-9A11-20231FF87B5A}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -5074,52 +5098,52 @@
     <filterColumn colId="15" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{DD282435-2C2B-4691-B43F-3A454A86ADF0}" name="Temperature zone">
+    <tableColumn id="1" xr3:uid="{EDBA0716-8D09-453B-B867-D734BB273273}" name="Temperature zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{9F6E82C4-3071-42FC-93D6-968F926A0031}" name="MAT (ºC)" dataDxfId="27" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{362D9B5A-5BDF-4D20-AEE9-44EE5CA47472}" name="MAT (ºC)" dataDxfId="15" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{B27891F1-2A40-4958-9F1E-6BEBC12FF7C4}" name="Anaerobic lagoon" dataDxfId="26" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{02734B5F-8E99-48B0-8AFD-5D124B34FC2E}" name="Anaerobic lagoon" dataDxfId="14" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{5662A798-B4DE-4CC1-A843-7A6191D9632B}" name="Digester / covered lagoons" dataDxfId="25" dataCellStyle="Content normal">
+    <tableColumn id="4" xr3:uid="{A99A40B6-6526-4E7B-8907-C79C81154353}" name="Digester / covered lagoons" dataDxfId="13" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{605030C8-492D-4496-BF8E-7FA67C7FE1EA}" name="Liquid systems" dataDxfId="24" dataCellStyle="Content normal">
+    <tableColumn id="5" xr3:uid="{8EC7811A-5957-4303-B6C1-8C02C7F3874D}" name="Liquid systems" dataDxfId="12" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{0002A82C-EACF-411E-A58B-682D7665BB39}" name="Daily spread" dataDxfId="23" dataCellStyle="Content normal">
+    <tableColumn id="6" xr3:uid="{CF854FEA-BA45-4097-B4A8-613400CC7B7C}" name="Daily spread" dataDxfId="11" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{4BF9F484-91EC-450F-8028-73876D34E694}" name="Composting (passive windrow)" dataDxfId="22" dataCellStyle="Content normal">
+    <tableColumn id="7" xr3:uid="{256FC14B-3AAE-41ED-BC85-E23034611119}" name="Composting (passive windrow)" dataDxfId="10" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{8A5C68A4-F5AA-4764-A03E-2279AB444523}" name="Solid storage" dataDxfId="21" dataCellStyle="Content normal">
+    <tableColumn id="8" xr3:uid="{D34CD105-5F3D-4C97-A69A-C45F0554A9F6}" name="Solid storage" dataDxfId="9" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{123BF989-3B2E-4BA3-8E54-20C4BE277CFE}" name="Pit storage" dataDxfId="20" dataCellStyle="Content normal">
+    <tableColumn id="9" xr3:uid="{5D362D2B-8937-483C-91EB-73C8289D01E0}" name="Pit storage" dataDxfId="8" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{8DAAE1D4-960B-4197-A78A-30E617DF6E41}" name="Deep litter" dataDxfId="19" dataCellStyle="Content normal">
+    <tableColumn id="10" xr3:uid="{01FEDDEA-105A-4F7A-8063-CC4AB0023BE7}" name="Deep litter" dataDxfId="7" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{34450AE7-D05C-4631-8EE5-4679D80792CD}" name="Poultry manure with bedding" dataDxfId="18" dataCellStyle="Content normal">
+    <tableColumn id="11" xr3:uid="{6DD86747-26C4-4628-B797-F18D306EE9F5}" name="Poultry manure with bedding" dataDxfId="6" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{3C9DF90B-C67E-43D8-8207-6500A71BC3F4}" name="Poultry manure without bedding" dataDxfId="17" dataCellStyle="Content normal">
+    <tableColumn id="12" xr3:uid="{074792B9-0B22-4676-893B-02626C137D46}" name="Poultry manure without bedding" dataDxfId="5" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{89E1FE1C-A229-4E74-BA5A-27BCE54D61FC}" name="Direct processing" dataDxfId="16" dataCellStyle="Content normal">
+    <tableColumn id="13" xr3:uid="{6F6A2A0F-FCEA-4196-A8A3-7F6A414720D5}" name="Direct processing" dataDxfId="4" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{12B2DF86-A0C2-49AA-921F-AD97795AEDAB}" name="Direct application" dataDxfId="15" dataCellStyle="Content normal">
+    <tableColumn id="14" xr3:uid="{25617266-488F-4561-AD41-D73A03A353F1}" name="Direct application" dataDxfId="3" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{782429A0-44D3-4681-BFA0-84CC3419FDAC}" name="Pasture range and paddock" dataDxfId="14" dataCellStyle="Content normal">
+    <tableColumn id="15" xr3:uid="{F1D43D45-E8C9-4B8A-B8FB-AD14A03B3CBE}" name="Pasture range and paddock" dataDxfId="2" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{FF208E44-6053-4431-AA07-E648AB1553AE}" name="MAT raw" dataDxfId="13" dataCellStyle="Content normal">
+    <tableColumn id="16" xr3:uid="{0E77FE88-E605-4FB3-BABB-0DE5602481CD}" name="MAT raw" dataDxfId="1" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5128,16 +5152,16 @@
 </file>
 
 <file path=xl/tables/table22.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="27" xr:uid="{6D5D4212-3420-44AD-9282-E9DBF49BF3A5}" name="Table_SourceData_Common_EFOrganicFertCropResidues" displayName="Table_SourceData_Common_EFOrganicFertCropResidues" ref="D257:E259" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="39" xr:uid="{5703C3BD-C6EC-49C8-B80F-08D95B37F5F5}" name="Table_SourceData_Common_EFOrganicFertCropResidues" displayName="Table_SourceData_Common_EFOrganicFertCropResidues" ref="D257:E259" totalsRowShown="0">
   <autoFilter ref="D257:E259" xr:uid="{56E01C14-1BB8-4015-9158-4CEB4D3B605C}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{27068885-8281-4700-BCD0-1F0F37B151C2}" name="Climate Zone">
+    <tableColumn id="1" xr3:uid="{DE4A49FA-F17F-4010-8199-0AECFDC56C16}" name="Climate Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{4BCC72ED-670B-4B3C-AECD-20306DA91098}" name="EFNi &amp; EFN2Oi" dataDxfId="12" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{23A52A90-7B5E-45DE-BAB7-5FCDA26BD6F8}" name="EFNi &amp; EFN2Oi" dataDxfId="0" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5238,20 +5262,20 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{39B225CC-22FF-489B-944A-4F2BEE1F8643}" name="Table_AustralianStates" displayName="Table_AustralianStates" ref="D6:F14" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{4CC0FA2D-F236-4FA4-A4AB-16DD3082EFF1}" name="Table_AustralianStates" displayName="Table_AustralianStates" ref="D6:F14" totalsRowShown="0">
   <autoFilter ref="D6:F14" xr:uid="{E0906749-7FC7-47DE-82F6-F796C4463018}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{0ACCCA86-D47A-49E6-B57D-A4B7CE23D744}" name="State/Territory">
+    <tableColumn id="1" xr3:uid="{7C8CC3F7-1F3A-4ACF-80CD-70DBCC6302E2}" name="State/Territory">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{B27BEAA4-A451-46EC-B597-B9703A1B45A7}" name="Common Name">
+    <tableColumn id="2" xr3:uid="{E0D976A2-258F-456E-9A0A-3ACEE6433023}" name="Common Name">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{9FC59DF2-1592-4CD6-AF02-761876063B49}" name="Abbreviation">
+    <tableColumn id="3" xr3:uid="{A4E2291F-308E-4DCC-94D8-8402210DAB7C}" name="Abbreviation">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5260,12 +5284,12 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{0A034682-B3AF-4777-98F1-9BE6449F5298}" name="Table_WASA4Areas" displayName="Table_WASA4Areas" ref="D20:D30" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{F66A21CD-97D0-4DFD-A07D-AFA5C4B83482}" name="Table_WASA4Areas" displayName="Table_WASA4Areas" ref="D20:D30" totalsRowShown="0">
   <autoFilter ref="D20:D30" xr:uid="{5FA81339-C6C8-4D36-BEEA-6C4AEDD9E676}">
     <filterColumn colId="0" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{6DBBCDA6-30C0-4638-8E70-258F978DAC2B}" name="SA 4 Name">
+    <tableColumn id="1" xr3:uid="{5A8C3B5C-65E6-43A7-AD03-EFA8A646E46C}" name="SA 4 Name">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5274,16 +5298,16 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{591615C9-B0E8-48DF-83C0-32D82AC8F59D}" name="Table_GWPData" displayName="Table_GWPData" ref="D36:E43" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="23" xr:uid="{3194DE87-7B8E-4F4A-B07F-2135F74CCB15}" name="Table_GWPData" displayName="Table_GWPData" ref="D36:E43" totalsRowShown="0">
   <autoFilter ref="D36:E43" xr:uid="{B8E87A66-3E41-4AD3-925D-01EE21B43D7A}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{56F20BC2-56F5-427B-8FF1-7EF09C514D4E}" name="Gas">
+    <tableColumn id="1" xr3:uid="{5BE5BAFA-F63C-47D6-AA89-54999E5643E7}" name="Gas">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{C03A9D3C-DC7B-4F14-83E7-72FA50D1D978}" name="CO2-e factor">
+    <tableColumn id="2" xr3:uid="{8FC2654C-AC0A-423C-82C1-4ACFDA775C94}" name="CO2-e factor">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5292,7 +5316,7 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{C2AF2589-D67C-4A7B-8DF4-E3C3EA7870C2}" name="Table_GasToMolecularConversionFactor" displayName="Table_GasToMolecularConversionFactor" ref="D47:H54" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="24" xr:uid="{6CC29DBA-7D7A-4305-B57F-6B26ECAAEB19}" name="Table_GasToMolecularConversionFactor" displayName="Table_GasToMolecularConversionFactor" ref="D47:H54" totalsRowShown="0">
   <autoFilter ref="D47:H54" xr:uid="{C1F562BB-DAA6-45BB-951A-7BAFA5B64B45}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -5301,19 +5325,19 @@
     <filterColumn colId="4" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{F494CD3D-C587-4121-ACC7-41E23F5D8191}" name="Gas">
+    <tableColumn id="1" xr3:uid="{856EBDC2-CAD0-4095-82B6-48E43D6679EF}" name="Gas">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{259B97AB-2FE6-4FFB-A603-AD4E4F868E5E}" name="Conversion factor">
+    <tableColumn id="5" xr3:uid="{01D5A72D-A244-4963-B6C6-FE99F9FB5DC2}" name="Conversion factor">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{20CFD2D3-87F3-4A7E-8D15-1F8646164388}" name="Conversion factor 1">
+    <tableColumn id="2" xr3:uid="{715A88DB-11B5-4E12-9732-6DB84FF7F9FF}" name="Conversion factor 1">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{76ABA1C2-D154-4611-93A1-492948E1A4E1}" name="Conversion factor 2">
+    <tableColumn id="3" xr3:uid="{83D0A398-2CF5-471B-9915-A6513C75FE04}" name="Conversion factor 2">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{E61BB90F-07C1-464B-861B-4976CFBE2EEC}" name="Conversion factor combined">
+    <tableColumn id="4" xr3:uid="{3BEF8B8F-BF63-4D61-B5A1-B58E6277797B}" name="Conversion factor combined">
       <calculatedColumnFormula>Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 1]]/Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 2]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7450,62 +7474,62 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F49">
-    <cfRule type="cellIs" dxfId="11" priority="62" operator="lessThan">
+    <cfRule type="cellIs" dxfId="47" priority="62" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F128:F129">
-    <cfRule type="cellIs" dxfId="10" priority="21" operator="lessThan">
+    <cfRule type="cellIs" dxfId="46" priority="21" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F140:F141">
-    <cfRule type="cellIs" dxfId="9" priority="20" operator="lessThan">
+    <cfRule type="cellIs" dxfId="45" priority="20" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F152:F153">
-    <cfRule type="cellIs" dxfId="8" priority="19" operator="lessThan">
+    <cfRule type="cellIs" dxfId="44" priority="19" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F164:F165">
-    <cfRule type="cellIs" dxfId="7" priority="18" operator="lessThan">
+    <cfRule type="cellIs" dxfId="43" priority="18" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F252:F253">
-    <cfRule type="cellIs" dxfId="6" priority="93" operator="lessThan">
+    <cfRule type="cellIs" dxfId="42" priority="93" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F257:F258">
-    <cfRule type="cellIs" dxfId="5" priority="92" operator="lessThan">
+    <cfRule type="cellIs" dxfId="41" priority="92" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F262:F263">
-    <cfRule type="cellIs" dxfId="4" priority="91" operator="lessThan">
+    <cfRule type="cellIs" dxfId="40" priority="91" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F286:F287">
-    <cfRule type="cellIs" dxfId="3" priority="85" operator="lessThan">
+    <cfRule type="cellIs" dxfId="39" priority="85" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F291:F292">
-    <cfRule type="cellIs" dxfId="2" priority="84" operator="lessThan">
+    <cfRule type="cellIs" dxfId="38" priority="84" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F296:F297">
-    <cfRule type="cellIs" dxfId="1" priority="83" operator="lessThan">
+    <cfRule type="cellIs" dxfId="37" priority="83" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H45:H47 E212:G212">
-    <cfRule type="cellIs" dxfId="0" priority="79" operator="lessThan">
+    <cfRule type="cellIs" dxfId="36" priority="79" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15104,7 +15128,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CEB3E54E-9905-434A-883A-4B73532B3F1C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1163C6D-A6A6-4601-955D-5E31CC5AAC07}">
   <dimension ref="A1:BY259"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
@@ -19096,6 +19120,19 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgAFwAdQAwADAAMgA3AEYAcgB5AFwAdQAwADAAMgA3ACAAdABvACAAXAB1ADAAMAAyADcARAByAHkAXAB1ADAAMAAyADcALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIAVwBlAHQAIABvAHIAIABEAHIAeQAgAFoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAHcAYQByAG0AIAAvACAAYwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALwAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0ACAAYQBuAGQAIABoAGkAZwBoACAAdABlAG0AcAAgAGMAbABhAHMAcwBlAHMAIAB0AG8AIABhAGMAYwBvAG0AbQBvAGQAYQB0AGUAIABjAGwAaQBtAGEAdABlACAAcwBjAGUAbgBhAHIAaQBvAHMAIABlAHgAYwBsAHUAZABlAGQAIABiAHkAIABWAEUARQBSAEcAIABjAHIAaQB0AGUAcgBpAGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBpAHgAZQBkACAAdAB5AHAAbwAgAGkAbgAgAE0AQQBUACAAdgBhAGwAdQBlACAAZgBvAHIAIAB3AGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABjAGgAYQBuAGcAZQBkACAAMQAwACAAdABvACAAMQAxAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAG0AaQBuACAAYQBuAGQAIABtAGEAeAAgAGMAbwBsAHUAbQBuAHMAIABmAG8AcgAgAE0AQQBUACwAIABNAEEAUAAsACAAZgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgAsACAAZQBsAGUAdgBhAHQAaQBvAG4ALAAgAE0AQQBQADoAUABFAFQAIAB0AG8AIABjAGEAbABjAHUAbABhAHQAZQAgAHoAbwBuAGUAcwAgAGYAcgBvAG0AIAByAGUAYQBsACAAYwBsAGkAbQBhAHQAZQAgAGQAYQB0AGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBBAEYAIABhAGMAYwBlAHAAdABzACAAcgBhAGkAbgBmAGEAbABsACAAYQBzACAAYQAgAHAAcgBvAHgAeQAgAGYAbwByACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUAFwAIgAsACAAXAAiAE0AQQBQAFwAIgAsACAAXAAiAEYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIAXAAiACwAIABcACIARQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAHQAZQBtAHAAXAAiACwAIABcACIATQBhAHgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AaQBuACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AYQB4ACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AaQBuACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGEAeAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBpAG4AIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGEAeAAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADIAMAAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAG0AIAAtACAAZCIgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAxADAAMAAwAC4AMAAwADEALAAgADIAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQBcACIALAAgADEAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB0AGUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFQAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAUAAgAD0AIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEUAVAAgAD0AIABwAG8AdABlAG4AdABpAGEAbAAgAGUAdgBhAHAAbwB0AHIAYQBuAHMAcABpAHIAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAE0AQQBUACAAbQBpAG4AIABhAG4AZAAgAE0AQQBUACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AZQBkAGkAYQBuACAAQQBuAG4AdQBhAGwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAAoAE0AQQBUACkAXAAiACwAIABcACIATQBpAG4AIABNAEEAVABcACIALAAgAFwAIgBNAGEAeAAgAE0AQQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiIAAyADYAIABDAFwAIgAsACAAMgA2ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgAFwAIgAxADUAIAAtACAAMgA1ACAAQwBcACIALAAgADEANQAsACAAMgA1AC4AOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIiAAMQA0ACAAQwBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEANAAuADkAOQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABaAG8AbgBlAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AaQBuAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAXAB1ADAAMAAzAGUAIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAXAB1ADAAMAAzAGUAowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABkAG8AZQBzACAAbgBvAHQAIABvAGMAYwB1AHIAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAGQiowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBzACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAWQBlAHMAIAAtACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvACAALQAgAG4AbwB0ACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAZABhAHQAYQAgAHMAYwBvAHIAZQBzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFgAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAdABhACAAcwBvAHUAcgBjAGUAXAAiACwAIABcACIARABhAHQAYQAgAHMAYwBvAHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAHQAZQByAG4AYQB0AGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUAIABvAHIAIAByAGUAZwBpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAGkAbgB0AGUAbgBzAGkAdAB5ACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIABhAHAAcAByAG8AdgBlAGQAIABtAGUAdABoAG8AZABcACIALAAgADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBlAHIAaQBmAGkAZQBkACAAYwByAGUAZABlAG4AdABpAGEAbAAgAG0AYQB0AGMAaABpAG4AZwAgAEkAUwBPADEANAAwADYANwBcACIALAAgADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIAAoADMALgBEAC4AYgAuADIAKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBMAEUAQQBDAEgAXAAiACwAMAAuADIANABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AIAAzAC4ARAAuAEIAXwAxADAAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAGwAZQBhAGMAaABcACIALAAwAC4AMAAxADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADUALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACwAXAAiAEUARgBOADIATwBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5AFwAIgAsACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAA1ADkALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAXAAiACwAMAAuADAAMAA3ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABsAG8AdwAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAMgA5ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAaABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAOAAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAMAAuADAAMQA5ADkALAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsADAALgAwADAANQAzACwAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAMAAuADAAMAA2ADQALAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABjAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnACkAXAAiACwAMAAuADAAMAAzACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBDAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABzAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnACkAXAAiACwAMAAuADAAMAA1ACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBTAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAMAAuADAAMAAyADYALAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABkAHUAcABsAGkAYwBhAHQAZQAgAFwAdQAwADAAMgA3AEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcAHUAMAAwADIANwAsACAAXAB1ADAAMAAyADcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcAHUAMAAwADIANwAgAGEAbgBkACAAXAB1ADAAMAAyADcAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AG4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAdQAwADAAMgA3ACAAcgBvAHcAIAB3AGkAdABoACAAcwBhAG0AZQAgAEUARgAgAGYAbwByACAAbABvAHcAIABhAG4AZAAgAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXABuAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXABuAEkAUABDAEMAOgAgAE4AMgBPACAARQBNAEkAUwBTAEkATwBOAFMAIABGAFIATwBNACAATQBBAE4AQQBHAEUARAAgAFMATwBJAEwAUwAsACAAQQBOAEQAIABDAE8AMgAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAEwASQBNAEUAIABBAE4ARAAgAFUAUgBFAEEAIABBAFAAUABMAEkAQwBBAFQASQBPAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAFcARQBUACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAQwBoAGEAcAB0AGUAcgAgADEALAAgAHMAZQBjAHQAaQBvAG4AIAAxAC4AOAAuADIAIABMAGUAYQBjAGgAaQBuAGcALAAgAGMAbABpAG0AYQB0AGUAIABhAG4AZAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAUgBlAGYAaQBuAGUAbQBlAG4AdAAgAFYAbwBsAHUAbQBlACAANAA6ACAAQwBoAGEAcAB0AGUAcgAgADEAMQA6ACAATgAyAE8AIABFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABNAGEAbgBhAGcAZQBkACAAUwBvAGkAbABzACwAIABhAG4AZAAgAEMATwAyACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATABpAG0AZQAgAGEAbgBkACAAVQByAGUAYQAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlACAAaQByAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBwAHIAaQBuAGsAbABlAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAcgBmAGEAYwBlACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABUAGEAYgBsAGUAIABjAHIAZQBhAHQAZQBkACAAYgBhAHMAZQBkACAAbwBuACAAVgBFAEUAUgBHACAAdABlAHgAdAAgAFwAdQAwADAAMgA3AEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuAFwAdQAwADAAMgA3AFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAOgAgAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAFAAUgBQACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgAyAE8AIAAtACAATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIABcACIARQBGAFAAUgBQAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAB1ADAAMAAyADcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAdQAwADAAMgA3ACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AbwBuAHQAaABzACAAdABvACAAUwBlAGEAcwBvAG4AcwAgAE0AYQBwAHAAaQBuAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AbgB0AGgAXAAiACwAIABcACIAUwBlAGEAcwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAYQBuAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBiAHIAdQBhAHIAeQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAHIAYwBoAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHAAcgBpAGwAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQB5AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbgBlAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbAB5AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAZwB1AHMAdABcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAHAAdABlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AYwB0AG8AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB2AGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGMAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAbgB1AHIAZQAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAIAATICAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAegBvAG4AZQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA4AC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAyACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAIAAoALoAQwApAFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAUwBsAHUAcgByAHkAIAAoAHcAaQB0AGgAbwB1AHQAIABuAGEAdAB1AHIAYQBsACAAYwByAHUAcwB0ACkAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAGIAKQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABTAHQAbwByAGEAZwBlACAAXAB1ADAAMAAzAGMAMQAgAG0AbwBuAHQAaABcACIALAAgAFwAIgBEAGUAZQBwACAATABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAE0AYQBuAHUAcgBlACAAKAB3AGkAdABoAC8AdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACkAXAAiACwAIABcACIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAaQBuAHQAbwAgAHAAZQBsAGwAZQB0AGkAegBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACwAIABSAGEAbgBnAGUAIABhAG4AZAAgAFAAYQBkAGQAbwBjAGsAIAAoAGMAKQAoAGQAKQBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAXAAiAGQiMQAwAFwAIgAsACAAMAAuADYANgAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMQAsACAAMAAuADYAOAAsACAAMAAuADEALAAgADAALgAxADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAyACwAIAAwAC4ANwAsACAAMAAuADEALAAgADAALgAxADMALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAzACwAIAAwAC4ANwAxACwAIAAwAC4AMQAsACAAMAAuADEANAAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADQALAAgADAALgA3ADMALAAgADAALgAxACwAIAAwAC4AMQA1ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADUALAAgADAALgA3ADQALAAgADAALgAxACwAIAAwAC4AMQA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA2ACwAIAAwAC4ANwA1ACwAIAAwAC4AMQAsACAAMAAuADEAOAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANwAsACAAMAAuADcANgAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA4ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIAMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOQAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADAALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA2ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAxACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIAOQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMgAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAzADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADMALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA0ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANQAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANgAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADQALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANwAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANAA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIABcACIAZSIyADgAXAAiACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwBcACIALAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZABcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgAgAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAcgBvAHcAIABvAGYAIABOAEkAUgAgAE0ATQBBACAAZABlAGYAaQBuAGkAdABpAG8AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuACAARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AFAAbwB1AGwAdAByAHkAIAB3AGkAdABoACAAYQBuAGQAIAB3AGkAdABoAG8AdQB0ACAAbABpAHQAdABlAHIAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABzAGUAcABhAHIAYQB0AGUAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AE0AQQBUACAAcgBhAHcAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHQAbwAgAGEAbABsAG8AdwAgAGwAbwBvAGsAdQBwACAAbwBmACAAbgB1AG0AYgBlAHIAcwAuAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBuAGQAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYATgBpACAAXAB1ADAAMAAyADYAIABFAEYATgAyAE8AaQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADEALgA0AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBOAGkAIABcAHUAMAAwADIANgAgAEUARgBOADIATwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAE4AMgBPACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUATgAyAE8AOgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXABuAEcAVwBQAE4AMgBPADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBOADIATwAsACAARwBXAFAAXwBOADIATwAsAFwAbgAgACAAIAAgAEUAXwBOADIATwAgACoAIABHAFcAUABfAE4AMgBPAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AE4AMgBPAH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AE4AMgBPAH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBOADIATwBcACIALABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAATgAyAE8AXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAEMASAA0ACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUAQwBIADQAOgAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXABuAEcAVwBQAEMASAA0ADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBDAEgANAAsACAARwBXAFAAXwBDAEgANAAsAFwAbgAgACAAIAAgAEUAXwBDAEgANAAgACoAIABHAFcAUABfAEMASAA0AFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEMASAA0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AEMASAA0AH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AEMASAA0AH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAEgANABcACIALABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAAQwBIADQAXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkALABcAG4AIAAgACAAIABSAE8AVwAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAgAC0AIAAxAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACwAXABuACAAIABDAE8ATABVAE0ATgAoAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAQQByAHIAYQB5AEQAYQB0AGEALAAgAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAIABbAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAXQAsAFwAbgAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgAEkATgBEAEUAWAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABVAE4ASQBRAFUARQAoAEEAcgByAGEAeQBEAGEAdABhACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwAoACkALQBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwAKQAgACsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApACwAIAAxACwAIABDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAIABcACIAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAASQBGACgASQBTAE4AVQBNAEIARQBSACgAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgAgACAAIAAgACkALAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkALAAgADAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABbAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlAF0ALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAMQAsACAAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACkAKgAoAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlADIAKQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE8AbgBlAEMAbwBsAHUAbQBuAEEAbgBkAEgAZQBhAGQAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBmAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQAsACAAXAAiAFwAIgAsACAAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQwBlAGwAbAAsACAARABlAGwAaQBtAGkAdABlAHIALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEAXQAsACAAWwBDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgBdACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgBYAE0ATAAoAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAdQAwADAAMwBjAHQAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAIABcAHUAMAAwADIANgBcAG4AIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFMAVQBCAFMAVABJAFQAVQBUAEUAKABDAGUAbABsACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEALABcACIAXAAiACkALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABEAGUAbABpAG0AaQB0AGUAcgAsAFwAIgBcAHUAMAAwADMAYwAvAHMAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAXABuACAAIAAgACAAIAAgACAAIAApACAAXAB1ADAAMAAyADYAXABuACAAIAAgACAAIAAgACAAIABcACIAXAB1ADAAMAAzAGMALwBzAFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAC8AdABcAHUAMAAwADMAZQBcACIALABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAvAC8AcwBcACIAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAdgBnAFQAZQBtAHAALABhAHYAZwBSAGEAaQBuACwAZgByAG8AcwB0AEQAYQB5AHMALABlAGwAZQB2ACwAbQBhAHAAXwBwAGUAdAAsAFwAbgAgACAAIAAgAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACwAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkALABtAGEAeABGAHIAbwBzAHQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4AUABFAFQAQQByAHIAYQB5ACwAbQBhAHgAUABFAFQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAYwBsAGkAbQBhAHQAZQBaAG8AbgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBSAGEAaQBuACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AYQB2AGcAUgBhAGkAbgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AZgByAG8AcwB0AEQAYQB5AHMAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AG0AYQBwAF8AcABlAHQAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AG0AYQBwAF8AcABlAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABBAEsARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAGMAbABpAG0AYQB0AGUAWgBvAG4AZQBBAHIAcgBhAHkALABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgADEAXABuACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAE0AaQBuAEEAcgByAGEAeQAsACAATQBhAHgAQQByAHIAYQB5ACwAIABJAHQAZQBtAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAE0AaQBuAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBhAHgAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABJAHQAZQBtAEEAcgByAGEAeQAsACAAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAQwByAGkAdABlAHIAaQBhADEALAAgAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5ACwAIABRAHUAYQBuAHQAaQB0AHkALAAgAFsATQB1AGwAdABpAHAAbABpAGUAcgBdACwAIABbAEMAcgBpAHQAZQByAGkAYQAyAF0ALABbAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQBdACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAG0AdQBsAHQAaQBwAGwAaQBlAHIALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgATQB1AGwAdABpAHAAbABpAGUAcgApACwAMQAsAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsAFwAbgAgACAAIAAgAHEAdQBhAG4AdABpAHQAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACoATQB1AGwAdABpAHAAbABpAGUAcgAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMQApACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADIALABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAcgBpAHQAZQByAGkAYQAyACkALAAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADIAKQApACwAXABuACAAIAAgACAAUwBVAE0AUABSAE8ARABVAEMAVAAoAGMAcgBpAHQAZQByAGkAYQAxACoAYwByAGkAdABlAHIAaQBhADIAKgBxAHUAYQBuAHQAaQB0AHkAKQBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAXABuACAAIAAgACAAIAAgACAAIABBACwAUwAtADMANgA1ACwAXABuACAAIAAgACAAIAAgACAAIAB5AGEALABZAEUAQQBSACgAQQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AGIALABZAEUAQQBSACgARQApACwAXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApAFwAdQAwADAAMwBjACAAUwApACwAXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAFwAdQAwADAAMwBlACAARQApACwAXABuACAAIAAgACAAIAAgACAAIABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsACAALwAqAGgAZQBsAHAAZQByADoAIABlAG4AZAAgAGQAYQB0AGUAIABmAG8AcgAgAGEAIAByAGUAcABvAHIAdABpAG4AZwAgAHAAZQByAGkAbwBkACAAcwB0AGEAcgB0AGkAbgBnACAAYQB0ACAAYQAgAGcAaQB2AGUAbgAgAGQAYQB0AGUAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAIAAvACoAbwBuAGwAeQAgAG4AZQBlAGQAIAB0AG8AIABsAG8AbwBrACAAYgBhAGMAawAgADMANgA1ACAAZABhAHkAcwAoAG0AYQB4ACAAbwB2AGUAcgBsAGEAcAAgAHcAaQBuAGQAbwB3ACkAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYQAgAGUAbgBkAHMAIABiAGUAZgBvAHIAZQAgAFMALABpAHQAIABjAGEAbgBcAHUAMAAwADIANwB0ACAAbwB2AGUAcgBsAGEAcAA7ACAAbQBvAHYAZQAgAHQAbwAgAG4AZQB4AHQAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAXAB1ADAAMAAzAGMAUwApACwAIAAvACoAaQBmACAAdABoAGUAIABhAG4AYwBoAG8AcgAgAGYAbwByACAAeQBiACAAcwB0AGEAcgB0AHMAIABhAGYAdABlAHIAIABFACwAaQB0ACAAYwBhAG4AXAB1ADAAMAAyADcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABwAHIAZQB2AGkAbwB1AHMAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAXAB1ADAAMAAzAGUARQApACwAXABuACAAIAAgACAAIAAgACAAIABuACwATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAcgBzACwAUwBFAFEAVQBFAE4AQwBFACgAbgAsADEALABmAGkAcgBzAHQAWQBlAGEAcgAsADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMALABEAEEAVABFACgAeQByAHMALABtACwAZAApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzACwATQBBAFAAKABzAHQAYQByAHQAcwAsAFAAZQByAGkAbwBkAEUAbgBkACkALABcAG4AIAAgACAAIAAgACAAIAAgAHQAYQBnACwASQBGACgAcwB0AGEAcgB0AHMAPQBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXAAiACAAKABUAGgAaQBzACAAcgBlAHAAbwByAHQAaQBuAGcAIABjAHkAYwBsAGUAKQBcACIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzAFQAZQB4AHQALABUAEUAWABUACgAcwB0AGEAcgB0AHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzAFQAZQB4AHQALABUAEUAWABUACgAZQBuAGQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAG4APQAwACwAXAAiAFwAIgAsAEgAUwBUAEEAQwBLACgAcwB0AGEAcgB0AHMAVABlAHgAdAAgAFwAdQAwADAAMgA2ACAAXAAiACAAdABvACAAXAAiACAAXAB1ADAAMAAyADYAIABlAG4AZABzAFQAZQB4AHQAIABcAHUAMAAwADIANgAgAHQAYQBnACkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQBcAG4APQBMAEEATQBCAEQAQQAoAEYAdQBuAGMAdABpAG8AbgAsACAAVABFAFgAVABCAEUARgBPAFIARQAoAEYATwBSAE0AVQBMAEEAVABFAFgAVAAoAEYAdQBuAGMAdABpAG8AbgApACwAIABcACIAKABcACIAKQApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBBAHIAcgBhAHkALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5ACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkALABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAA9AFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABJAEYAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACAAPQAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALAAgAFwAIgBBAG4AeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5AD0AUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZABBAHIAcgBhAHkAPQBJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkAPQBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQAIAArACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAFwAdQAwADAAMwBlADAALAAgADEALAAgADAAKQBcAG4AIAAgACAAIAApACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsAFwAbgAgACAAIAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAdQAwADAAMgA3AFwAIgAgAFwAdQAwADAAMgA2ACAAcwBoACAAXAB1ADAAMAAyADYAIABcACIAXAB1ADAAMAAyADcAIQBcACIAIABcAHUAMAAwADIANgAgAGEAZABkAHIAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsARABpAGYAZgBlAHIAZQBuAHQAUwBoAGUAZQB0AFwAbgA9AEwAQQBNAEIARABBACgAVABhAHIAZwBlAHQAQwBlAGwAbAAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABzAGgALAAgAFQARQBYAFQAQQBGAFQARQBSACgAQwBFAEwATAAoAFwAIgBmAGkAbABlAG4AYQBtAGUAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALAAgAFwAIgBdAFwAIgApACwAXABuACAAIAAgACAAYQBkAGQAcgAsACAAQwBFAEwATAAoAFwAIgBhAGQAZAByAGUAcwBzAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAXABuACAAIAAgACAAXAAiACMAXAAiACAAXAB1ADAAMAAyADYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAxAF8AMgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADEALAAgADIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAzAF8ANABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADMALAAgADQAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBHAGUAdABNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAATQBNAFMALAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFwAbgAgACAAIAAgACAAIAAgACAATQBFAEQASQBBAE4AKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFUATgBEACgAVABlAG0AcABlAHIAYQB0AHUAcgBlACwAIAAwACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEkATgAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0AQQBYACgAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAE0ATQBTACwAIABNAE0AUwBBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUgBlAHMAdQBsAHQAcwBJAHQAZQBtAEYAcgBvAG0ARQBxAHUAYQB0AGkAbwBuAFQAaQB0AGwAZQBBAG4AZABTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAaQB0AGwAZQBDAGUAbABsACwAIABTAG8AdQByAGMAZQBDAGUAbABsACwAXABuACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAEwARQBGAFQAKABTAG8AdQByAGMAZQBDAGUAbABsACwAIABGAEkATgBEACgAXAAiACwAXAAiACwAIABTAG8AdQByAGMAZQBDAGUAbABsACkAIAAtADEAKQAsACAAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFwAIgAsACAAXAAiAFwAIgApACAAXAB1ADAAMAAyADYAIABcACIAIABcACIAIABcAHUAMAAwADIANgAgAFQAaQB0AGwAZQBDAGUAbABsAFwAbgApADsAIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ARgB1AGUAbAAgAHMAYwBvAHAAZQAgADEAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAALQAgAFMAdABhAHQAaQBvAG4AYQByAHkAIABnAGEAcwBlAG8AdQBzACAAZgB1AGUAbABzAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8AVABpAHQAbABlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIARgB1AGUAbAAgAHMAYwBvAHAAZQAgADEAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAALQAgAFMAdABhAHQAaQBvAG4AYQByAHkAIABnAGEAcwBlAG8AdQBzACAAZgB1AGUAbABzAFwAIgApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBEAGkAcgBlAGMAdAAgACgAUwBjAG8AcABlACAAMQApACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAdABoAGUAIABjAG8AbgBzAHUAbQBwAHQAaQBvAG4AIABvAGYAIABnAGEAcwBlAG8AdQBzACAAZgB1AGUAbABzACAAaQBuAGMAbAB1AGQAaQBuAGcAIABsAGkAcQB1AGUAZgBpAGUAZAAgAG4AYQB0AHUAcgBhAGwAIABnAGEAcwAgACAAXAAiACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAE4AYQB0AGkAbwBuAGEAbAAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABBAGMAYwBvAHUAbgB0AHMAIABGAGEAYwB0AG8AcgBzACAAMgAwADIANQAgAC0AIABUAGEAYgBsAGUAIAA1AFwAIgApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAOQAsACAANwAsAFwAbgAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBGAHUAZQBsACAAYwBvAG0AYgB1AHMAdABlAGQAXAAiACwAIABcACIARQBuAGUAcgBnAHkAIABDAG8AbgB0AGUAbgB0ACAARgBhAGMAdABvAHIAIAAoAEcASgAgAHAAZQByACAAdQBuAGkAdAAgAG8AZgAgAGYAdQBlAGwAKQBcACIALAAgAFwAIgBGAHUAZQBsACAAdQBuAGkAdABcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAxACAARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAIAAoAGsAZwAgAEMATwAyACAALQAgAGUAIAAvACAARwBKACkAIABDAE8AMgBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAxACAARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAIAAoAGsAZwAgAEMATwAyACAALQAgAGUAIAAvACAARwBKACkAIABDAEgANABcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAxACAARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAIAAoAGsAZwAgAEMATwAyACAALQAgAGUAIAAvACAARwBKACkAIABOADIATwBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAxACAARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAIAAoAGsAZwAgAEMATwAyACAALQAgAGUAIAAvACAARwBKACkAIABDAG8AbQBiAGkAbgBlAGQAIABnAGEAcwBlAHMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIATgBhAHQAdQByAGEAbAAgAGcAYQBzACAAZABpAHMAdAByAGkAYgB1AHQAZQBkACAAaQBuACAAYQAgAHAAaQBwAGUAbABpAG4AZQBcACIALAAgADAALgAwADMAOQAzACwAIABcACIAbQAzAFwAIgAsACAANQAxAC4ANAAsACAAMAAuADEALAAgADAALgAwADMALAAgADUAMQAuADUAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBhAGwAIABzAGUAYQBtACAAbQBlAHQAaABhAG4AZQAgAHQAaABhAHQAIABpAHMAIABjAGEAcAB0AHUAcgBlAGQAIABmAG8AcgAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AXAAiACwAIAAwAC4AMAAzADcANwAsACAAXAAiAG0AMwBcACIALAAgADUAMQAuADQALAAgADAALgAyACwAIAAwAC4AMAAzACwAIAA1ADEALgA2ADMAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AYQBsACAAbQBpAG4AZQAgAHcAYQBzAHQAZQAgAGcAYQBzACAAdABoAGEAdAAgAGkAcwAgAGMAYQBwAHQAdQByAGUAZAAgAGYAbwByACAAYwBvAG0AYgB1AHMAdABpAG8AbgBcACIALAAgADAALgAwADMANwA3ACwAIABcACIAbQAzAFwAIgAsACAANQAxAC4AOQAsACAANAAuADYALAAgADAALgAzACwAIAA1ADYALgA4ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBvAG0AcAByAGUAcwBzAGUAZAAgAG4AYQB0AHUAcgBhAGwAIABnAGEAcwAoAHIAZQB2AGUAcgB0AGkAbgBnACAAdABvACAAcwB0AGEAbgBkAGEAcgBkACAAYwBvAG4AZABpAHQAaQBvAG4AcwApAFwAIgAsACAAMAAuADAAMwA5ADMALAAgAFwAIgBtADMAXAAiACwAIAA1ADEALgA0ACwAIAAwAC4AMQAsACAAMAAuADAAMwAsACAANQAxAC4ANQAzADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVQBuAHAAcgBvAGMAZQBzAHMAZQBkACAAbgBhAHQAdQByAGEAbAAgAGcAYQBzAFwAIgAsACAAMAAuADAAMwA5ADMALAAgAFwAIgBtADMAXAAiACwAIAA1ADEALgA0ACwAIAAwAC4AMQAsACAAMAAuADAAMwAsACAANQAxAC4ANQAzADsAXABuACAAIAAgACAAIAAgACAAIABcACIARQB0AGgAYQBuAGUAXAAiACwAIAAwAC4AMAA2ADIAOQAsACAAXAAiAG0AMwBcACIALAAgADUANgAuADUALAAgADAALgAwADMALAAgADAALgAwADMALAAgADUANgAuADUANgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBrAGUAIABvAHYAZQBuACAAZwBhAHMAXAAiACwAIAAwAC4AMAAxADgAMQAsACAAXAAiAG0AMwBcACIALAAgADMANwAuADAALAAgADAALgAwADMALAAgADAALgAwADUALAAgADMANwAuADAAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEIAbABhAHMAdAAgAGYAdQByAG4AYQBjAGUAIABnAGEAcwBcACIALAAgADAALgAwADAANAAwACwAIABcACIAbQAzAFwAIgAsACAAMgAzADQALgAwACwAIAAwAC4AMAAzACwAIAAwAC4AMAAyACwAIAAyADMANAAuADAANQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFQAbwB3AG4AIABnAGEAcwBcACIALAAgADAALgAwADMAOQAwACwAIABcACIAbQAzAFwAIgAsACAANgAwAC4AMgAsACAAMAAuADAANAAsACAAMAAuADAAMwAsACAANgAwAC4AMgA3ADsAXABuACAAIAAgACAAIAAgACAAIABcACIATABpAHEAdQBlAGYAaQBlAGQAIABuAGEAdAB1AHIAYQBsACAAZwBhAHMAXAAiACwAIAAyADUALgAzACwAIABcACIAawBMAFwAIgAsACAANQAxAC4ANAAsACAAMAAuADEALAAgADAALgAwADMALAAgADUAMQAuADUAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEcAYQBzAGUAbwB1AHMAIABmAG8AcwBzAGkAbAAgAGYAdQBlAGwAcwAgAG8AdABoAGUAcgAgAHQAaABhAG4AIAB0AGgAbwBzAGUAIABtAGUAbgB0AGkAbwBuAGUAZAAgAGkAbgAgAHQAaABlACAAaQB0AGUAbQBzACAAYQBiAG8AdgBlAFwAIgAsACAAMAAuADAAMwA5ADAALAAgAFwAIgBtADMAXAAiACwAIAA1ADEALgA0ACwAIAAwAC4AMQAsACAAMAAuADAAMwAsACAANQAxAC4ANQAzADsAXABuACAAIAAgACAAIAAgACAAIABcACIATABhAG4AZABmAGkAbABsACAAYgBpAG8AZwBhAHMAIAB0AGgAYQB0ACAAaQBzACAAYwBhAHAAdAB1AHIAZQBkACAAZgBvAHIAIABjAG8AbQBiAHUAcwB0AGkAbwBuACAAKABtAGUAdABoAGEAbgBlACAAbwBuAGwAeQApAFwAIgAsACAAMAAuADAAMwA3ADcALAAgAFwAIgBtADMAXAAiACwAIAAwAC4AMAAsACAANgAuADQALAAgADAALgAwADMALAAgADYALgA0ADMAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAGwAdQBkAGcAZQAgAGIAaQBvAGcAYQBzACAAdABoAGEAdAAgAGkAcwAgAGMAYQBwAHQAdQByAGUAZAAgAGYAbwByACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgACgAbQBlAHQAaABhAG4AZQAgAG8AbgBsAHkAKQBcACIALAAgADAALgAwADMANwA3ACwAIABcACIAbQAzAFwAIgAsACAAMAAuADAALAAgADYALgA0ACwAIAAwAC4AMAAzACwAIAA2AC4ANAAzADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQQAgAGIAaQBvAGcAYQBzACAAdABoAGEAdAAgAGkAcwAgAGMAYQBwAHQAdQByAGUAZAAgAGYAbwByACAAYwBvAG0AYgB1AHMAdABpAG8AbgAsACAAbwB0AGgAZQByACAAdABoAGEAbgAgAHQAaABvAHMAZQAgAG0AZQBuAHQAaQBvAG4AZQBkACAAaQBuACAAdABoAGUAIABpAHQAZQBtAHMAIABhAGIAbwB2AGUAXAAiACwAIAAwAC4AMAAzADcAMAAsACAAXAAiAG0AMwBcACIALAAgADAALgAwACwAIAA2AC4ANAAsACAAMAAuADAAMwAsACAANgAuADQAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEIAaQBvAG0AZQB0AGgAYQBuAGUAXAAiACwAIAAwAC4AMAAzADkAMwAsACAAXAAiAG0AMwBcACIALAAgADAALgAwACwAIAAwAC4AMQAsACAAMAAuADAAMwAsACAAMAAuADEAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAeQBkAHIAbwBnAGUAbgBcACIALAAgADAALgAwADEAMgAyACwAIABcACIAbQAzAFwAIgAsACAAMAAuADAALAAgADAALgAwACwAIAAwAC4ANQAsACAAMAAuADUAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBOAGEAdAB1AHIAYQBsACAAZwBhAHMAIABkAGkAcwB0AHIAaQBiAHUAdABlAGQAIABpAG4AIABhACAAcABpAHAAZQBsAGkAbgBlACAALQAgAEcAaQBnAGEAagBvAHUAbABlAHMAXAAiACwAIAAxACwAIABcACIARwBKAFwAIgAsACAANQAxAC4ANAAsACAAMAAuADEALAAgADAALgAwADMALAAgADUAMQAuADUAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFQAbwB3AG4AIABnAGEAcwAgAC0AIABHAGkAZwBhAGoAbwB1AGwAZQBzAFwAIgAsACAAMQAsACAAXAAiAEcASgBcACIALAAgADYAMAAuADIALAAgADAALgAwADQALAAgADAALgAwADMALAAgADYAMAAuADIANwBcAG4AIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgApACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAFwAdQAwADAAMgA3AE4AYQB0AHUAcgBhAGwAIABnAGEAcwAgAGQAaQBzAHQAcgBpAGIAdQB0AGUAZAAgAGkAbgAgAGEAIABwAGkAcABlAGwAaQBuAGUAIAAtACAARwBpAGcAYQBqAG8AdQBsAGUAcwBcAHUAMAAwADIANwAgAGEAbgBkACAAXAB1ADAAMAAyADcAVABvAHcAbgAgAGcAYQBzACAALQAgAEcAaQBnAGEAagBvAHUAbABlAHMAXAB1ADAAMAAyADcAIAB3AGUAcgBlACAAYQBkAGQAZQBkACwAIABlAGEAYwBoACAAdwBpAHQAaAAgAGEAbgAgAGUAbgBlAHIAZwB5ACAAYwBvAG4AdABlAG4AdAAgAGYAYQBjAHQAbwByACAAbwBmACAAMQAgAEcASgAgAHAAZQByACAAdQBuAGkAdAAgAG8AZgAgAGYAdQBlAGwALgAgAFQAaABpAHMAIABpAHMAIABmAG8AcgAgAHUAcwBlAHIAcwAgAHcAaABvACAAaABhAHYAZQAgAGYAdQBlAGwAIABjAG8AbgBzAHUAbQBwAHQAaQBvAG4AIABkAGEAdABhACAAaQBuACAARwBKACAAcgBhAHQAaABlAHIAIAB0AGgAYQBuACAAbQAzAC4AXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ARgB1AGUAbAAgAHMAYwBvAHAAZQAgADMAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAALQAgAFMAdABhAHQAaQBvAG4AYQByAHkAIABnAGEAcwBlAG8AdQBzACAAZgB1AGUAbABzAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8AVABpAHQAbABlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIARgB1AGUAbAAgAHMAYwBvAHAAZQAgADMAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAALQAgAFMAdABhAHQAaQBvAG4AYQByAHkAIABnAGEAcwBlAG8AdQBzACAAZgB1AGUAbABzAFwAIgApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBJAG4AZABpAHIAZQBjAHQAIAAoAFMAYwBvAHAAZQAgADMAKQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAHQAaABlACAAYwBvAG4AcwB1AG0AcAB0AGkAbwBuACAAbwBmACAAbgBhAHQAdQByAGEAbAAgAGcAYQBzAC4AXAAiACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAE4AYQB0AGkAbwBuAGEAbAAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABBAGMAYwBvAHUAbgB0AHMAIABGAGEAYwB0AG8AcgBzACAAMgAwADIANQAgAC0AIABUAGEAYgBsAGUAIAA2AFwAIgApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALABcAG4AIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIABcACIAUwB0AGEAdABlACAAbwByACAAdABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAUwBjAG8AcABlACAAMwAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByAHMAIABmAG8AcgAgAE4AYQB0AHUAcgBhAGwAIABHAGEAcwAgACgAawBnACAAQwBPADIAIAAtACAAZQAgAC8AIABHAEoAKQAgAE0AZQB0AHIAbwBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAzACAARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAcwAgAGYAbwByACAATgBhAHQAdQByAGEAbAAgAEcAYQBzACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAATgBvAG4AIAAtACAATQBlAHQAcgBvAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE4AZQB3ACAAUwBvAHUAdABoACAAVwBhAGwAZQBzAFwAIgAsACAAMQAzAC4AMQAsACAAMQA0AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEEAQwBUAFwAIgAsACAAMQAzAC4AMQAsACAAMQA0AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgADQALgAwACwAIAA0AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIAA4AC4AOAAsACAANwAuADkAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAG8AdQB0AGgAIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgADEAMAAuADcALAAgADEAMAAuADYAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIAA0AC4AMQAsACAANAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBUAGEAcwBtAGEAbgBpAGEAXAAiACwAIAA0AC4AMAAsACAANAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AcgB0AGgAZQByAG4AIABUAGUAcgByAGkAdABvAHIAeQBcACIALAAgADQALgAxACwAIAA0AC4AMABcAG4AIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgApACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAE4AUwBXACAAYQBuAGQAIABBAEMAVAAgAHMAcABsAGkAdAAgAGkAbgB0AG8AIABzAGUAcABhAHIAYQB0AGUAIAByAG8AdwBzAC4AIABcAHUAMAAwADIANwBDAFwAdQAwADAAMgA3ACAAVgBhAGwAdQBlAHMAIABmAG8AcgAgAFQAYQBzAG0AYQBuAGkAYQAgAGEAbgBkACAATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAIAByAGUAcABsAGEAYwBlAGQAIAB3AGkAdABoACAAdABoAG8AcwBlACAAZgBvAHIAIABWAGkAYwB0AG8AcgBpAGEAIABhAG4AZAAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAHIAZQBzAHAAZQBjAHQAaQB2AGUAbAB5AC4AIAAoAFMAZQBlACAAYQBwAHAAZQBuAGQAaQBjAGUAcwApAFwAIgApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBBAHAAcABlAG4AZABpAGMAZQBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMgAsACAAMgAsAFwAbgAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAtAFwAIgAsACAAXAAiAEEAcwAgAFMAYwBvAHAAZQAgADMAIABmAGEAYwB0AG8AcgBzACAAYQByAGUAIABjAGEAbABjAHUAbABhAHQAZQBkACAAYQB0ACAAdABoAGUAIABwAG8AaQBuAHQAIAB3AGgAZQByAGUAIABuAGEAdAB1AHIAYQBsACAAZwBhAHMAIABpAHMAIABkAGUAbABpAHYAZQByAGUAZAAgAHQAbwAgAGUAbgBkACAAdQBzAGUAcgBzACwAIABpAHQAIABpAHMAIABuAGUAYwBlAHMAcwBhAHIAeQAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAYwBvAG4AcwB1AG0AcAB0AGkAbwBuACAAYQB0ACAAZQBhAGMAaAAgAG8AZgAgAHQAaABlACAAbABvAGEAZAAgAGMAZQBuAHQAcgBlAHMALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBHAGEAcwAgAHIAZQBhAGMAaABlAHMAIABlAG4AZAAgAHUAcwBlAHIAcwAgAGUAaQB0AGgAZQByACAAZgByAG8AbQAgAHQAaABlACAAbQBlAHQAcgBvACAAZABpAHMAdAByAGkAYgB1AHQAaQBvAG4AIABuAGUAdAB3AG8AcgBrAHMAIABvAHIAIABkAGkAcgBlAGMAdAAgAGYAcgBvAG0AIAB0AGgAZQAgAGgAaQBnAGgAIAAtACAAcAByAGUAcwBzAHUAcgBlACAAZABpAHMAdAByAGkAYgB1AHQAaQBvAG4AIABwAGkAcABlAGwAaQBuAGUAcwAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAEgAbwB1AHMAZQBoAG8AbABkAHMAIABhAG4AZAAgAGMAbwBtAG0AZQByAGMAaQBhAGwAIAB1AHMAZQByAHMAIAB0AGUAbgBkACAAdABvACAAYgBlACAAcwBlAHIAdgBlAGQAIABiAHkAIAB0AGgAZQAgAGYAbwByAG0AZQByACwAIABhAG4AZAAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQAgAGcAZQBuAGUAcgBhAHQAbwByAHMAIABhAG4AZAAgAGwAYQByAGcAZQAgAGkAbgBkAHUAcwB0AHIAaQBhAGwAIABwAGwAYQBuAHQAcwAgAGYAcgBvAG0AIAB0AGgAZQAgAGwAYQB0AHQAZQByAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIALQBcACIALAAgAFwAIgBNAGUAdAByAG8AIABpAHMAIABkAGUAZgBpAG4AZQBkACAAYQBzACAAbABvAGMAYQB0AGUAZAAgAG8AbgAgAG8AcgAgAGUAYQBzAHQAIABvAGYAIAB0AGgAZQAgAGQAaQB2AGkAZABpAG4AZwAgAHIAYQBuAGcAZQAgAGkAbgAgAE4AUwBXACwAIABpAG4AYwBsAHUAZABpAG4AZwAgAEMAYQBuAGIAZQByAHIAYQAgAGEAbgBkACAAUQB1AGUAYQBuAGIAZQB5AGEAbgAsACAATQBlAGwAYgBvAHUAcgBuAGUALAAgAEIAcgBpAHMAYgBhAG4AZQAsACAAQQBkAGUAbABhAGkAZABlACAAbwByACAAUABlAHIAdABoAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIATwB0AGgAZQByAHcAaQBzAGUALAAgAHQAaABlACAAbgBvAG4AIAAtACAAbQBlAHQAcgBvACAAZgBhAGMAdABvAHIAIABzAGgAbwB1AGwAZAAgAGIAZQAgAHUAcwBlAGQALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAtAFwAIgAsACAAXAAiAEYAYQBjAHQAbwByAHMAIABhAHIAZQAgAGMAYQBsAGMAdQBsAGEAdABlAGQAIABmAG8AcgAgAGEAbABsACAAbgBhAHQAdQByAGEAbAAgAGcAYQBzACAAZABpAHMAdAByAGkAYgB1AHQAZQBkACAAaQBuACAAYQAgAHAAaQBwAGUAbABpAG4AZQAgAHcAaABpAGMAaAAgAG0AYQB5ACAAaQBuAGMAbAB1AGQAZQAgAGMAbwBhAGwAIABzAGUAYQBtACAAbQBlAHQAaABhAG4AZQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAC0AXAAiACwAIABcACIAVABhAGIAbABlACAANgAgAGkAcwAgAG4AbwB0ACAAYQBwAHAAbABpAGMAYQBiAGwAZQAgAHQAbwAgAGUAdABoAGEAbgBlAC4AIABTAGUAZQAgAFQAYQBiAGwAZQAgADcAIABJAG4AZABpAHIAZQBjAHQAIAAoAFMAYwBvAHAAZQAgADMAKQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHQAaABlACAAYwBvAG4AcwB1AG0AcAB0AGkAbwBuACAAbwBmACAAZQB0AGgAYQBuAGUALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAtAFwAIgAsACAAXAAiAEMAIAA9ACAAQwBvAG4AZgBpAGQAZQBuAHQAaQBhAGwALgAgAFMAYwBvAHAAZQAgADMAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABUAGEAcwBtAGEAbgBpAGEAIABhAG4AZAAgAHQAaABlACAATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAIABhAHIAZQAgAG4AbwB0ACAAYQB2AGEAaQBsAGEAYgBsAGUAIABkAHUAZQAgAHQAbwAgAGMAbwBuAGYAaQBkAGUAbgB0AGkAYQBsAGkAdAB5ACAAYwBvAG4AcwB0AHIAYQBpAG4AdABzACAAdABoAGEAdAAgAGEAcgBpAHMAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBmAHIAbwBtACAAdABoAGUAIAB1AHMAZQAgAG8AZgAgAGEAIABsAGkAbQBpAHQAZQBkACAAbgB1AG0AYgBlAHIAIABvAGYAIABOAEcARQBSACAAZABhAHQAYQAgAGkAbgBwAHUAdABzAC4AIABJAHQAIABpAHMAIABzAHUAZwBnAGUAcwB0AGUAZAAgAHQAaABhAHQAIABmAG8AcgAgAFQAYQBzAG0AYQBuAGkAYQAgAHQAaABlACAAdQBzAGUAIABvAGYAIAB0AGgAZQAgAFYAaQBjAHQAbwByAGkAYQBuACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGkAcwAgAGEAcABwAHIAbwBwAHIAaQBhAHQAZQAsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAHcAaABpAGwAZQAgAGYAbwByACAATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAIAB0AGgAZQAgAHUAcwBlACAAbwBmACAAdABoAGUAIABXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABpAHMAIABhAHAAcAByAG8AcAByAGkAYQB0AGUALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAtAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADMAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZABvACAAbgBvAHQAIABpAG4AYwBsAHUAZABlACAAZgB1AGcAaQB0AGkAdgBlACAAZQBtAGkAcwBzAGkAbwBuACAAbABlAGEAawBhAGcAZQAgAGYAcgBvAG0AIABsAG8AdwAgAHAAcgBlAHMAcwB1AHIAZQAgAG4AYQB0AHUAcgBhAGwAIABnAGEAcwAgAGQAaQBzAHQAcgBpAGIAdQB0AGkAbwBuACAAcABpAHAAZQBsAGkAbgBlACAAbgBlAHQAdwBvAHIAawBzACAAdwBoAGkAbABlACAAdABoAG8AcwBlACAAZgByAG8AbQAgAGgAaQBnAGgAIABwAHIAZQBzAHMAdQByAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAZwBhAHMAIABuAGUAdAB3AG8AcgBrAHMAIABhAHIAZQAgAGMAbwBuAHMAaQBkAGUAcgBlAGQAIABuAGUAZwBsAGkAZwBpAGIAbABlAC4AXAAiAFwAbgAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACkAKQApADsAXABuAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBGAHUAZQBsACAAcwBjAG8AcABlACAAMQAgAGEAbgBkACAAMwAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIAAtACAAUwB0AGEAdABpAG8AbgBhAHIAeQAgAGwAaQBxAHUAaQBkACAAZgB1AGUAbABzAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBMAGkAcQB1AGkAZABfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEYAdQBlAGwAIABzAGMAbwBwAGUAIAAxACAAYQBuAGQAIAAzACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAC0AIABTAHQAYQB0AGkAbwBuAGEAcgB5ACAAbABpAHEAdQBpAGQAIABmAHUAZQBsAHMAXAAiACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkATABpAHEAdQBpAGQAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBEAGkAcgBlAGMAdAAgACgAUwBjAG8AcABlACAAMQApACAAYQBuAGQAIABpAG4AZABpAHIAZQBjAHQAIAAoAHMAYwBvAHAAZQAgADMAKQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAHQAaABlACAAYwBvAG4AcwB1AG0AcAB0AGkAbwBuACAAbwBmACAAbABpAHEAdQBpAGQAIABmAHUAZQBsAHMALAAgAGkAbgBjAGwAdQBkAGkAbgBnACAAYwBlAHIAdABhAGkAbgAgAHAAZQB0AHIAbwBsAGUAdQBtACAAYgBhAHMAZQBkACAAcAByAG8AZAB1AGMAdABzACAAZgBvAHIAIABzAHQAYQB0AGkAbwBuAGEAcgB5ACAAZQBuAGUAcgBnAHkAIABwAHUAcgBwAG8AcwBlAHMALgBcACIAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBMAGkAcQB1AGkAZABfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAE4AYQB0AGkAbwBuAGEAbAAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABBAGMAYwBvAHUAbgB0AHMAIABGAGEAYwB0AG8AcgBzACAAMgAwADIANQAgAC0AIABUAGEAYgBsAGUAIAA4AFwAIgApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEwAaQBxAHUAaQBkAF8ARABhAHQAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyADUALAAgADgALABcAG4AIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIABcACIARgB1AGUAbAAgAGMAbwBtAGIAdQBzAHQAZQBkAFwAIgAsACAAXAAiAEUAbgBlAHIAZwB5ACAAQwBvAG4AdABlAG4AdAAgAEYAYQBjAHQAbwByACAAKABHAEoAIABwAGUAcgAgAHUAbgBpAHQAIABvAGYAIABmAHUAZQBsACkAXAAiACwAIABcACIARgB1AGUAbAAgAHUAbgBpAHQAXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAAQwBPADIAXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAAQwBIADQAXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAATgAyAE8AXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAAQwBvAG0AYgBpAG4AZQBkACAAZwBhAHMAZQBzAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADMAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgAgACgAawBnACAAQwBPADIAIAAtACAAZQAgAC8AIABHAEoAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAdAByAG8AbABlAHUAbQAgAGIAYQBzAGUAZAAgAG8AaQBsAHMAIAAoAG8AdABoAGUAcgAgAHQAaABhAG4AIABwAGUAdAByAG8AbABlAHUAbQAgAGIAYQBzAGUAZAAgAG8AaQBsACAAdQBzAGUAZAAgAGEAcwAgAGYAdQBlAGwAKQAsACAAZQAuAGcALgAgAGwAdQBiAHIAaQBjAGEAbgB0AHMAXAAiACwAIAAzADgALgA4ACwAIABcACIAawBsAFwAIgAsACAAMQAzAC4AOQAsACAAMAAuADAALAAgADAALgAwACwAIAAxADMALgA5ACwAIAAxADgALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUABlAHQAcgBvAGwAZQB1AG0AIABiAGEAcwBlAGQAIABnAHIAZQBhAHMAZQBzAFwAIgAsACAAMwA4AC4AOAAsACAAXAAiAGsAbABcACIALAAgADMALgA1ACwAIAAwAC4AMAAsACAAMAAuADAALAAgADMALgA1ACwAIAAxADgALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwByAHUAZABlACAAbwBpAGwAIABpAG4AYwBsAHUAZABpAG4AZwAgAGMAcgB1AGQAZQAgAG8AaQBsACAAYwBvAG4AZABlAG4AcwBhAHQAZQBzAFwAIgAsACAANAA1AC4AMwAsACAAXAAiAHQAXAAiACwAIAA2ADkALgA2ACwAIAAwAC4AMAA4ACwAIAAwAC4AMgAsACAANgA5AC4AOAA4ACwAIABcACIATgBFAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAG4AYQB0AHUAcgBhAGwAIABnAGEAcwAgAGwAaQBxAHUAaQBkAHMAXAAiACwAIAA0ADYALgA1ACwAIABcACIAdABcACIALAAgADYAMQAuADAALAAgADAALgAwADgALAAgADAALgAyACwAIAA2ADEALgAyADgALAAgAFwAIgBOAEUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQQB1AHQAbwBtAG8AdABpAHYAZQAgAGcAYQBzAG8AbABpAG4AZQAgAC8AIABwAGUAdAByAG8AbAAgACgAbwB0AGgAZQByACAAdABoAGEAbgAgAGYAbwByACAAdQBzAGUAIABhAHMAIABmAHUAZQBsACAAaQBuACAAYQBuACAAYQBpAHIAYwByAGEAZgB0ACkAXAAiACwAIAAzADQALgAyACwAIABcACIAawBMAFwAIgAsACAANgA3AC4ANAAsACAAMAAuADIALAAgADAALgAyACwAIAA2ADcALgA4ADAALAAgADEANwAuADIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAHYAaQBhAHQAaQBvAG4AIABnAGEAcwBvAGwAaQBuAGUAXAAiACwAIAAzADMALgAxACwAIABcACIAawBMAFwAIgAsACAANgA3ACwAIAAwAC4AMgAsACAAMAAuADIALAAgADYANwAuADQAMAAsACAAMQA4AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEsAZQByAG8AcwBlAG4AZQAgACgAbwB0AGgAZQByACAAdABoAGEAbgAgAGYAbwByACAAdQBzAGUAIABhAHMAIABmAHUAZQBsACAAaQBuACAAYQBuACAAYQBpAHIAYwByAGEAZgB0ACkAXAAiACwAIAAzADcALgA1ACwAIABcACIAawBMAFwAIgAsACAANgA4AC4AOQAsACAAMAAuADAAMQAsACAAMAAuADIALAAgADYAOQAuADEAMQAsACAAMQA4AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEEAdgBpAGEAdABpAG8AbgAgAHQAdQByAGIAaQBuAGUAIABmAHUAZQBsACAALwAgAGsAZQByAG8AcwBlAG4AZQBcACIALAAgADMANgAuADgALAAgAFwAIgBrAEwAXAAiACwAIAA2ADkALgA2ACwAIAAwAC4AMAAyACwAIAAwAC4AMgAsACAANgA5AC4AOAAyACwAIAAxADgALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABlAGEAdABpAG4AZwAgAG8AaQBsAFwAIgAsACAAMwA3AC4AMwAsACAAXAAiAGsATABcACIALAAgADYAOQAuADUALAAgADAALgAwADMALAAgADAALgAyACwAIAA2ADkALgA3ADMALAAgADEAOAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBEAGkAZQBzAGUAbAAgAG8AaQBsAFwAIgAsACAAMwA4AC4ANgAsACAAXAAiAGsATABcACIALAAgADYAOQAuADkALAAgADAALgAxACwAIAAwAC4AMgAsACAANwAwAC4AMgAwACwAIAAxADcALgAzADsAXABuACAAIAAgACAAIAAgACAAIABcACIARgB1AGUAbAAgAG8AaQBsAFwAIgAsACAAMwA5AC4ANwAsACAAXAAiAGsATABcACIALAAgADcAMwAuADYALAAgADAALgAwADQALAAgADAALgAyACwAIAA3ADMALgA4ADQALAAgADEAOAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBMAGkAcQB1AGUAZgBpAGUAZAAgAGEAcgBvAG0AYQB0AGkAYwAgAGgAeQBkAHIAbwBjAGEAcgBiAG8AbgBzAFwAIgAsACAAMwA0AC4ANAAsACAAXAAiAGsATABcACIALAAgADYAOQAuADcALAAgADAALgAwADMALAAgADAALgAyACwAIAA2ADkALgA5ADMALAAgADEAOAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAG8AbAB2AGUAbgB0AHMAOgAgAG0AaQBuAGUAcgBhAGwAIAB0AHUAcgBwAGUAbgB0AGkAbgBlACAAbwByACAAdwBoAGkAdABlACAAcwBwAGkAcgBpAHQAcwBcACIALAAgADMANAAuADQALAAgAFwAIgBrAEwAXAAiACwAIAA2ADkALgA3ACwAIAAwAC4AMAAzACwAIAAwAC4AMgAsACAANgA5AC4AOQAzACwAIAAxADgALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIATABpAHEAdQBlAGYAaQBlAGQAIABwAGUAdAByAG8AbABlAHUAbQAgAGcAYQBzACAAKABMAFAARwApAFwAIgAsACAAMgA1AC4ANwAsACAAXAAiAGsATABcACIALAAgADYAMAAuADIALAAgADAALgAyACwAIAAwAC4AMgAsACAANgAwAC4ANgAwACwAIAAyADAALgAyADsAXABuACAAIAAgACAAIAAgACAAIABcACIATgBhAHAAaAB0AGgAYQBcACIALAAgADMAMQAuADQALAAgAFwAIgBrAEwAXAAiACwAIAA2ADkALgA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxACwAIAA2ADkALgA4ADIALAAgADEAOAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAdAByAG8AbABlAHUAbQAgAGMAbwBrAGUAXAAiACwAIAAzADQALgAyACwAIABcACIAdABcACIALAAgADkAMgAuADYALAAgADAALgAwADgALAAgADAALgAyACwAIAA5ADIALgA4ADgALAAgADEAOAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAGUAZgBpAG4AZQByAHkAIABnAGEAcwAgAGEAbgBkACAAbABpAHEAdQBpAGQAcwBcACIALAAgADQAMgAuADkALAAgAFwAIgB0AFwAIgAsACAANQA0AC4ANwAsACAAMAAuADAAMwAsACAAMAAuADAAMwAsACAANQA0AC4ANwA2ACwAIAAxADgALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgBlAGYAaQBuAGUAcgB5ACAAYwBvAGsAZQBcACIALAAgADMANAAuADIALAAgAFwAIgB0AFwAIgAsACAAOQAyAC4ANgAsACAAMAAuADAAOAAsACAAMAAuADIALAAgADkAMgAuADgAOAAsACAAMQA4AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFAAZQB0AHIAbwBsAGUAdQBtACAAYgBhAHMAZQBkACAAcAByAG8AZAB1AGMAdABzACAAbwB0AGgAZQByACAAdABoAGEAbgAgAG0AZQBuAHQAaQBvAG4AZQBkACAAaQBuACAAdABoAGUAIABpAHQAZQBtAHMAIABhAGIAbwB2AGUAXAAiACwAIAAzADQALgA0ACwAIABcACIAawBMAFwAIgAsACAANgA5AC4AOAAsACAAMAAuADAAMgAsACAAMAAuADEALAAgADYAOQAuADkAMgAsACAAMQA4AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEIAaQBvAGQAaQBlAHMAZQBsAFwAIgAsACAAMwA0AC4ANgAsACAAXAAiAGsATABcACIALAAgADAALgAwACwAIAAwAC4AMAA4ACwAIAAwAC4AMgAsACAAMAAuADIAOAAsACAAXAAiAE4ARQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBFAHQAaABhAG4AbwBsACAAZgBvAHIAIAB1AHMAZQAgAGEAcwAgAGEAIABmAHUAZQBsACAAaQBuACAAYQBuACAAaQBuAHQAZQByAG4AYQBsACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgAGUAbgBnAGkAbgBlAFwAIgAsACAAMgAzAC4ANAAsACAAXAAiAGsATABcACIALAAgADAALgAwACwAIAAwAC4AMAA4ACwAIAAwAC4AMgAsACAAMAAuADIAOAAsACAAXAAiAE4ARQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBCAGkAbwBmAHUAZQBsAHMAIABvAHQAaABlAHIAIAB0AGgAYQBuACAAdABoAG8AcwBlACAAbQBlAG4AdABpAG8AbgBlAGQAIABpAG4AIAB0AGgAZQAgAGkAdABlAG0AcwAgAGEAYgBvAHYAZQAgAGEAbgBkACAAYgBlAGwAbwB3AFwAIgAsACAAMgAzAC4ANAAsACAAXAAiAGsATABcACIALAAgADAALgAwACwAIAAwAC4AMAA4ACwAIAAwAC4AMgAsACAAMAAuADIAOAAsACAAXAAiAE4ARQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAGUAbgBlAHcAYQBiAGwAZQAgAGEAdgBpAGEAdABpAG8AbgAgAGsAZQByAG8AcwBlAG4AZQBcACIALAAgADMANgAuADgALAAgAFwAIgBrAEwAXAAiACwAIAAwAC4AMAAsACAAMAAuADAAMgAsACAAMAAuADIALAAgADAALgAyADIALAAgAFwAIgBOAEUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgBlAG4AZQB3AGEAYgBsAGUAIABkAGkAZQBzAGUAbABcACIALAAgADMAOAAuADYALAAgAFwAIgBrAEwAXAAiACwAIAAwAC4AMAAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMwAwACwAIABcACIATgBFAFwAIgBcAG4AIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgApACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkATABpAHEAdQBpAGQAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAXAB1ADAAMAAyADcATgBFAFwAdQAwADAAMgA3ACAAdgBhAGwAdQBlAHMAIAByAGUAdAB1AHIAbgBlAGQAIABhAHMAIAB6AGUAcgBvACAAZgBvAHIAIABjAGEAbABjAHUAbABhAHQAaQBvAG4AcwAuAFwAIgApADsAXABuAFwAbgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAEYAdQBlAGwAIABzAGMAbwBwAGUAIAAxACAAYQBuAGQAIAAzACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAC0AIABUAHIAYQBuAHMAcABvAHIAdABcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AF8AVABpAHQAbABlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIARgB1AGUAbAAgAHMAYwBvAHAAZQAgADEAIABhAG4AZAAgADMAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAALQAgAFQAcgBhAG4AcwBwAG8AcgB0AFwAIgApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBUAHIAYQBuAHMAcABvAHIAdABfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEQAaQByAGUAYwB0ACAAKABzAGMAbwBwAGUAIAAxACkAIABhAG4AZAAgAGkAbgBkAGkAcgBlAGMAdAAgACgAcwBjAG8AcABlACAAMwApACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAdABoAGUAIABjAG8AbgBzAHUAbQBwAHQAaQBvAG4AIABvAGYAIAB0AHIAYQBuAHMAcABvAHIAdAAgAGYAdQBlAGwAcwAgAGkAbgAgAGQAaQBmAGYAZQByAGUAbgB0ACAAdAByAGEAbgBzAHAAbwByAHQAIABlAHEAdQBpAHAAbQBlAG4AdABcACIAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAVAByAGEAbgBzAHAAbwByAHQAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABOAGEAdABpAG8AbgBhAGwAIABHAHIAZQBlAG4AaABvAHUAcwBlACAAQQBjAGMAbwB1AG4AdABzACAARgBhAGMAdABvAHIAcwAgADIAMAAyADUAIAAtACAAVABhAGIAbABlACAAOQBcACIAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAVAByAGEAbgBzAHAAbwByAHQAXwBEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIANgAsACAAMQAwACwAXABuACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBhAG4AcwBwAG8AcgB0ACAAdAB5AHAAZQBcACIALAAgAFwAIgBGAHUAZQBsACAAYwBvAG0AYgB1AHMAdABlAGQAXAAiACwAIABcACIARQBuAGUAcgBnAHkAIABDAG8AbgB0AGUAbgB0ACAARgBhAGMAdABvAHIAKABHAEoAIABwAGUAcgAgAHUAbgBpAHQAIABvAGYAIABmAHUAZQBsACkAXAAiACwAIABcACIARgB1AGUAbAAgAHUAbgBpAHQAXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAAQwBPADIAXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAAQwBIADQAXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAATgAyAE8AXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAAQwBvAG0AYgBpAG4AZQBkACAAZwBhAHMAZQBzAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADMAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgAgACgAawBnACAAQwBPADIAIAAtACAAZQAgAC8AIABHAEoAKQBcACIALAAgAFwAIgBTAG8AdQByAGMAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAGEAcgBzACAAYQBuAGQAIABsAGkAZwBoAHQAIABjAG8AbQBtAGUAcgBjAGkAYQBsACAAdgBlAGgAaQBjAGwAZQBzAFwAIgAsACAAXAAiAEcAYQBzAG8AbABpAG4AZQBcACIALAAgADMANAAuADIALAAgAFwAIgBrAGwAXAAiACwAIAA2ADcALgA0ACwAIAAwAC4AMAAyACwAIAAwAC4AMgAsACAANgA3AC4ANgAyACwAIAAxADcALgAyACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBhAHIAcwAgAGEAbgBkACAAbABpAGcAaAB0ACAAYwBvAG0AbQBlAHIAYwBpAGEAbAAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBEAGkAZQBzAGUAbAAgAG8AaQBsAFwAIgAsACAAMwA4AC4ANgAsACAAXAAiAGsAbABcACIALAAgADYAOQAuADkALAAgADAALgAwADEALAAgADAALgA1ACwAIAA3ADAALgA0ADEALAAgADEANwAuADMALAAgAFwAIgBOAEcAQQBGACAAMgAwADIANQA6ACAAVABhAGIAbABlACAAOQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAGEAcgBzACAAYQBuAGQAIABsAGkAZwBoAHQAIABjAG8AbQBtAGUAcgBjAGkAYQBsACAAdgBlAGgAaQBjAGwAZQBzAFwAIgAsACAAXAAiAEwAaQBxAHUAZQBmAGkAZQBkACAAcABlAHQAcgBvAGwAZQB1AG0AIABnAGEAcwAgACgATABQAEcAKQBcACIALAAgADIANgAuADIALAAgAFwAIgBrAGwAXAAiACwAIAA2ADAALgAyACwAIAAwAC4ANQAsACAAMAAuADMALAAgADYAMQAuADAAMAAsACAAMgAwAC4AMgAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAYQByAHMAIABhAG4AZAAgAGwAaQBnAGgAdAAgAGMAbwBtAG0AZQByAGMAaQBhAGwAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIARgB1AGUAbAAgAG8AaQBsAFwAIgAsACAAMwA5AC4ANwAsACAAXAAiAGsAbABcACIALAAgADcAMwAuADYALAAgADAALgAwADgALAAgADAALgA1ACwAIAA3ADQALgAxADgALAAgADEAOAAuADAALAAgAFwAIgBOAEcAQQBGACAAMgAwADIANQA6ACAAVABhAGIAbABlACAAOQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAGEAcgBzACAAYQBuAGQAIABsAGkAZwBoAHQAIABjAG8AbQBtAGUAcgBjAGkAYQBsACAAdgBlAGgAaQBjAGwAZQBzAFwAIgAsACAAXAAiAEUAdABoAGEAbgBvAGwAXAAiACwAIAAyADMALgA0ACwAIABcACIAawBsAFwAIgAsACAAMAAuADAALAAgADAALgAyACwAIAAwAC4AMgAsACAAMAAuADQALAAgAFwAIgBOAEUAXAAiACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBhAHIAcwAgAGEAbgBkACAAbABpAGcAaAB0ACAAYwBvAG0AbQBlAHIAYwBpAGEAbAAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBCAGkAbwBkAGkAZQBzAGUAbABcACIALAAgADMANAAuADYALAAgAFwAIgBrAGwAXAAiACwAIAAwAC4AMAAsACAAMAAuADgALAAgADEALgA3ACwAIAAyAC4ANQAsACAAXAAiAE4ARQBcACIALAAgAFwAIgBOAEcAQQBGACAAMgAwADIANQA6ACAAVABhAGIAbABlACAAOQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAGEAcgBzACAAYQBuAGQAIABsAGkAZwBoAHQAIABjAG8AbQBtAGUAcgBjAGkAYQBsACAAdgBlAGgAaQBjAGwAZQBzAFwAIgAsACAAXAAiAFIAZQBuAGUAdwBhAGIAbABlACAAZABpAGUAcwBlAGwAXAAiACwAIAAzADgALgA2ACwAIABcACIAawBsAFwAIgAsACAAMAAuADAALAAgADAALgAwADEALAAgADAALgA1ACwAIAAwAC4ANQAxACwAIABcACIATgBFAFwAIgAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAYQByAHMAIABhAG4AZAAgAGwAaQBnAGgAdAAgAGMAbwBtAG0AZQByAGMAaQBhAGwAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIATwB0AGgAZQByACAAYgBpAG8AZgB1AGUAbABzAFwAIgAsACAAMgAzAC4ANAAsACAAXAAiAGsAbABcACIALAAgADAALgAwACwAIAAwAC4AOAAsACAAMQAuADcALAAgADIALgA1ACwAIABcACIATgBFAFwAIgAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEwAaQBnAGgAdAAgAGQAdQB0AHkAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIAQwBvAG0AcAByAGUAcwBzAGUAZAAgAG4AYQB0AHUAcgBhAGwAIABnAGEAcwBcACIALAAgADAALgAwADMAOQAzACwAIABcACIAbQAzAFwAIgAsACAANQAxAC4ANAAsACAANwAuADMALAAgADAALgAzACwAIAA1ADkALgAwACwAIAAxADgALgAwACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIATABpAGcAaAB0ACAAZAB1AHQAeQAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBMAGkAcQB1AGUAZgBpAGUAZAAgAG4AYQB0AHUAcgBhAGwAIABnAGEAcwBcACIALAAgADIANQAuADMALAAgAFwAIgBrAGwAXAAiACwAIAA1ADEALgA0ACwAIAA3AC4AMwAsACAAMAAuADMALAAgADUAOQAuADAALAAgADEAOAAuADAALAAgAFwAIgBOAEcAQQBGACAAMgAwADIANQA6ACAAVABhAGIAbABlACAAOQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAGUAYQB2AHkAIABkAHUAdAB5ACAAdgBlAGgAaQBjAGwAZQBzAFwAIgAsACAAXAAiAEMAbwBtAHAAcgBlAHMAcwBlAGQAIABuAGEAdAB1AHIAYQBsACAAZwBhAHMAXAAiACwAIAAwAC4AMAAzADkAMwAsACAAXAAiAG0AMwBcACIALAAgADUAMQAuADQALAAgADIALgA4ACwAIAAwAC4AMwAsACAANQA0AC4ANQAsACAAMQA4AC4AMAAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAZQBhAHYAeQAgAGQAdQB0AHkAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIATABpAHEAdQBlAGYAaQBlAGQAIABuAGEAdAB1AHIAYQBsACAAZwBhAHMAXAAiACwAIAAyADUALgAzACwAIABcACIAawBsAFwAIgAsACAANQAxAC4ANAAsACAAMgAuADgALAAgADAALgAzACwAIAA1ADQALgA1ACwAIAAxADgALgAwACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABlAGEAdgB5ACAAZAB1AHQAeQAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBEAGkAZQBzAGUAbAAgAG8AaQBsACAALQAgAEUAdQByAG8AIABpAHYAIABvAHIAIABoAGkAZwBoAGUAcgBcACIALAAgADMAOAAuADYALAAgAFwAIgBrAGwAXAAiACwAIAA2ADkALgA5ACwAIAAwAC4AMAA3ACwAIAAwAC4ANAAsACAANwAwAC4AMwA3ACwAIAAxADcALgAzACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABlAGEAdgB5ACAAZAB1AHQAeQAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBEAGkAZQBzAGUAbAAgAG8AaQBsACAALQAgAEUAdQByAG8AIABpAGkAaQBcACIALAAgADMAOAAuADYALAAgAFwAIgBrAGwAXAAiACwAIAA2ADkALgA5ACwAIAAwAC4AMQAsACAAMAAuADQALAAgADcAMAAuADQALAAgADEANwAuADMALAAgAFwAIgBOAEcAQQBGACAAMgAwADIANQA6ACAAVABhAGIAbABlACAAOQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAGUAYQB2AHkAIABkAHUAdAB5ACAAdgBlAGgAaQBjAGwAZQBzAFwAIgAsACAAXAAiAEQAaQBlAHMAZQBsACAAbwBpAGwAIAAtACAARQB1AHIAbwAgAGkAXAAiACwAIAAzADgALgA2ACwAIABcACIAawBsAFwAIgAsACAANgA5AC4AOQAsACAAMAAuADIALAAgADAALgA0ACwAIAA3ADAALgA1ACwAIAAxADcALgAzACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABlAGEAdgB5ACAAZAB1AHQAeQAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBSAGUAbgBlAHcAYQBiAGwAZQAgAGQAaQBlAHMAZQBsACAAEyAgAEUAdQByAG8AIABpAHYAIABvAHIAIABoAGkAZwBoAGUAcgBcACIALAAgADMAOAAuADYALAAgAFwAIgBrAGwAXAAiACwAIAAwAC4AMAAsACAAMAAuADAANwAsACAAMAAuADQALAAgADAALgA0ADcALAAgAFwAIgBOAEUAXAAiACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABlAGEAdgB5ACAAZAB1AHQAeQAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBSAGUAbgBlAHcAYQBiAGwAZQAgAGQAaQBlAHMAZQBsACAAEyAgAEUAdQByAG8AIABpAGkAaQBcACIALAAgADMAOAAuADYALAAgAFwAIgBrAGwAXAAiACwAIAAwAC4AMAAsACAAMAAuADEALAAgADAALgA0ACwAIAAwAC4ANQAsACAAXAAiAE4ARQBcACIALAAgAFwAIgBOAEcAQQBGACAAMgAwADIANQA6ACAAVABhAGIAbABlACAAOQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAGUAYQB2AHkAIABkAHUAdAB5ACAAdgBlAGgAaQBjAGwAZQBzAFwAIgAsACAAXAAiAFIAZQBuAGUAdwBhAGIAbABlACAAZABpAGUAcwBlAGwAIAATICAARQB1AHIAbwAgAGkAXAAiACwAIAAzADgALgA2ACwAIABcACIAawBsAFwAIgAsACAAMAAuADAALAAgADAALgAyACwAIAAwAC4ANAAsACAAMAAuADYALAAgAFwAIgBOAEUAXAAiACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQQB2AGkAYQB0AGkAbwBuAFwAIgAsACAAXAAiAEcAYQBzAG8AbABpAG4AZQAgAGYAbwByACAAdQBzAGUAIABhAHMAIABmAHUAZQBsACAAaQBuACAAYQBuACAAYQBpAHIAYwByAGEAZgB0AFwAIgAsACAAMwAzAC4AMQAsACAAXAAiAGsAbABcACIALAAgADYANwAuADAALAAgADAALgAwADYALAAgADAALgA2ACwAIAA2ADcALgA2ADYALAAgADEAOAAuADAALAAgAFwAIgBOAEcAQQBGACAAMgAwADIANQA6ACAAVABhAGIAbABlACAAOQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAHYAaQBhAHQAaQBvAG4AXAAiACwAIABcACIASwBlAHIAbwBzAGUAbgBlACAAZgBvAHIAIAB1AHMAZQAgAGEAcwAgAGYAdQBlAGwAIABpAG4AIABhAG4AIABhAGkAcgBjAHIAYQBmAHQAXAAiACwAIAAzADYALgA4ACwAIABcACIAawBsAFwAIgAsACAANgA5AC4ANgAsACAAMAAuADAAMQAsACAAMAAuADYALAAgADcAMAAuADIAMQAsACAAMQA4AC4AMAAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEEAdgBpAGEAdABpAG8AbgBcACIALAAgAFwAIgBSAGUAbgBlAHcAYQBiAGwAZQAgAGEAdgBpAGEAdABpAG8AbgAgAGsAZQByAG8AcwBlAG4AZQBcACIALAAgADMANgAuADgALAAgAFwAIgBrAGwAXAAiACwAIAAwAC4AMAAsACAAMAAuADAAMQAsACAAMAAuADYALAAgADAALgA2ADEALAAgAFwAIgBOAEUAXAAiACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVgBlAHMAcwBlAGwAcwBcACIALAAgAFwAIgBHAGEAcwBvAGwAaQBuAGUAXAAiACwAIAAzADQALgAyACwAIABcACIAawBMAFwAIgAsACAANgA3AC4ANAAsACAAMQAwAC4AMQAsACAAMAAuADMALAAgAFwAIgBcACIALAAgADEANwAuADIALAAgAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4ANAAuADIALgAxAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFYAZQBzAHMAZQBsAHMAXAAiACwAIABcACIARABpAGUAcwBlAGwAIABvAGkAbABcACIALAAgADMAOAAuADYALAAgAFwAIgBrAEwAXAAiACwAIAA2ADkALgA5ACwAIAAwAC4AMgAsACAAMAAuADUALAAgAFwAIgBcACIALAAgADEANwAuADMALAAgAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4ANAAuADIALgAxAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFYAZQBzAHMAZQBsAHMAXAAiACwAIABcACIARgB1AGUAbAAgAE8AaQBsAFwAIgAsACAAMwA5AC4ANwAsACAAXAAiAGsATABcACIALAAgADcAMwAuADYALAAgADAALgAyACwAIAAwAC4ANQAsACAAXAAiAFwAIgAsACAAMQA4AC4AMAAsACAAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgA0AC4AMgAuADEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwBmAGYALQByAG8AYQBkACAAQQBnAHIAaQBjAHUAbAB0AHUAcgBlACAAYQBuAGQAIABmAG8AcgBlAHMAdAByAHkAIABlAHEAdQBpAHAAbQBlAG4AdABcACIALAAgAFwAIgBEAGkAZQBzAGUAbAAgAG8AaQBsAFwAIgAsACAAMwA4AC4ANgAsACAAXAAiAGsATABcACIALAAgADYAOQAuADkALAAgADAALgAzACwAIAAwAC4ANQAsACAAXAAiAFwAIgAsACAAMQA3AC4AMwAsACAAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgA0AC4AMgAuADEAXAAiAFwAbgAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACkAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAVAByAGEAbgBzAHAAbwByAHQAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAXAB1ADAAMAAyADcATgBFAFwAdQAwADAAMgA3ACAAdgBhAGwAdQBlAHMAIAByAGUAdAB1AHIAbgBlAGQAIABhAHMAIAB6AGUAcgBvACAAZgBvAHIAIABjAGEAbABjAHUAbABhAHQAaQBvAG4AcwAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBGAHUAZQBsACAAcwBjAG8AcABlACAAMQAgAGEAbgBkACAAMwAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIAAtACAATwBmAGYALQByAGEAZAAgAGUAcQB1AGkAcABtAGUAbgB0ACAAYQBuAGQAIAB2AGUAcwBzAGUAbABzAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAVAByAGEAbgBzAHAAbwByAHQATwBmAGYAUgBvAGEAZABfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEYAdQBlAGwAIABzAGMAbwBwAGUAIAAxACAAYQBuAGQAIAAzACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAC0AIABPAGYAZgAtAHIAbwBhAGQAIABlAHEAdQBpAHAAbQBlAG4AdAAgAGEAbgBkACAAdgBlAHMAcwBlAGwAcwBcACIAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAVAByAGEAbgBzAHAAbwByAHQATwBmAGYAUgBvAGEAZABfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEQAaQByAGUAYwB0ACAAKABzAGMAbwBwAGUAIAAxACkAIABhAG4AZAAgAGkAbgBkAGkAcgBlAGMAdAAgACgAcwBjAG8AcABlACAAMwApACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAdABoAGUAIABjAG8AbgBzAHUAbQBwAHQAaQBvAG4AIABvAGYAIABmAHUAZQBsAHMAIABpAG4AIABvAGYAZgAtAHIAbwBhAGQAIABlAHEAdQBpAHAAbQBlAG4AdAAgAGEAbgBkACAAdgBlAHMAcwBlAGwAcwBcACIAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAVAByAGEAbgBzAHAAbwByAHQATwBmAGYAUgBvAGEAZABfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADQALgAyAC4AMQBcACIAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAVAByAGEAbgBzAHAAbwByAHQATwBmAGYAUgBvAGEAZABfAEQAYQB0AGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAANwAsAFwAbgAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAYQBuAHMAcABvAHIAdAAgAHQAeQBwAGUAIAB0AFwAIgAsACAAXAAiAEYAdQBlAGwAIAB0AHkAcABlACAAcQBcACIALAAgAFwAIgBFAEMAVAByAGEAbgBzACwAcQAgACgARwBKAC8AawBMACkAXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAEMATwAyACAARQBGAFQAcgBhAG4ALAAxACwAdABxAGcAIAAoAGsAZwAgAEMATwAyAC0AZQAvAEcASgApAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAIABDAEgANAAgAEUARgBUAHIAYQBuACwAMQAsAHQAZwBnACAAKABrAGcAIABDAE8AMgAtAGUALwBHAEoAKQBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAxACAATgAyAE8AIABFAEYAVAByAGEAbgAsADEALAB0AGcAZwAgACgAawBnACAAQwBPADIALQBlAC8ARwBKACkAXAAiACwAIABcACIAUwBjAG8AcABlACAAMwAgAEUARgBUAHIAYQBuAHMALAAzACwAcQAgACgAawBnACAAQwBPADIALQBlAC8ARwBKACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVgBlAHMAcwBlAGwAXAAiACwAIABcACIAUABlAHQAcgBvAGwAXAAiACwAIAAzADQALgAyACwAIAA2ADcALgA0ACwAIAAxADAALgAxACwAIAAwAC4AMwAsACAAMQA3AC4AMgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFYAZQBzAHMAZQBsAFwAIgAsACAAXAAiAEQAaQBlAHMAZQBsAFwAIgAsACAAMwA4AC4ANgAsACAANgA5AC4AOQAsACAAMAAuADIALAAgADAALgA1ACwAIAAxADcALgAzADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVgBlAHMAcwBlAGwAXAAiACwAIABcACIARgB1AGUAbAAgAE8AaQBsAFwAIgAsACAAMwA5AC4ANwAsACAANwAzAC4ANgAsACAAMAAuADIALAAgADAALgA1ACwAIAAxADgALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwBmAGYALQByAG8AYQBkACAAQQBnAHIAaQBjAHUAbAB0AHUAcgBlACAAYQBuAGQAIABmAG8AcgBlAHMAdAByAHkAIABlAHEAdQBpAHAAbQBlAG4AdABcACIALAAgAFwAIgBEAGkAZQBzAGUAbABcACIALAAgADMAOAAuADYALAAgADYAOQAuADkALAAgADAALgAzACwAIAAwAC4ANQAsACAAMQA3AC4AMwBcAG4AIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgApACkAKQA7AFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEYAdQBlAGwAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBGAHUAZQBsAF8ARwBlAHQAVAByAGEAbgBzAHAAbwByAHQARgB1AGUAbABTAHQAcgBpAG4AZwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEMAZQBsAGwALABcAG4AIAAgACAAIABMAEUARgBUACgAQwBlAGwAbAAsACAARgBJAE4ARAAoAFwAIgAsACAAXAAiACwAQwBlAGwAbAApACAALQAxACkAXABuACkAOwBcAG4AXABuAEYAdQBlAGwAXwBHAGUAdABTAHQAYQB0AGkAbwBuAGEAcgB5AEYAdQBlAGwAUwB0AHIAaQBuAGcAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABDAGUAbABsACwAXABuACAAIAAgACAAUgBJAEcASABUACgAQwBlAGwAbAAsAEwARQBOACgAQwBlAGwAbAApAC0ARgBJAE4ARAAoAFwAIgAsACAAXAAiACwAQwBlAGwAbAApACkAXABuACkAOwBcAG4AXABuAEYAdQBlAGwAXwBUAG8AdABhAGwAQwBvAG4AcwB1AG0AcAB0AGkAbwBuAFwAbgA9ACAATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABGAHUAZQBsAEMAbwBuAHMAdQBtAHAAdABpAG8AbgBBAHIAcgBhAHkALAAgAEYAdQBlAGwAVQBzAGUAQQByAHIAYQB5ACwAIABGAHUAZQBsAFUAcwBlACwAIABGAHUAZQBsAFQAeQBwAGUAQQByAHIAYQB5ACwAIABGAHUAZQBsAFQAeQBwAGUALABcAG4AIAAgACAAIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAUwBVAE0AKABcAG4AIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABcAG4AIAAgACAAIAAgACAAIAAgAEYAdQBlAGwAQwBvAG4AcwB1AG0AcAB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgACAAIAAgACAAKABGAHUAZQBsAFQAeQBwAGUAQQByAHIAYQB5ACAAPQAgAEYAdQBlAGwAVAB5AHAAZQApACAAKgAgAFwAbgAgACAAIAAgACAAIAAgACAAKABGAHUAZQBsAFUAcwBlAEEAcgByAGEAeQAgAD0AIABGAHUAZQBsAFUAcwBlACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQAsAFwAbgAgACAAIAAgADAAXABuACAAIAApAFwAbgApADsAIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AOAA6ACAARgB1AGUAbAAgAFUAcwBlAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADgALgAxACAARgB1AGUAbAAgAFUAcwBlACAALQAgAFQAcgBhAG4AcwBwAG8AcgB0ACAAZgB1AGUAbABcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBcAG4AVgBFAEUAUgBHAF8AOABfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABRACwAIABFAEMALAAgAEUARgAsAFwAbgAgACAAIAAgACgAUQAgACoAIABFAEMAIAAqACAARQBGACkAIAAqACAAMQAwACAAXgAgAC0AIAAzAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADgAXwAxAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AVAByAGEAbgBzAHAAbwByAHQAXABuAEUAbQBpAHMAcwBpAG8AbgBzACAAZgBvAHIAIABlAGEAYwBoACAARwBIAEcAIABmAHIAbwBtACAAdABoAGUAIABjAG8AbQBiAHUAcwB0AGkAbwBuACAAbwBmACAAZgB1AGUAbABzACAAZgBvAHIAIAB0AHIAYQBuAHMAcABvAHIAdAAgAGUAbgBlAHIAZwB5ACAAcAB1AHIAcABvAHMAZQBzAFwAbgBRACAAOgAgAEEAbQBvAHUAbgB0ACAAbwBmACAAZgB1AGUAbAAgAHQAeQBwAGUAIABxACAAYwBvAG0AYgB1AHMAdABlAGQAIABmAG8AcgAgAHQAcgBhAG4AcwBwAG8AcgB0ACAAZQBuAGUAcgBnAHkAIABwAHUAcgBwAG8AcwBlAHMAIAA6ACAAawBMAFwAbgBFAEMAIAA6ACAAZQBuAGUAcgBnAHkAIABjAG8AbgB0AGUAbgB0ACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHQAcgBhAG4AcwBwAG8AcgB0ACAAZQBuAGUAcgBnAHkAIABwAHUAcgBwAG8AcwBlAHMAIAA6ACAARwBKAC8AawBMAFwAbgBFAEYAIAA6ACAAUwBjAG8AcABlACAAMQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AHIAYQBuAHMAcABvAHIAdAAgAGUAbgBlAHIAZwB5ACAAcAB1AHIAcABvAHMAZQBzACAAZgBvAHIAIABlAGEAYwBoACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzACAAOgAgAGsAZwAgAEMATwAyAGUAIAAvACAARwBKAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFwAbgBWAEUARQBSAEcAXwA4AF8AMQBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFQAcgBhAG4AcwBwAG8AcgB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFEAXwBUAHIAYQBuAHMAdABxACwAIABFAEMAXwBUAHIAYQBuAHMAcQAsACAARQBGAF8AVAByAGEAbgBzADEAdABxAGcALABcAG4AIAAgACAAIABWAEUARQBSAEcAXwA4AF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuACgAUQBfAFQAcgBhAG4AcwB0AHEALAAgAEUAQwBfAFQAcgBhAG4AcwBxACwAIABFAEYAXwBUAHIAYQBuAHMAMQB0AHEAZwApAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAFYARQBFAFIARwBfADgAXwAxAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AVAByAGEAbgBzAHAAbwByAHQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgBzACAAZgBvAHIAIABlAGEAYwBoACAARwBIAEcAIABmAHIAbwBtACAAdABoAGUAIABjAG8AbQBiAHUAcwB0AGkAbwBuACAAbwBmACAAZgB1AGUAbABzACAAZgBvAHIAIAB0AHIAYQBuAHMAcABvAHIAdAAgAGUAbgBlAHIAZwB5ACAAcAB1AHIAcABvAHMAZQBzAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA4AF8AMQBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFQAcgBhAG4AcwBwAG8AcgB0AF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AZwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOABfADEAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBUAHIAYQBuAHMAcABvAHIAdABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgAtAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADgAXwAxAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AVAByAGEAbgBzAHAAbwByAHQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAOAAuADEALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADgAXwAxAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AVAByAGEAbgBzAHAAbwByAHQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAE4AYQB0AGkAbwBuAGEAbAAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABBAGMAYwBvAHUAbgB0AHMAIABGAGEAYwB0AG8AcgBzACAAMgAwADIANQAgAC0AIAAyAC4AMwAgAEUAcwB0AGkAbQBhAHQAaQBuAGcAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIAB0AHIAYQBuAHMAcABvAHIAdAAgAGYAdQBlAGwAcwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOABfADEAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBUAHIAYQBuAHMAcABvAHIAdABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwBnAD0AXABcAHMAdQBtAFwAXABuAG8AbABpAG0AaQB0AHMAXwB0ACAAXABcAHMAdQBtAFwAXABuAG8AbABpAG0AaQB0AHMAXwBxAFwAXABsAGUAZgB0ACgAUQBfAHsAVAByAGEAbgBzACwAdABxAH0AXABcAHQAaQBtAGUAcwAgAEUAQwBfAHsAVAByAGEAbgBzACwAcQB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AFQAcgBhAG4AcwAsADEALAB0AHEAZwB9AFwAXAByAGkAZwBoAHQAKQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOABfADEAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBUAHIAYQBuAHMAcABvAHIAdABfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANwAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQBfAFQAcgBhAG4AcwB0AHEAXAAiACwAIABcACIAQQBtAG8AdQBuAHQAIABvAGYAIABmAHUAZQBsACAAdAB5AHAAZQAgAHEAIABjAG8AbQBiAHUAcwB0AGUAZAAgAGYAbwByACAAdAByAGEAbgBzAHAAbwByAHQAIABlAG4AZQByAGcAeQAgAHAAdQByAHAAbwBzAGUAcwBcACIALAAgAFwAIgBWAGEAcgBpAGUAcwAgAGIAYQBzAGUAZAAgAG8AbgAgAGYAdQBlAGwAIAB0AHkAcABlADoAIABrAEwALAAgAG0AMwAsACAARwBKAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAF8AVAByAGEAbgBzAHEAXAAiACwAIABcACIARQBuAGUAcgBnAHkAIABjAG8AbgB0AGUAbgB0ACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHQAcgBhAG4AcwBwAG8AcgB0ACAAZQBuAGUAcgBnAHkAIABwAHUAcgBwAG8AcwBlAHMAXAAiACwAIABcACIARwBKACAALwAgAHUAbgBpAHQAIABvAGYAIABmAHUAZQBsAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8AVAByAGEAbgBzADEAdABxAGcAXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AHIAYQBuAHMAcABvAHIAdAAgAGUAbgBlAHIAZwB5ACAAcAB1AHIAcABvAHMAZQBzACAAZgBvAHIAIABlAGEAYwBoACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAFwAIgAsACAAXAAiAGsAZwAgAEMATwAyAGUAIAAvACAARwBKAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAcQBcACIALAAgAFwAIgBGAHUAZQBsACAAdAB5AHAAZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBhAG4AcwBcACIALAAgAFwAIgBUAHIAYQBuAHMAcABvAHIAdAAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AXAAiACwAIABcACIAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBnAFwAIgAsACAAXAAiAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBcACIALAAgAFwAIgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEAXAAiACwAIABcACIAUwBjAG8AcABlACAAMQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA4AF8AMgBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFMAdABhAHQAaQBvAG4AYQByAHkAXABuAEUAbQBpAHMAcwBpAG8AbgBzACAAZgBvAHIAIABlAGEAYwBoACAARwBIAEcAIABmAHIAbwBtACAAdABoAGUAIABzAHQAYQB0AGkAbwBuAGEAcgB5ACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgAG8AZgAgAGYAdQBlAGwAcwBcAG4AUQAgADoAIABBAG0AbwB1AG4AdAAgAG8AZgAgAGYAdQBlAGwAIAB0AHkAcABlACAAcQAgAHUAcwBlAGQAIABmAG8AcgAgAHMAdABhAHQAaQBvAG4AYQByAHkAIABjAG8AbQBiAHUAcwB0AGkAbwBuACAAbwBwAGUAcgBhAHQAaQBvAG4AcwAgADoAIABrAEwAXABuAEUAQwAgADoAIABFAG4AZQByAGcAeQAgAGMAbwBuAHQAZQBuAHQAIABmAGEAYwB0AG8AcgAgAGYAbwByACAAcwB0AGEAdABpAG8AbgBhAHIAeQAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AIABvAHAAZQByAGEAdABpAG8AbgBzACAAOgAgAEcASgAvAGsATABcAG4ARQBGACAAOgAgAFMAYwBvAHAAZQAgADEAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAcwB0AGEAdABpAG8AbgBhAHIAeQAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AIABmAG8AcgAgAGUAYQBjAGgAIABnAHIAZQBlAG4AaABvAHUAcwBlACAAZwBhAHMAIAA6ACAAawBnACAAQwBPADIAZQAgAC8AIABHAEoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAFYARQBFAFIARwBfADgAXwAyAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AUwB0AGEAdABpAG8AbgBhAHIAeQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABRAF8AUwBDAHEALAAgAEUAQwBfAFMAQwBxACwAIABFAEYAXwBTAEMAMQBxAGcALABcAG4AIAAgACAAIABWAEUARQBSAEcAXwA4AF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuACgAUQBfAFMAQwBxACwAIABFAEMAXwBTAEMAcQAsACAARQBGAF8AUwBDADEAcQBnACkAXABuACAAIAApAFwAbgA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOABfADIAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBTAHQAYQB0AGkAbwBuAGEAcgB5AF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAGYAbwByACAAZQBhAGMAaAAgAEcASABHACAAZgByAG8AbQAgAHQAaABlACAAcwB0AGEAdABpAG8AbgBhAHIAeQAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AIABvAGYAIABmAHUAZQBsAHMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADgAXwAyAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AUwB0AGEAdABpAG8AbgBhAHIAeQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAGcAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADgAXwAyAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AUwB0AGEAdABpAG8AbgBhAHIAeQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgAtAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADgAXwAyAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AUwB0AGEAdABpAG8AbgBhAHIAeQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA4AC4AMgAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOABfADIAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBTAHQAYQB0AGkAbwBuAGEAcgB5AF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABOAGEAdABpAG8AbgBhAGwAIABHAHIAZQBlAG4AaABvAHUAcwBlACAAQQBjAGMAbwB1AG4AdABzACAARgBhAGMAdABvAHIAcwAgADIAMAAyADUAIAAtACAAMgAuADIAIABFAHMAdABpAG0AYQB0AGkAbgBnACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAcwB0AGEAdABpAG8AbgBhAHIAeQAgAGUAbgBlAHIAZwB5ACAAcwBvAHUAcgBjAGUAcwAgAC0AIABDAGEAbABjAHUAbABhAHQAaQBuAGcAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABzAHQAYQB0AGkAbwBuAGEAcgB5ACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgAG8AZgAgAGwAaQBxAHUAaQBkACAAZgB1AGUAbABzAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA4AF8AMgBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFMAdABhAHQAaQBvAG4AYQByAHkAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AZwA9AFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AdAAgAFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AcQBcAFwAbABlAGYAdAAoAFEAXwB7AFMAQwAsAHEAfQBcAFwAdABpAG0AZQBzACAARQBDAF8AewBTAEMALABxAH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAUwBDACwAMQAsAHEAZwB9AFwAXAByAGkAZwBoAHQAKQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOABfADIAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBTAHQAYQB0AGkAbwBuAGEAcgB5AF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA3ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBRAF8AUwBDAHEAXAAiACwAIABcACIAQQBtAG8AdQBuAHQAIABvAGYAIABmAHUAZQBsACAAdAB5AHAAZQAgAHEAIAB1AHMAZQBkACAAZgBvAHIAIABzAHQAYQB0AGkAbwBuAGEAcgB5ACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgAG8AcABlAHIAYQB0AGkAbwBuAHMAXAAiACwAIABcACIAVgBhAHIAaQBlAHMAIABiAGEAcwBlAGQAIABvAG4AIABmAHUAZQBsACAAdAB5AHAAZQA6ACAAawBMACwAIABtADMALAAgAEcASgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAQwBfAFMAQwBxAFwAIgAsACAAXAAiAEUAbgBlAHIAZwB5ACAAYwBvAG4AdABlAG4AdAAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABzAHQAYQB0AGkAbwBuAGEAcgB5ACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgAG8AcABlAHIAYQB0AGkAbwBuAHMAXAAiACwAIABcACIARwBKACAALwAgAHUAbgBpAHQAIABvAGYAIABmAHUAZQBsAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8AUwBDADEAcQBnAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAcwB0AGEAdABpAG8AbgBhAHIAeQAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AIABmAG8AcgAgAGUAYQBjAGgAIABnAHIAZQBlAG4AaABvAHUAcwBlACAAZwBhAHMAXAAiACwAIABcACIAawBnACAAQwBPADIAZQAgAC8AIABHAEoAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBxAFwAIgAsACAAXAAiAEYAdQBlAGwAIAB0AHkAcABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBDAFwAIgAsACAAXAAiAFMAdABhAHQAaQBvAG4AYQByAHkAIABjAG8AbQBiAHUAcwB0AGkAbwBuAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAZwBcACIALAAgAFwAIgBHAHIAZQBlAG4AaABvAHUAcwBlACAAZwBhAHMAXAAiACwAIABcACIAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAXAAiACwAIABcACIAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADkAOgAgAFIAZQBmAHIAaQBnAGUAcgBhAG4AdAAgAFUAcwBlAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADkALgAxACAAUgBlAGYAcgBpAGcAZQByAGEAbgB0ACAAVQBzAGUAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAXABuAFQAaABlACAAdABvAHQAYQBsACAAZQBtAGkAcwBzAGkAbwBuAHMAIABvAGYAIAByAGUAZgByAGkAZwBlAHIAYQBuAHQAIABsAGUAYQBrAGkAbgBnACAAZAB1AHIAaQBuAGcAIABvAHAAZQByAGEAdABpAG8AbgAgACgAbgBvAHQAIABkAHUAcgBpAG4AZwAgAGkAbgBzAHQAYQBsAGwAYQB0AGkAbwBuACAAbwByACAAZABpAHMAcABvAHMAYQBsACkAXABuAEcAVwBQAFIAIAA6ACAARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABvAGYAIAByAGUAZgByAGkAZwBlAHIAYQBuAHQAIABSACAAOgAgAEQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXABuAGMAaABhAHIAZwBlAF8AUgBhACAAOgAgAEEAbQBvAHUAbgB0ACAAbwBmACAAcgBlAGYAcgBpAGcAZQByAGEAbgB0ACAAUgAgAGMAbwBuAHQAYQBpAG4AZQBkACAAaQBuACAAYQBwAHAAbABpAGEAbgBjAGUAIABhACAAOgAgAGsAZwBcAG4AbABlAGEAawBhAGcAZQByAGEAdABlAF8AYQAgADoAIABQAHIAYwBlAG4AdABhAGcAZQAgAG8AZgAgAHQAbwB0AGEAbAAgAGMAaABhAHIAZwBlACAAbABlAGEAawBlAGQAIABmAHIAbwBtACAAYQBwAHAAbABpAGEAbgBjAGUAIABhACAAZQBhAGMAaAAgAHkAZQBhAHIAIAA6ACAAUABlAHIAYwBlAG4AdABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYwBoAGEAcgBnAGUAXwBSAGEALAAgAGwAZQBhAGsAYQBnAGUAcgBhAHQAZQBfAGEALABcAG4AIAAgACAAIAAoAGMAaABhAHIAZwBlAF8AUgBhACAAKgAgACgAbABlAGEAawBhAGcAZQByAGEAdABlAF8AYQAvADEAMAAwACkAKQAgACoAIAAxADAAIABeACAALQAgADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBHAFcAUABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8AUgAsACAARwBXAFAAXwBSACwAXABuACAAIAAgACAAKAAoAEUAXwBSACAAKgAgADEAMABeADMAKQAgACoAIABHAFcAUABfAFIAKQAgACoAIAAxADAAXgAtADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVABoAGUAIAB0AG8AdABhAGwAIABlAG0AaQBzAHMAaQBvAG4AcwAgAG8AZgAgAHIAZQBmAHIAaQBnAGUAcgBhAG4AdAAgAGwAZQBhAGsAaQBuAGcAIABkAHUAcgBpAG4AZwAgAG8AcABlAHIAYQB0AGkAbwBuACAAKABuAG8AdAAgAGQAdQByAGkAbgBnACAAaQBuAHMAdABhAGwAbABhAHQAaQBvAG4AIABvAHIAIABkAGkAcwBwAG8AcwBhAGwAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcARwBXAFAAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdAAgAGwAZQBhAGsAYQBnAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGMAbwBuAHYAZQByAHQAZQBkACAAdABvACAAQwBPADIALQBlAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAFIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAAcgBlAGYAcgBpAGcAZQByAGEAbgB0ACAAZwBhAHMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAEcAVwBQAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAC0AZQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAOQAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAE4AYQB0AGkAbwBuAGEAbAAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABBAGMAYwBvAHUAbgB0AHMAIABGAGEAYwB0AG8AcgBzACAAMgAwADIANQAgAC0AIAAzAC4AMQAgAEUAcwB0AGkAbQBhAHQAaQBuAGcAIABpAG4AZAB1AHMAdAByAGkAYQBsACAAcAByAG8AYwBlAHMAcwBlAHMAIABlAG0AaQBzAHMAaQBvAG4AcwAgAC0AIABSAGUAZgByAGkAZwBlAHIAYQBuAHQAIABsAGUAYQBrAGEAZwBlAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBfAFIAZQBhAGQAYQBiAGwAZQBFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGMAaABhAHIAZwBlAF8AUgBhACAAKgAgACgAbABlAGEAawBhAGcAZQByAGEAdABlAF8AYQAvADEAMAAwACkAIAAqACAAMQAwACAAXgAgAC0AIAAzAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwBSACAAPQAgAFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AYQAgAFwAXABsAGUAZgB0ACgAIABjAGgAYQByAGcAZQBfAHsAUgBhAH0AIABcAFwAdABpAG0AZQBzACAAXABcAGYAcgBhAGMAewBsAGUAYQBrAGEAZwBlAFwAXAAsAHIAYQB0AGUAXwBhAH0AewAxADAAMAB9ACAAXABcAHIAaQBnAGgAdAApACAAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAEcAVwBQAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAEMATwAyAGUAIAA9ACAAXABcAGwAZQBmAHQAKABFAF8AUgAgAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7ADMAfQAgAFwAXAByAGkAZwBoAHQAKQAgAFwAXAB0AGkAbQBlAHMAIABHAFcAUABfAFIAIABcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGMAaABhAHIAZwBlAF8AUgBhAFwAIgAsACAAXAAiAEEAbQBvAHUAbgB0ACAAbwBmACAAcgBlAGYAcgBpAGcAZQByAGEAbgB0ACAAUgAgAGMAbwBuAHQAYQBpAG4AZQBkACAAaQBuACAAYQBwAHAAbABpAGEAbgBjAGUAIABhAFwAIgAsACAAXAAiAGsAZwBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGwAZQBhAGsAYQBnAGUAcgBhAHQAZQBfAGEAXAAiACwAIABcACIAUAByAGMAZQBuAHQAYQBnAGUAIABvAGYAIAB0AG8AdABhAGwAIABjAGgAYQByAGcAZQAgAGwAZQBhAGsAZQBkACAAZgByAG8AbQAgAGEAcABwAGwAaQBhAG4AYwBlACAAYQAgAGUAYQBjAGgAIAB5AGUAYQByAFwAIgAsACAAXAAiAFAAZQByAGMAZQBuAHQAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBhAFwAIgAsACAAXAAiAEEAcABwAGwAaQBhAG4AYwBlACAAdAB5AHAAZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAXAAiACwAIABcACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAEcAVwBQAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAF8AUgBcACIALAAgAFwAIgBUAG8AdABhAGwAIABlAG0AaQBzAHMAaQBvAG4AcwAgAG8AZgAgAHIAZQBmAHIAaQBnAGUAcgBhAG4AdAAgAFIAXAAiACwAIABcACIAdAAgAHIAZQBmAHIAaQBnAGUAcgBhAG4AdAAgAGcAYQBzAFwAIgAsACAAXAAiAEMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAAOQAuADEALgAxACAAKAAxACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAF8AUgBcACIALAAgAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAG8AZgAgAHIAZQBmAHIAaQBnAGUAcgBhAG4AdAAgAFIAXAAiACwAIABcACIARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ATgAgAFMATwBVAFIAQwBFADoAIABBAGQAZABlAGQAIABlAHEAdQBhAHQAaQBvAG4AIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAcgBlAGYAcgBpAGcAZQByAGEAbgB0ACAAUgAgAHQAbwAgAEMATwAyAC0AZQAgAHUAcwBpAG4AZwAgAHQAaABlACAAcgBlAGYAcgBpAGcAZQByAGEAbgB0AFwAdQAwADAAMgA3AHMAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgACgARwBXAFAAKQAuAFwAIgApADsAIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAEEAcABwAGUAbgBkAGkAeAAgADIAIABHAGwAbwBiAGEAbAAgAFcAYQByAG0AaQBuAGcAIABQAG8AdABlAG4AdABpAGEAbABzADoAIABUAGEAYgBsAGUAIAAyADMAIABHAGwAbwBiAGEAbAAgAFcAYQByAG0AaQBuAGcAIABQAG8AdABlAG4AdABpAGEAbABzAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABHAFcAUABfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEcAbABvAGIAYQBsACAAVwBhAHIAbQBpAG4AZwAgAFAAbwB0AGUAbgB0AGkAYQBsAHMAXAAiACkAKQA7AFwAbgBcAG4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBDAGgAZQBtAGkAYwBhAGwARwBXAFAAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABHAFcAUABfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAE4AYQB0AGkAbwBuAGEAbAAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABBAGMAYwBvAHUAbgB0AHMAIABGAGEAYwB0AG8AcgBzACAAMgAwADIANQAgAC0AIABBAHAAcABlAG4AZABpAHgAIAAyACAALQAgAFQAYQBiAGwAZQAgADIAMwBcACIAKQApADsAXABuAFwAbgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABHAFcAUABfAEQAYQB0AGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwA5ACwAIAA1ACwAXABuACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEcAYQBzAFwAIgAsACAAXAAiAEMAaABlAG0AaQBjAGEAbAAgAGYAbwByAG0AdQBsAGEAXAAiACwAIABcACIARwBsAG8AYgBhAGwAIABXAGEAcgBtAGkAbgBnACAAUABvAHQAZQBuAHQAaQBhAGwAIAAoAEEAUgA1ACkAXAAiACwAIABcACIARwBhAHMAIAAtACAARgBDACAAbgBhAG0AZQBcACIALAAgAFwAIgBBAGQAaQB0AGkAbwBuAGEAbAAgAGQAYQB0AGEAIABzAG8AdQByAGMAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAXAAiACwAIABcACIAQwBPADIAXAAiACwAIAAxACwAIABcACIAQwBPADIAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIATQBlAHQAaABhAG4AZQBcACIALAAgAFwAIgBDAEgANABcACIALAAgADIAOAAsACAAXAAiAEMASAA0AFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAXAAiACwAIABcACIATgAyAE8AXAAiACwAIAAyADYANQAsACAAXAAiAE4AMgBPAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFMAdQBsAHAAaAB1AHIAIABoAGUAeABhAGYAbAB1AG8AcgBpAGQAZQBcACIALAAgAFwAIgBTAEYANgBcACIALAAgADIAMwA1ADAAMAAsACAAXAAiAFMARgA2AFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgARgBDAC0AMgAzACAAKABSAC0AMgAzACkAXAAiACwAIABcACIAQwBIAEYAMwBcACIALAAgACAAMQAyADQAMAAwACwAIABcACIASABGAEMALQAyADMAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABGAEMALQAzADIAIAAoAFIALQAzADIAKQBcACIALAAgAFwAIgBDAEgAMgBGADIAXAAiACwAIAA2ADcANwAsACAAXAAiAEgARgBDAC0AMwAyAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgARgBDAC0ANAAxACAAKABSAC0ANAAxACkAXAAiACwAIABcACIAQwBIADMARgBcACIALAAgACAAMQAxADYALAAgAFwAIgBIAEYAQwAtADQAMQBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAEYAQwAtADQAMwAtADEAMABtAGUAZQAgACgAUgAtADQAMwAxADAAbQBlAGUAKQBcACIALAAgAFwAIgBDADUASAAyAEYAMQAwAFwAIgAsACAAMQA2ADUAMAAsACAAXAAiAEgARgBDAC0ANAAzAC0AMQAwAG0AZQBlAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgARgBDAC0AMQAyADUAIAAoAFIALQAxADIANQApAFwAIgAsACAAXAAiAEMAMgBIAEYANQBcACIALAAgACAAMwAxADcAMAAsACAAXAAiAEgARgBDAC0AMQAyADUAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABGAEMALQAxADMANAAgACgAUgAtADEAMwA0ACkAXAAiACwAIABcACIAQwAyAEgAMgBGADQAIAAoAEMASABGADIAQwBIAEYAMgApAFwAIgAsACAAIAAxADEAMgAwACwAIABcACIASABGAEMALQAxADMANABcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAEYAQwAtADEAMwA0AGEAIAAoAFIALQAxADMANABhACkAXAAiACwAIABcACIAQwAyAEgAMgBGADQAIAAoAEMASAAyAEYAQwBGADMAKQBcACIALAAgADEAMwAwADAALAAgAFwAIgBIAEYAQwAtADEAMwA0AGEAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABGAEMALQAxADQAMwAgACgAUgAtADEANAAzACkAXAAiACwAIABcACIAQwAyAEgAMwBGADMAIAAoAEMASABGADIAQwBIADIARgApAFwAIgAsACAAMwAyADgALAAgAFwAIgBIAEYAQwAtADEANAAzAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgARgBDAC0AMQA0ADMAYQAgACgAUgAtADEANAAzAGEAKQBcACIALAAgAFwAIgBDADIASAAzAEYAMwAgACgAQwBGADMAQwBIADMAKQBcACIALAAgADQAOAAwADAALAAgAFwAIgBIAEYAQwAtADEANAAzAGEAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABGAEMALQAxADUAMgBhACAAKABSAC0AMQA1ADIAYQApAFwAIgAsACAAXAAiAEMAMgBIADQARgAyACAAKABDAEgAMwBDAEgARgAyACkAXAAiACwAIAAxADMAOAAsACAAXAAiAEgARgBDAC0AMQA1ADIAYQBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAEYAQwAtADIAMgA3AGUAYQAgACgAUgAtADIAMgA3AGUAYQApAFwAIgAsACAAXAAiAEMAMwBIAEYANwBcACIALAAgADMAMwA1ADAALAAgAFwAIgBIAEYAQwAtADIAMgA3AGUAYQBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAEYAQwAtADIAMwA2AGYAYQAgACgAUgAtADIAMwA2AGYAYQApAFwAIgAsACAAXAAiAEMAMwBIADIARgA2AFwAIgAsACAAOAAwADYAMAAsACAAXAAiAEgARgBDAC0AMgAzADYAZgBhAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgARgBDAC0AMgA0ADUAYwBhACAAKABSAC0AMgA0ADUAYwBhACkAXAAiACwAIABcACIAQwAzAEgAMwBGADUAXAAiACwAIAA3ADEANgAsACAAXAAiAEgARgBDAC0AMgA0ADUAYwBhAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgARgBDAC0AMgA0ADUAZgBhACAAKABSAC0AMgA0ADUAZgBhACkAXAAiACwAIABcACIAQwBIAEYAMgBDAEgAMgBDAEYAMwBcACIALAAgADgANQA4ACwAIABcACIASABGAEMALQAyADQANQBmAGEAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABGAEMALQAzADYANQBtAGYAYwAgACgAUgAtADMANgA1AG0AZgBjACkAXAAiACwAIABcACIAQwBIADMAQwBGADIAQwBIADIAQwBGADMAXAAiACwAIAA4ADAANAAsACAAXAAiAEgARgBDAC0AMwA2ADUAbQBmAGMAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABDAEYAQwAtADIAMgAgACgAUgAtADIAMgApAFwAIgAsACAAXAAiAEMASABDAGwARgAyAFwAIgAsACAAMQA3ADYAMAAsACAAXAAiAEgAQwBGAEMALQAyADIAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABDAEYAQwAtADEAMgAzACAAKABSAC0AMQAyADMAKQBcACIALAAgAFwAIgBDAEgAQwBsADIAMgBDAEYAMwBcACIALAAgADcAOQAsACAAXAAiAEgAQwBGAEMALQAxADIAMwBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAEMARgBDAC0AMQAyADQAIAAoAFIALQAxADIANAApAFwAIgAsACAAXAAiAEMASABDAGwARgBDAEYAMwBcACIALAAgADUAMgA3ACwAIABcACIASABDAEYAQwAtADEAMgA0AFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAQwBGAEMALQAxADQAMQBiACAAKABSAC0AMQA0ADEAYgApAFwAIgAsACAAXAAiAEMASAAzAEMAQwBsADIARgBcACIALAAgADcAOAAyACwAIABcACIASABDAEYAQwAtADEANAAxAGIAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABDAEYAQwAtADEANAAyAGIAIAAoAFIALQAxADQAMgBiACkAXAAiACwAIABcACIAQwBIADIAQwBDAGwARgAyAFwAIgAsACAAMQA5ADgAMAAsACAAXAAiAEgAQwBGAEMALQAxADQAMgBiAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAQwBGAEMALQAyADIANQBjAGEAIAAoAFIALQAyADIANQBjAGEAKQBcACIALAAgAFwAIgBDAEgAQwBsADIAQwBGADIAQwBGADMAXAAiACwAIAAxADIANwAsACAAXAAiAEgAQwBGAEMALQAyADIANQBjAGEAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABDAEYAQwAtADIAMgA1AGMAYgAgACgAUgAtADIAMgA1AGMAYgApAFwAIgAsACAAXAAiAEMASABDAGwARgBDAEYAMgBDAEMASQBGADIAXAAiACwAIAA1ADIANQAsACAAXAAiAEgAQwBGAEMALQAyADIANQBjAGIAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUABGAEMALQAxADQAIABQAGUAcgBmAGwAdQBvAHIAbwBtAGUAdABoAGEAbgBlACAAKAB0AGUAdAByAGEAZgBsAHUAbwByAG8AbQBlAHQAaABhAG4AZQApAFwAIgAsACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAAsACAAXAAiAFAARgBDAC0AMQA0AFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFAARgBDAC0AMQAxADYAIABQAGUAcgBmAGwAdQBvAHIAbwBlAHQAaABhAG4AZQAgACgAaABlAHgAYQBmAGwAdQBvAHIAbwBlAHQAaABhAG4AZQApAFwAIgAsACAAXAAiAEMAMgBGADYAXAAiACwAIAAxADEAMQAwADAALAAgAFwAIgBQAEYAQwAtADEAMQA2AFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFAARgBDAC0AMgAxADgAIABQAGUAcgBmAGwAdQBvAHIAbwBwAHIAbwBwAGEAbgBlAFwAIgAsACAAXAAiAEMAMwBGADgAXAAiACwAIAA4ADkAMAAwACwAIABcACIAUABGAEMALQAyADEAOABcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAEYAQwAtADMAMQAtADEAMAAgAFAAZQByAGYAbAB1AG8AcgBvAGIAdQB0AGEAbgBlAFwAIgAsACAAXAAiAEMANABGADEAMABcACIALAAgADkAMgAwADAALAAgAFwAIgBQAEYAQwAtADMAMQAtADEAMABcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAEYAQwAtADMAMQA4ACAAUABlAHIAZgBsAHUAbwByAG8AYwB5AGMAbABvAGIAdQB0AGEAbgBlAFwAIgAsACAAXAAiAGMALQBDADQARgA4AFwAIgAsACAAOQA1ADQAMAAsACAAXAAiAFAARgBDAC0AMwAxADgAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUABGAEMALQA0ADEALQAxADIAIABQAGUAcgBmAGwAdQBvAHIAbwBwAGUAbgB0AGEAbgBlAFwAIgAsACAAXAAiAEMANQBGADEAMgBcACIALAAgADgANQA1ADAALAAgAFwAIgBQAEYAQwAtADQAMQAtADEAMgBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAEYAQwAtADUAMQAtADEANAAgAFAAZQByAGYAbAB1AG8AcgBvAGgAZQB4AGEAbgBlAFwAIgAsACAAXAAiAEMANgBGADEANABcACIALAAgADcAOQAxADAALAAgAFwAIgBQAEYAQwAtADUAMQAtADEANABcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAEYAQwAtADkAMQAtADEAOAAgAFAAZQByAGYAbAB1AG4AYQBmAGUAbgBlAFwAIgAsACAAXAAiAEMAMQAwAEYAMQA4AFwAIgAsACAANwAxADkAMAAsACAAXAAiAFAARgBDAC0AOQAxAC0AMQA4AFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMARgBDAC0AMQAyAFwAIgAsACAAXAAiAEMAQwBsADIARgAyAFwAIgAsACAAMQAwADIAMAAwACwAIABcACIAQwBGAEMALQAxADIAXAAiACwAIABcACIASQBQAEMAQwAgAEcAbABvAGIAYQBsACAAVwBhAHIAbQBpAG4AZwAgAFAAbwB0AGUAbgB0AGkAYQBsACAAVgBhAGwAdQBlAHMAIAB2ADIALgAwACAALQAgACgAQQBSADUAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAEYAQwAtADEAMwBcACIALAAgAFwAIgBDAEMAbABGADMAXAAiACwAIAAxADMAOQAwADAALAAgAFwAIgBDAEYAQwAtADEAMwBcACIALAAgAFwAIgBJAFAAQwBDACAARwBsAG8AYgBhAGwAIABXAGEAcgBtAGkAbgBnACAAUABvAHQAZQBuAHQAaQBhAGwAIABWAGEAbAB1AGUAcwAgAHYAMgAuADAAIAAtACAAKABBAFIANQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMARgBDAC0AMQAxADQAXAAiACwAIABcACIAQwBDAGwARgAyAEMAQwBsAEYAMgBcACIALAAgADgANQA5ADAALAAgAFwAIgBDAEYAQwAtADEAMQA0AFwAIgAsACAAXAAiAEkAUABDAEMAIABHAGwAbwBiAGEAbAAgAFcAYQByAG0AaQBuAGcAIABQAG8AdABlAG4AdABpAGEAbAAgAFYAYQBsAHUAZQBzACAAdgAyAC4AMAAgAC0AIAAoAEEAUgA1ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBGAEMALQAxADEANQBcACIALAAgAFwAIgBDAEMAbABGADIAQwBGADMAXAAiACwAIAA3ADYANwAwACwAIABcACIAQwBGAEMALQAxADEANQBcACIALAAgAFwAIgBJAFAAQwBDACAARwBsAG8AYgBhAGwAIABXAGEAcgBtAGkAbgBnACAAUABvAHQAZQBuAHQAaQBhAGwAIABWAGEAbAB1AGUAcwAgAHYAMgAuADAAIAAtACAAKABBAFIANQApAFwAIgBcAG4AIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgApACkAKQA7AFwAbgBcAG4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBDAGgAZQBtAGkAYwBhAGwARwBXAFAAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABcAHUAMAAwADIANwBHAEEAUwAgAC0AIABGAEMAIABuAGEAbQBlAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AIAB3AGkAdABoACAAdAByAHUAbgBjAGEAdABlAGQAIABnAGEAcwAgAG4AYQBtAGUAIAB0AG8AIABhAGwAbABvAHcAIABtAGEAdABjAGgAaQBuAGcAIAB3AGkAdABoACAAbwB0AGgAZQByACAAdABhAGIAbABlAHMALgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAGcAYQBzAGUAcwAgAGYAcgBvAG0AIABJAFAAQwBDACAARwBsAG8AYgBhAGwAIABXAGEAcgBtAGkAbgBnACAAUABvAHQAZQBuAHQAaQBhAGwAIABWAGEAbAB1AGUAcwAgAHYAMgAuADAAIAAtACAAKABBAFIANQApAC4AIABBAGQAZABlAGQAIABcAHUAMAAwADIANwBBAGQAZABpAHQAaQBvAG4AYQBsACAAZABhAHQAYQAgAHMAbwB1AHIAYwBlAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4ALgBcACIAKQApADsAXABuAFwAbgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAEEAcABwAGUAbgBkAGkAeAAgADIAIABHAGwAbwBiAGEAbAAgAFcAYQByAG0AaQBuAGcAIABQAG8AdABlAG4AdABpAGEAbABzADoAIABCAGwAZQBuAGQAZQBkACAAcgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AQwBoAGUAbQBpAGMAYQBsAEIAbABlAG4AZABzAF8AVABpAHQAbABlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAQgBsAGUAbgBkAGUAZAAgAHIAZQBmAHIAaQBnAGUAcgBhAG4AdABzACAAKABtAGEAbgB5ACAAYwBvAG4AdABhAGkAbgBpAG4AZwAgAEgARgBDAFMAIABhAG4AZAAvAG8AcgAgAFAARgBDAFMAKQBcACIAKQApADsAXABuAFwAbgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABCAGwAZQBuAGQAcwBfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AQwBoAGUAbQBpAGMAYQBsAEIAbABlAG4AZABzAF8AUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAEEAYwBjAG8AdQBuAHQAcwAgAEYAYQBjAHQAbwByAHMAIAAyADAAMgA1ACAALQAgAEEAcABwAGUAbgBkAGkAeAAgADIAIAAtACAAVABhAGIAbABlACAAMgA0AFwAIgApACkAOwBcAG4AXABuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AQwBoAGUAbQBpAGMAYQBsAEIAbABlAG4AZABzAF8ARABhAHQAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ADEALAAgADMALABcAG4AIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIABcACIAQgBsAGUAbgBkAFwAIgAsACAAXAAiAEMAbwBuAHMAdABpAHQAdQBlAG4AdABzAFwAIgAsACAAXAAiAEMAbwBtAHAAbwBzAGkAdABpAG8AbgAgACgAJQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADAAMABcACIALAAgAFwAIgBDAEYAQwAtADEAMgAvAEMARgBDAC0AMQAxADQAXAAiACwAIABcACIAUgAtADQAMAAwACAAYwBhAG4AIABoAGEAdgBlACAAdgBhAHIAaQBvAHUAcwAgAHAAcgBvAHAAbwByAHQAaQBvAG4AcwAgAG8AZgAgAEMARgBDAC0AMQAyACAAYQBuAGQAIABDAEYAQwAtADEAMQA0AC4AIABUAGgAZQAgAGUAeABhAGMAdAAgAGMAbwBtAHAAbwBzAGkAdABpAG8AbgAgAG4AZQBlAGQAcwAgAHQAbwAgAGIAZQAgAHMAcABlAGMAaQBmAGkAZQBkACwAIABlAC4AZwAuACwAIABSAC0ANAAwADAAIAAoADYAMAAvADQAMAApAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMAAxAEEAXAAiACwAIABcACIASABDAEYAQwAtADIAMgAvAEgARgBDAC0AMQA1ADIAYQAvAEgAQwBGAEMALQAxADIANABcACIALAAgAFwAIgAoADUAMwAuADAALwAxADMALgAwAC8AMwA0AC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADAAMQBCAFwAIgAsACAAXAAiAEgAQwBGAEMALQAyADIALwBIAEYAQwAtADEANQAyAGEALwBIAEMARgBDAC0AMQAyADQAXAAiACwAIABcACIAKAA2ADEALgAwAC8AMQAxAC4AMAAvADIAOAAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAwADEAQwBcACIALAAgAFwAIgBIAEMARgBDAC0AMgAyAC8ASABGAEMALQAxADUAMgBhAC8ASABDAEYAQwAtADEAMgA0AFwAIgAsACAAXAAiACgAMwAzAC4AMAAvADEANQAuADAALwA1ADIALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMAAyAEEAXAAiACwAIABcACIASABGAEMALQAxADIANQAvAEgAQwAtADIAOQAwAC8ASABDAEYAQwAtADIAMgBcACIALAAgAFwAIgAoADYAMAAuADAALwAyAC4AMAAvADMAOAAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAwADIAQgBcACIALAAgAFwAIgBIAEYAQwAtADEAMgA1AC8ASABDAC0AMgA5ADAALwBIAEMARgBDAC0AMgAyAFwAIgAsACAAXAAiACgAMwA4AC4AMAAvADIALgAwAC8ANgAwAC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADAAMwBBAFwAIgAsACAAXAAiAEgAQwAtADIAOQAwAC8ASABDAEYAQwAtADIAMgAvAFAARgBDAC0AMgAxADgAXAAiACwAIABcACIAKAA1AC4AMAAvADcANQAuADAALwAyADAALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMAAzAEIAXAAiACwAIABcACIASABDAC0AMgA5ADAALwBIAEMARgBDAC0AMgAyAC8AUABGAEMALQAyADEAOABcACIALAAgAFwAIgAoADUALgAwAC8ANQA2AC4AMAAvADMAOQAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAwADQAQQBcACIALAAgAFwAIgBIAEYAQwAtADEAMgA1AC8ASABGAEMALQAxADQAMwBhAC8ASABGAEMALQAxADMANABhAFwAIgAsACAAXAAiACgANAA0AC4AMAAvADUAMgAuADAALwA0AC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADAANQBBAFwAIgAsACAAXAAiAEgAQwBGAEMALQAyADIALwAgAEgARgBDAC0AMQA1ADIAYQAvAEgAQwBGAEMALQAxADQAMgBiAC8AUABGAEMALQAzADEAOABcACIALAAgAFwAIgAoADQANQAuADAALwA3AC4AMAAvADUALgA1AC8ANAAyAC4ANQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADAANgBBAFwAIgAsACAAXAAiAEgAQwBGAEMALQAyADIALwBIAEMALQA2ADAAMABhAC8ASABDAEYAQwAtADEANAAyAGIAXAAiACwAIABcACIAKAA1ADUALgAwAC8AMQA0AC4AMAAvADQAMQAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAwADcAQQBcACIALAAgAFwAIgBIAEYAQwAtADMAMgAvAEgARgBDAC0AMQAyADUALwBIAEYAQwAtADEAMwA0AGEAXAAiACwAIABcACIAKAAyADAALgAwAC8ANAAwAC4AMAAvADQAMAAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAwADcAQgBcACIALAAgAFwAIgBIAEYAQwAtADMAMgAvAEgARgBDAC0AMQAyADUALwBIAEYAQwAtADEAMwA0AGEAXAAiACwAIABcACIAKAAxADAALgAwAC8ANwAwAC4AMAAvADIAMAAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAwADcAQwBcACIALAAgAFwAIgBIAEYAQwAtADMAMgAvAEgARgBDAC0AMQAyADUALwBIAEYAQwAtADEAMwA0AGEAXAAiACwAIABcACIAKAAyADMALgAwAC8AMgA1AC4AMAAvADUAMgAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAwADcARABcACIALAAgAFwAIgBIAEYAQwAtADMAMgAvAEgARgBDAC0AMQAyADUALwBIAEYAQwAtADEAMwA0AGEAXAAiACwAIABcACIAKAAxADUALgAwAC8AMQA1AC4AMAAvADcAMAAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAwADcARQBcACIALAAgAFwAIgBIAEYAQwAtADMAMgAvAEgARgBDAC0AMQAyADUALwBIAEYAQwAtADEAMwA0AGEAXAAiACwAIABcACIAKAAyADUALgAwAC8AMQA1AC4AMAAvADYAMAAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAwADgAQQBcACIALAAgAFwAIgBIAEYAQwAtADEAMgA1AC8ASABGAEMALQAxADQAMwBhAC8ASABDAEYAQwAtADIAMgBcACIALAAgAFwAIgAoADcALgAwAC8ANAA2AC4AMAAvADQANwAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAwADkAQQBcACIALAAgAFwAIgBIAEMARgBDAC0AMgAyAC8ASABDAEYAQwAtADEAMgA0AC8ASABDAEYAQwAtADEANAAyAGIAXAAiACwAIABcACIAKAA2ADAALgAwAC8AMgA1AC4AMAAvADEANQAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAwADkAQgBcACIALAAgAFwAIgBIAEMARgBDAC0AMgAyAC8ASABDAEYAQwAtADEAMgA0AC8ASABDAEYAQwAtADEANAAyAGIAXAAiACwAIABcACIAKAA2ADUALgAwAC8AMgA1AC4AMAAvADEAMAAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAxADAAQQBcACIALAAgAFwAIgBIAEYAQwAtADMAMgAvAEgARgBDAC0AMQAyADUAXAAiACwAIABcACIAKAA1ADAALgAwAC8ANQAwAC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADEAMABCAFwAIgAsACAAXAAiAEgARgBDAC0AMwAyAC8ASABGAEMALQAxADIANQBcACIALAAgAFwAIgAoADQANQAuADAALwA1ADUALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMQAxAEEAXAAiACwAIABcACIASABDAC0AMQAyADcAMAAvAEgAQwBGAEMALQAyADIALwBIAEYAQwAtADEANQAyAGEAXAAiACwAIABcACIAKAAxAC4ANQAvADgANwAuADUALwAxADEALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMQAxAEIAXAAiACwAIABcACIASABDAC0AMQAyADcAMAAvAEgAQwBGAEMALQAyADIALwBIAEYAQwAtADEANQAyAGEAXAAiACwAIABcACIAKAAzAC4AMAAvADkANAAuADAALwAzAC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADEAMQBDAFwAIgAsACAAXAAiAEgAQwAtADEAMgA3ADAALwBIAEMARgBDAC0AMgAyAC8ASABGAEMALQAxADUAMgBhAFwAIgAsACAAXAAiACgAMwAuADAALwA5ADUALgA1AC8AMQAuADUAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAxADIAQQBcACIALAAgAFwAIgBIAEMARgBDAC0AMgAyAC8AUABGAEMALQAyADEAOAAvAEgAQwBGAEMALQAxADQAMgBiAFwAIgAsACAAXAAiACgANwAwAC4AMAAvADUALgAwAC8AMgA1AC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADEAMwBBAFwAIgAsACAAXAAiAFAARgBDAC0AMgAxADgALwBIAEYAQwAtADEAMwA0AGEALwBIAEMALQA2ADAAMABhAFwAIgAsACAAXAAiACgAOQAuADAALwA4ADgALgAwAC8AMwAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAxADQAQQBcACIALAAgAFwAIgBIAEMARgBDAC0AMgAyAC8ASABDAEYAQwAtADEAMgA0AC8ASABDAC0ANgAwADAAYQAvAEgAQwBGAEMALQAxADQAMgBiAFwAIgAsACAAXAAiACgANQAxAC4AMAAvADIAOAAuADUALwA0AC4AMAAvADEANgAuADUAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAxADQAQgBcACIALAAgAFwAIgBIAEMARgBDAC0AMgAyAC8ASABDAEYAQwAtADEAMgA0AC8ASABDAC0ANgAwADAAYQAvAEgAQwBGAEMALQAxADQAMgBiAFwAIgAsACAAXAAiACgANQAwAC4AMAAvADMAOQAuADAALwAxAC4ANQAvADkALgA1ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMQA1AEEAXAAiACwAIABcACIASABDAEYAQwAtADIAMgAvAEgARgBDAC0AMQA1ADIAYQBcACIALAAgAFwAIgAoADgAMgAuADAALwAxADgALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMQA1AEIAXAAiACwAIABcACIASABDAEYAQwAtADIAMgAvAEgARgBDAC0AMQA1ADIAYQBcACIALAAgAFwAIgAoADIANQAuADAALwA3ADUALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMQA2AEEAXAAiACwAIABcACIASABGAEMALQAxADMANABhAC8ASABDAEYAQwAtADEAMgA0AC8ASABDAC0ANgAwADAAXAAiACwAIABcACIAKAA1ADkALgAwAC8AMwA5AC4ANQAvADEALgA1ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMQA3AEEAXAAiACwAIABcACIASABGAEMALQAxADIANQAvAEgARgBDAC0AMQAzADQAYQAvAEgAQwAtADYAMAAwAFwAIgAsACAAXAAiACgANAA2AC4ANgAvADUAMAAuADAALwAzAC4ANAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADEAOABBAFwAIgAsACAAXAAiAEgAQwAtADIAOQAwAC8ASABDAEYAQwAtADIAMgAvAEgARgBDAC0AMQA1ADIAYQBcACIALAAgAFwAIgAoADEALgA1AC8AOQA2AC4AMAAvADIALgA1ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMQA5AEEAXAAiACwAIABcACIASABGAEMALQAxADIANQAvAEgARgBDAC0AMQAzADQAYQAvAEgARQAtAEUAMQA3ADAAXAAiACwAIABcACIAKAA3ADcALgAwAC8AMQA5AC4AMAAvADQALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMgAwAEEAXAAiACwAIABcACIASABGAEMALQAxADMANABhAC8ASABDAEYAQwAtADEANAAyAGIAXAAiACwAIABcACIAKAA4ADgALgAwAC8AMQAyAC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADIAMQBBAFwAIgAsACAAXAAiAEgARgBDAC0AMQAyADUALwBIAEYAQwAtADEAMwA0AGEAXAAiACwAIABcACIAKAA1ADgALgAwAC8ANAAyAC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADIAMgBBAFwAIgAsACAAXAAiAEgARgBDAC0AMQAyADUALwBIAEYAQwAtADEAMwA0AGEALwBIAEMALQA2ADAAMABhAFwAIgAsACAAXAAiACgAOAA1AC4AMQAvADEAMQAuADUALwAzAC4ANAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADIAMgBCAFwAIgAsACAAXAAiAEgARgBDAC0AMQAyADUALwBIAEYAQwAtADEAMwA0AGEALwBIAEMALQA2ADAAMABhAFwAIgAsACAAXAAiACgANQA1AC4AMAAvADQAMgAuADAALwAzAC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADIAMgBDAFwAIgAsACAAXAAiAEgARgBDAC0AMQAyADUALwBIAEYAQwAtADEAMwA0AGEALwBIAEMALQA2ADAAMABhAFwAIgAsACAAXAAiACgAOAAyAC4AMAAvADEANQAuADAALwAzAC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA1ADAAMABcACIALAAgAFwAIgBDAEYAQwAtADEAMgAvAEgARgBDAC0AMQA1ADIAYQBcACIALAAgAFwAIgAoADcAMwAuADgALwAyADYALgAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADUAMAAxAFwAIgAsACAAXAAiAEgAQwBGAEMALQAyADIALwBDAEYAQwAtADEAMgBcACIALAAgAFwAIgAoADcANQAuADAALwAyADUALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADUAMAAyAFwAIgAsACAAXAAiAEgAQwBGAEMALQAyADIALwBDAEYAQwAtADEAMQA1AFwAIgAsACAAXAAiACgANAA4AC4AOAAvADUAMQAuADIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANQAwADMAXAAiACwAIABcACIASABGAEMALQAyADMALwBDAEYAQwAtADEAMwBcACIALAAgAFwAIgAoADQAMAAuADEALwA1ADkALgA5ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADUAMAA0AFwAIgAsACAAXAAiAEgARgBDAC0AMwAyAC8AQwBGAEMALQAxADEANQBcACIALAAgAFwAIgAoADQAOAAuADIALwA1ADEALgA4ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADUAMAA1AFwAIgAsACAAXAAiAEMARgBDAC0AMQAyAC8ASABDAEYAQwAtADMAMQBcACIALAAgAFwAIgAoADcAOAAuADAALwAyADIALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADUAMAA2AFwAIgAsACAAXAAiAEMARgBDAC0AMwAxAC8AQwBGAEMALQAxADEANABcACIALAAgAFwAIgAoADUANQAuADEALwA0ADQALgA5ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADUAMAA3AEEAXAAiACwAIABcACIASABGAEMALQAxADIANQAvAEgARgBDAC0AMQA0ADMAYQBcACIALAAgAFwAIgAoADUAMAAuADAALwA1ADAALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADUAMAA4AEEAXAAiACwAIABcACIASABGAEMALQAyADMALwBQAEYAQwAtADEAMQA2AFwAIgAsACAAXAAiACgAMwA5AC4AMAAvADYAMQAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANQAwADgAQgBcACIALAAgAFwAIgBIAEYAQwAtADIAMwAvAFAARgBDAC0AMQAxADYAXAAiACwAIABcACIAKAA0ADYALgAwAC8ANQA0AC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA1ADAAOQBBAFwAIgAsACAAXAAiAEgAQwBGAEMALQAyADIALwBQAEYAQwAtADIAMQA4AFwAIgAsACAAXAAiACgANAA0AC4AMAAvADUANgAuADAAKQBcACIAXABuACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AKQApACkAOwBcAG4AXABuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AQwBoAGUAbQBpAGMAYQBsAEIAbABlAG4AZABzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAARgBpAHgAZQBkACAAdAB5AHAAbwAgAC0AIABjAGgAYQBuAGcAZQBkACAASABDADYAMAAwAGEAIAB0AG8AIABIAEMALQA2ADAAMABhACAAZgBvAHIAIABiAGwAZQBuAGQAIABSAC0ANAAxADQAQgAuACAARgBpAHgAZQBkACAAdAB5AHAAbwAgAGYAbwByACAAYgBsAGUAbgBkACAAUgAtADQAMAA1AEEAIAAtACAAQwBoAGEAbgBnAGUAZAAgAEgAQwBGAEMAMQA0ADIAYgAgAHQAbwAgAEgAQwBGAEMALQAxADQAMgBiAC4AXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ATABlAGEAawBhAGcAZQAgAHIAYQB0AGUAcwAgAGYAbwByACAAYwBvAG0AbQBvAG4AIAByAGUAZgByAGkAZwBlAHIAYQB0AGkAbwBuACAAYQBuAGQAIABhAGkAcgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBMAGUAYQBrAGEAZwBlAFIAYQB0AGUAcwBfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEkAbgBkAGkAYwBhAHQAaQB2AGUAIABsAGUAYQBrAGEAZwBlACAAcgBhAHQAZQBzACAAZgBvAHIAIABjAG8AbQBtAG8AbgAgAHIAZQBmAHIAaQBnAGUAcgBhAHQAaQBvAG4AIABhAG4AZAAgAGEAaQByACAALQAgAGMAbwBuAGQAaQB0AGkAbwBuAGkAbgBnACAAZQBxAHUAaQBwAG0AZQBuAHQAXAAiACkAKQA7AFwAbgBcAG4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBMAGUAYQBrAGEAZwBlAFIAYQB0AGUAcwBfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ATABlAGEAawBhAGcAZQBSAGEAdABlAHMAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABOAGEAdABpAG8AbgBhAGwAIABHAHIAZQBlAG4AaABvAHUAcwBlACAAQQBjAGMAbwB1AG4AdABzACAARgBhAGMAdABvAHIAcwAgADIAMAAyADUAIAAtACAAVABhAGIAbABlACAAMQAwAFwAIgApACkAOwBcAG4AXABuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ATABlAGEAawBhAGcAZQBSAGEAdABlAHMAXwBEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADgAMQAsACAAMgAsAFwAbgAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwBkAHUAYwB0AFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAbABlAGEAawBhAGcAZQAgAHIAYQB0AGUAIAAoACUAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBEAG8AbQBlAHMAdABpAGMAIAByAGUAZgByAGkAZwBlAHIAYQB0AG8AcgBzAFwAIgAsACAAMQAuADcAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAYQBuAHMAcABvAHIAdAAgAHIAZQBmAHIAaQBnAGUAcgBhAHQAaQBvAG4AXAAiACwAIAAxADUALgA3ADsAXABuACAAIAAgACAAIAAgACAAIABcACIARABvAG0AZQBzAHQAaQBjACAAQQAvAEMAIABwAG8AcgB0AGEAYgBsAGUAXAAiACwAIAAyAC4ANQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEQAbwBtAGUAcwB0AGkAYwAgAEEALwBDACAAcwBwAGwAaQB0AFwAIgAsACAAMwAuADUAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBEAG8AbQBlAHMAdABpAGMAIABBAC8AQwAgAHAAYQBjAGsAYQBnAGUAZABcACIALAAgADIALgA1ADsAXABuACAAIAAgACAAIAAgACAAIABcACIATABpAGcAaAB0ACAAdgBlAGgAaQBjAGwAZQAgAEEALwBDAFwAIgAsACAANgAuADcAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAGUAYQB2AHkAIAB2AGUAaABpAGMAbABlACAAQQAvAEMAXAAiACwAIAAxADAALgA4AFwAbgAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACkAKQApADsAXABuAFwAbgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEwAZQBhAGsAYQBnAGUAUgBhAHQAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBDAGEAbABjAHUAbABhAHQAZQBCAGwAZQBuAGQARwBXAFAAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAEMAbwBuAHMAdABpAHQAdQBlAG4AdABGAGEAYwB0AGkAbwBuADEALAAgAEMAbwBuAHMAdABpAHQAdQBlAG4AdABHAFcAUAAxACwAIABcAG4AIAAgAEMAbwBuAHMAdABpAHQAdQBlAG4AdABGAGEAYwB0AGkAbwBuADIALAAgAEMAbwBuAHMAdABpAHQAdQBlAG4AdABHAFcAUAAyACwAIABcAG4AIAAgAEMAbwBuAHMAdABpAHQAdQBlAG4AdABGAGEAYwB0AGkAbwBuADMALAAgAEMAbwBuAHMAdABpAHQAdQBlAG4AdABHAFcAUAAzACwAIABcAG4AIAAgAEMAbwBuAHMAdABpAHQAdQBlAG4AdABGAGEAYwB0AGkAbwBuADQALAAgAEMAbwBuAHMAdABpAHQAdQBlAG4AdABHAFcAUAA0ACwAXABuACAAIAAoAEMAbwBuAHMAdABpAHQAdQBlAG4AdABGAGEAYwB0AGkAbwBuADEAIAAqACAAQwBvAG4AcwB0AGkAdAB1AGUAbgB0AEcAVwBQADEAKQAgACsAXABuACAAIAAoAEMAbwBuAHMAdABpAHQAdQBlAG4AdABGAGEAYwB0AGkAbwBuADIAIAAqACAAQwBvAG4AcwB0AGkAdAB1AGUAbgB0AEcAVwBQADIAKQAgACsAXABuACAAIAAoAEMAbwBuAHMAdABpAHQAdQBlAG4AdABGAGEAYwB0AGkAbwBuADMAIAAqACAAQwBvAG4AcwB0AGkAdAB1AGUAbgB0AEcAVwBQADMAKQAgACsAXABuACAAIAAoAEMAbwBuAHMAdABpAHQAdQBlAG4AdABGAGEAYwB0AGkAbwBuADQAIAAqACAAQwBvAG4AcwB0AGkAdAB1AGUAbgB0AEcAVwBQADQAKQBcAG4AKQA7ACIAfQBdACwAIgBwAHIAbwBqAGUAYwB0AE4AYQBtAGUAcwAiADoAWwAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATwBuAGUAQwBvAGwAdQBtAG4AQQBuAGQASABlAGEAZABlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABOADIATwBFAEYARgByAG8AbQBQAHIAbwBkAEkAcgByAGkAZwBhAHQAaQBvAG4AUgBhAGkAbgBmAGEAbABsACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBDAG8AbgB2AGUAcgB0AFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAFQAbwBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBUAGkAdABsAGUAIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADEARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8ARABlAHMAYwByAGkAcAB0AGkAbwBuACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAEQAYQB0AGEAIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADEARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8AVABpAHQAbABlACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBTAG8AdQByAGMAZQAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBEAGEAdABhACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBMAGkAcQB1AGkAZABfAFQAaQB0AGwAZQAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEwAaQBxAHUAaQBkAF8ARABlAHMAYwByAGkAcAB0AGkAbwBuACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkATABpAHEAdQBpAGQAXwBTAG8AdQByAGMAZQAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEwAaQBxAHUAaQBkAF8ARABhAHQAYQAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEwAaQBxAHUAaQBkAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAVAByAGEAbgBzAHAAbwByAHQAXwBUAGkAdABsAGUAIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAVAByAGEAbgBzAHAAbwByAHQAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAVAByAGEAbgBzAHAAbwByAHQAXwBTAG8AdQByAGMAZQAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBUAHIAYQBuAHMAcABvAHIAdABfAEQAYQB0AGEAIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAVAByAGEAbgBzAHAAbwByAHQAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBUAHIAYQBuAHMAcABvAHIAdABPAGYAZgBSAG8AYQBkAF8AVABpAHQAbABlACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AE8AZgBmAFIAbwBhAGQAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAVAByAGEAbgBzAHAAbwByAHQATwBmAGYAUgBvAGEAZABfAFMAbwB1AHIAYwBlACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AE8AZgBmAFIAbwBhAGQAXwBEAGEAdABhACIALAAiAEYAdQBlAGwAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBGAHUAZQBsAF8ARwBlAHQAVAByAGEAbgBzAHAAbwByAHQARgB1AGUAbABTAHQAcgBpAG4AZwAiACwAIgBGAHUAZQBsAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4ARgB1AGUAbABfAEcAZQB0AFMAdABhAHQAaQBvAG4AYQByAHkARgB1AGUAbABTAHQAcgBpAG4AZwAiACwAIgBGAHUAZQBsAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4ARgB1AGUAbABfAFQAbwB0AGEAbABDAG8AbgBzAHUAbQBwAHQAaQBvAG4AIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AMQBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFQAcgBhAG4AcwBwAG8AcgB0ACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwAxAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AVAByAGEAbgBzAHAAbwByAHQAXwBUAGkAdABsAGUAIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfADEAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBUAHIAYQBuAHMAcABvAHIAdABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AMQBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFQAcgBhAG4AcwBwAG8AcgB0AF8AVQBuAGkAdAAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AMQBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFQAcgBhAG4AcwBwAG8AcgB0AF8AUwBvAHUAcgBjAGUAIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfADEAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBUAHIAYQBuAHMAcABvAHIAdABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwAxAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AVAByAGEAbgBzAHAAbwByAHQAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwAxAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AVAByAGEAbgBzAHAAbwByAHQAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AMgBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFMAdABhAHQAaQBvAG4AYQByAHkAIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfADIAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBTAHQAYQB0AGkAbwBuAGEAcgB5AF8AVABpAHQAbABlACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwAyAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AUwB0AGEAdABpAG8AbgBhAHIAeQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AMgBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFMAdABhAHQAaQBvAG4AYQByAHkAXwBVAG4AaQB0ACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwAyAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AUwB0AGEAdABpAG8AbgBhAHIAeQBfAFMAbwB1AHIAYwBlACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwAyAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AUwB0AGEAdABpAG8AbgBhAHIAeQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwAyAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AUwB0AGEAdABpAG8AbgBhAHIAeQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfADIAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBTAHQAYQB0AGkAbwBuAGEAcgB5AF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfAFgAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4ARwBlAG4AZQByAGkAYwAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AWABfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBHAGUAbgBlAHIAaQBjAF8AVABpAHQAbABlACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwBYAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAEcAZQBuAGUAcgBpAGMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfAFgAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4ARwBlAG4AZQByAGkAYwBfAFUAbgBpAHQAIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfAFgAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4ARwBlAG4AZQByAGkAYwBfAFMAbwB1AHIAYwBlACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwBYAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAEcAZQBuAGUAcgBpAGMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AWABfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBHAGUAbgBlAHIAaQBjAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AWABfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBHAGUAbgBlAHIAaQBjAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfAFgAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4ARwBlAG4AZQByAGkAYwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcARwBXAFAAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAF8AVABpAHQAbABlACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBHAFcAUABfAFQAaQB0AGwAZQAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBfAFUAbgBpAHQAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAEcAVwBQAF8AVQBuAGkAdAAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAXwBTAG8AdQByAGMAZQAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcARwBXAFAAXwBTAG8AdQByAGMAZQAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAXwBSAGUAYQBkAGEAYgBsAGUARQBxAHUAYQB0AGkAbwBuACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAEcAVwBQAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcARwBXAFAAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABHAFcAUABfAFQAaQB0AGwAZQAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABHAFcAUABfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABHAFcAUABfAFMAbwB1AHIAYwBlACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AQwBoAGUAbQBpAGMAYQBsAEcAVwBQAF8ARABhAHQAYQAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABHAFcAUABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AQwBoAGUAbQBpAGMAYQBsAEIAbABlAG4AZABzAF8AVABpAHQAbABlACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AQwBoAGUAbQBpAGMAYQBsAEIAbABlAG4AZABzAF8ARABlAHMAYwByAGkAcAB0AGkAbwBuACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AQwBoAGUAbQBpAGMAYQBsAEIAbABlAG4AZABzAF8AUwBvAHUAcgBjAGUAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBDAGgAZQBtAGkAYwBhAGwAQgBsAGUAbgBkAHMAXwBEAGEAdABhACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AQwBoAGUAbQBpAGMAYQBsAEIAbABlAG4AZABzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBMAGUAYQBrAGEAZwBlAFIAYQB0AGUAcwBfAFQAaQB0AGwAZQAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEwAZQBhAGsAYQBnAGUAUgBhAHQAZQBzAF8ARABlAHMAYwByAGkAcAB0AGkAbwBuACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ATABlAGEAawBhAGcAZQBSAGEAdABlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEwAZQBhAGsAYQBnAGUAUgBhAHQAZQBzAF8ARABhAHQAYQAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEwAZQBhAGsAYQBnAGUAUgBhAHQAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAYQBsAGMAdQBsAGEAdABlAEIAbABlAG4AZABHAFcAUAAiAF0ALAAiAGwAbwBjAGEAbABlACIAOgB7ACIAbABpAHMAdABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHIAbwB3AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAYwBvAGwAdQBtAG4AUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHQAaABvAHUAcwBhAG4AZABzAFAAbwBzAGkAdABpAG8AbgBzACIAOgBbADMAXQAsACIAZABlAGMAaQBtAGEAbABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAuACIALAAiAGQAYQB0AGUATwByAGQAZQByACIAOgAiAEQATQBZACIALAAiAGMAdQByAHIAZQBuAGMAeQBTAHkAbQBiAG8AbAAiADoAIgAkACIALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwATABlAGEAZAAiADoAdAByAHUAZQAsACIAaQBzAEMAdQByAHIAZQBuAGMAeQBTAGUAcABCAHkAUwBwAGEAYwBlACIAOgBmAGEAbABzAGUALAAiAHIAbwB3AEwAZQB0AHQAZQByACIAOgAiAFIAIgAsACIAYwBvAGwAdQBtAG4ATABlAHQAdABlAHIAIgA6ACIAQwAiACwAIgByAGMATABlAGYAdABCAHIAYQBjAGsAZQB0ACIAOgAiAFsAIgAsACIAcgBjAFIAaQBnAGgAdABCAHIAYQBjAGsAZQB0ACIAOgAiAF0AIgAsACIAcwB0AGEAdABlAG0AZQBuAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIAOwAiACwAIgBsAG8AYwBhAGwAZQBOAGEAbQBlACIAOgAiAGUAbgAtAHUAcwAiAH0AfQA=</AFEJSONBlob>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
@@ -19104,19 +19141,6 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgAFwAdQAwADAAMgA3AEYAcgB5AFwAdQAwADAAMgA3ACAAdABvACAAXAB1ADAAMAAyADcARAByAHkAXAB1ADAAMAAyADcALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIAVwBlAHQAIABvAHIAIABEAHIAeQAgAFoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAHcAYQByAG0AIAAvACAAYwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALwAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0ACAAYQBuAGQAIABoAGkAZwBoACAAdABlAG0AcAAgAGMAbABhAHMAcwBlAHMAIAB0AG8AIABhAGMAYwBvAG0AbQBvAGQAYQB0AGUAIABjAGwAaQBtAGEAdABlACAAcwBjAGUAbgBhAHIAaQBvAHMAIABlAHgAYwBsAHUAZABlAGQAIABiAHkAIABWAEUARQBSAEcAIABjAHIAaQB0AGUAcgBpAGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBpAHgAZQBkACAAdAB5AHAAbwAgAGkAbgAgAE0AQQBUACAAdgBhAGwAdQBlACAAZgBvAHIAIAB3AGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABjAGgAYQBuAGcAZQBkACAAMQAwACAAdABvACAAMQAxAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAG0AaQBuACAAYQBuAGQAIABtAGEAeAAgAGMAbwBsAHUAbQBuAHMAIABmAG8AcgAgAE0AQQBUACwAIABNAEEAUAAsACAAZgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgAsACAAZQBsAGUAdgBhAHQAaQBvAG4ALAAgAE0AQQBQADoAUABFAFQAIAB0AG8AIABjAGEAbABjAHUAbABhAHQAZQAgAHoAbwBuAGUAcwAgAGYAcgBvAG0AIAByAGUAYQBsACAAYwBsAGkAbQBhAHQAZQAgAGQAYQB0AGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBBAEYAIABhAGMAYwBlAHAAdABzACAAcgBhAGkAbgBmAGEAbABsACAAYQBzACAAYQAgAHAAcgBvAHgAeQAgAGYAbwByACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUAFwAIgAsACAAXAAiAE0AQQBQAFwAIgAsACAAXAAiAEYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIAXAAiACwAIABcACIARQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAHQAZQBtAHAAXAAiACwAIABcACIATQBhAHgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AaQBuACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AYQB4ACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AaQBuACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGEAeAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBpAG4AIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGEAeAAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADIAMAAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAG0AIAAtACAAZCIgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAxADAAMAAwAC4AMAAwADEALAAgADIAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQBcACIALAAgADEAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB0AGUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFQAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAUAAgAD0AIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEUAVAAgAD0AIABwAG8AdABlAG4AdABpAGEAbAAgAGUAdgBhAHAAbwB0AHIAYQBuAHMAcABpAHIAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAE0AQQBUACAAbQBpAG4AIABhAG4AZAAgAE0AQQBUACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AZQBkAGkAYQBuACAAQQBuAG4AdQBhAGwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAAoAE0AQQBUACkAXAAiACwAIABcACIATQBpAG4AIABNAEEAVABcACIALAAgAFwAIgBNAGEAeAAgAE0AQQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiIAAyADYAIABDAFwAIgAsACAAMgA2ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgAFwAIgAxADUAIAAtACAAMgA1ACAAQwBcACIALAAgADEANQAsACAAMgA1AC4AOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIiAAMQA0ACAAQwBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEANAAuADkAOQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABaAG8AbgBlAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AaQBuAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAXAB1ADAAMAAzAGUAIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAXAB1ADAAMAAzAGUAowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABkAG8AZQBzACAAbgBvAHQAIABvAGMAYwB1AHIAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAGQiowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBzACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAWQBlAHMAIAAtACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvACAALQAgAG4AbwB0ACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAZABhAHQAYQAgAHMAYwBvAHIAZQBzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFgAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAdABhACAAcwBvAHUAcgBjAGUAXAAiACwAIABcACIARABhAHQAYQAgAHMAYwBvAHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAHQAZQByAG4AYQB0AGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUAIABvAHIAIAByAGUAZwBpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAGkAbgB0AGUAbgBzAGkAdAB5ACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIABhAHAAcAByAG8AdgBlAGQAIABtAGUAdABoAG8AZABcACIALAAgADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBlAHIAaQBmAGkAZQBkACAAYwByAGUAZABlAG4AdABpAGEAbAAgAG0AYQB0AGMAaABpAG4AZwAgAEkAUwBPADEANAAwADYANwBcACIALAAgADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIAAoADMALgBEAC4AYgAuADIAKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBMAEUAQQBDAEgAXAAiACwAMAAuADIANABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AIAAzAC4ARAAuAEIAXwAxADAAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAGwAZQBhAGMAaABcACIALAAwAC4AMAAxADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADUALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACwAXAAiAEUARgBOADIATwBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5AFwAIgAsACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAA1ADkALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAXAAiACwAMAAuADAAMAA3ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABsAG8AdwAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAMgA5ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAaABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAOAAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAMAAuADAAMQA5ADkALAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsADAALgAwADAANQAzACwAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAMAAuADAAMAA2ADQALAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABjAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnACkAXAAiACwAMAAuADAAMAAzACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBDAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABzAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnACkAXAAiACwAMAAuADAAMAA1ACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBTAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAMAAuADAAMAAyADYALAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABkAHUAcABsAGkAYwBhAHQAZQAgAFwAdQAwADAAMgA3AEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcAHUAMAAwADIANwAsACAAXAB1ADAAMAAyADcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcAHUAMAAwADIANwAgAGEAbgBkACAAXAB1ADAAMAAyADcAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AG4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAdQAwADAAMgA3ACAAcgBvAHcAIAB3AGkAdABoACAAcwBhAG0AZQAgAEUARgAgAGYAbwByACAAbABvAHcAIABhAG4AZAAgAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXABuAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXABuAEkAUABDAEMAOgAgAE4AMgBPACAARQBNAEkAUwBTAEkATwBOAFMAIABGAFIATwBNACAATQBBAE4AQQBHAEUARAAgAFMATwBJAEwAUwAsACAAQQBOAEQAIABDAE8AMgAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAEwASQBNAEUAIABBAE4ARAAgAFUAUgBFAEEAIABBAFAAUABMAEkAQwBBAFQASQBPAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAFcARQBUACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAQwBoAGEAcAB0AGUAcgAgADEALAAgAHMAZQBjAHQAaQBvAG4AIAAxAC4AOAAuADIAIABMAGUAYQBjAGgAaQBuAGcALAAgAGMAbABpAG0AYQB0AGUAIABhAG4AZAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAUgBlAGYAaQBuAGUAbQBlAG4AdAAgAFYAbwBsAHUAbQBlACAANAA6ACAAQwBoAGEAcAB0AGUAcgAgADEAMQA6ACAATgAyAE8AIABFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABNAGEAbgBhAGcAZQBkACAAUwBvAGkAbABzACwAIABhAG4AZAAgAEMATwAyACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATABpAG0AZQAgAGEAbgBkACAAVQByAGUAYQAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlACAAaQByAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBwAHIAaQBuAGsAbABlAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAcgBmAGEAYwBlACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABUAGEAYgBsAGUAIABjAHIAZQBhAHQAZQBkACAAYgBhAHMAZQBkACAAbwBuACAAVgBFAEUAUgBHACAAdABlAHgAdAAgAFwAdQAwADAAMgA3AEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuAFwAdQAwADAAMgA3AFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAOgAgAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAFAAUgBQACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgAyAE8AIAAtACAATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIABcACIARQBGAFAAUgBQAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAB1ADAAMAAyADcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAdQAwADAAMgA3ACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AbwBuAHQAaABzACAAdABvACAAUwBlAGEAcwBvAG4AcwAgAE0AYQBwAHAAaQBuAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AbgB0AGgAXAAiACwAIABcACIAUwBlAGEAcwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAYQBuAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBiAHIAdQBhAHIAeQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAHIAYwBoAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHAAcgBpAGwAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQB5AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbgBlAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbAB5AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAZwB1AHMAdABcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAHAAdABlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AYwB0AG8AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB2AGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGMAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAbgB1AHIAZQAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAIAATICAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAegBvAG4AZQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA4AC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAyACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAIAAoALoAQwApAFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAUwBsAHUAcgByAHkAIAAoAHcAaQB0AGgAbwB1AHQAIABuAGEAdAB1AHIAYQBsACAAYwByAHUAcwB0ACkAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAGIAKQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABTAHQAbwByAGEAZwBlACAAXAB1ADAAMAAzAGMAMQAgAG0AbwBuAHQAaABcACIALAAgAFwAIgBEAGUAZQBwACAATABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAE0AYQBuAHUAcgBlACAAKAB3AGkAdABoAC8AdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACkAXAAiACwAIABcACIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAaQBuAHQAbwAgAHAAZQBsAGwAZQB0AGkAegBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACwAIABSAGEAbgBnAGUAIABhAG4AZAAgAFAAYQBkAGQAbwBjAGsAIAAoAGMAKQAoAGQAKQBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAXAAiAGQiMQAwAFwAIgAsACAAMAAuADYANgAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMQAsACAAMAAuADYAOAAsACAAMAAuADEALAAgADAALgAxADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAyACwAIAAwAC4ANwAsACAAMAAuADEALAAgADAALgAxADMALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAzACwAIAAwAC4ANwAxACwAIAAwAC4AMQAsACAAMAAuADEANAAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADQALAAgADAALgA3ADMALAAgADAALgAxACwAIAAwAC4AMQA1ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADUALAAgADAALgA3ADQALAAgADAALgAxACwAIAAwAC4AMQA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA2ACwAIAAwAC4ANwA1ACwAIAAwAC4AMQAsACAAMAAuADEAOAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANwAsACAAMAAuADcANgAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA4ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIAMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOQAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADAALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA2ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAxACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIAOQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMgAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAzADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADMALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA0ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANQAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANgAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADQALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANwAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANAA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIABcACIAZSIyADgAXAAiACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwBcACIALAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZABcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgAgAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAcgBvAHcAIABvAGYAIABOAEkAUgAgAE0ATQBBACAAZABlAGYAaQBuAGkAdABpAG8AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuACAARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AFAAbwB1AGwAdAByAHkAIAB3AGkAdABoACAAYQBuAGQAIAB3AGkAdABoAG8AdQB0ACAAbABpAHQAdABlAHIAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABzAGUAcABhAHIAYQB0AGUAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AE0AQQBUACAAcgBhAHcAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHQAbwAgAGEAbABsAG8AdwAgAGwAbwBvAGsAdQBwACAAbwBmACAAbgB1AG0AYgBlAHIAcwAuAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBuAGQAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYATgBpACAAXAB1ADAAMAAyADYAIABFAEYATgAyAE8AaQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADEALgA0AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBOAGkAIABcAHUAMAAwADIANgAgAEUARgBOADIATwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAE4AMgBPACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUATgAyAE8AOgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXABuAEcAVwBQAE4AMgBPADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBOADIATwAsACAARwBXAFAAXwBOADIATwAsAFwAbgAgACAAIAAgAEUAXwBOADIATwAgACoAIABHAFcAUABfAE4AMgBPAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AE4AMgBPAH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AE4AMgBPAH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBOADIATwBcACIALABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAATgAyAE8AXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAEMASAA0ACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUAQwBIADQAOgAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXABuAEcAVwBQAEMASAA0ADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBDAEgANAAsACAARwBXAFAAXwBDAEgANAAsAFwAbgAgACAAIAAgAEUAXwBDAEgANAAgACoAIABHAFcAUABfAEMASAA0AFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEMASAA0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AEMASAA0AH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AEMASAA0AH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAEgANABcACIALABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAAQwBIADQAXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkALABcAG4AIAAgACAAIABSAE8AVwAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAgAC0AIAAxAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACwAXABuACAAIABDAE8ATABVAE0ATgAoAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAQQByAHIAYQB5AEQAYQB0AGEALAAgAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAIABbAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAXQAsAFwAbgAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgAEkATgBEAEUAWAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABVAE4ASQBRAFUARQAoAEEAcgByAGEAeQBEAGEAdABhACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwAoACkALQBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwAKQAgACsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApACwAIAAxACwAIABDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAIABcACIAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAASQBGACgASQBTAE4AVQBNAEIARQBSACgAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgAgACAAIAAgACkALAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkALAAgADAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABbAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlAF0ALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAMQAsACAAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACkAKgAoAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlADIAKQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE8AbgBlAEMAbwBsAHUAbQBuAEEAbgBkAEgAZQBhAGQAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBmAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQAsACAAXAAiAFwAIgAsACAAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQwBlAGwAbAAsACAARABlAGwAaQBtAGkAdABlAHIALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEAXQAsACAAWwBDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgBdACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgBYAE0ATAAoAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAdQAwADAAMwBjAHQAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAIABcAHUAMAAwADIANgBcAG4AIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFMAVQBCAFMAVABJAFQAVQBUAEUAKABDAGUAbABsACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEALABcACIAXAAiACkALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABEAGUAbABpAG0AaQB0AGUAcgAsAFwAIgBcAHUAMAAwADMAYwAvAHMAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAXABuACAAIAAgACAAIAAgACAAIAApACAAXAB1ADAAMAAyADYAXABuACAAIAAgACAAIAAgACAAIABcACIAXAB1ADAAMAAzAGMALwBzAFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAC8AdABcAHUAMAAwADMAZQBcACIALABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAvAC8AcwBcACIAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAdgBnAFQAZQBtAHAALABhAHYAZwBSAGEAaQBuACwAZgByAG8AcwB0AEQAYQB5AHMALABlAGwAZQB2ACwAbQBhAHAAXwBwAGUAdAAsAFwAbgAgACAAIAAgAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACwAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkALABtAGEAeABGAHIAbwBzAHQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4AUABFAFQAQQByAHIAYQB5ACwAbQBhAHgAUABFAFQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAYwBsAGkAbQBhAHQAZQBaAG8AbgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBSAGEAaQBuACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AYQB2AGcAUgBhAGkAbgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AZgByAG8AcwB0AEQAYQB5AHMAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AG0AYQBwAF8AcABlAHQAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AG0AYQBwAF8AcABlAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABBAEsARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAGMAbABpAG0AYQB0AGUAWgBvAG4AZQBBAHIAcgBhAHkALABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgADEAXABuACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAE0AaQBuAEEAcgByAGEAeQAsACAATQBhAHgAQQByAHIAYQB5ACwAIABJAHQAZQBtAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAE0AaQBuAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBhAHgAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABJAHQAZQBtAEEAcgByAGEAeQAsACAAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAQwByAGkAdABlAHIAaQBhADEALAAgAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5ACwAIABRAHUAYQBuAHQAaQB0AHkALAAgAFsATQB1AGwAdABpAHAAbABpAGUAcgBdACwAIABbAEMAcgBpAHQAZQByAGkAYQAyAF0ALABbAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQBdACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAG0AdQBsAHQAaQBwAGwAaQBlAHIALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgATQB1AGwAdABpAHAAbABpAGUAcgApACwAMQAsAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsAFwAbgAgACAAIAAgAHEAdQBhAG4AdABpAHQAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACoATQB1AGwAdABpAHAAbABpAGUAcgAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMQApACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADIALABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAcgBpAHQAZQByAGkAYQAyACkALAAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADIAKQApACwAXABuACAAIAAgACAAUwBVAE0AUABSAE8ARABVAEMAVAAoAGMAcgBpAHQAZQByAGkAYQAxACoAYwByAGkAdABlAHIAaQBhADIAKgBxAHUAYQBuAHQAaQB0AHkAKQBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAXABuACAAIAAgACAAIAAgACAAIABBACwAUwAtADMANgA1ACwAXABuACAAIAAgACAAIAAgACAAIAB5AGEALABZAEUAQQBSACgAQQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AGIALABZAEUAQQBSACgARQApACwAXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApAFwAdQAwADAAMwBjACAAUwApACwAXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAFwAdQAwADAAMwBlACAARQApACwAXABuACAAIAAgACAAIAAgACAAIABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsACAALwAqAGgAZQBsAHAAZQByADoAIABlAG4AZAAgAGQAYQB0AGUAIABmAG8AcgAgAGEAIAByAGUAcABvAHIAdABpAG4AZwAgAHAAZQByAGkAbwBkACAAcwB0AGEAcgB0AGkAbgBnACAAYQB0ACAAYQAgAGcAaQB2AGUAbgAgAGQAYQB0AGUAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAIAAvACoAbwBuAGwAeQAgAG4AZQBlAGQAIAB0AG8AIABsAG8AbwBrACAAYgBhAGMAawAgADMANgA1ACAAZABhAHkAcwAoAG0AYQB4ACAAbwB2AGUAcgBsAGEAcAAgAHcAaQBuAGQAbwB3ACkAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYQAgAGUAbgBkAHMAIABiAGUAZgBvAHIAZQAgAFMALABpAHQAIABjAGEAbgBcAHUAMAAwADIANwB0ACAAbwB2AGUAcgBsAGEAcAA7ACAAbQBvAHYAZQAgAHQAbwAgAG4AZQB4AHQAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAXAB1ADAAMAAzAGMAUwApACwAIAAvACoAaQBmACAAdABoAGUAIABhAG4AYwBoAG8AcgAgAGYAbwByACAAeQBiACAAcwB0AGEAcgB0AHMAIABhAGYAdABlAHIAIABFACwAaQB0ACAAYwBhAG4AXAB1ADAAMAAyADcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABwAHIAZQB2AGkAbwB1AHMAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAXAB1ADAAMAAzAGUARQApACwAXABuACAAIAAgACAAIAAgACAAIABuACwATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAcgBzACwAUwBFAFEAVQBFAE4AQwBFACgAbgAsADEALABmAGkAcgBzAHQAWQBlAGEAcgAsADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMALABEAEEAVABFACgAeQByAHMALABtACwAZAApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzACwATQBBAFAAKABzAHQAYQByAHQAcwAsAFAAZQByAGkAbwBkAEUAbgBkACkALABcAG4AIAAgACAAIAAgACAAIAAgAHQAYQBnACwASQBGACgAcwB0AGEAcgB0AHMAPQBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXAAiACAAKABUAGgAaQBzACAAcgBlAHAAbwByAHQAaQBuAGcAIABjAHkAYwBsAGUAKQBcACIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzAFQAZQB4AHQALABUAEUAWABUACgAcwB0AGEAcgB0AHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzAFQAZQB4AHQALABUAEUAWABUACgAZQBuAGQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAG4APQAwACwAXAAiAFwAIgAsAEgAUwBUAEEAQwBLACgAcwB0AGEAcgB0AHMAVABlAHgAdAAgAFwAdQAwADAAMgA2ACAAXAAiACAAdABvACAAXAAiACAAXAB1ADAAMAAyADYAIABlAG4AZABzAFQAZQB4AHQAIABcAHUAMAAwADIANgAgAHQAYQBnACkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQBcAG4APQBMAEEATQBCAEQAQQAoAEYAdQBuAGMAdABpAG8AbgAsACAAVABFAFgAVABCAEUARgBPAFIARQAoAEYATwBSAE0AVQBMAEEAVABFAFgAVAAoAEYAdQBuAGMAdABpAG8AbgApACwAIABcACIAKABcACIAKQApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBBAHIAcgBhAHkALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5ACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkALABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAA9AFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABJAEYAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACAAPQAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALAAgAFwAIgBBAG4AeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5AD0AUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZABBAHIAcgBhAHkAPQBJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkAPQBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQAIAArACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAFwAdQAwADAAMwBlADAALAAgADEALAAgADAAKQBcAG4AIAAgACAAIAApACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsAFwAbgAgACAAIAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAdQAwADAAMgA3AFwAIgAgAFwAdQAwADAAMgA2ACAAcwBoACAAXAB1ADAAMAAyADYAIABcACIAXAB1ADAAMAAyADcAIQBcACIAIABcAHUAMAAwADIANgAgAGEAZABkAHIAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsARABpAGYAZgBlAHIAZQBuAHQAUwBoAGUAZQB0AFwAbgA9AEwAQQBNAEIARABBACgAVABhAHIAZwBlAHQAQwBlAGwAbAAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABzAGgALAAgAFQARQBYAFQAQQBGAFQARQBSACgAQwBFAEwATAAoAFwAIgBmAGkAbABlAG4AYQBtAGUAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALAAgAFwAIgBdAFwAIgApACwAXABuACAAIAAgACAAYQBkAGQAcgAsACAAQwBFAEwATAAoAFwAIgBhAGQAZAByAGUAcwBzAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAXABuACAAIAAgACAAXAAiACMAXAAiACAAXAB1ADAAMAAyADYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAxAF8AMgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADEALAAgADIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAzAF8ANABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADMALAAgADQAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBHAGUAdABNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAATQBNAFMALAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFwAbgAgACAAIAAgACAAIAAgACAATQBFAEQASQBBAE4AKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBJAE4AKABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEEAWAAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABNAE0AUwAsACAATQBNAFMAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFIAZQBzAHUAbAB0AHMASQB0AGUAbQBGAHIAbwBtAEUAcQB1AGEAdABpAG8AbgBUAGkAdABsAGUAQQBuAGQAUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGkAdABsAGUAQwBlAGwAbAAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAAsAFwAbgAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABMAEUARgBUACgAUwBvAHUAcgBjAGUAQwBlAGwAbAAsACAARgBJAE4ARAAoAFwAIgAsAFwAIgAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAApACAALQAxACkALAAgAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABcACIALAAgAFwAIgBcACIAKQAgAFwAdQAwADAAMgA2ACAAXAAiACAAXAAiACAAXAB1ADAAMAAyADYAIABUAGkAdABsAGUAQwBlAGwAbABcAG4AKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8ARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAEYAdQBlAGwAIABzAGMAbwBwAGUAIAAxACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAC0AIABTAHQAYQB0AGkAbwBuAGEAcgB5ACAAZwBhAHMAZQBvAHUAcwAgAGYAdQBlAGwAcwBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEYAdQBlAGwAIABzAGMAbwBwAGUAIAAxACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAC0AIABTAHQAYQB0AGkAbwBuAGEAcgB5ACAAZwBhAHMAZQBvAHUAcwAgAGYAdQBlAGwAcwBcACIAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8ARABlAHMAYwByAGkAcAB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIARABpAHIAZQBjAHQAIAAoAFMAYwBvAHAAZQAgADEAKQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAHQAaABlACAAYwBvAG4AcwB1AG0AcAB0AGkAbwBuACAAbwBmACAAZwBhAHMAZQBvAHUAcwAgAGYAdQBlAGwAcwAgAGkAbgBjAGwAdQBkAGkAbgBnACAAbABpAHEAdQBlAGYAaQBlAGQAIABuAGEAdAB1AHIAYQBsACAAZwBhAHMAIAAgAFwAIgApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABOAGEAdABpAG8AbgBhAGwAIABHAHIAZQBlAG4AaABvAHUAcwBlACAAQQBjAGMAbwB1AG4AdABzACAARgBhAGMAdABvAHIAcwAgADIAMAAyADUAIAAtACAAVABhAGIAbABlACAANQBcACIAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8ARABhAHQAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADkALAAgADcALABcAG4AIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIABcACIARgB1AGUAbAAgAGMAbwBtAGIAdQBzAHQAZQBkAFwAIgAsACAAXAAiAEUAbgBlAHIAZwB5ACAAQwBvAG4AdABlAG4AdAAgAEYAYQBjAHQAbwByACAAKABHAEoAIABwAGUAcgAgAHUAbgBpAHQAIABvAGYAIABmAHUAZQBsACkAXAAiACwAIABcACIARgB1AGUAbAAgAHUAbgBpAHQAXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAAQwBPADIAXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAAQwBIADQAXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAATgAyAE8AXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAAQwBvAG0AYgBpAG4AZQBkACAAZwBhAHMAZQBzAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE4AYQB0AHUAcgBhAGwAIABnAGEAcwAgAGQAaQBzAHQAcgBpAGIAdQB0AGUAZAAgAGkAbgAgAGEAIABwAGkAcABlAGwAaQBuAGUAXAAiACwAIAAwAC4AMAAzADkAMwAsACAAXAAiAG0AMwBcACIALAAgADUAMQAuADQALAAgADAALgAxACwAIAAwAC4AMAAzACwAIAA1ADEALgA1ADMAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AYQBsACAAcwBlAGEAbQAgAG0AZQB0AGgAYQBuAGUAIAB0AGgAYQB0ACAAaQBzACAAYwBhAHAAdAB1AHIAZQBkACAAZgBvAHIAIABjAG8AbQBiAHUAcwB0AGkAbwBuAFwAIgAsACAAMAAuADAAMwA3ADcALAAgAFwAIgBtADMAXAAiACwAIAA1ADEALgA0ACwAIAAwAC4AMgAsACAAMAAuADAAMwAsACAANQAxAC4ANgAzADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBvAGEAbAAgAG0AaQBuAGUAIAB3AGEAcwB0AGUAIABnAGEAcwAgAHQAaABhAHQAIABpAHMAIABjAGEAcAB0AHUAcgBlAGQAIABmAG8AcgAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AXAAiACwAIAAwAC4AMAAzADcANwAsACAAXAAiAG0AMwBcACIALAAgADUAMQAuADkALAAgADQALgA2ACwAIAAwAC4AMwAsACAANQA2AC4AOAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBtAHAAcgBlAHMAcwBlAGQAIABuAGEAdAB1AHIAYQBsACAAZwBhAHMAKAByAGUAdgBlAHIAdABpAG4AZwAgAHQAbwAgAHMAdABhAG4AZABhAHIAZAAgAGMAbwBuAGQAaQB0AGkAbwBuAHMAKQBcACIALAAgADAALgAwADMAOQAzACwAIABcACIAbQAzAFwAIgAsACAANQAxAC4ANAAsACAAMAAuADEALAAgADAALgAwADMALAAgADUAMQAuADUAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFUAbgBwAHIAbwBjAGUAcwBzAGUAZAAgAG4AYQB0AHUAcgBhAGwAIABnAGEAcwBcACIALAAgADAALgAwADMAOQAzACwAIABcACIAbQAzAFwAIgAsACAANQAxAC4ANAAsACAAMAAuADEALAAgADAALgAwADMALAAgADUAMQAuADUAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEUAdABoAGEAbgBlAFwAIgAsACAAMAAuADAANgAyADkALAAgAFwAIgBtADMAXAAiACwAIAA1ADYALgA1ACwAIAAwAC4AMAAzACwAIAAwAC4AMAAzACwAIAA1ADYALgA1ADYAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AawBlACAAbwB2AGUAbgAgAGcAYQBzAFwAIgAsACAAMAAuADAAMQA4ADEALAAgAFwAIgBtADMAXAAiACwAIAAzADcALgAwACwAIAAwAC4AMAAzACwAIAAwAC4AMAA1ACwAIAAzADcALgAwADgAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBCAGwAYQBzAHQAIABmAHUAcgBuAGEAYwBlACAAZwBhAHMAXAAiACwAIAAwAC4AMAAwADQAMAAsACAAXAAiAG0AMwBcACIALAAgADIAMwA0AC4AMAAsACAAMAAuADAAMwAsACAAMAAuADAAMgAsACAAMgAzADQALgAwADUAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBUAG8AdwBuACAAZwBhAHMAXAAiACwAIAAwAC4AMAAzADkAMAAsACAAXAAiAG0AMwBcACIALAAgADYAMAAuADIALAAgADAALgAwADQALAAgADAALgAwADMALAAgADYAMAAuADIANwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEwAaQBxAHUAZQBmAGkAZQBkACAAbgBhAHQAdQByAGEAbAAgAGcAYQBzAFwAIgAsACAAMgA1AC4AMwAsACAAXAAiAGsATABcACIALAAgADUAMQAuADQALAAgADAALgAxACwAIAAwAC4AMAAzACwAIAA1ADEALgA1ADMAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBHAGEAcwBlAG8AdQBzACAAZgBvAHMAcwBpAGwAIABmAHUAZQBsAHMAIABvAHQAaABlAHIAIAB0AGgAYQBuACAAdABoAG8AcwBlACAAbQBlAG4AdABpAG8AbgBlAGQAIABpAG4AIAB0AGgAZQAgAGkAdABlAG0AcwAgAGEAYgBvAHYAZQBcACIALAAgADAALgAwADMAOQAwACwAIABcACIAbQAzAFwAIgAsACAANQAxAC4ANAAsACAAMAAuADEALAAgADAALgAwADMALAAgADUAMQAuADUAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEwAYQBuAGQAZgBpAGwAbAAgAGIAaQBvAGcAYQBzACAAdABoAGEAdAAgAGkAcwAgAGMAYQBwAHQAdQByAGUAZAAgAGYAbwByACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgACgAbQBlAHQAaABhAG4AZQAgAG8AbgBsAHkAKQBcACIALAAgADAALgAwADMANwA3ACwAIABcACIAbQAzAFwAIgAsACAAMAAuADAALAAgADYALgA0ACwAIAAwAC4AMAAzACwAIAA2AC4ANAAzADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUwBsAHUAZABnAGUAIABiAGkAbwBnAGEAcwAgAHQAaABhAHQAIABpAHMAIABjAGEAcAB0AHUAcgBlAGQAIABmAG8AcgAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AIAAoAG0AZQB0AGgAYQBuAGUAIABvAG4AbAB5ACkAXAAiACwAIAAwAC4AMAAzADcANwAsACAAXAAiAG0AMwBcACIALAAgADAALgAwACwAIAA2AC4ANAAsACAAMAAuADAAMwAsACAANgAuADQAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEEAIABiAGkAbwBnAGEAcwAgAHQAaABhAHQAIABpAHMAIABjAGEAcAB0AHUAcgBlAGQAIABmAG8AcgAgAGMAbwBtAGIAdQBzAHQAaQBvAG4ALAAgAG8AdABoAGUAcgAgAHQAaABhAG4AIAB0AGgAbwBzAGUAIABtAGUAbgB0AGkAbwBuAGUAZAAgAGkAbgAgAHQAaABlACAAaQB0AGUAbQBzACAAYQBiAG8AdgBlAFwAIgAsACAAMAAuADAAMwA3ADAALAAgAFwAIgBtADMAXAAiACwAIAAwAC4AMAAsACAANgAuADQALAAgADAALgAwADMALAAgADYALgA0ADMAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBCAGkAbwBtAGUAdABoAGEAbgBlAFwAIgAsACAAMAAuADAAMwA5ADMALAAgAFwAIgBtADMAXAAiACwAIAAwAC4AMAAsACAAMAAuADEALAAgADAALgAwADMALAAgADAALgAxADMAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAHkAZAByAG8AZwBlAG4AXAAiACwAIAAwAC4AMAAxADIAMgAsACAAXAAiAG0AMwBcACIALAAgADAALgAwACwAIAAwAC4AMAAsACAAMAAuADUALAAgADAALgA1ADsAXABuACAAIAAgACAAIAAgACAAIABcACIATgBhAHQAdQByAGEAbAAgAGcAYQBzACAAZABpAHMAdAByAGkAYgB1AHQAZQBkACAAaQBuACAAYQAgAHAAaQBwAGUAbABpAG4AZQAgAC0AIABHAGkAZwBhAGoAbwB1AGwAZQBzAFwAIgAsACAAMQAsACAAXAAiAEcASgBcACIALAAgADUAMQAuADQALAAgADAALgAxACwAIAAwAC4AMAAzACwAIAA1ADEALgA1ADMAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBUAG8AdwBuACAAZwBhAHMAIAAtACAARwBpAGcAYQBqAG8AdQBsAGUAcwBcACIALAAgADEALAAgAFwAIgBHAEoAXAAiACwAIAA2ADAALgAyACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAzACwAIAA2ADAALgAyADcAXABuACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AKQApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABcAHUAMAAwADIANwBOAGEAdAB1AHIAYQBsACAAZwBhAHMAIABkAGkAcwB0AHIAaQBiAHUAdABlAGQAIABpAG4AIABhACAAcABpAHAAZQBsAGkAbgBlACAALQAgAEcAaQBnAGEAagBvAHUAbABlAHMAXAB1ADAAMAAyADcAIABhAG4AZAAgAFwAdQAwADAAMgA3AFQAbwB3AG4AIABnAGEAcwAgAC0AIABHAGkAZwBhAGoAbwB1AGwAZQBzAFwAdQAwADAAMgA3ACAAdwBlAHIAZQAgAGEAZABkAGUAZAAsACAAZQBhAGMAaAAgAHcAaQB0AGgAIABhAG4AIABlAG4AZQByAGcAeQAgAGMAbwBuAHQAZQBuAHQAIABmAGEAYwB0AG8AcgAgAG8AZgAgADEAIABHAEoAIABwAGUAcgAgAHUAbgBpAHQAIABvAGYAIABmAHUAZQBsAC4AIABUAGgAaQBzACAAaQBzACAAZgBvAHIAIAB1AHMAZQByAHMAIAB3AGgAbwAgAGgAYQB2AGUAIABmAHUAZQBsACAAYwBvAG4AcwB1AG0AcAB0AGkAbwBuACAAZABhAHQAYQAgAGkAbgAgAEcASgAgAHIAYQB0AGgAZQByACAAdABoAGEAbgAgAG0AMwAuAFwAIgApACkAOwBcAG4AXABuAFwAbgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAEYAdQBlAGwAIABzAGMAbwBwAGUAIAAzACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAC0AIABTAHQAYQB0AGkAbwBuAGEAcgB5ACAAZwBhAHMAZQBvAHUAcwAgAGYAdQBlAGwAcwBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEYAdQBlAGwAIABzAGMAbwBwAGUAIAAzACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAC0AIABTAHQAYQB0AGkAbwBuAGEAcgB5ACAAZwBhAHMAZQBvAHUAcwAgAGYAdQBlAGwAcwBcACIAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8ARABlAHMAYwByAGkAcAB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIASQBuAGQAaQByAGUAYwB0ACAAKABTAGMAbwBwAGUAIAAzACkAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIAB0AGgAZQAgAGMAbwBuAHMAdQBtAHAAdABpAG8AbgAgAG8AZgAgAG4AYQB0AHUAcgBhAGwAIABnAGEAcwAuAFwAIgApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABOAGEAdABpAG8AbgBhAGwAIABHAHIAZQBlAG4AaABvAHUAcwBlACAAQQBjAGMAbwB1AG4AdABzACAARgBhAGMAdABvAHIAcwAgADIAMAAyADUAIAAtACAAVABhAGIAbABlACAANgBcACIAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8ARABhAHQAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAzACwAXABuACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAgAG8AcgAgAHQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADMAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgBzACAAZgBvAHIAIABOAGEAdAB1AHIAYQBsACAARwBhAHMAIAAoAGsAZwAgAEMATwAyACAALQAgAGUAIAAvACAARwBKACkAIABNAGUAdAByAG8AXAAiACwAIABcACIAUwBjAG8AcABlACAAMwAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByAHMAIABmAG8AcgAgAE4AYQB0AHUAcgBhAGwAIABHAGEAcwAgACgAawBnACAAQwBPADIAIAAtACAAZQAgAC8AIABHAEoAKQAgAE4AbwBuACAALQAgAE0AZQB0AHIAbwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBOAGUAdwAgAFMAbwB1AHQAaAAgAFcAYQBsAGUAcwBcACIALAAgADEAMwAuADEALAAgADEANAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAEMAVABcACIALAAgADEAMwAuADEALAAgADEANAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIAA0AC4AMAAsACAANAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBRAHUAZQBlAG4AcwBsAGEAbgBkAFwAIgAsACAAOAAuADgALAAgADcALgA5ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIAAxADAALgA3ACwAIAAxADAALgA2ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAANAAuADEALAAgADQALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAANAAuADAALAAgADQALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIAA0AC4AMQAsACAANAAuADAAXABuACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AKQApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABOAFMAVwAgAGEAbgBkACAAQQBDAFQAIABzAHAAbABpAHQAIABpAG4AdABvACAAcwBlAHAAYQByAGEAdABlACAAcgBvAHcAcwAuACAAXAB1ADAAMAAyADcAQwBcAHUAMAAwADIANwAgAFYAYQBsAHUAZQBzACAAZgBvAHIAIABUAGEAcwBtAGEAbgBpAGEAIABhAG4AZAAgAE4AbwByAHQAaABlAHIAbgAgAFQAZQByAHIAaQB0AG8AcgB5ACAAcgBlAHAAbABhAGMAZQBkACAAdwBpAHQAaAAgAHQAaABvAHMAZQAgAGYAbwByACAAVgBpAGMAdABvAHIAaQBhACAAYQBuAGQAIABXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAByAGUAcwBwAGUAYwB0AGkAdgBlAGwAeQAuACAAKABTAGUAZQAgAGEAcABwAGUAbgBkAGkAYwBlAHMAKQBcACIAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8AQQBwAHAAZQBuAGQAaQBjAGUAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADIALAAgADIALABcAG4AIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIABcACIALQBcACIALAAgAFwAIgBBAHMAIABTAGMAbwBwAGUAIAAzACAAZgBhAGMAdABvAHIAcwAgAGEAcgBlACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAGEAdAAgAHQAaABlACAAcABvAGkAbgB0ACAAdwBoAGUAcgBlACAAbgBhAHQAdQByAGEAbAAgAGcAYQBzACAAaQBzACAAZABlAGwAaQB2AGUAcgBlAGQAIAB0AG8AIABlAG4AZAAgAHUAcwBlAHIAcwAsACAAaQB0ACAAaQBzACAAbgBlAGMAZQBzAHMAYQByAHkAIAB0AG8AIABjAGEAbABjAHUAbABhAHQAZQAgAGMAbwBuAHMAdQBtAHAAdABpAG8AbgAgAGEAdAAgAGUAYQBjAGgAIABvAGYAIAB0AGgAZQAgAGwAbwBhAGQAIABjAGUAbgB0AHIAZQBzAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIARwBhAHMAIAByAGUAYQBjAGgAZQBzACAAZQBuAGQAIAB1AHMAZQByAHMAIABlAGkAdABoAGUAcgAgAGYAcgBvAG0AIAB0AGgAZQAgAG0AZQB0AHIAbwAgAGQAaQBzAHQAcgBpAGIAdQB0AGkAbwBuACAAbgBlAHQAdwBvAHIAawBzACAAbwByACAAZABpAHIAZQBjAHQAIABmAHIAbwBtACAAdABoAGUAIABoAGkAZwBoACAALQAgAHAAcgBlAHMAcwB1AHIAZQAgAGQAaQBzAHQAcgBpAGIAdQB0AGkAbwBuACAAcABpAHAAZQBsAGkAbgBlAHMALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBIAG8AdQBzAGUAaABvAGwAZABzACAAYQBuAGQAIABjAG8AbQBtAGUAcgBjAGkAYQBsACAAdQBzAGUAcgBzACAAdABlAG4AZAAgAHQAbwAgAGIAZQAgAHMAZQByAHYAZQBkACAAYgB5ACAAdABoAGUAIABmAG8AcgBtAGUAcgAsACAAYQBuAGQAIABlAGwAZQBjAHQAcgBpAGMAaQB0AHkAIABnAGUAbgBlAHIAYQB0AG8AcgBzACAAYQBuAGQAIABsAGEAcgBnAGUAIABpAG4AZAB1AHMAdAByAGkAYQBsACAAcABsAGEAbgB0AHMAIABmAHIAbwBtACAAdABoAGUAIABsAGEAdAB0AGUAcgAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAC0AXAAiACwAIABcACIATQBlAHQAcgBvACAAaQBzACAAZABlAGYAaQBuAGUAZAAgAGEAcwAgAGwAbwBjAGEAdABlAGQAIABvAG4AIABvAHIAIABlAGEAcwB0ACAAbwBmACAAdABoAGUAIABkAGkAdgBpAGQAaQBuAGcAIAByAGEAbgBnAGUAIABpAG4AIABOAFMAVwAsACAAaQBuAGMAbAB1AGQAaQBuAGcAIABDAGEAbgBiAGUAcgByAGEAIABhAG4AZAAgAFEAdQBlAGEAbgBiAGUAeQBhAG4ALAAgAE0AZQBsAGIAbwB1AHIAbgBlACwAIABCAHIAaQBzAGIAYQBuAGUALAAgAEEAZABlAGwAYQBpAGQAZQAgAG8AcgAgAFAAZQByAHQAaAAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAE8AdABoAGUAcgB3AGkAcwBlACwAIAB0AGgAZQAgAG4AbwBuACAALQAgAG0AZQB0AHIAbwAgAGYAYQBjAHQAbwByACAAcwBoAG8AdQBsAGQAIABiAGUAIAB1AHMAZQBkAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIALQBcACIALAAgAFwAIgBGAGEAYwB0AG8AcgBzACAAYQByAGUAIABjAGEAbABjAHUAbABhAHQAZQBkACAAZgBvAHIAIABhAGwAbAAgAG4AYQB0AHUAcgBhAGwAIABnAGEAcwAgAGQAaQBzAHQAcgBpAGIAdQB0AGUAZAAgAGkAbgAgAGEAIABwAGkAcABlAGwAaQBuAGUAIAB3AGgAaQBjAGgAIABtAGEAeQAgAGkAbgBjAGwAdQBkAGUAIABjAG8AYQBsACAAcwBlAGEAbQAgAG0AZQB0AGgAYQBuAGUALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAtAFwAIgAsACAAXAAiAFQAYQBiAGwAZQAgADYAIABpAHMAIABuAG8AdAAgAGEAcABwAGwAaQBjAGEAYgBsAGUAIAB0AG8AIABlAHQAaABhAG4AZQAuACAAUwBlAGUAIABUAGEAYgBsAGUAIAA3ACAASQBuAGQAaQByAGUAYwB0ACAAKABTAGMAbwBwAGUAIAAzACkAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIAB0AGgAZQAgAGMAbwBuAHMAdQBtAHAAdABpAG8AbgAgAG8AZgAgAGUAdABoAGEAbgBlAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIALQBcACIALAAgAFwAIgBDACAAPQAgAEMAbwBuAGYAaQBkAGUAbgB0AGkAYQBsAC4AIABTAGMAbwBwAGUAIAAzACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAVABhAHMAbQBhAG4AaQBhACAAYQBuAGQAIAB0AGgAZQAgAE4AbwByAHQAaABlAHIAbgAgAFQAZQByAHIAaQB0AG8AcgB5ACAAYQByAGUAIABuAG8AdAAgAGEAdgBhAGkAbABhAGIAbABlACAAZAB1AGUAIAB0AG8AIABjAG8AbgBmAGkAZABlAG4AdABpAGEAbABpAHQAeQAgAGMAbwBuAHMAdAByAGEAaQBuAHQAcwAgAHQAaABhAHQAIABhAHIAaQBzAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAZgByAG8AbQAgAHQAaABlACAAdQBzAGUAIABvAGYAIABhACAAbABpAG0AaQB0AGUAZAAgAG4AdQBtAGIAZQByACAAbwBmACAATgBHAEUAUgAgAGQAYQB0AGEAIABpAG4AcAB1AHQAcwAuACAASQB0ACAAaQBzACAAcwB1AGcAZwBlAHMAdABlAGQAIAB0AGgAYQB0ACAAZgBvAHIAIABUAGEAcwBtAGEAbgBpAGEAIAB0AGgAZQAgAHUAcwBlACAAbwBmACAAdABoAGUAIABWAGkAYwB0AG8AcgBpAGEAbgAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABpAHMAIABhAHAAcAByAG8AcAByAGkAYQB0AGUALABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgB3AGgAaQBsAGUAIABmAG8AcgAgAE4AbwByAHQAaABlAHIAbgAgAFQAZQByAHIAaQB0AG8AcgB5ACAAdABoAGUAIAB1AHMAZQAgAG8AZgAgAHQAaABlACAAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAaQBzACAAYQBwAHAAcgBvAHAAcgBpAGEAdABlAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIALQBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAzACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGQAbwAgAG4AbwB0ACAAaQBuAGMAbAB1AGQAZQAgAGYAdQBnAGkAdABpAHYAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGwAZQBhAGsAYQBnAGUAIABmAHIAbwBtACAAbABvAHcAIABwAHIAZQBzAHMAdQByAGUAIABuAGEAdAB1AHIAYQBsACAAZwBhAHMAIABkAGkAcwB0AHIAaQBiAHUAdABpAG8AbgAgAHAAaQBwAGUAbABpAG4AZQAgAG4AZQB0AHcAbwByAGsAcwAgAHcAaABpAGwAZQAgAHQAaABvAHMAZQAgAGYAcgBvAG0AIABoAGkAZwBoACAAcAByAGUAcwBzAHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAGcAYQBzACAAbgBlAHQAdwBvAHIAawBzACAAYQByAGUAIABjAG8AbgBzAGkAZABlAHIAZQBkACAAbgBlAGcAbABpAGcAaQBiAGwAZQAuAFwAIgBcAG4AIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgApACkAKQA7AFwAbgBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ARgB1AGUAbAAgAHMAYwBvAHAAZQAgADEAIABhAG4AZAAgADMAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAALQAgAFMAdABhAHQAaQBvAG4AYQByAHkAIABsAGkAcQB1AGkAZAAgAGYAdQBlAGwAcwBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkATABpAHEAdQBpAGQAXwBUAGkAdABsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBGAHUAZQBsACAAcwBjAG8AcABlACAAMQAgAGEAbgBkACAAMwAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIAAtACAAUwB0AGEAdABpAG8AbgBhAHIAeQAgAGwAaQBxAHUAaQBkACAAZgB1AGUAbABzAFwAIgApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEwAaQBxAHUAaQBkAF8ARABlAHMAYwByAGkAcAB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIARABpAHIAZQBjAHQAIAAoAFMAYwBvAHAAZQAgADEAKQAgAGEAbgBkACAAaQBuAGQAaQByAGUAYwB0ACAAKABzAGMAbwBwAGUAIAAzACkAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIAB0AGgAZQAgAGMAbwBuAHMAdQBtAHAAdABpAG8AbgAgAG8AZgAgAGwAaQBxAHUAaQBkACAAZgB1AGUAbABzACwAIABpAG4AYwBsAHUAZABpAG4AZwAgAGMAZQByAHQAYQBpAG4AIABwAGUAdAByAG8AbABlAHUAbQAgAGIAYQBzAGUAZAAgAHAAcgBvAGQAdQBjAHQAcwAgAGYAbwByACAAcwB0AGEAdABpAG8AbgBhAHIAeQAgAGUAbgBlAHIAZwB5ACAAcAB1AHIAcABvAHMAZQBzAC4AXAAiACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkATABpAHEAdQBpAGQAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABOAGEAdABpAG8AbgBhAGwAIABHAHIAZQBlAG4AaABvAHUAcwBlACAAQQBjAGMAbwB1AG4AdABzACAARgBhAGMAdABvAHIAcwAgADIAMAAyADUAIAAtACAAVABhAGIAbABlACAAOABcACIAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBMAGkAcQB1AGkAZABfAEQAYQB0AGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgA1ACwAIAA4ACwAXABuACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEYAdQBlAGwAIABjAG8AbQBiAHUAcwB0AGUAZABcACIALAAgAFwAIgBFAG4AZQByAGcAeQAgAEMAbwBuAHQAZQBuAHQAIABGAGEAYwB0AG8AcgAgACgARwBKACAAcABlAHIAIAB1AG4AaQB0ACAAbwBmACAAZgB1AGUAbAApAFwAIgAsACAAXAAiAEYAdQBlAGwAIAB1AG4AaQB0AFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgAgACgAawBnACAAQwBPADIAIAAtACAAZQAgAC8AIABHAEoAKQAgAEMATwAyAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgAgACgAawBnACAAQwBPADIAIAAtACAAZQAgAC8AIABHAEoAKQAgAEMASAA0AFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgAgACgAawBnACAAQwBPADIAIAAtACAAZQAgAC8AIABHAEoAKQAgAE4AMgBPAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgAgACgAawBnACAAQwBPADIAIAAtACAAZQAgAC8AIABHAEoAKQAgAEMAbwBtAGIAaQBuAGUAZAAgAGcAYQBzAGUAcwBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAzACAARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAIAAoAGsAZwAgAEMATwAyACAALQAgAGUAIAAvACAARwBKACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUABlAHQAcgBvAGwAZQB1AG0AIABiAGEAcwBlAGQAIABvAGkAbABzACAAKABvAHQAaABlAHIAIAB0AGgAYQBuACAAcABlAHQAcgBvAGwAZQB1AG0AIABiAGEAcwBlAGQAIABvAGkAbAAgAHUAcwBlAGQAIABhAHMAIABmAHUAZQBsACkALAAgAGUALgBnAC4AIABsAHUAYgByAGkAYwBhAG4AdABzAFwAIgAsACAAMwA4AC4AOAAsACAAXAAiAGsAbABcACIALAAgADEAMwAuADkALAAgADAALgAwACwAIAAwAC4AMAAsACAAMQAzAC4AOQAsACAAMQA4AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFAAZQB0AHIAbwBsAGUAdQBtACAAYgBhAHMAZQBkACAAZwByAGUAYQBzAGUAcwBcACIALAAgADMAOAAuADgALAAgAFwAIgBrAGwAXAAiACwAIAAzAC4ANQAsACAAMAAuADAALAAgADAALgAwACwAIAAzAC4ANQAsACAAMQA4AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAcgB1AGQAZQAgAG8AaQBsACAAaQBuAGMAbAB1AGQAaQBuAGcAIABjAHIAdQBkAGUAIABvAGkAbAAgAGMAbwBuAGQAZQBuAHMAYQB0AGUAcwBcACIALAAgADQANQAuADMALAAgAFwAIgB0AFwAIgAsACAANgA5AC4ANgAsACAAMAAuADAAOAAsACAAMAAuADIALAAgADYAOQAuADgAOAAsACAAXAAiAE4ARQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABuAGEAdAB1AHIAYQBsACAAZwBhAHMAIABsAGkAcQB1AGkAZABzAFwAIgAsACAANAA2AC4ANQAsACAAXAAiAHQAXAAiACwAIAA2ADEALgAwACwAIAAwAC4AMAA4ACwAIAAwAC4AMgAsACAANgAxAC4AMgA4ACwAIABcACIATgBFAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEEAdQB0AG8AbQBvAHQAaQB2AGUAIABnAGEAcwBvAGwAaQBuAGUAIAAvACAAcABlAHQAcgBvAGwAIAAoAG8AdABoAGUAcgAgAHQAaABhAG4AIABmAG8AcgAgAHUAcwBlACAAYQBzACAAZgB1AGUAbAAgAGkAbgAgAGEAbgAgAGEAaQByAGMAcgBhAGYAdAApAFwAIgAsACAAMwA0AC4AMgAsACAAXAAiAGsATABcACIALAAgADYANwAuADQALAAgADAALgAyACwAIAAwAC4AMgAsACAANgA3AC4AOAAwACwAIAAxADcALgAyADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQQB2AGkAYQB0AGkAbwBuACAAZwBhAHMAbwBsAGkAbgBlAFwAIgAsACAAMwAzAC4AMQAsACAAXAAiAGsATABcACIALAAgADYANwAsACAAMAAuADIALAAgADAALgAyACwAIAA2ADcALgA0ADAALAAgADEAOAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBLAGUAcgBvAHMAZQBuAGUAIAAoAG8AdABoAGUAcgAgAHQAaABhAG4AIABmAG8AcgAgAHUAcwBlACAAYQBzACAAZgB1AGUAbAAgAGkAbgAgAGEAbgAgAGEAaQByAGMAcgBhAGYAdAApAFwAIgAsACAAMwA3AC4ANQAsACAAXAAiAGsATABcACIALAAgADYAOAAuADkALAAgADAALgAwADEALAAgADAALgAyACwAIAA2ADkALgAxADEALAAgADEAOAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAHYAaQBhAHQAaQBvAG4AIAB0AHUAcgBiAGkAbgBlACAAZgB1AGUAbAAgAC8AIABrAGUAcgBvAHMAZQBuAGUAXAAiACwAIAAzADYALgA4ACwAIABcACIAawBMAFwAIgAsACAANgA5AC4ANgAsACAAMAAuADAAMgAsACAAMAAuADIALAAgADYAOQAuADgAMgAsACAAMQA4AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAZQBhAHQAaQBuAGcAIABvAGkAbABcACIALAAgADMANwAuADMALAAgAFwAIgBrAEwAXAAiACwAIAA2ADkALgA1ACwAIAAwAC4AMAAzACwAIAAwAC4AMgAsACAANgA5AC4ANwAzACwAIAAxADgALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIARABpAGUAcwBlAGwAIABvAGkAbABcACIALAAgADMAOAAuADYALAAgAFwAIgBrAEwAXAAiACwAIAA2ADkALgA5ACwAIAAwAC4AMQAsACAAMAAuADIALAAgADcAMAAuADIAMAAsACAAMQA3AC4AMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEYAdQBlAGwAIABvAGkAbABcACIALAAgADMAOQAuADcALAAgAFwAIgBrAEwAXAAiACwAIAA3ADMALgA2ACwAIAAwAC4AMAA0ACwAIAAwAC4AMgAsACAANwAzAC4AOAA0ACwAIAAxADgALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIATABpAHEAdQBlAGYAaQBlAGQAIABhAHIAbwBtAGEAdABpAGMAIABoAHkAZAByAG8AYwBhAHIAYgBvAG4AcwBcACIALAAgADMANAAuADQALAAgAFwAIgBrAEwAXAAiACwAIAA2ADkALgA3ACwAIAAwAC4AMAAzACwAIAAwAC4AMgAsACAANgA5AC4AOQAzACwAIAAxADgALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUwBvAGwAdgBlAG4AdABzADoAIABtAGkAbgBlAHIAYQBsACAAdAB1AHIAcABlAG4AdABpAG4AZQAgAG8AcgAgAHcAaABpAHQAZQAgAHMAcABpAHIAaQB0AHMAXAAiACwAIAAzADQALgA0ACwAIABcACIAawBMAFwAIgAsACAANgA5AC4ANwAsACAAMAAuADAAMwAsACAAMAAuADIALAAgADYAOQAuADkAMwAsACAAMQA4AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEwAaQBxAHUAZQBmAGkAZQBkACAAcABlAHQAcgBvAGwAZQB1AG0AIABnAGEAcwAgACgATABQAEcAKQBcACIALAAgADIANQAuADcALAAgAFwAIgBrAEwAXAAiACwAIAA2ADAALgAyACwAIAAwAC4AMgAsACAAMAAuADIALAAgADYAMAAuADYAMAAsACAAMgAwAC4AMgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE4AYQBwAGgAdABoAGEAXAAiACwAIAAzADEALgA0ACwAIABcACIAawBMAFwAIgAsACAANgA5AC4AOAAsACAAMAAuADAAMQAsACAAMAAuADAAMQAsACAANgA5AC4AOAAyACwAIAAxADgALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUABlAHQAcgBvAGwAZQB1AG0AIABjAG8AawBlAFwAIgAsACAAMwA0AC4AMgAsACAAXAAiAHQAXAAiACwAIAA5ADIALgA2ACwAIAAwAC4AMAA4ACwAIAAwAC4AMgAsACAAOQAyAC4AOAA4ACwAIAAxADgALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgBlAGYAaQBuAGUAcgB5ACAAZwBhAHMAIABhAG4AZAAgAGwAaQBxAHUAaQBkAHMAXAAiACwAIAA0ADIALgA5ACwAIABcACIAdABcACIALAAgADUANAAuADcALAAgADAALgAwADMALAAgADAALgAwADMALAAgADUANAAuADcANgAsACAAMQA4AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBmAGkAbgBlAHIAeQAgAGMAbwBrAGUAXAAiACwAIAAzADQALgAyACwAIABcACIAdABcACIALAAgADkAMgAuADYALAAgADAALgAwADgALAAgADAALgAyACwAIAA5ADIALgA4ADgALAAgADEAOAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAdAByAG8AbABlAHUAbQAgAGIAYQBzAGUAZAAgAHAAcgBvAGQAdQBjAHQAcwAgAG8AdABoAGUAcgAgAHQAaABhAG4AIABtAGUAbgB0AGkAbwBuAGUAZAAgAGkAbgAgAHQAaABlACAAaQB0AGUAbQBzACAAYQBiAG8AdgBlAFwAIgAsACAAMwA0AC4ANAAsACAAXAAiAGsATABcACIALAAgADYAOQAuADgALAAgADAALgAwADIALAAgADAALgAxACwAIAA2ADkALgA5ADIALAAgADEAOAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBCAGkAbwBkAGkAZQBzAGUAbABcACIALAAgADMANAAuADYALAAgAFwAIgBrAEwAXAAiACwAIAAwAC4AMAAsACAAMAAuADAAOAAsACAAMAAuADIALAAgADAALgAyADgALAAgAFwAIgBOAEUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIARQB0AGgAYQBuAG8AbAAgAGYAbwByACAAdQBzAGUAIABhAHMAIABhACAAZgB1AGUAbAAgAGkAbgAgAGEAbgAgAGkAbgB0AGUAcgBuAGEAbAAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AIABlAG4AZwBpAG4AZQBcACIALAAgADIAMwAuADQALAAgAFwAIgBrAEwAXAAiACwAIAAwAC4AMAAsACAAMAAuADAAOAAsACAAMAAuADIALAAgADAALgAyADgALAAgAFwAIgBOAEUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQgBpAG8AZgB1AGUAbABzACAAbwB0AGgAZQByACAAdABoAGEAbgAgAHQAaABvAHMAZQAgAG0AZQBuAHQAaQBvAG4AZQBkACAAaQBuACAAdABoAGUAIABpAHQAZQBtAHMAIABhAGIAbwB2AGUAIABhAG4AZAAgAGIAZQBsAG8AdwBcACIALAAgADIAMwAuADQALAAgAFwAIgBrAEwAXAAiACwAIAAwAC4AMAAsACAAMAAuADAAOAAsACAAMAAuADIALAAgADAALgAyADgALAAgAFwAIgBOAEUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgBlAG4AZQB3AGEAYgBsAGUAIABhAHYAaQBhAHQAaQBvAG4AIABrAGUAcgBvAHMAZQBuAGUAXAAiACwAIAAzADYALgA4ACwAIABcACIAawBMAFwAIgAsACAAMAAuADAALAAgADAALgAwADIALAAgADAALgAyACwAIAAwAC4AMgAyACwAIABcACIATgBFAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBuAGUAdwBhAGIAbABlACAAZABpAGUAcwBlAGwAXAAiACwAIAAzADgALgA2ACwAIABcACIAawBMAFwAIgAsACAAMAAuADAALAAgADAALgAxACwAIAAwAC4AMgAsACAAMAAuADMAMAAsACAAXAAiAE4ARQBcACIAXABuACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AKQApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEwAaQBxAHUAaQBkAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAFwAdQAwADAAMgA3AE4ARQBcAHUAMAAwADIANwAgAHYAYQBsAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAYQBzACAAegBlAHIAbwAgAGYAbwByACAAYwBhAGwAYwB1AGwAYQB0AGkAbwBuAHMALgBcACIAKQA7AFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBGAHUAZQBsACAAcwBjAG8AcABlACAAMQAgAGEAbgBkACAAMwAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIAAtACAAVAByAGEAbgBzAHAAbwByAHQAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBUAHIAYQBuAHMAcABvAHIAdABfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEYAdQBlAGwAIABzAGMAbwBwAGUAIAAxACAAYQBuAGQAIAAzACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAC0AIABUAHIAYQBuAHMAcABvAHIAdABcACIAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAVAByAGEAbgBzAHAAbwByAHQAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBEAGkAcgBlAGMAdAAgACgAcwBjAG8AcABlACAAMQApACAAYQBuAGQAIABpAG4AZABpAHIAZQBjAHQAIAAoAHMAYwBvAHAAZQAgADMAKQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAHQAaABlACAAYwBvAG4AcwB1AG0AcAB0AGkAbwBuACAAbwBmACAAdAByAGEAbgBzAHAAbwByAHQAIABmAHUAZQBsAHMAIABpAG4AIABkAGkAZgBmAGUAcgBlAG4AdAAgAHQAcgBhAG4AcwBwAG8AcgB0ACAAZQBxAHUAaQBwAG0AZQBuAHQAXAAiACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AF8AUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAEEAYwBjAG8AdQBuAHQAcwAgAEYAYQBjAHQAbwByAHMAIAAyADAAMgA1ACAALQAgAFQAYQBiAGwAZQAgADkAXAAiACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AF8ARABhAHQAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyADYALAAgADEAMAAsAFwAbgAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAYQBuAHMAcABvAHIAdAAgAHQAeQBwAGUAXAAiACwAIABcACIARgB1AGUAbAAgAGMAbwBtAGIAdQBzAHQAZQBkAFwAIgAsACAAXAAiAEUAbgBlAHIAZwB5ACAAQwBvAG4AdABlAG4AdAAgAEYAYQBjAHQAbwByACgARwBKACAAcABlAHIAIAB1AG4AaQB0ACAAbwBmACAAZgB1AGUAbAApAFwAIgAsACAAXAAiAEYAdQBlAGwAIAB1AG4AaQB0AFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgAgACgAawBnACAAQwBPADIAIAAtACAAZQAgAC8AIABHAEoAKQAgAEMATwAyAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgAgACgAawBnACAAQwBPADIAIAAtACAAZQAgAC8AIABHAEoAKQAgAEMASAA0AFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgAgACgAawBnACAAQwBPADIAIAAtACAAZQAgAC8AIABHAEoAKQAgAE4AMgBPAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgAgACgAawBnACAAQwBPADIAIAAtACAAZQAgAC8AIABHAEoAKQAgAEMAbwBtAGIAaQBuAGUAZAAgAGcAYQBzAGUAcwBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAzACAARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAIAAoAGsAZwAgAEMATwAyACAALQAgAGUAIAAvACAARwBKACkAXAAiACwAIABcACIAUwBvAHUAcgBjAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBhAHIAcwAgAGEAbgBkACAAbABpAGcAaAB0ACAAYwBvAG0AbQBlAHIAYwBpAGEAbAAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBHAGEAcwBvAGwAaQBuAGUAXAAiACwAIAAzADQALgAyACwAIABcACIAawBsAFwAIgAsACAANgA3AC4ANAAsACAAMAAuADAAMgAsACAAMAAuADIALAAgADYANwAuADYAMgAsACAAMQA3AC4AMgAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAYQByAHMAIABhAG4AZAAgAGwAaQBnAGgAdAAgAGMAbwBtAG0AZQByAGMAaQBhAGwAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIARABpAGUAcwBlAGwAIABvAGkAbABcACIALAAgADMAOAAuADYALAAgAFwAIgBrAGwAXAAiACwAIAA2ADkALgA5ACwAIAAwAC4AMAAxACwAIAAwAC4ANQAsACAANwAwAC4ANAAxACwAIAAxADcALgAzACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBhAHIAcwAgAGEAbgBkACAAbABpAGcAaAB0ACAAYwBvAG0AbQBlAHIAYwBpAGEAbAAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBMAGkAcQB1AGUAZgBpAGUAZAAgAHAAZQB0AHIAbwBsAGUAdQBtACAAZwBhAHMAIAAoAEwAUABHACkAXAAiACwAIAAyADYALgAyACwAIABcACIAawBsAFwAIgAsACAANgAwAC4AMgAsACAAMAAuADUALAAgADAALgAzACwAIAA2ADEALgAwADAALAAgADIAMAAuADIALAAgAFwAIgBOAEcAQQBGACAAMgAwADIANQA6ACAAVABhAGIAbABlACAAOQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAGEAcgBzACAAYQBuAGQAIABsAGkAZwBoAHQAIABjAG8AbQBtAGUAcgBjAGkAYQBsACAAdgBlAGgAaQBjAGwAZQBzAFwAIgAsACAAXAAiAEYAdQBlAGwAIABvAGkAbABcACIALAAgADMAOQAuADcALAAgAFwAIgBrAGwAXAAiACwAIAA3ADMALgA2ACwAIAAwAC4AMAA4ACwAIAAwAC4ANQAsACAANwA0AC4AMQA4ACwAIAAxADgALgAwACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBhAHIAcwAgAGEAbgBkACAAbABpAGcAaAB0ACAAYwBvAG0AbQBlAHIAYwBpAGEAbAAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBFAHQAaABhAG4AbwBsAFwAIgAsACAAMgAzAC4ANAAsACAAXAAiAGsAbABcACIALAAgADAALgAwACwAIAAwAC4AMgAsACAAMAAuADIALAAgADAALgA0ACwAIABcACIATgBFAFwAIgAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAYQByAHMAIABhAG4AZAAgAGwAaQBnAGgAdAAgAGMAbwBtAG0AZQByAGMAaQBhAGwAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIAQgBpAG8AZABpAGUAcwBlAGwAXAAiACwAIAAzADQALgA2ACwAIABcACIAawBsAFwAIgAsACAAMAAuADAALAAgADAALgA4ACwAIAAxAC4ANwAsACAAMgAuADUALAAgAFwAIgBOAEUAXAAiACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBhAHIAcwAgAGEAbgBkACAAbABpAGcAaAB0ACAAYwBvAG0AbQBlAHIAYwBpAGEAbAAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBSAGUAbgBlAHcAYQBiAGwAZQAgAGQAaQBlAHMAZQBsAFwAIgAsACAAMwA4AC4ANgAsACAAXAAiAGsAbABcACIALAAgADAALgAwACwAIAAwAC4AMAAxACwAIAAwAC4ANQAsACAAMAAuADUAMQAsACAAXAAiAE4ARQBcACIALAAgAFwAIgBOAEcAQQBGACAAMgAwADIANQA6ACAAVABhAGIAbABlACAAOQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAGEAcgBzACAAYQBuAGQAIABsAGkAZwBoAHQAIABjAG8AbQBtAGUAcgBjAGkAYQBsACAAdgBlAGgAaQBjAGwAZQBzAFwAIgAsACAAXAAiAE8AdABoAGUAcgAgAGIAaQBvAGYAdQBlAGwAcwBcACIALAAgADIAMwAuADQALAAgAFwAIgBrAGwAXAAiACwAIAAwAC4AMAAsACAAMAAuADgALAAgADEALgA3ACwAIAAyAC4ANQAsACAAXAAiAE4ARQBcACIALAAgAFwAIgBOAEcAQQBGACAAMgAwADIANQA6ACAAVABhAGIAbABlACAAOQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBMAGkAZwBoAHQAIABkAHUAdAB5ACAAdgBlAGgAaQBjAGwAZQBzAFwAIgAsACAAXAAiAEMAbwBtAHAAcgBlAHMAcwBlAGQAIABuAGEAdAB1AHIAYQBsACAAZwBhAHMAXAAiACwAIAAwAC4AMAAzADkAMwAsACAAXAAiAG0AMwBcACIALAAgADUAMQAuADQALAAgADcALgAzACwAIAAwAC4AMwAsACAANQA5AC4AMAAsACAAMQA4AC4AMAAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEwAaQBnAGgAdAAgAGQAdQB0AHkAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIATABpAHEAdQBlAGYAaQBlAGQAIABuAGEAdAB1AHIAYQBsACAAZwBhAHMAXAAiACwAIAAyADUALgAzACwAIABcACIAawBsAFwAIgAsACAANQAxAC4ANAAsACAANwAuADMALAAgADAALgAzACwAIAA1ADkALgAwACwAIAAxADgALgAwACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABlAGEAdgB5ACAAZAB1AHQAeQAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBDAG8AbQBwAHIAZQBzAHMAZQBkACAAbgBhAHQAdQByAGEAbAAgAGcAYQBzAFwAIgAsACAAMAAuADAAMwA5ADMALAAgAFwAIgBtADMAXAAiACwAIAA1ADEALgA0ACwAIAAyAC4AOAAsACAAMAAuADMALAAgADUANAAuADUALAAgADEAOAAuADAALAAgAFwAIgBOAEcAQQBGACAAMgAwADIANQA6ACAAVABhAGIAbABlACAAOQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAGUAYQB2AHkAIABkAHUAdAB5ACAAdgBlAGgAaQBjAGwAZQBzAFwAIgAsACAAXAAiAEwAaQBxAHUAZQBmAGkAZQBkACAAbgBhAHQAdQByAGEAbAAgAGcAYQBzAFwAIgAsACAAMgA1AC4AMwAsACAAXAAiAGsAbABcACIALAAgADUAMQAuADQALAAgADIALgA4ACwAIAAwAC4AMwAsACAANQA0AC4ANQAsACAAMQA4AC4AMAAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAZQBhAHYAeQAgAGQAdQB0AHkAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIARABpAGUAcwBlAGwAIABvAGkAbAAgAC0AIABFAHUAcgBvACAAaQB2ACAAbwByACAAaABpAGcAaABlAHIAXAAiACwAIAAzADgALgA2ACwAIABcACIAawBsAFwAIgAsACAANgA5AC4AOQAsACAAMAAuADAANwAsACAAMAAuADQALAAgADcAMAAuADMANwAsACAAMQA3AC4AMwAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAZQBhAHYAeQAgAGQAdQB0AHkAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIARABpAGUAcwBlAGwAIABvAGkAbAAgAC0AIABFAHUAcgBvACAAaQBpAGkAXAAiACwAIAAzADgALgA2ACwAIABcACIAawBsAFwAIgAsACAANgA5AC4AOQAsACAAMAAuADEALAAgADAALgA0ACwAIAA3ADAALgA0ACwAIAAxADcALgAzACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABlAGEAdgB5ACAAZAB1AHQAeQAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBEAGkAZQBzAGUAbAAgAG8AaQBsACAALQAgAEUAdQByAG8AIABpAFwAIgAsACAAMwA4AC4ANgAsACAAXAAiAGsAbABcACIALAAgADYAOQAuADkALAAgADAALgAyACwAIAAwAC4ANAAsACAANwAwAC4ANQAsACAAMQA3AC4AMwAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAZQBhAHYAeQAgAGQAdQB0AHkAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIAUgBlAG4AZQB3AGEAYgBsAGUAIABkAGkAZQBzAGUAbAAgABMgIABFAHUAcgBvACAAaQB2ACAAbwByACAAaABpAGcAaABlAHIAXAAiACwAIAAzADgALgA2ACwAIABcACIAawBsAFwAIgAsACAAMAAuADAALAAgADAALgAwADcALAAgADAALgA0ACwAIAAwAC4ANAA3ACwAIABcACIATgBFAFwAIgAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAZQBhAHYAeQAgAGQAdQB0AHkAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIAUgBlAG4AZQB3AGEAYgBsAGUAIABkAGkAZQBzAGUAbAAgABMgIABFAHUAcgBvACAAaQBpAGkAXAAiACwAIAAzADgALgA2ACwAIABcACIAawBsAFwAIgAsACAAMAAuADAALAAgADAALgAxACwAIAAwAC4ANAAsACAAMAAuADUALAAgAFwAIgBOAEUAXAAiACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABlAGEAdgB5ACAAZAB1AHQAeQAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBSAGUAbgBlAHcAYQBiAGwAZQAgAGQAaQBlAHMAZQBsACAAEyAgAEUAdQByAG8AIABpAFwAIgAsACAAMwA4AC4ANgAsACAAXAAiAGsAbABcACIALAAgADAALgAwACwAIAAwAC4AMgAsACAAMAAuADQALAAgADAALgA2ACwAIABcACIATgBFAFwAIgAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEEAdgBpAGEAdABpAG8AbgBcACIALAAgAFwAIgBHAGEAcwBvAGwAaQBuAGUAIABmAG8AcgAgAHUAcwBlACAAYQBzACAAZgB1AGUAbAAgAGkAbgAgAGEAbgAgAGEAaQByAGMAcgBhAGYAdABcACIALAAgADMAMwAuADEALAAgAFwAIgBrAGwAXAAiACwAIAA2ADcALgAwACwAIAAwAC4AMAA2ACwAIAAwAC4ANgAsACAANgA3AC4ANgA2ACwAIAAxADgALgAwACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQQB2AGkAYQB0AGkAbwBuAFwAIgAsACAAXAAiAEsAZQByAG8AcwBlAG4AZQAgAGYAbwByACAAdQBzAGUAIABhAHMAIABmAHUAZQBsACAAaQBuACAAYQBuACAAYQBpAHIAYwByAGEAZgB0AFwAIgAsACAAMwA2AC4AOAAsACAAXAAiAGsAbABcACIALAAgADYAOQAuADYALAAgADAALgAwADEALAAgADAALgA2ACwAIAA3ADAALgAyADEALAAgADEAOAAuADAALAAgAFwAIgBOAEcAQQBGACAAMgAwADIANQA6ACAAVABhAGIAbABlACAAOQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAHYAaQBhAHQAaQBvAG4AXAAiACwAIABcACIAUgBlAG4AZQB3AGEAYgBsAGUAIABhAHYAaQBhAHQAaQBvAG4AIABrAGUAcgBvAHMAZQBuAGUAXAAiACwAIAAzADYALgA4ACwAIABcACIAawBsAFwAIgAsACAAMAAuADAALAAgADAALgAwADEALAAgADAALgA2ACwAIAAwAC4ANgAxACwAIABcACIATgBFAFwAIgAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFYAZQBzAHMAZQBsAHMAXAAiACwAIABcACIARwBhAHMAbwBsAGkAbgBlAFwAIgAsACAAMwA0AC4AMgAsACAAXAAiAGsATABcACIALAAgADYANwAuADQALAAgADEAMAAuADEALAAgADAALgAzACwAIABcACIAXAAiACwAIAAxADcALgAyACwAIABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADQALgAyAC4AMQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBWAGUAcwBzAGUAbABzAFwAIgAsACAAXAAiAEQAaQBlAHMAZQBsACAAbwBpAGwAXAAiACwAIAAzADgALgA2ACwAIABcACIAawBMAFwAIgAsACAANgA5AC4AOQAsACAAMAAuADIALAAgADAALgA1ACwAIABcACIAXAAiACwAIAAxADcALgAzACwAIABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADQALgAyAC4AMQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBWAGUAcwBzAGUAbABzAFwAIgAsACAAXAAiAEYAdQBlAGwAIABPAGkAbABcACIALAAgADMAOQAuADcALAAgAFwAIgBrAEwAXAAiACwAIAA3ADMALgA2ACwAIAAwAC4AMgAsACAAMAAuADUALAAgAFwAIgBcACIALAAgADEAOAAuADAALAAgAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4ANAAuADIALgAxAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AZgBmAC0AcgBvAGEAZAAgAEEAZwByAGkAYwB1AGwAdAB1AHIAZQAgAGEAbgBkACAAZgBvAHIAZQBzAHQAcgB5ACAAZQBxAHUAaQBwAG0AZQBuAHQAXAAiACwAIABcACIARABpAGUAcwBlAGwAIABvAGkAbABcACIALAAgADMAOAAuADYALAAgAFwAIgBrAEwAXAAiACwAIAA2ADkALgA5ACwAIAAwAC4AMwAsACAAMAAuADUALAAgAFwAIgBcACIALAAgADEANwAuADMALAAgAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4ANAAuADIALgAxAFwAIgBcAG4AIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgApACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAFwAdQAwADAAMgA3AE4ARQBcAHUAMAAwADIANwAgAHYAYQBsAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAYQBzACAAegBlAHIAbwAgAGYAbwByACAAYwBhAGwAYwB1AGwAYQB0AGkAbwBuAHMALgBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ARgB1AGUAbAAgAHMAYwBvAHAAZQAgADEAIABhAG4AZAAgADMAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAALQAgAE8AZgBmAC0AcgBhAGQAIABlAHEAdQBpAHAAbQBlAG4AdAAgAGEAbgBkACAAdgBlAHMAcwBlAGwAcwBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AE8AZgBmAFIAbwBhAGQAXwBUAGkAdABsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBGAHUAZQBsACAAcwBjAG8AcABlACAAMQAgAGEAbgBkACAAMwAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIAAtACAATwBmAGYALQByAG8AYQBkACAAZQBxAHUAaQBwAG0AZQBuAHQAIABhAG4AZAAgAHYAZQBzAHMAZQBsAHMAXAAiACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AE8AZgBmAFIAbwBhAGQAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBEAGkAcgBlAGMAdAAgACgAcwBjAG8AcABlACAAMQApACAAYQBuAGQAIABpAG4AZABpAHIAZQBjAHQAIAAoAHMAYwBvAHAAZQAgADMAKQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAHQAaABlACAAYwBvAG4AcwB1AG0AcAB0AGkAbwBuACAAbwBmACAAZgB1AGUAbABzACAAaQBuACAAbwBmAGYALQByAG8AYQBkACAAZQBxAHUAaQBwAG0AZQBuAHQAIABhAG4AZAAgAHYAZQBzAHMAZQBsAHMAXAAiACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AE8AZgBmAFIAbwBhAGQAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgA0AC4AMgAuADEAXAAiACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AE8AZgBmAFIAbwBhAGQAXwBEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADcALABcAG4AIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIABcACIAVAByAGEAbgBzAHAAbwByAHQAIAB0AHkAcABlACAAdABcACIALAAgAFwAIgBGAHUAZQBsACAAdAB5AHAAZQAgAHEAXAAiACwAIABcACIARQBDAFQAcgBhAG4AcwAsAHEAIAAoAEcASgAvAGsATAApAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAIABDAE8AMgAgAEUARgBUAHIAYQBuACwAMQAsAHQAcQBnACAAKABrAGcAIABDAE8AMgAtAGUALwBHAEoAKQBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAxACAAQwBIADQAIABFAEYAVAByAGEAbgAsADEALAB0AGcAZwAgACgAawBnACAAQwBPADIALQBlAC8ARwBKACkAXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAE4AMgBPACAARQBGAFQAcgBhAG4ALAAxACwAdABnAGcAIAAoAGsAZwAgAEMATwAyAC0AZQAvAEcASgApAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADMAIABFAEYAVAByAGEAbgBzACwAMwAsAHEAIAAoAGsAZwAgAEMATwAyAC0AZQAvAEcASgApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFYAZQBzAHMAZQBsAFwAIgAsACAAXAAiAFAAZQB0AHIAbwBsAFwAIgAsACAAMwA0AC4AMgAsACAANgA3AC4ANAAsACAAMQAwAC4AMQAsACAAMAAuADMALAAgADEANwAuADIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBWAGUAcwBzAGUAbABcACIALAAgAFwAIgBEAGkAZQBzAGUAbABcACIALAAgADMAOAAuADYALAAgADYAOQAuADkALAAgADAALgAyACwAIAAwAC4ANQAsACAAMQA3AC4AMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFYAZQBzAHMAZQBsAFwAIgAsACAAXAAiAEYAdQBlAGwAIABPAGkAbABcACIALAAgADMAOQAuADcALAAgADcAMwAuADYALAAgADAALgAyACwAIAAwAC4ANQAsACAAMQA4AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AZgBmAC0AcgBvAGEAZAAgAEEAZwByAGkAYwB1AGwAdAB1AHIAZQAgAGEAbgBkACAAZgBvAHIAZQBzAHQAcgB5ACAAZQBxAHUAaQBwAG0AZQBuAHQAXAAiACwAIABcACIARABpAGUAcwBlAGwAXAAiACwAIAAzADgALgA2ACwAIAA2ADkALgA5ACwAIAAwAC4AMwAsACAAMAAuADUALAAgADEANwAuADMAXABuACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AKQApACkAOwBcAG4AXABuAFwAbgBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBGAHUAZQBsAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIARgB1AGUAbABfAEcAZQB0AFQAcgBhAG4AcwBwAG8AcgB0AEYAdQBlAGwAUwB0AHIAaQBuAGcAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABDAGUAbABsACwAXABuACAAIAAgACAATABFAEYAVAAoAEMAZQBsAGwALAAgAEYASQBOAEQAKABcACIALAAgAFwAIgAsAEMAZQBsAGwAKQAgAC0AMQApAFwAbgApADsAXABuAFwAbgBGAHUAZQBsAF8ARwBlAHQAUwB0AGEAdABpAG8AbgBhAHIAeQBGAHUAZQBsAFMAdAByAGkAbgBnAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQwBlAGwAbAAsAFwAbgAgACAAIAAgAFIASQBHAEgAVAAoAEMAZQBsAGwALABMAEUATgAoAEMAZQBsAGwAKQAtAEYASQBOAEQAKABcACIALAAgAFwAIgAsAEMAZQBsAGwAKQApAFwAbgApADsAXABuAFwAbgBGAHUAZQBsAF8AVABvAHQAYQBsAEMAbwBuAHMAdQBtAHAAdABpAG8AbgBcAG4APQAgAEwAQQBNAEIARABBACgAXABuACAAIAAgACAARgB1AGUAbABDAG8AbgBzAHUAbQBwAHQAaQBvAG4AQQByAHIAYQB5ACwAIABGAHUAZQBsAFUAcwBlAEEAcgByAGEAeQAsACAARgB1AGUAbABVAHMAZQAsACAARgB1AGUAbABUAHkAcABlAEEAcgByAGEAeQAsACAARgB1AGUAbABUAHkAcABlACwAXABuACAAIAAgACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgAFMAVQBNACgAXABuACAAIAAgACAAIAAgAEYASQBMAFQARQBSACgAXABuACAAIAAgACAAIAAgACAAIABGAHUAZQBsAEMAbwBuAHMAdQBtAHAAdABpAG8AbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIAAgACAAIAAgACgARgB1AGUAbABUAHkAcABlAEEAcgByAGEAeQAgAD0AIABGAHUAZQBsAFQAeQBwAGUAKQAgACoAIABcAG4AIAAgACAAIAAgACAAIAAgACgARgB1AGUAbABVAHMAZQBBAHIAcgBhAHkAIAA9ACAARgB1AGUAbABVAHMAZQApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkALABcAG4AIAAgACAAIAAwAFwAbgAgACAAKQBcAG4AKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8ARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADgAOgAgAEYAdQBlAGwAIABVAHMAZQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA4AC4AMQAgAEYAdQBlAGwAIABVAHMAZQAgAC0AIABUAHIAYQBuAHMAcABvAHIAdAAgAGYAdQBlAGwAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4AXABuAFYARQBFAFIARwBfADgAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUQAsACAARQBDACwAIABFAEYALABcAG4AIAAgACAAIAAoAFEAIAAqACAARQBDACAAKgAgAEUARgApACAAKgAgADEAMAAgAF4AIAAtACAAMwBcAG4AIAAgACkAXABuADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA4AF8AMQBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFQAcgBhAG4AcwBwAG8AcgB0AFwAbgBFAG0AaQBzAHMAaQBvAG4AcwAgAGYAbwByACAAZQBhAGMAaAAgAEcASABHACAAZgByAG8AbQAgAHQAaABlACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgAG8AZgAgAGYAdQBlAGwAcwAgAGYAbwByACAAdAByAGEAbgBzAHAAbwByAHQAIABlAG4AZQByAGcAeQAgAHAAdQByAHAAbwBzAGUAcwBcAG4AUQAgADoAIABBAG0AbwB1AG4AdAAgAG8AZgAgAGYAdQBlAGwAIAB0AHkAcABlACAAcQAgAGMAbwBtAGIAdQBzAHQAZQBkACAAZgBvAHIAIAB0AHIAYQBuAHMAcABvAHIAdAAgAGUAbgBlAHIAZwB5ACAAcAB1AHIAcABvAHMAZQBzACAAOgAgAGsATABcAG4ARQBDACAAOgAgAGUAbgBlAHIAZwB5ACAAYwBvAG4AdABlAG4AdAAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AHIAYQBuAHMAcABvAHIAdAAgAGUAbgBlAHIAZwB5ACAAcAB1AHIAcABvAHMAZQBzACAAOgAgAEcASgAvAGsATABcAG4ARQBGACAAOgAgAFMAYwBvAHAAZQAgADEAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdAByAGEAbgBzAHAAbwByAHQAIABlAG4AZQByAGcAeQAgAHAAdQByAHAAbwBzAGUAcwAgAGYAbwByACAAZQBhAGMAaAAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwAgADoAIABrAGcAIABDAE8AMgBlACAALwAgAEcASgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AVgBFAEUAUgBHAF8AOABfADEAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBUAHIAYQBuAHMAcABvAHIAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABRAF8AVAByAGEAbgBzAHQAcQAsACAARQBDAF8AVAByAGEAbgBzAHEALAAgAEUARgBfAFQAcgBhAG4AcwAxAHQAcQBnACwAXABuACAAIAAgACAAVgBFAEUAUgBHAF8AOABfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgAoAFEAXwBUAHIAYQBuAHMAdABxACwAIABFAEMAXwBUAHIAYQBuAHMAcQAsACAARQBGAF8AVAByAGEAbgBzADEAdABxAGcAKQBcAG4AIAAgACkAXABuADsAXABuAFwAbgBWAEUARQBSAEcAXwA4AF8AMQBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFQAcgBhAG4AcwBwAG8AcgB0AF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAGYAbwByACAAZQBhAGMAaAAgAEcASABHACAAZgByAG8AbQAgAHQAaABlACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgAG8AZgAgAGYAdQBlAGwAcwAgAGYAbwByACAAdAByAGEAbgBzAHAAbwByAHQAIABlAG4AZQByAGcAeQAgAHAAdQByAHAAbwBzAGUAcwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOABfADEAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBUAHIAYQBuAHMAcABvAHIAdABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAGcAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADgAXwAxAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AVAByAGEAbgBzAHAAbwByAHQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAAQwBPADIALQBlAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA4AF8AMQBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFQAcgBhAG4AcwBwAG8AcgB0AF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADgALgAxAC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA4AF8AMQBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFQAcgBhAG4AcwBwAG8AcgB0AF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABOAGEAdABpAG8AbgBhAGwAIABHAHIAZQBlAG4AaABvAHUAcwBlACAAQQBjAGMAbwB1AG4AdABzACAARgBhAGMAdABvAHIAcwAgADIAMAAyADUAIAAtACAAMgAuADMAIABFAHMAdABpAG0AYQB0AGkAbgBnACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAdAByAGEAbgBzAHAAbwByAHQAIABmAHUAZQBsAHMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADgAXwAxAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AVAByAGEAbgBzAHAAbwByAHQAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AZwA9AFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AdAAgAFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AcQBcAFwAbABlAGYAdAAoAFEAXwB7AFQAcgBhAG4AcwAsAHQAcQB9AFwAXAB0AGkAbQBlAHMAIABFAEMAXwB7AFQAcgBhAG4AcwAsAHEAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBUAHIAYQBuAHMALAAxACwAdABxAGcAfQBcAFwAcgBpAGcAaAB0ACkAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADgAXwAxAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AVAByAGEAbgBzAHAAbwByAHQAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADcALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAXwBUAHIAYQBuAHMAdABxAFwAIgAsACAAXAAiAEEAbQBvAHUAbgB0ACAAbwBmACAAZgB1AGUAbAAgAHQAeQBwAGUAIABxACAAYwBvAG0AYgB1AHMAdABlAGQAIABmAG8AcgAgAHQAcgBhAG4AcwBwAG8AcgB0ACAAZQBuAGUAcgBnAHkAIABwAHUAcgBwAG8AcwBlAHMAXAAiACwAIABcACIAVgBhAHIAaQBlAHMAIABiAGEAcwBlAGQAIABvAG4AIABmAHUAZQBsACAAdAB5AHAAZQA6ACAAawBMACwAIABtADMALAAgAEcASgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAQwBfAFQAcgBhAG4AcwBxAFwAIgAsACAAXAAiAEUAbgBlAHIAZwB5ACAAYwBvAG4AdABlAG4AdAAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AHIAYQBuAHMAcABvAHIAdAAgAGUAbgBlAHIAZwB5ACAAcAB1AHIAcABvAHMAZQBzAFwAIgAsACAAXAAiAEcASgAgAC8AIAB1AG4AaQB0ACAAbwBmACAAZgB1AGUAbABcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAFQAcgBhAG4AcwAxAHQAcQBnAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdAByAGEAbgBzAHAAbwByAHQAIABlAG4AZQByAGcAeQAgAHAAdQByAHAAbwBzAGUAcwAgAGYAbwByACAAZQBhAGMAaAAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBcACIALAAgAFwAIgBrAGcAIABDAE8AMgBlACAALwAgAEcASgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAHEAXAAiACwAIABcACIARgB1AGUAbAAgAHQAeQBwAGUAXAAiACwAIABcACIAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAYQBuAHMAXAAiACwAIABcACIAVAByAGEAbgBzAHAAbwByAHQAIABjAG8AbQBiAHUAcwB0AGkAbwBuAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAZwBcACIALAAgAFwAIgBHAHIAZQBlAG4AaABvAHUAcwBlACAAZwBhAHMAXAAiACwAIABcACIAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAXAAiACwAIABcACIAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8AOABfADIAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBTAHQAYQB0AGkAbwBuAGEAcgB5AFwAbgBFAG0AaQBzAHMAaQBvAG4AcwAgAGYAbwByACAAZQBhAGMAaAAgAEcASABHACAAZgByAG8AbQAgAHQAaABlACAAcwB0AGEAdABpAG8AbgBhAHIAeQAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AIABvAGYAIABmAHUAZQBsAHMAXABuAFEAIAA6ACAAQQBtAG8AdQBuAHQAIABvAGYAIABmAHUAZQBsACAAdAB5AHAAZQAgAHEAIAB1AHMAZQBkACAAZgBvAHIAIABzAHQAYQB0AGkAbwBuAGEAcgB5ACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgAG8AcABlAHIAYQB0AGkAbwBuAHMAIAA6ACAAawBMAFwAbgBFAEMAIAA6ACAARQBuAGUAcgBnAHkAIABjAG8AbgB0AGUAbgB0ACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHMAdABhAHQAaQBvAG4AYQByAHkAIABjAG8AbQBiAHUAcwB0AGkAbwBuACAAbwBwAGUAcgBhAHQAaQBvAG4AcwAgADoAIABHAEoALwBrAEwAXABuAEUARgAgADoAIABTAGMAbwBwAGUAIAAxACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHMAdABhAHQAaQBvAG4AYQByAHkAIABjAG8AbQBiAHUAcwB0AGkAbwBuACAAZgBvAHIAIABlAGEAYwBoACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzACAAOgAgAGsAZwAgAEMATwAyAGUAIAAvACAARwBKAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFwAbgBWAEUARQBSAEcAXwA4AF8AMgBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFMAdABhAHQAaQBvAG4AYQByAHkAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUQBfAFMAQwBxACwAIABFAEMAXwBTAEMAcQAsACAARQBGAF8AUwBDADEAcQBnACwAXABuACAAIAAgACAAVgBFAEUAUgBHAF8AOABfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgAoAFEAXwBTAEMAcQAsACAARQBDAF8AUwBDAHEALAAgAEUARgBfAFMAQwAxAHEAZwApAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAFYARQBFAFIARwBfADgAXwAyAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AUwB0AGEAdABpAG8AbgBhAHIAeQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuAHMAIABmAG8AcgAgAGUAYQBjAGgAIABHAEgARwAgAGYAcgBvAG0AIAB0AGgAZQAgAHMAdABhAHQAaQBvAG4AYQByAHkAIABjAG8AbQBiAHUAcwB0AGkAbwBuACAAbwBmACAAZgB1AGUAbABzAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA4AF8AMgBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFMAdABhAHQAaQBvAG4AYQByAHkAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwBnAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA4AF8AMgBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFMAdABhAHQAaQBvAG4AYQByAHkAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAAQwBPADIALQBlAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA4AF8AMgBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFMAdABhAHQAaQBvAG4AYQByAHkAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAOAAuADIALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADgAXwAyAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AUwB0AGEAdABpAG8AbgBhAHIAeQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAEEAYwBjAG8AdQBuAHQAcwAgAEYAYQBjAHQAbwByAHMAIAAyADAAMgA1ACAALQAgADIALgAyACAARQBzAHQAaQBtAGEAdABpAG4AZwAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHMAdABhAHQAaQBvAG4AYQByAHkAIABlAG4AZQByAGcAeQAgAHMAbwB1AHIAYwBlAHMAIAAtACAAQwBhAGwAYwB1AGwAYQB0AGkAbgBnACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAcwB0AGEAdABpAG8AbgBhAHIAeQAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AIABvAGYAIABsAGkAcQB1AGkAZAAgAGYAdQBlAGwAcwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOABfADIAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBTAHQAYQB0AGkAbwBuAGEAcgB5AF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAGcAPQBcAFwAcwB1AG0AXABcAG4AbwBsAGkAbQBpAHQAcwBfAHQAIABcAFwAcwB1AG0AXABcAG4AbwBsAGkAbQBpAHQAcwBfAHEAXABcAGwAZQBmAHQAKABRAF8AewBTAEMALABxAH0AXABcAHQAaQBtAGUAcwAgAEUAQwBfAHsAUwBDACwAcQB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AFMAQwAsADEALABxAGcAfQBcAFwAcgBpAGcAaAB0ACkAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADgAXwAyAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AUwB0AGEAdABpAG8AbgBhAHIAeQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANwAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQBfAFMAQwBxAFwAIgAsACAAXAAiAEEAbQBvAHUAbgB0ACAAbwBmACAAZgB1AGUAbAAgAHQAeQBwAGUAIABxACAAdQBzAGUAZAAgAGYAbwByACAAcwB0AGEAdABpAG8AbgBhAHIAeQAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AIABvAHAAZQByAGEAdABpAG8AbgBzAFwAIgAsACAAXAAiAFYAYQByAGkAZQBzACAAYgBhAHMAZQBkACAAbwBuACAAZgB1AGUAbAAgAHQAeQBwAGUAOgAgAGsATAAsACAAbQAzACwAIABHAEoAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEMAXwBTAEMAcQBcACIALAAgAFwAIgBFAG4AZQByAGcAeQAgAGMAbwBuAHQAZQBuAHQAIABmAGEAYwB0AG8AcgAgAGYAbwByACAAcwB0AGEAdABpAG8AbgBhAHIAeQAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AIABvAHAAZQByAGEAdABpAG8AbgBzAFwAIgAsACAAXAAiAEcASgAgAC8AIAB1AG4AaQB0ACAAbwBmACAAZgB1AGUAbABcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAFMAQwAxAHEAZwBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAxACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHMAdABhAHQAaQBvAG4AYQByAHkAIABjAG8AbQBiAHUAcwB0AGkAbwBuACAAZgBvAHIAIABlAGEAYwBoACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAFwAIgAsACAAXAAiAGsAZwAgAEMATwAyAGUAIAAvACAARwBKAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAcQBcACIALAAgAFwAIgBGAHUAZQBsACAAdAB5AHAAZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAQwBcACIALAAgAFwAIgBTAHQAYQB0AGkAbwBuAGEAcgB5ACAAYwBvAG0AYgB1AHMAdABpAG8AbgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGcAXAAiACwAIABcACIARwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAMQBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAxAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA5ADoAIABSAGUAZgByAGkAZwBlAHIAYQBuAHQAIABVAHMAZQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA5AC4AMQAgAFIAZQBmAHIAaQBnAGUAcgBhAG4AdAAgAFUAcwBlAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAFwAbgBUAGgAZQAgAHQAbwB0AGEAbAAgAGUAbQBpAHMAcwBpAG8AbgBzACAAbwBmACAAcgBlAGYAcgBpAGcAZQByAGEAbgB0ACAAbABlAGEAawBpAG4AZwAgAGQAdQByAGkAbgBnACAAbwBwAGUAcgBhAHQAaQBvAG4AIAAoAG4AbwB0ACAAZAB1AHIAaQBuAGcAIABpAG4AcwB0AGEAbABsAGEAdABpAG8AbgAgAG8AcgAgAGQAaQBzAHAAbwBzAGEAbAApAFwAbgBHAFcAUABSACAAOgAgAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAbwBmACAAcgBlAGYAcgBpAGcAZQByAGEAbgB0ACAAUgAgADoAIABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAbgBjAGgAYQByAGcAZQBfAFIAYQAgADoAIABBAG0AbwB1AG4AdAAgAG8AZgAgAHIAZQBmAHIAaQBnAGUAcgBhAG4AdAAgAFIAIABjAG8AbgB0AGEAaQBuAGUAZAAgAGkAbgAgAGEAcABwAGwAaQBhAG4AYwBlACAAYQAgADoAIABrAGcAXABuAGwAZQBhAGsAYQBnAGUAcgBhAHQAZQBfAGEAIAA6ACAAUAByAGMAZQBuAHQAYQBnAGUAIABvAGYAIAB0AG8AdABhAGwAIABjAGgAYQByAGcAZQAgAGwAZQBhAGsAZQBkACAAZgByAG8AbQAgAGEAcABwAGwAaQBhAG4AYwBlACAAYQAgAGUAYQBjAGgAIAB5AGUAYQByACAAOgAgAFAAZQByAGMAZQBuAHQAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGMAaABhAHIAZwBlAF8AUgBhACwAIABsAGUAYQBrAGEAZwBlAHIAYQB0AGUAXwBhACwAXABuACAAIAAgACAAKABjAGgAYQByAGcAZQBfAFIAYQAgACoAIAAoAGwAZQBhAGsAYQBnAGUAcgBhAHQAZQBfAGEALwAxADAAMAApACkAIAAqACAAMQAwACAAXgAgAC0AIAAzAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcARwBXAFAAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAARQBfAFIALAAgAEcAVwBQAF8AUgAsAFwAbgAgACAAIAAgACgAKABFAF8AUgAgACoAIAAxADAAXgAzACkAIAAqACAARwBXAFAAXwBSACkAIAAqACAAMQAwAF4ALQAzAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAaABlACAAdABvAHQAYQBsACAAZQBtAGkAcwBzAGkAbwBuAHMAIABvAGYAIAByAGUAZgByAGkAZwBlAHIAYQBuAHQAIABsAGUAYQBrAGkAbgBnACAAZAB1AHIAaQBuAGcAIABvAHAAZQByAGEAdABpAG8AbgAgACgAbgBvAHQAIABkAHUAcgBpAG4AZwAgAGkAbgBzAHQAYQBsAGwAYQB0AGkAbwBuACAAbwByACAAZABpAHMAcABvAHMAYQBsACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAEcAVwBQAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAIABsAGUAYQBrAGEAZwBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABjAG8AbgB2AGUAcgB0AGUAZAAgAHQAbwAgAEMATwAyAC0AZQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwBSAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBHAFcAUABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAHIAZQBmAHIAaQBnAGUAcgBhAG4AdAAgAGcAYQBzAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBHAFcAUABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgAtAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADkALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAEcAVwBQAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABOAGEAdABpAG8AbgBhAGwAIABHAHIAZQBlAG4AaABvAHUAcwBlACAAQQBjAGMAbwB1AG4AdABzACAARgBhAGMAdABvAHIAcwAgADIAMAAyADUAIAAtACAAMwAuADEAIABFAHMAdABpAG0AYQB0AGkAbgBnACAAaQBuAGQAdQBzAHQAcgBpAGEAbAAgAHAAcgBvAGMAZQBzAHMAZQBzACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAtACAAUgBlAGYAcgBpAGcAZQByAGEAbgB0ACAAbABlAGEAawBhAGcAZQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAXwBSAGUAYQBkAGEAYgBsAGUARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBjAGgAYQByAGcAZQBfAFIAYQAgACoAIAAoAGwAZQBhAGsAYQBnAGUAcgBhAHQAZQBfAGEALwAxADAAMAApACAAKgAgADEAMAAgAF4AIAAtACAAMwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AUgAgAD0AIABcAFwAcwB1AG0AXABcAG4AbwBsAGkAbQBpAHQAcwBfAGEAIABcAFwAbABlAGYAdAAoACAAYwBoAGEAcgBnAGUAXwB7AFIAYQB9ACAAXABcAHQAaQBtAGUAcwAgAFwAXABmAHIAYQBjAHsAbABlAGEAawBhAGcAZQBcAFwALAByAGEAdABlAF8AYQB9AHsAMQAwADAAfQAgAFwAXAByAGkAZwBoAHQAKQAgAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBHAFcAUABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwBDAE8AMgBlACAAPQAgAFwAXABsAGUAZgB0ACgARQBfAFIAIABcAFwAdABpAG0AZQBzACAAMQAwAF4AewAzAH0AIABcAFwAcgBpAGcAaAB0ACkAIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwBSACAAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBjAGgAYQByAGcAZQBfAFIAYQBcACIALAAgAFwAIgBBAG0AbwB1AG4AdAAgAG8AZgAgAHIAZQBmAHIAaQBnAGUAcgBhAG4AdAAgAFIAIABjAG8AbgB0AGEAaQBuAGUAZAAgAGkAbgAgAGEAcABwAGwAaQBhAG4AYwBlACAAYQBcACIALAAgAFwAIgBrAGcAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBsAGUAYQBrAGEAZwBlAHIAYQB0AGUAXwBhAFwAIgAsACAAXAAiAFAAcgBjAGUAbgB0AGEAZwBlACAAbwBmACAAdABvAHQAYQBsACAAYwBoAGEAcgBnAGUAIABsAGUAYQBrAGUAZAAgAGYAcgBvAG0AIABhAHAAcABsAGkAYQBuAGMAZQAgAGEAIABlAGEAYwBoACAAeQBlAGEAcgBcACIALAAgAFwAIgBQAGUAcgBjAGUAbgB0AFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAYQBcACIALAAgAFwAIgBBAHAAcABsAGkAYQBuAGMAZQAgAHQAeQBwAGUAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAFwAIgAsACAAXAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBHAFcAUABfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBfAFIAXAAiACwAIABcACIAVABvAHQAYQBsACAAZQBtAGkAcwBzAGkAbwBuAHMAIABvAGYAIAByAGUAZgByAGkAZwBlAHIAYQBuAHQAIABSAFwAIgAsACAAXAAiAHQAIAByAGUAZgByAGkAZwBlAHIAYQBuAHQAIABnAGEAcwBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADkALgAxAC4AMQAgACgAMQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAFcAUABfAFIAXAAiACwAIABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABvAGYAIAByAGUAZgByAGkAZwBlAHIAYQBuAHQAIABSAFwAIgAsACAAXAAiAEQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAE4AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAZQBxAHUAYQB0AGkAbwBuACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAHIAZQBmAHIAaQBnAGUAcgBhAG4AdAAgAFIAIAB0AG8AIABDAE8AMgAtAGUAIAB1AHMAaQBuAGcAIAB0AGgAZQAgAHIAZQBmAHIAaQBnAGUAcgBhAG4AdABcAHUAMAAwADIANwBzACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIAAoAEcAVwBQACkALgBcACIAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBTAG8AdQByAGMAZQBEAGEAdABhACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBBAHAAcABlAG4AZABpAHgAIAAyACAARwBsAG8AYgBhAGwAIABXAGEAcgBtAGkAbgBnACAAUABvAHQAZQBuAHQAaQBhAGwAcwA6ACAAVABhAGIAbABlACAAMgAzACAARwBsAG8AYgBhAGwAIABXAGEAcgBtAGkAbgBnACAAUABvAHQAZQBuAHQAaQBhAGwAcwBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBDAGgAZQBtAGkAYwBhAGwARwBXAFAAXwBUAGkAdABsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBHAGwAbwBiAGEAbAAgAFcAYQByAG0AaQBuAGcAIABQAG8AdABlAG4AdABpAGEAbABzAFwAIgApACkAOwBcAG4AXABuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AQwBoAGUAbQBpAGMAYQBsAEcAVwBQAF8ARABlAHMAYwByAGkAcAB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBDAGgAZQBtAGkAYwBhAGwARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABOAGEAdABpAG8AbgBhAGwAIABHAHIAZQBlAG4AaABvAHUAcwBlACAAQQBjAGMAbwB1AG4AdABzACAARgBhAGMAdABvAHIAcwAgADIAMAAyADUAIAAtACAAQQBwAHAAZQBuAGQAaQB4ACAAMgAgAC0AIABUAGEAYgBsAGUAIAAyADMAXAAiACkAKQA7AFwAbgBcAG4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBDAGgAZQBtAGkAYwBhAGwARwBXAFAAXwBEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMAOQAsACAANQAsAFwAbgAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBHAGEAcwBcACIALAAgAFwAIgBDAGgAZQBtAGkAYwBhAGwAIABmAG8AcgBtAHUAbABhAFwAIgAsACAAXAAiAEcAbABvAGIAYQBsACAAVwBhAHIAbQBpAG4AZwAgAFAAbwB0AGUAbgB0AGkAYQBsACAAKABBAFIANQApAFwAIgAsACAAXAAiAEcAYQBzACAALQAgAEYAQwAgAG4AYQBtAGUAXAAiACwAIABcACIAQQBkAGkAdABpAG8AbgBhAGwAIABkAGEAdABhACAAcwBvAHUAcgBjAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlAFwAIgAsACAAXAAiAEMATwAyAFwAIgAsACAAMQAsACAAXAAiAEMATwAyAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE0AZQB0AGgAYQBuAGUAXAAiACwAIABcACIAQwBIADQAXAAiACwAIAAyADgALAAgAFwAIgBDAEgANABcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlAFwAIgAsACAAXAAiAE4AMgBPAFwAIgAsACAAMgA2ADUALAAgAFwAIgBOADIATwBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAbABwAGgAdQByACAAaABlAHgAYQBmAGwAdQBvAHIAaQBkAGUAXAAiACwAIABcACIAUwBGADYAXAAiACwAIAAyADMANQAwADAALAAgAFwAIgBTAEYANgBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAEYAQwAtADIAMwAgACgAUgAtADIAMwApAFwAIgAsACAAXAAiAEMASABGADMAXAAiACwAIAAgADEAMgA0ADAAMAAsACAAXAAiAEgARgBDAC0AMgAzAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgARgBDAC0AMwAyACAAKABSAC0AMwAyACkAXAAiACwAIABcACIAQwBIADIARgAyAFwAIgAsACAANgA3ADcALAAgAFwAIgBIAEYAQwAtADMAMgBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAEYAQwAtADQAMQAgACgAUgAtADQAMQApAFwAIgAsACAAXAAiAEMASAAzAEYAXAAiACwAIAAgADEAMQA2ACwAIABcACIASABGAEMALQA0ADEAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABGAEMALQA0ADMALQAxADAAbQBlAGUAIAAoAFIALQA0ADMAMQAwAG0AZQBlACkAXAAiACwAIABcACIAQwA1AEgAMgBGADEAMABcACIALAAgADEANgA1ADAALAAgAFwAIgBIAEYAQwAtADQAMwAtADEAMABtAGUAZQBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAEYAQwAtADEAMgA1ACAAKABSAC0AMQAyADUAKQBcACIALAAgAFwAIgBDADIASABGADUAXAAiACwAIAAgADMAMQA3ADAALAAgAFwAIgBIAEYAQwAtADEAMgA1AFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgARgBDAC0AMQAzADQAIAAoAFIALQAxADMANAApAFwAIgAsACAAXAAiAEMAMgBIADIARgA0ACAAKABDAEgARgAyAEMASABGADIAKQBcACIALAAgACAAMQAxADIAMAAsACAAXAAiAEgARgBDAC0AMQAzADQAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABGAEMALQAxADMANABhACAAKABSAC0AMQAzADQAYQApAFwAIgAsACAAXAAiAEMAMgBIADIARgA0ACAAKABDAEgAMgBGAEMARgAzACkAXAAiACwAIAAxADMAMAAwACwAIABcACIASABGAEMALQAxADMANABhAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgARgBDAC0AMQA0ADMAIAAoAFIALQAxADQAMwApAFwAIgAsACAAXAAiAEMAMgBIADMARgAzACAAKABDAEgARgAyAEMASAAyAEYAKQBcACIALAAgADMAMgA4ACwAIABcACIASABGAEMALQAxADQAMwBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAEYAQwAtADEANAAzAGEAIAAoAFIALQAxADQAMwBhACkAXAAiACwAIABcACIAQwAyAEgAMwBGADMAIAAoAEMARgAzAEMASAAzACkAXAAiACwAIAA0ADgAMAAwACwAIABcACIASABGAEMALQAxADQAMwBhAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgARgBDAC0AMQA1ADIAYQAgACgAUgAtADEANQAyAGEAKQBcACIALAAgAFwAIgBDADIASAA0AEYAMgAgACgAQwBIADMAQwBIAEYAMgApAFwAIgAsACAAMQAzADgALAAgAFwAIgBIAEYAQwAtADEANQAyAGEAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABGAEMALQAyADIANwBlAGEAIAAoAFIALQAyADIANwBlAGEAKQBcACIALAAgAFwAIgBDADMASABGADcAXAAiACwAIAAzADMANQAwACwAIABcACIASABGAEMALQAyADIANwBlAGEAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABGAEMALQAyADMANgBmAGEAIAAoAFIALQAyADMANgBmAGEAKQBcACIALAAgAFwAIgBDADMASAAyAEYANgBcACIALAAgADgAMAA2ADAALAAgAFwAIgBIAEYAQwAtADIAMwA2AGYAYQBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAEYAQwAtADIANAA1AGMAYQAgACgAUgAtADIANAA1AGMAYQApAFwAIgAsACAAXAAiAEMAMwBIADMARgA1AFwAIgAsACAANwAxADYALAAgAFwAIgBIAEYAQwAtADIANAA1AGMAYQBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAEYAQwAtADIANAA1AGYAYQAgACgAUgAtADIANAA1AGYAYQApAFwAIgAsACAAXAAiAEMASABGADIAQwBIADIAQwBGADMAXAAiACwAIAA4ADUAOAAsACAAXAAiAEgARgBDAC0AMgA0ADUAZgBhAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgARgBDAC0AMwA2ADUAbQBmAGMAIAAoAFIALQAzADYANQBtAGYAYwApAFwAIgAsACAAXAAiAEMASAAzAEMARgAyAEMASAAyAEMARgAzAFwAIgAsACAAOAAwADQALAAgAFwAIgBIAEYAQwAtADMANgA1AG0AZgBjAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAQwBGAEMALQAyADIAIAAoAFIALQAyADIAKQBcACIALAAgAFwAIgBDAEgAQwBsAEYAMgBcACIALAAgADEANwA2ADAALAAgAFwAIgBIAEMARgBDAC0AMgAyAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAQwBGAEMALQAxADIAMwAgACgAUgAtADEAMgAzACkAXAAiACwAIABcACIAQwBIAEMAbAAyADIAQwBGADMAXAAiACwAIAA3ADkALAAgAFwAIgBIAEMARgBDAC0AMQAyADMAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABDAEYAQwAtADEAMgA0ACAAKABSAC0AMQAyADQAKQBcACIALAAgAFwAIgBDAEgAQwBsAEYAQwBGADMAXAAiACwAIAA1ADIANwAsACAAXAAiAEgAQwBGAEMALQAxADIANABcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAEMARgBDAC0AMQA0ADEAYgAgACgAUgAtADEANAAxAGIAKQBcACIALAAgAFwAIgBDAEgAMwBDAEMAbAAyAEYAXAAiACwAIAA3ADgAMgAsACAAXAAiAEgAQwBGAEMALQAxADQAMQBiAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAQwBGAEMALQAxADQAMgBiACAAKABSAC0AMQA0ADIAYgApAFwAIgAsACAAXAAiAEMASAAyAEMAQwBsAEYAMgBcACIALAAgADEAOQA4ADAALAAgAFwAIgBIAEMARgBDAC0AMQA0ADIAYgBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAEMARgBDAC0AMgAyADUAYwBhACAAKABSAC0AMgAyADUAYwBhACkAXAAiACwAIABcACIAQwBIAEMAbAAyAEMARgAyAEMARgAzAFwAIgAsACAAMQAyADcALAAgAFwAIgBIAEMARgBDAC0AMgAyADUAYwBhAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAQwBGAEMALQAyADIANQBjAGIAIAAoAFIALQAyADIANQBjAGIAKQBcACIALAAgAFwAIgBDAEgAQwBsAEYAQwBGADIAQwBDAEkARgAyAFwAIgAsACAANQAyADUALAAgAFwAIgBIAEMARgBDAC0AMgAyADUAYwBiAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFAARgBDAC0AMQA0ACAAUABlAHIAZgBsAHUAbwByAG8AbQBlAHQAaABhAG4AZQAgACgAdABlAHQAcgBhAGYAbAB1AG8AcgBvAG0AZQB0AGgAYQBuAGUAKQBcACIALAAgAFwAIgBDAEYANABcACIALAAgADYANgAzADAALAAgAFwAIgBQAEYAQwAtADEANABcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAEYAQwAtADEAMQA2ACAAUABlAHIAZgBsAHUAbwByAG8AZQB0AGgAYQBuAGUAIAAoAGgAZQB4AGEAZgBsAHUAbwByAG8AZQB0AGgAYQBuAGUAKQBcACIALAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAxADEAMAAwACwAIABcACIAUABGAEMALQAxADEANgBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAEYAQwAtADIAMQA4ACAAUABlAHIAZgBsAHUAbwByAG8AcAByAG8AcABhAG4AZQBcACIALAAgAFwAIgBDADMARgA4AFwAIgAsACAAOAA5ADAAMAAsACAAXAAiAFAARgBDAC0AMgAxADgAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUABGAEMALQAzADEALQAxADAAIABQAGUAcgBmAGwAdQBvAHIAbwBiAHUAdABhAG4AZQBcACIALAAgAFwAIgBDADQARgAxADAAXAAiACwAIAA5ADIAMAAwACwAIABcACIAUABGAEMALQAzADEALQAxADAAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUABGAEMALQAzADEAOAAgAFAAZQByAGYAbAB1AG8AcgBvAGMAeQBjAGwAbwBiAHUAdABhAG4AZQBcACIALAAgAFwAIgBjAC0AQwA0AEYAOABcACIALAAgADkANQA0ADAALAAgAFwAIgBQAEYAQwAtADMAMQA4AFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFAARgBDAC0ANAAxAC0AMQAyACAAUABlAHIAZgBsAHUAbwByAG8AcABlAG4AdABhAG4AZQBcACIALAAgAFwAIgBDADUARgAxADIAXAAiACwAIAA4ADUANQAwACwAIABcACIAUABGAEMALQA0ADEALQAxADIAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUABGAEMALQA1ADEALQAxADQAIABQAGUAcgBmAGwAdQBvAHIAbwBoAGUAeABhAG4AZQBcACIALAAgAFwAIgBDADYARgAxADQAXAAiACwAIAA3ADkAMQAwACwAIABcACIAUABGAEMALQA1ADEALQAxADQAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUABGAEMALQA5ADEALQAxADgAIABQAGUAcgBmAGwAdQBuAGEAZgBlAG4AZQBcACIALAAgAFwAIgBDADEAMABGADEAOABcACIALAAgADcAMQA5ADAALAAgAFwAIgBQAEYAQwAtADkAMQAtADEAOABcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAEYAQwAtADEAMgBcACIALAAgAFwAIgBDAEMAbAAyAEYAMgBcACIALAAgADEAMAAyADAAMAAsACAAXAAiAEMARgBDAC0AMQAyAFwAIgAsACAAXAAiAEkAUABDAEMAIABHAGwAbwBiAGEAbAAgAFcAYQByAG0AaQBuAGcAIABQAG8AdABlAG4AdABpAGEAbAAgAFYAYQBsAHUAZQBzACAAdgAyAC4AMAAgAC0AIAAoAEEAUgA1ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBGAEMALQAxADMAXAAiACwAIABcACIAQwBDAGwARgAzAFwAIgAsACAAMQAzADkAMAAwACwAIABcACIAQwBGAEMALQAxADMAXAAiACwAIABcACIASQBQAEMAQwAgAEcAbABvAGIAYQBsACAAVwBhAHIAbQBpAG4AZwAgAFAAbwB0AGUAbgB0AGkAYQBsACAAVgBhAGwAdQBlAHMAIAB2ADIALgAwACAALQAgACgAQQBSADUAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAEYAQwAtADEAMQA0AFwAIgAsACAAXAAiAEMAQwBsAEYAMgBDAEMAbABGADIAXAAiACwAIAA4ADUAOQAwACwAIABcACIAQwBGAEMALQAxADEANABcACIALAAgAFwAIgBJAFAAQwBDACAARwBsAG8AYgBhAGwAIABXAGEAcgBtAGkAbgBnACAAUABvAHQAZQBuAHQAaQBhAGwAIABWAGEAbAB1AGUAcwAgAHYAMgAuADAAIAAtACAAKABBAFIANQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMARgBDAC0AMQAxADUAXAAiACwAIABcACIAQwBDAGwARgAyAEMARgAzAFwAIgAsACAANwA2ADcAMAAsACAAXAAiAEMARgBDAC0AMQAxADUAXAAiACwAIABcACIASQBQAEMAQwAgAEcAbABvAGIAYQBsACAAVwBhAHIAbQBpAG4AZwAgAFAAbwB0AGUAbgB0AGkAYQBsACAAVgBhAGwAdQBlAHMAIAB2ADIALgAwACAALQAgACgAQQBSADUAKQBcACIAXABuACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AKQApACkAOwBcAG4AXABuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AQwBoAGUAbQBpAGMAYQBsAEcAVwBQAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcARwBBAFMAIAAtACAARgBDACAAbgBhAG0AZQBcAHUAMAAwADIANwAgAGMAbwBsAHUAbQBuACAAdwBpAHQAaAAgAHQAcgB1AG4AYwBhAHQAZQBkACAAZwBhAHMAIABuAGEAbQBlACAAdABvACAAYQBsAGwAbwB3ACAAbQBhAHQAYwBoAGkAbgBnACAAdwBpAHQAaAAgAG8AdABoAGUAcgAgAHQAYQBiAGwAZQBzAC4AIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABnAGEAcwBlAHMAIABmAHIAbwBtACAASQBQAEMAQwAgAEcAbABvAGIAYQBsACAAVwBhAHIAbQBpAG4AZwAgAFAAbwB0AGUAbgB0AGkAYQBsACAAVgBhAGwAdQBlAHMAIAB2ADIALgAwACAALQAgACgAQQBSADUAKQAuACAAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcAQQBkAGQAaQB0AGkAbwBuAGEAbAAgAGQAYQB0AGEAIABzAG8AdQByAGMAZQBcAHUAMAAwADIANwAgAGMAbwBsAHUAbQBuAC4AXAAiACkAKQA7AFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBBAHAAcABlAG4AZABpAHgAIAAyACAARwBsAG8AYgBhAGwAIABXAGEAcgBtAGkAbgBnACAAUABvAHQAZQBuAHQAaQBhAGwAcwA6ACAAQgBsAGUAbgBkAGUAZAAgAHIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABCAGwAZQBuAGQAcwBfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEIAbABlAG4AZABlAGQAIAByAGUAZgByAGkAZwBlAHIAYQBuAHQAcwAgACgAbQBhAG4AeQAgAGMAbwBuAHQAYQBpAG4AaQBuAGcAIABIAEYAQwBTACAAYQBuAGQALwBvAHIAIABQAEYAQwBTACkAXAAiACkAKQA7AFwAbgBcAG4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBDAGgAZQBtAGkAYwBhAGwAQgBsAGUAbgBkAHMAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABCAGwAZQBuAGQAcwBfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAE4AYQB0AGkAbwBuAGEAbAAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABBAGMAYwBvAHUAbgB0AHMAIABGAGEAYwB0AG8AcgBzACAAMgAwADIANQAgAC0AIABBAHAAcABlAG4AZABpAHgAIAAyACAALQAgAFQAYQBiAGwAZQAgADIANABcACIAKQApADsAXABuAFwAbgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABCAGwAZQBuAGQAcwBfAEQAYQB0AGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAxACwAIAAzACwAXABuACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEIAbABlAG4AZABcACIALAAgAFwAIgBDAG8AbgBzAHQAaQB0AHUAZQBuAHQAcwBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwBpAHQAaQBvAG4AIAAoACUAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAwADAAXAAiACwAIABcACIAQwBGAEMALQAxADIALwBDAEYAQwAtADEAMQA0AFwAIgAsACAAXAAiAFIALQA0ADAAMAAgAGMAYQBuACAAaABhAHYAZQAgAHYAYQByAGkAbwB1AHMAIABwAHIAbwBwAG8AcgB0AGkAbwBuAHMAIABvAGYAIABDAEYAQwAtADEAMgAgAGEAbgBkACAAQwBGAEMALQAxADEANAAuACAAVABoAGUAIABlAHgAYQBjAHQAIABjAG8AbQBwAG8AcwBpAHQAaQBvAG4AIABuAGUAZQBkAHMAIAB0AG8AIABiAGUAIABzAHAAZQBjAGkAZgBpAGUAZAAsACAAZQAuAGcALgAsACAAUgAtADQAMAAwACAAKAA2ADAALwA0ADAAKQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADAAMQBBAFwAIgAsACAAXAAiAEgAQwBGAEMALQAyADIALwBIAEYAQwAtADEANQAyAGEALwBIAEMARgBDAC0AMQAyADQAXAAiACwAIABcACIAKAA1ADMALgAwAC8AMQAzAC4AMAAvADMANAAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAwADEAQgBcACIALAAgAFwAIgBIAEMARgBDAC0AMgAyAC8ASABGAEMALQAxADUAMgBhAC8ASABDAEYAQwAtADEAMgA0AFwAIgAsACAAXAAiACgANgAxAC4AMAAvADEAMQAuADAALwAyADgALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMAAxAEMAXAAiACwAIABcACIASABDAEYAQwAtADIAMgAvAEgARgBDAC0AMQA1ADIAYQAvAEgAQwBGAEMALQAxADIANABcACIALAAgAFwAIgAoADMAMwAuADAALwAxADUALgAwAC8ANQAyAC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADAAMgBBAFwAIgAsACAAXAAiAEgARgBDAC0AMQAyADUALwBIAEMALQAyADkAMAAvAEgAQwBGAEMALQAyADIAXAAiACwAIABcACIAKAA2ADAALgAwAC8AMgAuADAALwAzADgALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMAAyAEIAXAAiACwAIABcACIASABGAEMALQAxADIANQAvAEgAQwAtADIAOQAwAC8ASABDAEYAQwAtADIAMgBcACIALAAgAFwAIgAoADMAOAAuADAALwAyAC4AMAAvADYAMAAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAwADMAQQBcACIALAAgAFwAIgBIAEMALQAyADkAMAAvAEgAQwBGAEMALQAyADIALwBQAEYAQwAtADIAMQA4AFwAIgAsACAAXAAiACgANQAuADAALwA3ADUALgAwAC8AMgAwAC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADAAMwBCAFwAIgAsACAAXAAiAEgAQwAtADIAOQAwAC8ASABDAEYAQwAtADIAMgAvAFAARgBDAC0AMgAxADgAXAAiACwAIABcACIAKAA1AC4AMAAvADUANgAuADAALwAzADkALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMAA0AEEAXAAiACwAIABcACIASABGAEMALQAxADIANQAvAEgARgBDAC0AMQA0ADMAYQAvAEgARgBDAC0AMQAzADQAYQBcACIALAAgAFwAIgAoADQANAAuADAALwA1ADIALgAwAC8ANAAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAwADUAQQBcACIALAAgAFwAIgBIAEMARgBDAC0AMgAyAC8AIABIAEYAQwAtADEANQAyAGEALwBIAEMARgBDAC0AMQA0ADIAYgAvAFAARgBDAC0AMwAxADgAXAAiACwAIABcACIAKAA0ADUALgAwAC8ANwAuADAALwA1AC4ANQAvADQAMgAuADUAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAwADYAQQBcACIALAAgAFwAIgBIAEMARgBDAC0AMgAyAC8ASABDAC0ANgAwADAAYQAvAEgAQwBGAEMALQAxADQAMgBiAFwAIgAsACAAXAAiACgANQA1AC4AMAAvADEANAAuADAALwA0ADEALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMAA3AEEAXAAiACwAIABcACIASABGAEMALQAzADIALwBIAEYAQwAtADEAMgA1AC8ASABGAEMALQAxADMANABhAFwAIgAsACAAXAAiACgAMgAwAC4AMAAvADQAMAAuADAALwA0ADAALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMAA3AEIAXAAiACwAIABcACIASABGAEMALQAzADIALwBIAEYAQwAtADEAMgA1AC8ASABGAEMALQAxADMANABhAFwAIgAsACAAXAAiACgAMQAwAC4AMAAvADcAMAAuADAALwAyADAALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMAA3AEMAXAAiACwAIABcACIASABGAEMALQAzADIALwBIAEYAQwAtADEAMgA1AC8ASABGAEMALQAxADMANABhAFwAIgAsACAAXAAiACgAMgAzAC4AMAAvADIANQAuADAALwA1ADIALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMAA3AEQAXAAiACwAIABcACIASABGAEMALQAzADIALwBIAEYAQwAtADEAMgA1AC8ASABGAEMALQAxADMANABhAFwAIgAsACAAXAAiACgAMQA1AC4AMAAvADEANQAuADAALwA3ADAALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMAA3AEUAXAAiACwAIABcACIASABGAEMALQAzADIALwBIAEYAQwAtADEAMgA1AC8ASABGAEMALQAxADMANABhAFwAIgAsACAAXAAiACgAMgA1AC4AMAAvADEANQAuADAALwA2ADAALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMAA4AEEAXAAiACwAIABcACIASABGAEMALQAxADIANQAvAEgARgBDAC0AMQA0ADMAYQAvAEgAQwBGAEMALQAyADIAXAAiACwAIABcACIAKAA3AC4AMAAvADQANgAuADAALwA0ADcALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMAA5AEEAXAAiACwAIABcACIASABDAEYAQwAtADIAMgAvAEgAQwBGAEMALQAxADIANAAvAEgAQwBGAEMALQAxADQAMgBiAFwAIgAsACAAXAAiACgANgAwAC4AMAAvADIANQAuADAALwAxADUALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMAA5AEIAXAAiACwAIABcACIASABDAEYAQwAtADIAMgAvAEgAQwBGAEMALQAxADIANAAvAEgAQwBGAEMALQAxADQAMgBiAFwAIgAsACAAXAAiACgANgA1AC4AMAAvADIANQAuADAALwAxADAALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMQAwAEEAXAAiACwAIABcACIASABGAEMALQAzADIALwBIAEYAQwAtADEAMgA1AFwAIgAsACAAXAAiACgANQAwAC4AMAAvADUAMAAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAxADAAQgBcACIALAAgAFwAIgBIAEYAQwAtADMAMgAvAEgARgBDAC0AMQAyADUAXAAiACwAIABcACIAKAA0ADUALgAwAC8ANQA1AC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADEAMQBBAFwAIgAsACAAXAAiAEgAQwAtADEAMgA3ADAALwBIAEMARgBDAC0AMgAyAC8ASABGAEMALQAxADUAMgBhAFwAIgAsACAAXAAiACgAMQAuADUALwA4ADcALgA1AC8AMQAxAC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADEAMQBCAFwAIgAsACAAXAAiAEgAQwAtADEAMgA3ADAALwBIAEMARgBDAC0AMgAyAC8ASABGAEMALQAxADUAMgBhAFwAIgAsACAAXAAiACgAMwAuADAALwA5ADQALgAwAC8AMwAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAxADEAQwBcACIALAAgAFwAIgBIAEMALQAxADIANwAwAC8ASABDAEYAQwAtADIAMgAvAEgARgBDAC0AMQA1ADIAYQBcACIALAAgAFwAIgAoADMALgAwAC8AOQA1AC4ANQAvADEALgA1ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMQAyAEEAXAAiACwAIABcACIASABDAEYAQwAtADIAMgAvAFAARgBDAC0AMgAxADgALwBIAEMARgBDAC0AMQA0ADIAYgBcACIALAAgAFwAIgAoADcAMAAuADAALwA1AC4AMAAvADIANQAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAxADMAQQBcACIALAAgAFwAIgBQAEYAQwAtADIAMQA4AC8ASABGAEMALQAxADMANABhAC8ASABDAC0ANgAwADAAYQBcACIALAAgAFwAIgAoADkALgAwAC8AOAA4AC4AMAAvADMALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMQA0AEEAXAAiACwAIABcACIASABDAEYAQwAtADIAMgAvAEgAQwBGAEMALQAxADIANAAvAEgAQwAtADYAMAAwAGEALwBIAEMARgBDAC0AMQA0ADIAYgBcACIALAAgAFwAIgAoADUAMQAuADAALwAyADgALgA1AC8ANAAuADAALwAxADYALgA1ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMQA0AEIAXAAiACwAIABcACIASABDAEYAQwAtADIAMgAvAEgAQwBGAEMALQAxADIANAAvAEgAQwAtADYAMAAwAGEALwBIAEMARgBDAC0AMQA0ADIAYgBcACIALAAgAFwAIgAoADUAMAAuADAALwAzADkALgAwAC8AMQAuADUALwA5AC4ANQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADEANQBBAFwAIgAsACAAXAAiAEgAQwBGAEMALQAyADIALwBIAEYAQwAtADEANQAyAGEAXAAiACwAIABcACIAKAA4ADIALgAwAC8AMQA4AC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADEANQBCAFwAIgAsACAAXAAiAEgAQwBGAEMALQAyADIALwBIAEYAQwAtADEANQAyAGEAXAAiACwAIABcACIAKAAyADUALgAwAC8ANwA1AC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADEANgBBAFwAIgAsACAAXAAiAEgARgBDAC0AMQAzADQAYQAvAEgAQwBGAEMALQAxADIANAAvAEgAQwAtADYAMAAwAFwAIgAsACAAXAAiACgANQA5AC4AMAAvADMAOQAuADUALwAxAC4ANQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADEANwBBAFwAIgAsACAAXAAiAEgARgBDAC0AMQAyADUALwBIAEYAQwAtADEAMwA0AGEALwBIAEMALQA2ADAAMABcACIALAAgAFwAIgAoADQANgAuADYALwA1ADAALgAwAC8AMwAuADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAxADgAQQBcACIALAAgAFwAIgBIAEMALQAyADkAMAAvAEgAQwBGAEMALQAyADIALwBIAEYAQwAtADEANQAyAGEAXAAiACwAIABcACIAKAAxAC4ANQAvADkANgAuADAALwAyAC4ANQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADEAOQBBAFwAIgAsACAAXAAiAEgARgBDAC0AMQAyADUALwBIAEYAQwAtADEAMwA0AGEALwBIAEUALQBFADEANwAwAFwAIgAsACAAXAAiACgANwA3AC4AMAAvADEAOQAuADAALwA0AC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADIAMABBAFwAIgAsACAAXAAiAEgARgBDAC0AMQAzADQAYQAvAEgAQwBGAEMALQAxADQAMgBiAFwAIgAsACAAXAAiACgAOAA4AC4AMAAvADEAMgAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAyADEAQQBcACIALAAgAFwAIgBIAEYAQwAtADEAMgA1AC8ASABGAEMALQAxADMANABhAFwAIgAsACAAXAAiACgANQA4AC4AMAAvADQAMgAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAyADIAQQBcACIALAAgAFwAIgBIAEYAQwAtADEAMgA1AC8ASABGAEMALQAxADMANABhAC8ASABDAC0ANgAwADAAYQBcACIALAAgAFwAIgAoADgANQAuADEALwAxADEALgA1AC8AMwAuADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAyADIAQgBcACIALAAgAFwAIgBIAEYAQwAtADEAMgA1AC8ASABGAEMALQAxADMANABhAC8ASABDAC0ANgAwADAAYQBcACIALAAgAFwAIgAoADUANQAuADAALwA0ADIALgAwAC8AMwAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAyADIAQwBcACIALAAgAFwAIgBIAEYAQwAtADEAMgA1AC8ASABGAEMALQAxADMANABhAC8ASABDAC0ANgAwADAAYQBcACIALAAgAFwAIgAoADgAMgAuADAALwAxADUALgAwAC8AMwAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANQAwADAAXAAiACwAIABcACIAQwBGAEMALQAxADIALwBIAEYAQwAtADEANQAyAGEAXAAiACwAIABcACIAKAA3ADMALgA4AC8AMgA2AC4AMgApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA1ADAAMQBcACIALAAgAFwAIgBIAEMARgBDAC0AMgAyAC8AQwBGAEMALQAxADIAXAAiACwAIABcACIAKAA3ADUALgAwAC8AMgA1AC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA1ADAAMgBcACIALAAgAFwAIgBIAEMARgBDAC0AMgAyAC8AQwBGAEMALQAxADEANQBcACIALAAgAFwAIgAoADQAOAAuADgALwA1ADEALgAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADUAMAAzAFwAIgAsACAAXAAiAEgARgBDAC0AMgAzAC8AQwBGAEMALQAxADMAXAAiACwAIABcACIAKAA0ADAALgAxAC8ANQA5AC4AOQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA1ADAANABcACIALAAgAFwAIgBIAEYAQwAtADMAMgAvAEMARgBDAC0AMQAxADUAXAAiACwAIABcACIAKAA0ADgALgAyAC8ANQAxAC4AOAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA1ADAANQBcACIALAAgAFwAIgBDAEYAQwAtADEAMgAvAEgAQwBGAEMALQAzADEAXAAiACwAIABcACIAKAA3ADgALgAwAC8AMgAyAC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA1ADAANgBcACIALAAgAFwAIgBDAEYAQwAtADMAMQAvAEMARgBDAC0AMQAxADQAXAAiACwAIABcACIAKAA1ADUALgAxAC8ANAA0AC4AOQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA1ADAANwBBAFwAIgAsACAAXAAiAEgARgBDAC0AMQAyADUALwBIAEYAQwAtADEANAAzAGEAXAAiACwAIABcACIAKAA1ADAALgAwAC8ANQAwAC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA1ADAAOABBAFwAIgAsACAAXAAiAEgARgBDAC0AMgAzAC8AUABGAEMALQAxADEANgBcACIALAAgAFwAIgAoADMAOQAuADAALwA2ADEALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADUAMAA4AEIAXAAiACwAIABcACIASABGAEMALQAyADMALwBQAEYAQwAtADEAMQA2AFwAIgAsACAAXAAiACgANAA2AC4AMAAvADUANAAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANQAwADkAQQBcACIALAAgAFwAIgBIAEMARgBDAC0AMgAyAC8AUABGAEMALQAyADEAOABcACIALAAgAFwAIgAoADQANAAuADAALwA1ADYALgAwACkAXAAiAFwAbgAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACkAKQApADsAXABuAFwAbgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABCAGwAZQBuAGQAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAYwBoAGEAbgBnAGUAZAAgAEgAQwA2ADAAMABhACAAdABvACAASABDAC0ANgAwADAAYQAgAGYAbwByACAAYgBsAGUAbgBkACAAUgAtADQAMQA0AEIALgAgAEYAaQB4AGUAZAAgAHQAeQBwAG8AIABmAG8AcgAgAGIAbABlAG4AZAAgAFIALQA0ADAANQBBACAALQAgAEMAaABhAG4AZwBlAGQAIABIAEMARgBDADEANAAyAGIAIAB0AG8AIABIAEMARgBDAC0AMQA0ADIAYgAuAFwAIgApACkAOwBcAG4AXABuAFwAbgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAEwAZQBhAGsAYQBnAGUAIAByAGEAdABlAHMAIABmAG8AcgAgAGMAbwBtAG0AbwBuACAAcgBlAGYAcgBpAGcAZQByAGEAdABpAG8AbgAgAGEAbgBkACAAYQBpAHIAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ATABlAGEAawBhAGcAZQBSAGEAdABlAHMAXwBUAGkAdABsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBJAG4AZABpAGMAYQB0AGkAdgBlACAAbABlAGEAawBhAGcAZQAgAHIAYQB0AGUAcwAgAGYAbwByACAAYwBvAG0AbQBvAG4AIAByAGUAZgByAGkAZwBlAHIAYQB0AGkAbwBuACAAYQBuAGQAIABhAGkAcgAgAC0AIABjAG8AbgBkAGkAdABpAG8AbgBpAG4AZwAgAGUAcQB1AGkAcABtAGUAbgB0AFwAIgApACkAOwBcAG4AXABuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ATABlAGEAawBhAGcAZQBSAGEAdABlAHMAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEwAZQBhAGsAYQBnAGUAUgBhAHQAZQBzAF8AUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAEEAYwBjAG8AdQBuAHQAcwAgAEYAYQBjAHQAbwByAHMAIAAyADAAMgA1ACAALQAgAFQAYQBiAGwAZQAgADEAMABcACIAKQApADsAXABuAFwAbgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEwAZQBhAGsAYQBnAGUAUgBhAHQAZQBzAF8ARABhAHQAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA4ADEALAAgADIALABcAG4AIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIABcACIAUAByAG8AZAB1AGMAdABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAGwAZQBhAGsAYQBnAGUAIAByAGEAdABlACAAKAAlACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIARABvAG0AZQBzAHQAaQBjACAAcgBlAGYAcgBpAGcAZQByAGEAdABvAHIAcwBcACIALAAgADEALgA3ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVAByAGEAbgBzAHAAbwByAHQAIAByAGUAZgByAGkAZwBlAHIAYQB0AGkAbwBuAFwAIgAsACAAMQA1AC4ANwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEQAbwBtAGUAcwB0AGkAYwAgAEEALwBDACAAcABvAHIAdABhAGIAbABlAFwAIgAsACAAMgAuADUAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBEAG8AbQBlAHMAdABpAGMAIABBAC8AQwAgAHMAcABsAGkAdABcACIALAAgADMALgA1ADsAXABuACAAIAAgACAAIAAgACAAIABcACIARABvAG0AZQBzAHQAaQBjACAAQQAvAEMAIABwAGEAYwBrAGEAZwBlAGQAXAAiACwAIAAyAC4ANQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEwAaQBnAGgAdAAgAHYAZQBoAGkAYwBsAGUAIABBAC8AQwBcACIALAAgADYALgA3ADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABlAGEAdgB5ACAAdgBlAGgAaQBjAGwAZQAgAEEALwBDAFwAIgAsACAAMQAwAC4AOABcAG4AIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgApACkAKQA7AFwAbgBcAG4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBMAGUAYQBrAGEAZwBlAFIAYQB0AGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAiACwAIgB0AGUAeAB0ACIAOgAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AQwBhAGwAYwB1AGwAYQB0AGUAQgBsAGUAbgBkAEcAVwBQAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARgBhAGMAdABpAG8AbgAxACwAIABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARwBXAFAAMQAsACAAXABuACAAIABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARgBhAGMAdABpAG8AbgAyACwAIABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARwBXAFAAMgAsACAAXABuACAAIABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARgBhAGMAdABpAG8AbgAzACwAIABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARwBXAFAAMwAsACAAXABuACAAIABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARgBhAGMAdABpAG8AbgA0ACwAIABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARwBXAFAANAAsAFwAbgAgACAAKABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARgBhAGMAdABpAG8AbgAxACAAKgAgAEMAbwBuAHMAdABpAHQAdQBlAG4AdABHAFcAUAAxACkAIAArAFwAbgAgACAAKABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARgBhAGMAdABpAG8AbgAyACAAKgAgAEMAbwBuAHMAdABpAHQAdQBlAG4AdABHAFcAUAAyACkAIAArAFwAbgAgACAAKABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARgBhAGMAdABpAG8AbgAzACAAKgAgAEMAbwBuAHMAdABpAHQAdQBlAG4AdABHAFcAUAAzACkAIAArAFwAbgAgACAAKABDAG8AbgBzAHQAaQB0AHUAZQBuAHQARgBhAGMAdABpAG8AbgA0ACAAKgAgAEMAbwBuAHMAdABpAHQAdQBlAG4AdABHAFcAUAA0ACkAXABuACkAOwAiAH0AXQAsACIAcAByAG8AagBlAGMAdABOAGEAbQBlAHMAIgA6AFsAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AQQBwAHAAZQBuAGQAaQBjAGUAcwAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAcgBhAHkASQBuAFQAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBUAHcAbwBDAG8AbAB1AG0AbgBzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE8AbgBlAEMAbwBsAHUAbQBuAEEAbgBkAEgAZQBhAGQAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABDAGwAaQBtAGEAdABlAFoAbwBuAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBQAGUAcgBpAG8AZABzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEcAZQB0AEYAcgBhAGMAVwBFAFQAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADEARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8AVABpAHQAbABlACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBTAG8AdQByAGMAZQAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBEAGEAdABhACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAFQAaQB0AGwAZQAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8AUwBvAHUAcgBjAGUAIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8ARABhAHQAYQAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBBAHAAcABlAG4AZABpAGMAZQBzACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkATABpAHEAdQBpAGQAXwBUAGkAdABsAGUAIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBMAGkAcQB1AGkAZABfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEwAaQBxAHUAaQBkAF8AUwBvAHUAcgBjAGUAIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBMAGkAcQB1AGkAZABfAEQAYQB0AGEAIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBMAGkAcQB1AGkAZABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AF8AVABpAHQAbABlACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AF8ARABlAHMAYwByAGkAcAB0AGkAbwBuACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AF8AUwBvAHUAcgBjAGUAIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAVAByAGEAbgBzAHAAbwByAHQAXwBEAGEAdABhACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAVAByAGEAbgBzAHAAbwByAHQATwBmAGYAUgBvAGEAZABfAFQAaQB0AGwAZQAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBUAHIAYQBuAHMAcABvAHIAdABPAGYAZgBSAG8AYQBkAF8ARABlAHMAYwByAGkAcAB0AGkAbwBuACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AE8AZgBmAFIAbwBhAGQAXwBTAG8AdQByAGMAZQAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBUAHIAYQBuAHMAcABvAHIAdABPAGYAZgBSAG8AYQBkAF8ARABhAHQAYQAiACwAIgBGAHUAZQBsAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4ARgB1AGUAbABfAEcAZQB0AFQAcgBhAG4AcwBwAG8AcgB0AEYAdQBlAGwAUwB0AHIAaQBuAGcAIgAsACIARgB1AGUAbABfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEYAdQBlAGwAXwBHAGUAdABTAHQAYQB0AGkAbwBuAGEAcgB5AEYAdQBlAGwAUwB0AHIAaQBuAGcAIgAsACIARgB1AGUAbABfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEYAdQBlAGwAXwBUAG8AdABhAGwAQwBvAG4AcwB1AG0AcAB0AGkAbwBuACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfADEAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBUAHIAYQBuAHMAcABvAHIAdAAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AMQBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFQAcgBhAG4AcwBwAG8AcgB0AF8AVABpAHQAbABlACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwAxAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AVAByAGEAbgBzAHAAbwByAHQAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfADEAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBUAHIAYQBuAHMAcABvAHIAdABfAFUAbgBpAHQAIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfADEAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBUAHIAYQBuAHMAcABvAHIAdABfAFMAbwB1AHIAYwBlACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwAxAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AVAByAGEAbgBzAHAAbwByAHQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AMQBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFQAcgBhAG4AcwBwAG8AcgB0AF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AMQBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFQAcgBhAG4AcwBwAG8AcgB0AF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfADIAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBTAHQAYQB0AGkAbwBuAGEAcgB5ACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwAyAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AUwB0AGEAdABpAG8AbgBhAHIAeQBfAFQAaQB0AGwAZQAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AMgBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFMAdABhAHQAaQBvAG4AYQByAHkAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfADIAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBTAHQAYQB0AGkAbwBuAGEAcgB5AF8AVQBuAGkAdAAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AMgBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFMAdABhAHQAaQBvAG4AYQByAHkAXwBTAG8AdQByAGMAZQAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AMgBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFMAdABhAHQAaQBvAG4AYQByAHkAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AMgBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFMAdABhAHQAaQBvAG4AYQByAHkAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwAyAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AUwB0AGEAdABpAG8AbgBhAHIAeQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwBYAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAEcAZQBuAGUAcgBpAGMAIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfAFgAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4ARwBlAG4AZQByAGkAYwBfAFQAaQB0AGwAZQAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AWABfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBHAGUAbgBlAHIAaQBjAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwBYAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAEcAZQBuAGUAcgBpAGMAXwBVAG4AaQB0ACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwBYAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAEcAZQBuAGUAcgBpAGMAXwBTAG8AdQByAGMAZQAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AWABfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBHAGUAbgBlAHIAaQBjAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfAFgAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4ARwBlAG4AZQByAGkAYwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfAFgAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4ARwBlAG4AZQByAGkAYwBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwBYAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAEcAZQBuAGUAcgBpAGMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAEcAVwBQACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBfAFQAaQB0AGwAZQAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcARwBXAFAAXwBUAGkAdABsAGUAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBHAFcAUABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAXwBVAG4AaQB0ACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBHAFcAUABfAFUAbgBpAHQAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAF8AUwBvAHUAcgBjAGUAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAEcAVwBQAF8AUwBvAHUAcgBjAGUAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAF8AUgBlAGEAZABhAGIAbABlAEUAcQB1AGEAdABpAG8AbgAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBHAFcAUABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAEcAVwBQAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBDAGgAZQBtAGkAYwBhAGwARwBXAFAAXwBUAGkAdABsAGUAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBDAGgAZQBtAGkAYwBhAGwARwBXAFAAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBDAGgAZQBtAGkAYwBhAGwARwBXAFAAXwBTAG8AdQByAGMAZQAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABHAFcAUABfAEQAYQB0AGEAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBDAGgAZQBtAGkAYwBhAGwARwBXAFAAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABCAGwAZQBuAGQAcwBfAFQAaQB0AGwAZQAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABCAGwAZQBuAGQAcwBfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABCAGwAZQBuAGQAcwBfAFMAbwB1AHIAYwBlACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AQwBoAGUAbQBpAGMAYQBsAEIAbABlAG4AZABzAF8ARABhAHQAYQAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABCAGwAZQBuAGQAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ATABlAGEAawBhAGcAZQBSAGEAdABlAHMAXwBUAGkAdABsAGUAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBMAGUAYQBrAGEAZwBlAFIAYQB0AGUAcwBfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEwAZQBhAGsAYQBnAGUAUgBhAHQAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBMAGUAYQBrAGEAZwBlAFIAYQB0AGUAcwBfAEQAYQB0AGEAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBMAGUAYQBrAGEAZwBlAFIAYQB0AGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBDAGEAbABjAHUAbABhAHQAZQBCAGwAZQBuAGQARwBXAFAAIgBdACwAIgBsAG8AYwBhAGwAZQAiADoAewAiAGwAaQBzAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgByAG8AdwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGMAbwBsAHUAbQBuAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBQAG8AcwBpAHQAaQBvAG4AcwAiADoAWwAzAF0ALAAiAGQAZQBjAGkAbQBhAGwAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALgAiACwAIgBkAGEAdABlAE8AcgBkAGUAcgAiADoAIgBEAE0AWQAiACwAIgBjAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwAIgA6ACIAJAAiACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsAEwAZQBhAGQAIgA6AHQAcgB1AGUALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwBlAHAAQgB5AFMAcABhAGMAZQAiADoAZgBhAGwAcwBlACwAIgByAG8AdwBMAGUAdAB0AGUAcgAiADoAIgBSACIALAAiAGMAbwBsAHUAbQBuAEwAZQB0AHQAZQByACIAOgAiAEMAIgAsACIAcgBjAEwAZQBmAHQAQgByAGEAYwBrAGUAdAAiADoAIgBbACIALAAiAHIAYwBSAGkAZwBoAHQAQgByAGEAYwBrAGUAdAAiADoAIgBdACIALAAiAHMAdABhAHQAZQBtAGUAbgB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAbABvAGMAYQBsAGUATgBhAG0AZQAiADoAIgBlAG4ALQB1AHMAIgB9AH0A</AFEJSONBlob>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
@@ -19315,12 +19339,9 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="09eef6d6-daa8-4301-8f9f-b1ec38079286"/>
-    <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -19334,9 +19355,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="09eef6d6-daa8-4301-8f9f-b1ec38079286"/>
+    <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/Excel/9_Refrigerants_WIP_v02.prename.bak.xlsx
+++ b/Excel/9_Refrigerants_WIP_v02.prename.bak.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\htdocs\zneagcrc\GAF-VEERG-Functions\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0B48590-F211-4EB9-A343-7920FFF4B11B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E787B43-AC50-4147-8588-40D691D1FDC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="2340" windowWidth="28800" windowHeight="15345" firstSheet="2" activeTab="6" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
+    <workbookView xWindow="1350" yWindow="360" windowWidth="36255" windowHeight="19140" firstSheet="2" activeTab="6" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
   </bookViews>
   <sheets>
     <sheet name="Home" sheetId="71" r:id="rId1"/>
@@ -21,9 +21,6 @@
     <sheet name="Constants - Refrigerants" sheetId="110" r:id="rId6"/>
     <sheet name="Constants - Common" sheetId="120" r:id="rId7"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId8"/>
-  </externalReferences>
   <definedNames>
     <definedName name="Common_Equations.Common_ConvertCH4ToCO2e">_xlfn.LAMBDA(_xlpm.E_CH4,_xlpm.GWP_CH4, _xlpm.E_CH4 * _xlpm.GWP_CH4)</definedName>
     <definedName name="Common_Equations.Common_ConvertCH4ToCO2e_Arguments">_xlfn.LAMBDA(_xlfn.MAKEARRAY(2, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"ECH4","Methane emissions (t CH4)";"GWPCH4","Global warming potential for methane (t CO2-e / t CH4)"}, _xlpm.r, _xlpm.c))))</definedName>
@@ -39,7 +36,17 @@
     <definedName name="Common_Equations.Common_ConvertN2OToCO2e_Title">_xlfn.LAMBDA("Convert nitrous oxide emissions to carbon dioxide equivalent emissions")</definedName>
     <definedName name="Common_Equations.Common_ConvertN2OToCO2e_Unit">_xlfn.LAMBDA("t CO2e")</definedName>
     <definedName name="Common_Equations.Common_ConvertN2OToCO2e_Variable">_xlfn.LAMBDA("EN2O CO2e")</definedName>
-    <definedName name="Common_InputFunctions.Common_GetMCFTemperatureZone">_xlfn.LAMBDA(_xlpm.Temperature,_xlpm.MMS,_xlpm.TemperatureArray,_xlpm.MMSArray,_xlpm.ReturnArray, _xlfn.XLOOKUP(MEDIAN(_xlpm.Temperature, MIN(_xlpm.TemperatureArray), MAX(_xlpm.TemperatureArray)), _xlpm.TemperatureArray, _xlfn.XLOOKUP(_xlpm.MMS, _xlpm.MMSArray, _xlpm.ReturnArray)))</definedName>
+    <definedName name="Common_InputFunctions.Common_GetMCFTemperatureZone">_xlfn.LAMBDA(_xlpm.Temperature,_xlpm.MMS,_xlpm.TemperatureArray,_xlpm.MMSArray,_xlpm.ReturnArray,
+    _xlfn.XLOOKUP(
+        MEDIAN(
+            ROUND(_xlpm.Temperature, 0),
+            MIN(_xlpm.TemperatureArray),
+            MAX(_xlpm.TemperatureArray)
+        ),
+        _xlpm.TemperatureArray,
+        _xlfn.XLOOKUP(_xlpm.MMS, _xlpm.MMSArray, _xlpm.ReturnArray)
+    )
+)</definedName>
     <definedName name="Common_InputFunctions.CommonCropping_GetFracWET">_xlfn.LAMBDA(_xlpm.LeachingZone,_xlpm.ProductionSystem,_xlpm.LeachingZoneLookup,_xlpm.LeachingZoneFracWETLookup,_xlpm.ProductionSystemLookup,_xlpm.ProductionSystemFracWETLookup, _xlfn.LET(_xlpm.LeachingZoneFracWET, Common_InputFunctions.Utility_LookupValueInTableNumber(_xlpm.LeachingZone, _xlpm.LeachingZoneLookup, _xlpm.LeachingZoneFracWETLookup), _xlpm.ProductionSystemFracWET, Common_InputFunctions.Utility_LookupValueInTableNumber(_xlpm.ProductionSystem, _xlpm.ProductionSystemLookup, _xlpm.ProductionSystemFracWETLookup), IF(_xlpm.LeachingZoneFracWET + _xlpm.ProductionSystemFracWET &gt; 0, 1, 0)))</definedName>
     <definedName name="Common_InputFunctions.getOverlappingReportingCycles">_xlfn.LAMBDA(_xlpm.ProductionCycleStart,_xlpm.ProductionCycleEnd,_xlpm.ReportingCycleStart, _xlfn.LET(_xlpm.S, _xlpm.ProductionCycleStart, _xlpm.E, _xlpm.ProductionCycleEnd, _xlpm.m, MONTH(_xlpm.ReportingCycleStart), _xlpm.d, DAY(_xlpm.ReportingCycleStart), _xlpm.PeriodEnd, _xlfn.LAMBDA(_xlpm.st, EDATE(_xlpm.st, 12) - 1), _xlpm.A, _xlpm.S - 365, _xlpm.ya, YEAR(_xlpm.A), _xlpm.yb, YEAR(_xlpm.E), _xlpm.firstYear, _xlpm.ya + (_xlpm.PeriodEnd(DATE(_xlpm.ya, _xlpm.m, _xlpm.d)) &lt; _xlpm.S), _xlpm.lastYear, _xlpm.yb - (DATE(_xlpm.yb, _xlpm.m, _xlpm.d) &gt; _xlpm.E), MAX(0, _xlpm.lastYear - _xlpm.firstYear + 1)))</definedName>
     <definedName name="Common_InputFunctions.getOverlappingReportingPeriods">_xlfn.LAMBDA(_xlpm.ProductionCycleStart,_xlpm.ProductionCycleEnd,_xlpm.ReportingCycleStart, _xlfn.LET(_xlpm.S, _xlpm.ProductionCycleStart, _xlpm.E, _xlpm.ProductionCycleEnd, _xlpm.m, MONTH(_xlpm.ReportingCycleStart), _xlpm.d, DAY(_xlpm.ReportingCycleStart), _xlpm.PeriodEnd, _xlfn.LAMBDA(_xlpm.st, EDATE(_xlpm.st, 12) - 1), _xlpm.A, _xlpm.S - 365, _xlpm.ya, YEAR(_xlpm.A), _xlpm.yb, YEAR(_xlpm.E), _xlpm.firstYear, _xlpm.ya + (_xlpm.PeriodEnd(DATE(_xlpm.ya, _xlpm.m, _xlpm.d)) &lt; _xlpm.S), _xlpm.lastYear, _xlpm.yb - (DATE(_xlpm.yb, _xlpm.m, _xlpm.d) &gt; _xlpm.E), _xlpm.n, MAX(0, _xlpm.lastYear - _xlpm.firstYear + 1), _xlpm.yrs, _xlfn.SEQUENCE(_xlpm.n, 1, _xlpm.firstYear, 1), _xlpm.starts, DATE(_xlpm.yrs, _xlpm.m, _xlpm.d), _xlpm.ends, _xlfn.MAP(_xlpm.starts, _xlpm.PeriodEnd), _xlpm.tag, IF(_xlpm.starts = _xlpm.ReportingCycleStart, " (This reporting cycle)", ""), _xlpm.startsText, TEXT(_xlpm.starts, "dd mmm yyyy"), _xlpm.endsText, TEXT(_xlpm.ends, "dd mmm yyyy"), IF(_xlpm.n = 0, "", _xlfn.HSTACK(_xlpm.startsText &amp; " to " &amp; _xlpm.endsText &amp; _xlpm.tag))))</definedName>
@@ -55,9 +62,28 @@
     <definedName name="Common_InputFunctions.Utility_LookupN2OEFFromProdIrrigationRainfall">_xlfn.LAMBDA(_xlpm.ProductionSystem,_xlpm.IrrigationMethod,_xlpm.RainfallZone,_xlpm.ProductionSystemArray,_xlpm.IrrigationMethodArray,_xlpm.RainfallZoneArray,_xlpm.ReturnArray, _xlfn.LET(_xlpm.IrrigationMethod, IF(_xlpm.IrrigationMethod = "Not irrigated", "Not irrigated", "Any"), _xlpm.RainfallZone, IF(_xlpm.IrrigationMethod = "Not irrigated", _xlpm.RainfallZone, "Any"), _xlfn.XLOOKUP(1, (_xlpm.ProductionSystemArray = _xlpm.ProductionSystem) * (_xlpm.IrrigationMethodArray = _xlpm.IrrigationMethod) * (_xlpm.RainfallZoneArray = _xlpm.RainfallZone), _xlpm.ReturnArray)))</definedName>
     <definedName name="Common_InputFunctions.Utility_LookupValueInTable">_xlfn.LAMBDA(_xlpm.LookupValue,_xlpm.LookupArray,_xlpm.ReturnArray, _xlfn.XLOOKUP(_xlpm.LookupValue, _xlpm.LookupArray, _xlpm.ReturnArray, ""))</definedName>
     <definedName name="Common_InputFunctions.Utility_LookupValueInTableNumber">_xlfn.LAMBDA(_xlpm.LookupValue,_xlpm.LookupArray,_xlpm.ReturnArray, IF(ISNUMBER(_xlfn.XLOOKUP(_xlpm.LookupValue, _xlpm.LookupArray, _xlpm.ReturnArray, "")), _xlfn.XLOOKUP(_xlpm.LookupValue, _xlpm.LookupArray, _xlpm.ReturnArray, ""), 0))</definedName>
-    <definedName name="Common_InputFunctions.Utility_LookupValueInTableOneColumnAndHeader">_xlfn.LAMBDA(_xlpm.LookupValue1,_xlpm.LookupValue2,_xlpm.LookupArray1,_xlpm.LookupArray2,_xlpm.ReturnArray, _xlfn.XLOOKUP(_xlpm.LookupValue1, _xlpm.LookupArray1, _xlfn.XLOOKUP(_xlpm.LookupValue2, _xlpm.LookupArray2, _xlpm.ReturnArray)))</definedName>
-    <definedName name="Common_InputFunctions.Utility_LookupValueInTableTwoColumns">_xlfn.LAMBDA(_xlpm.LookupValue1,_xlpm.LookupValue2,_xlpm.LookupArray1,_xlpm.LookupArray2,_xlpm.ReturnArray, _xlfn.XLOOKUP(1, (_xlpm.LookupArray1 = _xlpm.LookupValue1) * (_xlpm.LookupArray2 = _xlpm.LookupValue2), _xlpm.ReturnArray, ""))</definedName>
+    <definedName name="Common_InputFunctions.Utility_LookupValueInTableOneColumnAndHeader">_xlfn.LAMBDA(_xlpm.LookupValue1,_xlpm.LookupValue2,_xlpm.LookupArray1,_xlpm.LookupArray2,_xlpm.ReturnArray,_xlop.ValueIfFalse,
+    IFERROR(
+        _xlfn.XLOOKUP(_xlpm.LookupValue1, _xlpm.LookupArray1,
+            _xlfn.XLOOKUP(_xlpm.LookupValue2, _xlpm.LookupArray2, _xlpm.ReturnArray)
+        ),
+        IF(_xlfn.ISOMITTED(_xlpm.ValueIfFalse), "", _xlpm.ValueIfFalse)
+    )
+)</definedName>
+    <definedName name="Common_InputFunctions.Utility_LookupValueInTableTwoColumns">_xlfn.LAMBDA(_xlpm.LookupValue1,_xlpm.LookupValue2,_xlpm.LookupArray1,_xlpm.LookupArray2,_xlpm.ReturnArray,_xlop.ValueIFFalse,
+    _xlfn.XLOOKUP(1, (_xlpm.LookupArray1=_xlpm.LookupValue1)*(_xlpm.LookupArray2=_xlpm.LookupValue2), _xlpm.ReturnArray, IF(_xlfn.ISOMITTED(_xlpm.ValueIFFalse), "", _xlpm.ValueIFFalse))
+)</definedName>
+    <definedName name="Common_InputFunctions.Utility_ResultsItemFromEquationTitleAndSource">_xlfn.LAMBDA(_xlpm.TitleCell,_xlpm.SourceCell,
+    SUBSTITUTE(LEFT(_xlpm.SourceCell, FIND(",", _xlpm.SourceCell) -1), "VEERG 2026: ", "") &amp; " " &amp; _xlpm.TitleCell
+)</definedName>
     <definedName name="Common_InputFunctions.Utility_SourceHyperlink">_xlfn.LAMBDA(_xlpm.TargetCell, _xlfn.LET(_xlpm.sh, _xlfn.TEXTAFTER(CELL("filename", _xlpm.TargetCell), "]"), _xlpm.addr, CELL("address", _xlpm.TargetCell), "#'" &amp; _xlpm.sh &amp; "'!" &amp; _xlpm.addr))</definedName>
+    <definedName name="Common_InputFunctions.Utility_SourceHyperlinkDifferentSheet">_xlfn.LAMBDA(_xlpm.TargetCell,
+  _xlfn.LET(
+    _xlpm.sh, _xlfn.TEXTAFTER(CELL("filename", _xlpm.TargetCell), "]"),
+    _xlpm.addr, CELL("address", _xlpm.TargetCell),
+    "#" &amp; _xlpm.addr
+  )
+)</definedName>
     <definedName name="Common_InputFunctions.Utility_SplitStringIntoArray">_xlfn.LAMBDA(_xlpm.Cell,_xlpm.Delimiter,_xlop.CharacterToRemove1,_xlop.CharacterToRemove2, _xlfn.FILTERXML("&lt;t&gt;&lt;s&gt;" &amp; SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.Cell, _xlpm.CharacterToRemove1, ""), _xlpm.CharacterToRemove2, ""), _xlpm.Delimiter, "&lt;/s&gt;&lt;s&gt;") &amp; "&lt;/s&gt;&lt;/t&gt;", "//s"))</definedName>
     <definedName name="Common_InputFunctions.Utility_SumQuantityFromCriteria">_xlfn.LAMBDA(_xlpm.Criteria1,_xlpm.Criteria1TypeArray,_xlpm.Quantity,_xlop.Multiplier,_xlop.Criteria2,_xlop.Criteria2Array, _xlfn.LET(_xlpm.multiplier, IF(_xlfn.ISOMITTED(_xlpm.Multiplier), 1, _xlpm.Multiplier), _xlpm.quantity, _xlpm.Quantity * _xlpm.multiplier, _xlpm.criteria1, --(_xlpm.Criteria1TypeArray = _xlpm.Criteria1), _xlpm.criteria2, IF(_xlfn.ISOMITTED(_xlpm.Criteria2), 1, --(_xlpm.Criteria2Array = _xlpm.Criteria2)), SUMPRODUCT(_xlpm.criteria1 * _xlpm.criteria2 * _xlpm.quantity)))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(9, 3, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"State/Territory","Common Name","Abbreviation";"New South Wales","New South Wales","NSW";"Australian Capital Territory","ACT","ACT";"Victoria","Victoria","VIC";"Queensland","Queensland","QLD";"South Australia","South Australia","SA";"Western Australia","Western Australia","WA";"Tasmania","Tasmania","TAS";"Northern Territory","Northern Territory","NT"}, _xlpm.r, _xlpm.c))))</definedName>
@@ -241,30 +267,52 @@
     <definedName name="Fuel_Equations.VEERG_8_X_FuelCombustionGeneric_Unit">_xlfn.LAMBDA("t CO2-e")</definedName>
     <definedName name="Fuel_Equations.VEERG_8_X_FuelCombustionGeneric_Variable">_xlfn.LAMBDA("E_g")</definedName>
     <definedName name="Fuel_Equations.VEERG_8_X_FuelCombustionGeneric_Variation">_xlfn.LAMBDA("VARIATION ON SOURCE: This calculation uses averages of transport and stationary emission factors for fuel combustion where the usage is not known.")</definedName>
-    <definedName name="Fuel_InputFunctions.Fuel_GetStationaryFuelString">_xlfn.LAMBDA(_xlpm.Cell, RIGHT(_xlpm.Cell, LEN(_xlpm.Cell) - FIND(", ", _xlpm.Cell) - 1))</definedName>
+    <definedName name="Fuel_InputFunctions.Fuel_GetStationaryFuelString">_xlfn.LAMBDA(_xlpm.Cell,
+    RIGHT(_xlpm.Cell,LEN(_xlpm.Cell)-FIND(", ",_xlpm.Cell))
+)</definedName>
     <definedName name="Fuel_InputFunctions.Fuel_GetTransportFuelString">_xlfn.LAMBDA(_xlpm.Cell, LEFT(_xlpm.Cell, FIND(", ", _xlpm.Cell) - 1))</definedName>
     <definedName name="Fuel_InputFunctions.Fuel_TotalConsumption">_xlfn.LAMBDA(_xlpm.FuelConsumptionArray,_xlpm.FuelUseArray,_xlpm.FuelUse,_xlpm.FuelTypeArray,_xlpm.FuelType, IFERROR(SUM(_xlfn._xlws.FILTER(_xlpm.FuelConsumptionArray, (_xlpm.FuelTypeArray = _xlpm.FuelType) * (_xlpm.FuelUseArray = _xlpm.FuelUse))), 0))</definedName>
-    <definedName name="Fuel_SourceData.Fuel_Scope1EmissionFactorsStationaryGaseous_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(19, 7, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Fuel combusted","Energy Content Factor (GJ per unit of fuel)","Fuel unit","Scope 1 Emission Factor (kg CO2 - e / GJ) CO2","Scope 1 Emission Factor (kg CO2 - e / GJ) CH4","Scope 1 Emission Factor (kg CO2 - e / GJ) N2O","Scope 1 Emission Factor (kg CO2 - e / GJ) Combined gases";"Natural gas distributed in a pipeline",0.0393,"m3",51.4,0.1,0.03,51.53;"Coal seam methane that is captured for combustion",0.0377,"m3",51.4,0.2,0.03,51.63;"Coal mine waste gas that is captured for combustion",0.0377,"m3",51.9,4.6,0.3,56.8;"Compressed natural gas(reverting to standard conditions)",0.0393,"m3",51.4,0.1,0.03,51.53;"Unprocessed natural gas",0.0393,"m3",51.4,0.1,0.03,51.53;"Ethane",0.0629,"m3",56.5,0.03,0.03,56.56;"Coke oven gas",0.0181,"m3",37,0.03,0.05,37.08;"Blast furnace gas",0.004,"m3",234,0.03,0.02,234.05;"Town gas",0.039,"m3",60.2,0.04,0.03,60.27;"Liquefied natural gas",25.3,"kL",51.4,0.1,0.03,51.53;"Gaseous fossil fuels other than those mentioned in the items above",0.039,"m3",51.4,0.1,0.03,51.53;"Landfill biogas that is captured for combustion (methane only)",0.0377,"m3",0,6.4,0.03,6.43;"Sludge biogas that is captured for combustion (methane only)",0.0377,"m3",0,6.4,0.03,6.43;"A biogas that is captured for combustion, other than those mentioned in the items above",0.037,"m3",0,6.4,0.03,6.43;"Biomethane",0.0393,"m3",0,0.1,0.03,0.13;"Hydrogen",0.0122,"m3",0,0,0.5,0.5;"Natural gas distributed in a pipeline - Gigajoules",1,"GJ",51.4,0.1,0.03,51.53;"Town gas - Gigajoules",1,"GJ",60.2,0.04,0.03,60.27}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="Fuel_SourceData.Fuel_Scope1EmissionFactorsStationaryGaseous_Data">_xlfn.LAMBDA(
+  _xlfn.MAKEARRAY(19, 7,
+    _xlfn.LAMBDA(_xlpm.r,_xlpm.c,
+      INDEX({"Fuel combusted","Energy Content Factor (GJ per unit of fuel)","Fuel unit","Scope 1 Emission Factor (kg CO2 - e / GJ) CO2","Scope 1 Emission Factor (kg CO2 - e / GJ) CH4","Scope 1 Emission Factor (kg CO2 - e / GJ) N2O","Scope 1 Emission Factor (kg CO2 - e / GJ) Combined gases";"Natural gas distributed in a pipeline",0.0393,"m3",51.4,0.1,0.03,51.53;"Coal seam methane that is captured for combustion",0.0377,"m3",51.4,0.2,0.03,51.63;"Coal mine waste gas that is captured for combustion",0.0377,"m3",51.9,4.6,0.3,56.8;"Compressed natural gas(reverting to standard conditions)",0.0393,"m3",51.4,0.1,0.03,51.53;"Unprocessed natural gas",0.0393,"m3",51.4,0.1,0.03,51.53;"Ethane",0.0629,"m3",56.5,0.03,0.03,56.56;"Coke oven gas",0.0181,"m3",37,0.03,0.05,37.08;"Blast furnace gas",0.004,"m3",234,0.03,0.02,234.05;"Town gas",0.039,"m3",60.2,0.04,0.03,60.27;"Liquefied natural gas",25.3,"kL",51.4,0.1,0.03,51.53;"Gaseous fossil fuels other than those mentioned in the items above",0.039,"m3",51.4,0.1,0.03,51.53;"Landfill biogas that is captured for combustion (methane only)",0.0377,"m3",0,6.4,0.03,6.43;"Sludge biogas that is captured for combustion (methane only)",0.0377,"m3",0,6.4,0.03,6.43;"A biogas that is captured for combustion, other than those mentioned in the items above",0.037,"m3",0,6.4,0.03,6.43;"Biomethane",0.0393,"m3",0,0.1,0.03,0.13;"Hydrogen",0.0122,"m3",0,0,0.5,0.5;"Natural gas distributed in a pipeline - Gigajoules",1,"GJ",51.4,0.1,0.03,51.53;"Town gas - Gigajoules",1,"GJ",60.2,0.04,0.03,60.27}, _xlpm.r, _xlpm.c)
+)))</definedName>
     <definedName name="Fuel_SourceData.Fuel_Scope1EmissionFactorsStationaryGaseous_Description">_xlfn.LAMBDA(("Direct (Scope 1) emission factors for the consumption of gaseous fuels including liquefied natural gas  "))</definedName>
     <definedName name="Fuel_SourceData.Fuel_Scope1EmissionFactorsStationaryGaseous_Source">_xlfn.LAMBDA(("Australian National Greenhouse Accounts Factors 2025 - Table 5"))</definedName>
     <definedName name="Fuel_SourceData.Fuel_Scope1EmissionFactorsStationaryGaseous_Title">_xlfn.LAMBDA(("Fuel scope 1 emission factors - Stationary gaseous fuels"))</definedName>
     <definedName name="Fuel_SourceData.Fuel_Scope1EmissionFactorsStationaryGaseous_Variation">_xlfn.LAMBDA(("VARIATION OF SOURCE DATA: 'Natural gas distributed in a pipeline - Gigajoules' and 'Town gas - Gigajoules' were added, each with an energy content factor of 1 GJ per unit of fuel. This is for users who have fuel consumption data in GJ rather than m3."))</definedName>
-    <definedName name="Fuel_SourceData.Fuel_Scope1Scope3EmissionFactorsStationaryLiquid_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(25, 8, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Fuel combusted","Energy Content Factor (GJ per unit of fuel)","Fuel unit","Scope 1 Emission Factor (kg CO2 - e / GJ) CO2","Scope 1 Emission Factor (kg CO2 - e / GJ) CH4","Scope 1 Emission Factor (kg CO2 - e / GJ) N2O","Scope 1 Emission Factor (kg CO2 - e / GJ) Combined gases","Scope 3 Emission Factor (kg CO2 - e / GJ)";"Petroleum based oils (other than petroleum based oil used as fuel), e.g. lubricants",38.8,"kl",13.9,0,0,13.9,18;"Petroleum based greases",38.8,"kl",3.5,0,0,3.5,18;"Crude oil including crude oil condensates",45.3,"t",69.6,0.08,0.2,69.88,"NE";"Other natural gas liquids",46.5,"t",61,0.08,0.2,61.28,"NE";"Automotive gasoline / petrol (other than for use as fuel in an aircraft)",34.2,"kL",67.4,0.2,0.2,67.8,17.2;"Aviation gasoline",33.1,"kL",67,0.2,0.2,67.4,18;"Kerosene (other than for use as fuel in an aircraft)",37.5,"kL",68.9,0.01,0.2,69.11,18;"Aviation turbine fuel / kerosene",36.8,"kL",69.6,0.02,0.2,69.82,18;"Heating oil",37.3,"kL",69.5,0.03,0.2,69.73,18;"Diesel oil",38.6,"kL",69.9,0.1,0.2,70.2,17.3;"Fuel oil",39.7,"kL",73.6,0.04,0.2,73.84,18;"Liquefied aromatic hydrocarbons",34.4,"kL",69.7,0.03,0.2,69.93,18;"Solvents: mineral turpentine or white spirits",34.4,"kL",69.7,0.03,0.2,69.93,18;"Liquefied petroleum gas (LPG)",25.7,"kL",60.2,0.2,0.2,60.6,20.2;"Naphtha",31.4,"kL",69.8,0.01,0.01,69.82,18;"Petroleum coke",34.2,"t",92.6,0.08,0.2,92.88,18;"Refinery gas and liquids",42.9,"t",54.7,0.03,0.03,54.76,18;"Refinery coke",34.2,"t",92.6,0.08,0.2,92.88,18;"Petroleum based products other than mentioned in the items above",34.4,"kL",69.8,0.02,0.1,69.92,18;"Biodiesel",34.6,"kL",0,0.08,0.2,0.28,"NE";"Ethanol for use as a fuel in an internal combustion engine",23.4,"kL",0,0.08,0.2,0.28,"NE";"Biofuels other than those mentioned in the items above and below",23.4,"kL",0,0.08,0.2,0.28,"NE";"Renewable aviation kerosene",36.8,"kL",0,0.02,0.2,0.22,"NE";"Renewable diesel",38.6,"kL",0,0.1,0.2,0.3,"NE"}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="Fuel_SourceData.Fuel_Scope1Scope3EmissionFactorsStationaryLiquid_Data">_xlfn.LAMBDA(
+  _xlfn.MAKEARRAY(25, 8,
+    _xlfn.LAMBDA(_xlpm.r,_xlpm.c,
+      INDEX({"Fuel combusted","Energy Content Factor (GJ per unit of fuel)","Fuel unit","Scope 1 Emission Factor (kg CO2 - e / GJ) CO2","Scope 1 Emission Factor (kg CO2 - e / GJ) CH4","Scope 1 Emission Factor (kg CO2 - e / GJ) N2O","Scope 1 Emission Factor (kg CO2 - e / GJ) Combined gases","Scope 3 Emission Factor (kg CO2 - e / GJ)";"Petroleum based oils (other than petroleum based oil used as fuel), e.g. lubricants",38.8,"kl",13.9,0,0,13.9,18;"Petroleum based greases",38.8,"kl",3.5,0,0,3.5,18;"Crude oil including crude oil condensates",45.3,"t",69.6,0.08,0.2,69.88,"NE";"Other natural gas liquids",46.5,"t",61,0.08,0.2,61.28,"NE";"Automotive gasoline / petrol (other than for use as fuel in an aircraft)",34.2,"kL",67.4,0.2,0.2,67.8,17.2;"Aviation gasoline",33.1,"kL",67,0.2,0.2,67.4,18;"Kerosene (other than for use as fuel in an aircraft)",37.5,"kL",68.9,0.01,0.2,69.11,18;"Aviation turbine fuel / kerosene",36.8,"kL",69.6,0.02,0.2,69.82,18;"Heating oil",37.3,"kL",69.5,0.03,0.2,69.73,18;"Diesel oil",38.6,"kL",69.9,0.1,0.2,70.2,17.3;"Fuel oil",39.7,"kL",73.6,0.04,0.2,73.84,18;"Liquefied aromatic hydrocarbons",34.4,"kL",69.7,0.03,0.2,69.93,18;"Solvents: mineral turpentine or white spirits",34.4,"kL",69.7,0.03,0.2,69.93,18;"Liquefied petroleum gas (LPG)",25.7,"kL",60.2,0.2,0.2,60.6,20.2;"Naphtha",31.4,"kL",69.8,0.01,0.01,69.82,18;"Petroleum coke",34.2,"t",92.6,0.08,0.2,92.88,18;"Refinery gas and liquids",42.9,"t",54.7,0.03,0.03,54.76,18;"Refinery coke",34.2,"t",92.6,0.08,0.2,92.88,18;"Petroleum based products other than mentioned in the items above",34.4,"kL",69.8,0.02,0.1,69.92,18;"Biodiesel",34.6,"kL",0,0.08,0.2,0.28,"NE";"Ethanol for use as a fuel in an internal combustion engine",23.4,"kL",0,0.08,0.2,0.28,"NE";"Biofuels other than those mentioned in the items above and below",23.4,"kL",0,0.08,0.2,0.28,"NE";"Renewable aviation kerosene",36.8,"kL",0,0.02,0.2,0.22,"NE";"Renewable diesel",38.6,"kL",0,0.1,0.2,0.3,"NE"}, _xlpm.r, _xlpm.c)
+)))</definedName>
     <definedName name="Fuel_SourceData.Fuel_Scope1Scope3EmissionFactorsStationaryLiquid_Description">_xlfn.LAMBDA(("Direct (Scope 1) and indirect (scope 3) emission factors for the consumption of liquid fuels, including certain petroleum based products for stationary energy purposes."))</definedName>
     <definedName name="Fuel_SourceData.Fuel_Scope1Scope3EmissionFactorsStationaryLiquid_Source">_xlfn.LAMBDA(("Australian National Greenhouse Accounts Factors 2025 - Table 8"))</definedName>
     <definedName name="Fuel_SourceData.Fuel_Scope1Scope3EmissionFactorsStationaryLiquid_Title">_xlfn.LAMBDA(("Fuel scope 1 and 3 emission factors - Stationary liquid fuels"))</definedName>
     <definedName name="Fuel_SourceData.Fuel_Scope1Scope3EmissionFactorsStationaryLiquid_Variation">_xlfn.LAMBDA("VARIATION OF SOURCE DATA: 'NE' values returned as zero for calculations.")</definedName>
-    <definedName name="Fuel_SourceData.Fuel_Scope1Scope3EmissionFactorsTransport_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(26, 10, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Transport type","Fuel combusted","Energy Content Factor(GJ per unit of fuel)","Fuel unit","Scope 1 Emission Factor (kg CO2 - e / GJ) CO2","Scope 1 Emission Factor (kg CO2 - e / GJ) CH4","Scope 1 Emission Factor (kg CO2 - e / GJ) N2O","Scope 1 Emission Factor (kg CO2 - e / GJ) Combined gases","Scope 3 Emission Factor (kg CO2 - e / GJ)","Source";"Cars and light commercial vehicles","Gasoline",34.2,"kl",67.4,0.02,0.2,67.62,17.2,"NGAF 2025: Table 9";"Cars and light commercial vehicles","Diesel oil",38.6,"kl",69.9,0.01,0.5,70.41,17.3,"NGAF 2025: Table 9";"Cars and light commercial vehicles","Liquefied petroleum gas (LPG)",26.2,"kl",60.2,0.5,0.3,61,20.2,"NGAF 2025: Table 9";"Cars and light commercial vehicles","Fuel oil",39.7,"kl",73.6,0.08,0.5,74.18,18,"NGAF 2025: Table 9";"Cars and light commercial vehicles","Ethanol",23.4,"kl",0,0.2,0.2,0.4,"NE","NGAF 2025: Table 9";"Cars and light commercial vehicles","Biodiesel",34.6,"kl",0,0.8,1.7,2.5,"NE","NGAF 2025: Table 9";"Cars and light commercial vehicles","Renewable diesel",38.6,"kl",0,0.01,0.5,0.51,"NE","NGAF 2025: Table 9";"Cars and light commercial vehicles","Other biofuels",23.4,"kl",0,0.8,1.7,2.5,"NE","NGAF 2025: Table 9";"Light duty vehicles","Compressed natural gas",0.0393,"m3",51.4,7.3,0.3,59,18,"NGAF 2025: Table 9";"Light duty vehicles","Liquefied natural gas",25.3,"kl",51.4,7.3,0.3,59,18,"NGAF 2025: Table 9";"Heavy duty vehicles","Compressed natural gas",0.0393,"m3",51.4,2.8,0.3,54.5,18,"NGAF 2025: Table 9";"Heavy duty vehicles","Liquefied natural gas",25.3,"kl",51.4,2.8,0.3,54.5,18,"NGAF 2025: Table 9";"Heavy duty vehicles","Diesel oil - Euro iv or higher",38.6,"kl",69.9,0.07,0.4,70.37,17.3,"NGAF 2025: Table 9";"Heavy duty vehicles","Diesel oil - Euro iii",38.6,"kl",69.9,0.1,0.4,70.4,17.3,"NGAF 2025: Table 9";"Heavy duty vehicles","Diesel oil - Euro i",38.6,"kl",69.9,0.2,0.4,70.5,17.3,"NGAF 2025: Table 9";"Heavy duty vehicles","Renewable diesel – Euro iv or higher",38.6,"kl",0,0.07,0.4,0.47,"NE","NGAF 2025: Table 9";"Heavy duty vehicles","Renewable diesel – Euro iii",38.6,"kl",0,0.1,0.4,0.5,"NE","NGAF 2025: Table 9";"Heavy duty vehicles","Renewable diesel – Euro i",38.6,"kl",0,0.2,0.4,0.6,"NE","NGAF 2025: Table 9";"Aviation","Gasoline for use as fuel in an aircraft",33.1,"kl",67,0.06,0.6,67.66,18,"NGAF 2025: Table 9";"Aviation","Kerosene for use as fuel in an aircraft",36.8,"kl",69.6,0.01,0.6,70.21,18,"NGAF 2025: Table 9";"Aviation","Renewable aviation kerosene",36.8,"kl",0,0.01,0.6,0.61,"NE","NGAF 2025: Table 9";"Vessels","Gasoline",34.2,"kL",67.4,10.1,0.3,"",17.2,"VEERG 2026: Table A.4.2.1";"Vessels","Diesel oil",38.6,"kL",69.9,0.2,0.5,"",17.3,"VEERG 2026: Table A.4.2.1";"Vessels","Fuel Oil",39.7,"kL",73.6,0.2,0.5,"",18,"VEERG 2026: Table A.4.2.1";"Off-road Agriculture and forestry equipment","Diesel oil",38.6,"kL",69.9,0.3,0.5,"",17.3,"VEERG 2026: Table A.4.2.1"}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="Fuel_SourceData.Fuel_Scope1Scope3EmissionFactorsTransport_Data">_xlfn.LAMBDA(
+  _xlfn.MAKEARRAY(26, 10,
+    _xlfn.LAMBDA(_xlpm.r,_xlpm.c,
+      INDEX({"Transport type","Fuel combusted","Energy Content Factor(GJ per unit of fuel)","Fuel unit","Scope 1 Emission Factor (kg CO2 - e / GJ) CO2","Scope 1 Emission Factor (kg CO2 - e / GJ) CH4","Scope 1 Emission Factor (kg CO2 - e / GJ) N2O","Scope 1 Emission Factor (kg CO2 - e / GJ) Combined gases","Scope 3 Emission Factor (kg CO2 - e / GJ)","Source";"Cars and light commercial vehicles","Gasoline",34.2,"kl",67.4,0.02,0.2,67.62,17.2,"NGAF 2025: Table 9";"Cars and light commercial vehicles","Diesel oil",38.6,"kl",69.9,0.01,0.5,70.41,17.3,"NGAF 2025: Table 9";"Cars and light commercial vehicles","Liquefied petroleum gas (LPG)",26.2,"kl",60.2,0.5,0.3,61,20.2,"NGAF 2025: Table 9";"Cars and light commercial vehicles","Fuel oil",39.7,"kl",73.6,0.08,0.5,74.18,18,"NGAF 2025: Table 9";"Cars and light commercial vehicles","Ethanol",23.4,"kl",0,0.2,0.2,0.4,"NE","NGAF 2025: Table 9";"Cars and light commercial vehicles","Biodiesel",34.6,"kl",0,0.8,1.7,2.5,"NE","NGAF 2025: Table 9";"Cars and light commercial vehicles","Renewable diesel",38.6,"kl",0,0.01,0.5,0.51,"NE","NGAF 2025: Table 9";"Cars and light commercial vehicles","Other biofuels",23.4,"kl",0,0.8,1.7,2.5,"NE","NGAF 2025: Table 9";"Light duty vehicles","Compressed natural gas",0.0393,"m3",51.4,7.3,0.3,59,18,"NGAF 2025: Table 9";"Light duty vehicles","Liquefied natural gas",25.3,"kl",51.4,7.3,0.3,59,18,"NGAF 2025: Table 9";"Heavy duty vehicles","Compressed natural gas",0.0393,"m3",51.4,2.8,0.3,54.5,18,"NGAF 2025: Table 9";"Heavy duty vehicles","Liquefied natural gas",25.3,"kl",51.4,2.8,0.3,54.5,18,"NGAF 2025: Table 9";"Heavy duty vehicles","Diesel oil - Euro iv or higher",38.6,"kl",69.9,0.07,0.4,70.37,17.3,"NGAF 2025: Table 9";"Heavy duty vehicles","Diesel oil - Euro iii",38.6,"kl",69.9,0.1,0.4,70.4,17.3,"NGAF 2025: Table 9";"Heavy duty vehicles","Diesel oil - Euro i",38.6,"kl",69.9,0.2,0.4,70.5,17.3,"NGAF 2025: Table 9";"Heavy duty vehicles","Renewable diesel – Euro iv or higher",38.6,"kl",0,0.07,0.4,0.47,"NE","NGAF 2025: Table 9";"Heavy duty vehicles","Renewable diesel – Euro iii",38.6,"kl",0,0.1,0.4,0.5,"NE","NGAF 2025: Table 9";"Heavy duty vehicles","Renewable diesel – Euro i",38.6,"kl",0,0.2,0.4,0.6,"NE","NGAF 2025: Table 9";"Aviation","Gasoline for use as fuel in an aircraft",33.1,"kl",67,0.06,0.6,67.66,18,"NGAF 2025: Table 9";"Aviation","Kerosene for use as fuel in an aircraft",36.8,"kl",69.6,0.01,0.6,70.21,18,"NGAF 2025: Table 9";"Aviation","Renewable aviation kerosene",36.8,"kl",0,0.01,0.6,0.61,"NE","NGAF 2025: Table 9";"Vessels","Gasoline",34.2,"kL",67.4,10.1,0.3,"",17.2,"VEERG 2026: Table A.4.2.1";"Vessels","Diesel oil",38.6,"kL",69.9,0.2,0.5,"",17.3,"VEERG 2026: Table A.4.2.1";"Vessels","Fuel Oil",39.7,"kL",73.6,0.2,0.5,"",18,"VEERG 2026: Table A.4.2.1";"Off-road Agriculture and forestry equipment","Diesel oil",38.6,"kL",69.9,0.3,0.5,"",17.3,"VEERG 2026: Table A.4.2.1"}, _xlpm.r, _xlpm.c)
+)))</definedName>
     <definedName name="Fuel_SourceData.Fuel_Scope1Scope3EmissionFactorsTransport_Description">_xlfn.LAMBDA(("Direct (scope 1) and indirect (scope 3) emission factors for the consumption of transport fuels in different transport equipment"))</definedName>
     <definedName name="Fuel_SourceData.Fuel_Scope1Scope3EmissionFactorsTransport_Source">_xlfn.LAMBDA(("Australian National Greenhouse Accounts Factors 2025 - Table 9"))</definedName>
     <definedName name="Fuel_SourceData.Fuel_Scope1Scope3EmissionFactorsTransport_Title">_xlfn.LAMBDA(("Fuel scope 1 and 3 emission factors - Transport"))</definedName>
     <definedName name="Fuel_SourceData.Fuel_Scope1Scope3EmissionFactorsTransport_Variation">_xlfn.LAMBDA("VARIATION OF SOURCE DATA: 'NE' values returned as zero for calculations.")</definedName>
-    <definedName name="Fuel_SourceData.Fuel_Scope1Scope3EmissionFactorsTransportOffRoad_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(5, 7, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Transport type t","Fuel type q","ECTrans,q (GJ/kL)","Scope 1 CO2 EFTran,1,tqg (kg CO2-e/GJ)","Scope 1 CH4 EFTran,1,tgg (kg CO2-e/GJ)","Scope 1 N2O EFTran,1,tgg (kg CO2-e/GJ)","Scope 3 EFTrans,3,q (kg CO2-e/GJ)";"Vessel","Petrol",34.2,67.4,10.1,0.3,17.2;"Vessel","Diesel",38.6,69.9,0.2,0.5,17.3;"Vessel","Fuel Oil",39.7,73.6,0.2,0.5,18;"Off-road Agriculture and forestry equipment","Diesel",38.6,69.9,0.3,0.5,17.3}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="Fuel_SourceData.Fuel_Scope1Scope3EmissionFactorsTransportOffRoad_Data">_xlfn.LAMBDA(
+  _xlfn.MAKEARRAY(5, 7,
+    _xlfn.LAMBDA(_xlpm.r,_xlpm.c,
+      INDEX({"Transport type t","Fuel type q","ECTrans,q (GJ/kL)","Scope 1 CO2 EFTran,1,tqg (kg CO2-e/GJ)","Scope 1 CH4 EFTran,1,tgg (kg CO2-e/GJ)","Scope 1 N2O EFTran,1,tgg (kg CO2-e/GJ)","Scope 3 EFTrans,3,q (kg CO2-e/GJ)";"Vessel","Petrol",34.2,67.4,10.1,0.3,17.2;"Vessel","Diesel",38.6,69.9,0.2,0.5,17.3;"Vessel","Fuel Oil",39.7,73.6,0.2,0.5,18;"Off-road Agriculture and forestry equipment","Diesel",38.6,69.9,0.3,0.5,17.3}, _xlpm.r, _xlpm.c)
+)))</definedName>
     <definedName name="Fuel_SourceData.Fuel_Scope1Scope3EmissionFactorsTransportOffRoad_Description">_xlfn.LAMBDA(("Direct (scope 1) and indirect (scope 3) emission factors for the consumption of fuels in off-road equipment and vessels"))</definedName>
     <definedName name="Fuel_SourceData.Fuel_Scope1Scope3EmissionFactorsTransportOffRoad_Source">_xlfn.LAMBDA(("VEERG 2026: Table A.4.2.1"))</definedName>
     <definedName name="Fuel_SourceData.Fuel_Scope1Scope3EmissionFactorsTransportOffRoad_Title">_xlfn.LAMBDA(("Fuel scope 1 and 3 emission factors - Off-road equipment and vessels"))</definedName>
     <definedName name="Fuel_SourceData.Fuel_Scope3EmissionFactorsStationaryGaseous_Appendices">_xlfn.LAMBDA(_xlfn.MAKEARRAY(12, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"-","As Scope 3 factors are calculated at the point where natural gas is delivered to end users, it is necessary to calculate consumption at each of the load centres.";"","Gas reaches end users either from the metro distribution networks or direct from the high - pressure distribution pipelines.";"","Households and commercial users tend to be served by the former, and electricity generators and large industrial plants from the latter.";"-","Metro is defined as located on or east of the dividing range in NSW, including Canberra and Queanbeyan, Melbourne, Brisbane, Adelaide or Perth.";"","Otherwise, the non - metro factor should be used.";"-","Factors are calculated for all natural gas distributed in a pipeline which may include coal seam methane.";"-","Table 6 is not applicable to ethane. See Table 7 Indirect (Scope 3) emissions from the consumption of ethane.";"-","C = Confidential. Scope 3 emission factors for Tasmania and the Northern Territory are not available due to confidentiality constraints that arise";"","from the use of a limited number of NGER data inputs. It is suggested that for Tasmania the use of the Victorian emission factors is appropriate,";"","while for Northern Territory the use of the Western Australian emission factors is appropriate.";"-","Scope 3 emission factors do not include fugitive emission leakage from low pressure natural gas distribution pipeline networks while those from high pressure";"","gas networks are considered negligible."}, _xlpm.r, _xlpm.c))))</definedName>
-    <definedName name="Fuel_SourceData.Fuel_Scope3EmissionFactorsStationaryGaseous_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(9, 3, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"State or territory","Scope 3 Emission Factors for Natural Gas (kg CO2 - e / GJ) Metro","Scope 3 Emission Factors for Natural Gas (kg CO2 - e / GJ) Non - Metro";"New South Wales",13.1,14;"ACT",13.1,14;"Victoria",4,4;"Queensland",8.8,7.9;"South Australia",10.7,10.6;"Western Australia",4.1,4;"Tasmania",4,4;"Northern Territory",4.1,4}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="Fuel_SourceData.Fuel_Scope3EmissionFactorsStationaryGaseous_Data">_xlfn.LAMBDA(
+  _xlfn.MAKEARRAY(9, 3,
+    _xlfn.LAMBDA(_xlpm.r,_xlpm.c,
+      INDEX({"State or territory","Scope 3 Emission Factors for Natural Gas (kg CO2 - e / GJ) Metro","Scope 3 Emission Factors for Natural Gas (kg CO2 - e / GJ) Non - Metro";"New South Wales",13.1,14;"ACT",13.1,14;"Victoria",4,4;"Queensland",8.8,7.9;"South Australia",10.7,10.6;"Western Australia",4.1,4;"Tasmania",4,4;"Northern Territory",4.1,4}, _xlpm.r, _xlpm.c)
+)))</definedName>
     <definedName name="Fuel_SourceData.Fuel_Scope3EmissionFactorsStationaryGaseous_Description">_xlfn.LAMBDA(("Indirect (Scope 3) emission factors for the consumption of natural gas."))</definedName>
     <definedName name="Fuel_SourceData.Fuel_Scope3EmissionFactorsStationaryGaseous_Source">_xlfn.LAMBDA(("Australian National Greenhouse Accounts Factors 2025 - Table 6"))</definedName>
     <definedName name="Fuel_SourceData.Fuel_Scope3EmissionFactorsStationaryGaseous_Title">_xlfn.LAMBDA(("Fuel scope 3 emission factors - Stationary gaseous fuels"))</definedName>
@@ -2070,6 +2118,126 @@
   <dxfs count="60">
     <dxf>
       <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
@@ -2929,126 +3097,6 @@
         <patternFill patternType="none">
           <fgColor indexed="64"/>
           <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4661,26 +4709,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Home"/>
-      <sheetName val="Constants - Common"/>
-      <sheetName val="Acknowledgements"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
 <rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
   <global>
@@ -4789,49 +4817,49 @@
     <tableColumn id="1" xr3:uid="{F4D32187-9689-4807-97E3-B4C92D417D3A}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{D31F47AF-2C35-45B1-BB9E-25301AF21F11}" name="MAT" totalsRowDxfId="35" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{D31F47AF-2C35-45B1-BB9E-25301AF21F11}" name="MAT" totalsRowDxfId="47" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{3AA65C4C-AF27-4115-8193-750D88828575}" name="MAP" totalsRowDxfId="34" totalsRowCellStyle="Content bold">
+    <tableColumn id="3" xr3:uid="{3AA65C4C-AF27-4115-8193-750D88828575}" name="MAP" totalsRowDxfId="46" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{C95D7C2D-94FE-4B53-BE81-5D8690A7E23B}" name="Frost days per year" totalsRowDxfId="33" totalsRowCellStyle="Content bold">
+    <tableColumn id="4" xr3:uid="{C95D7C2D-94FE-4B53-BE81-5D8690A7E23B}" name="Frost days per year" totalsRowDxfId="45" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{78B75B35-D227-4BE6-BE0B-623E34096F44}" name="Elevation" totalsRowDxfId="32" totalsRowCellStyle="Content bold">
+    <tableColumn id="5" xr3:uid="{78B75B35-D227-4BE6-BE0B-623E34096F44}" name="Elevation" totalsRowDxfId="44" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{F2E5F8B3-348E-4E83-8B88-25C14A75B279}" name="MAP:PET" totalsRowDxfId="31" totalsRowCellStyle="Content bold">
+    <tableColumn id="6" xr3:uid="{F2E5F8B3-348E-4E83-8B88-25C14A75B279}" name="MAP:PET" totalsRowDxfId="43" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{85922B28-B16D-4DC4-A967-AE14609F23B9}" name="Min temp" totalsRowDxfId="30" totalsRowCellStyle="Content bold">
+    <tableColumn id="7" xr3:uid="{85922B28-B16D-4DC4-A967-AE14609F23B9}" name="Min temp" totalsRowDxfId="42" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{0235F957-3B8E-4193-9DC3-13B01DA62086}" name="Max temp" totalsRowDxfId="29" totalsRowCellStyle="Content bold">
+    <tableColumn id="8" xr3:uid="{0235F957-3B8E-4193-9DC3-13B01DA62086}" name="Max temp" totalsRowDxfId="41" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{16D7044C-C5D3-41F4-BC5E-78CF1E858FE4}" name="Min rainfall" totalsRowDxfId="28" totalsRowCellStyle="Content bold">
+    <tableColumn id="9" xr3:uid="{16D7044C-C5D3-41F4-BC5E-78CF1E858FE4}" name="Min rainfall" totalsRowDxfId="40" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{74526D7A-ED68-4FA8-9F13-C17608FE4E24}" name="Max rainfall" totalsRowDxfId="27" totalsRowCellStyle="Content bold">
+    <tableColumn id="10" xr3:uid="{74526D7A-ED68-4FA8-9F13-C17608FE4E24}" name="Max rainfall" totalsRowDxfId="39" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{6757D4E7-76CC-413F-875B-980B201E0504}" name="Min frost days" totalsRowDxfId="26" totalsRowCellStyle="Content bold">
+    <tableColumn id="11" xr3:uid="{6757D4E7-76CC-413F-875B-980B201E0504}" name="Min frost days" totalsRowDxfId="38" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{37E37A80-AB6B-4A5C-8522-62A6ED4FC83E}" name="Max frost days" totalsRowDxfId="25" totalsRowCellStyle="Content bold">
+    <tableColumn id="15" xr3:uid="{37E37A80-AB6B-4A5C-8522-62A6ED4FC83E}" name="Max frost days" totalsRowDxfId="37" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{EBB3FCD8-6E3F-43BE-A81F-9BA40DDCCF6A}" name="Min elevation" totalsRowDxfId="24" totalsRowCellStyle="Content bold">
+    <tableColumn id="12" xr3:uid="{EBB3FCD8-6E3F-43BE-A81F-9BA40DDCCF6A}" name="Min elevation" totalsRowDxfId="36" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{BA1B1A55-157F-49A2-B423-1D6618F9C39B}" name="Max elevation" totalsRowDxfId="23" totalsRowCellStyle="Content bold">
+    <tableColumn id="16" xr3:uid="{BA1B1A55-157F-49A2-B423-1D6618F9C39B}" name="Max elevation" totalsRowDxfId="35" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{FE7612EE-50DD-455B-A802-19744E0B2DC7}" name="Min MAP:PET" totalsRowDxfId="22" totalsRowCellStyle="Content bold">
+    <tableColumn id="13" xr3:uid="{FE7612EE-50DD-455B-A802-19744E0B2DC7}" name="Min MAP:PET" totalsRowDxfId="34" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{2E5EF2DF-58FB-4100-A2D7-FB96478581BA}" name="Max MAP:PET" totalsRowDxfId="21" totalsRowCellStyle="Content bold">
+    <tableColumn id="17" xr3:uid="{2E5EF2DF-58FB-4100-A2D7-FB96478581BA}" name="Max MAP:PET" totalsRowDxfId="33" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4849,7 +4877,7 @@
     <tableColumn id="1" xr3:uid="{2ED8E2F2-C8F1-4562-9242-D5E2772AB3D4}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{B7335F21-A9B1-4DEF-834C-281703478B2D}" name="Wet or Dry Zone" totalsRowDxfId="20" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{B7335F21-A9B1-4DEF-834C-281703478B2D}" name="Wet or Dry Zone" totalsRowDxfId="32" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4955,7 +4983,7 @@
     <tableColumn id="1" xr3:uid="{04B33934-32D4-463F-9CA5-2DB963128054}" name="Is in leaching zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{C4FA5E52-C277-4018-8AF0-C0FC73EDF70B}" name="FracWET" dataDxfId="19">
+    <tableColumn id="2" xr3:uid="{C4FA5E52-C277-4018-8AF0-C0FC73EDF70B}" name="FracWET" dataDxfId="31">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5003,7 +5031,7 @@
     <tableColumn id="1" xr3:uid="{B7346040-DB38-49E4-A9B9-D34F265E843C}" name="Irrigation type i">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{D960657A-BD1E-45D3-825A-C3C29BB6893B}" name="FracWET" dataDxfId="18" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{D960657A-BD1E-45D3-825A-C3C29BB6893B}" name="FracWET" dataDxfId="30" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5021,7 +5049,7 @@
     <tableColumn id="1" xr3:uid="{A7591274-8B84-419F-8426-A123AEF27A2B}" name="Climate zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{3B251A85-EA78-4BF5-AE28-FBBB25AE45AF}" name="EFPRP" dataDxfId="17" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{3B251A85-EA78-4BF5-AE28-FBBB25AE45AF}" name="EFPRP" dataDxfId="29" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5069,7 +5097,7 @@
     <tableColumn id="1" xr3:uid="{98D96C85-70B0-47BB-B6FA-37B5BBD3A0C5}" name="Month">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{50CEE149-B6ED-4E47-AC7F-E706418D8D14}" name="Season" dataDxfId="16" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{50CEE149-B6ED-4E47-AC7F-E706418D8D14}" name="Season" dataDxfId="28" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5101,49 +5129,49 @@
     <tableColumn id="1" xr3:uid="{EDBA0716-8D09-453B-B867-D734BB273273}" name="Temperature zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{362D9B5A-5BDF-4D20-AEE9-44EE5CA47472}" name="MAT (ºC)" dataDxfId="15" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{362D9B5A-5BDF-4D20-AEE9-44EE5CA47472}" name="MAT (ºC)" dataDxfId="27" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{02734B5F-8E99-48B0-8AFD-5D124B34FC2E}" name="Anaerobic lagoon" dataDxfId="14" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{02734B5F-8E99-48B0-8AFD-5D124B34FC2E}" name="Anaerobic lagoon" dataDxfId="26" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{A99A40B6-6526-4E7B-8907-C79C81154353}" name="Digester / covered lagoons" dataDxfId="13" dataCellStyle="Content normal">
+    <tableColumn id="4" xr3:uid="{A99A40B6-6526-4E7B-8907-C79C81154353}" name="Digester / covered lagoons" dataDxfId="25" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{8EC7811A-5957-4303-B6C1-8C02C7F3874D}" name="Liquid systems" dataDxfId="12" dataCellStyle="Content normal">
+    <tableColumn id="5" xr3:uid="{8EC7811A-5957-4303-B6C1-8C02C7F3874D}" name="Liquid systems" dataDxfId="24" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{CF854FEA-BA45-4097-B4A8-613400CC7B7C}" name="Daily spread" dataDxfId="11" dataCellStyle="Content normal">
+    <tableColumn id="6" xr3:uid="{CF854FEA-BA45-4097-B4A8-613400CC7B7C}" name="Daily spread" dataDxfId="23" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{256FC14B-3AAE-41ED-BC85-E23034611119}" name="Composting (passive windrow)" dataDxfId="10" dataCellStyle="Content normal">
+    <tableColumn id="7" xr3:uid="{256FC14B-3AAE-41ED-BC85-E23034611119}" name="Composting (passive windrow)" dataDxfId="22" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{D34CD105-5F3D-4C97-A69A-C45F0554A9F6}" name="Solid storage" dataDxfId="9" dataCellStyle="Content normal">
+    <tableColumn id="8" xr3:uid="{D34CD105-5F3D-4C97-A69A-C45F0554A9F6}" name="Solid storage" dataDxfId="21" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{5D362D2B-8937-483C-91EB-73C8289D01E0}" name="Pit storage" dataDxfId="8" dataCellStyle="Content normal">
+    <tableColumn id="9" xr3:uid="{5D362D2B-8937-483C-91EB-73C8289D01E0}" name="Pit storage" dataDxfId="20" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{01FEDDEA-105A-4F7A-8063-CC4AB0023BE7}" name="Deep litter" dataDxfId="7" dataCellStyle="Content normal">
+    <tableColumn id="10" xr3:uid="{01FEDDEA-105A-4F7A-8063-CC4AB0023BE7}" name="Deep litter" dataDxfId="19" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{6DD86747-26C4-4628-B797-F18D306EE9F5}" name="Poultry manure with bedding" dataDxfId="6" dataCellStyle="Content normal">
+    <tableColumn id="11" xr3:uid="{6DD86747-26C4-4628-B797-F18D306EE9F5}" name="Poultry manure with bedding" dataDxfId="18" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{074792B9-0B22-4676-893B-02626C137D46}" name="Poultry manure without bedding" dataDxfId="5" dataCellStyle="Content normal">
+    <tableColumn id="12" xr3:uid="{074792B9-0B22-4676-893B-02626C137D46}" name="Poultry manure without bedding" dataDxfId="17" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{6F6A2A0F-FCEA-4196-A8A3-7F6A414720D5}" name="Direct processing" dataDxfId="4" dataCellStyle="Content normal">
+    <tableColumn id="13" xr3:uid="{6F6A2A0F-FCEA-4196-A8A3-7F6A414720D5}" name="Direct processing" dataDxfId="16" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{25617266-488F-4561-AD41-D73A03A353F1}" name="Direct application" dataDxfId="3" dataCellStyle="Content normal">
+    <tableColumn id="14" xr3:uid="{25617266-488F-4561-AD41-D73A03A353F1}" name="Direct application" dataDxfId="15" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{F1D43D45-E8C9-4B8A-B8FB-AD14A03B3CBE}" name="Pasture range and paddock" dataDxfId="2" dataCellStyle="Content normal">
+    <tableColumn id="15" xr3:uid="{F1D43D45-E8C9-4B8A-B8FB-AD14A03B3CBE}" name="Pasture range and paddock" dataDxfId="14" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{0E77FE88-E605-4FB3-BABB-0DE5602481CD}" name="MAT raw" dataDxfId="1" dataCellStyle="Content normal">
+    <tableColumn id="16" xr3:uid="{0E77FE88-E605-4FB3-BABB-0DE5602481CD}" name="MAT raw" dataDxfId="13" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5161,7 +5189,7 @@
     <tableColumn id="1" xr3:uid="{DE4A49FA-F17F-4010-8199-0AECFDC56C16}" name="Climate Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{23A52A90-7B5E-45DE-BAB7-5FCDA26BD6F8}" name="EFNi &amp; EFN2Oi" dataDxfId="0" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{23A52A90-7B5E-45DE-BAB7-5FCDA26BD6F8}" name="EFNi &amp; EFN2Oi" dataDxfId="12" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7474,62 +7502,62 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F49">
-    <cfRule type="cellIs" dxfId="47" priority="62" operator="lessThan">
+    <cfRule type="cellIs" dxfId="11" priority="62" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F128:F129">
-    <cfRule type="cellIs" dxfId="46" priority="21" operator="lessThan">
+    <cfRule type="cellIs" dxfId="10" priority="21" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F140:F141">
-    <cfRule type="cellIs" dxfId="45" priority="20" operator="lessThan">
+    <cfRule type="cellIs" dxfId="9" priority="20" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F152:F153">
-    <cfRule type="cellIs" dxfId="44" priority="19" operator="lessThan">
+    <cfRule type="cellIs" dxfId="8" priority="19" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F164:F165">
-    <cfRule type="cellIs" dxfId="43" priority="18" operator="lessThan">
+    <cfRule type="cellIs" dxfId="7" priority="18" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F252:F253">
-    <cfRule type="cellIs" dxfId="42" priority="93" operator="lessThan">
+    <cfRule type="cellIs" dxfId="6" priority="93" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F257:F258">
-    <cfRule type="cellIs" dxfId="41" priority="92" operator="lessThan">
+    <cfRule type="cellIs" dxfId="5" priority="92" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F262:F263">
-    <cfRule type="cellIs" dxfId="40" priority="91" operator="lessThan">
+    <cfRule type="cellIs" dxfId="4" priority="91" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F286:F287">
-    <cfRule type="cellIs" dxfId="39" priority="85" operator="lessThan">
+    <cfRule type="cellIs" dxfId="3" priority="85" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F291:F292">
-    <cfRule type="cellIs" dxfId="38" priority="84" operator="lessThan">
+    <cfRule type="cellIs" dxfId="2" priority="84" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F296:F297">
-    <cfRule type="cellIs" dxfId="37" priority="83" operator="lessThan">
+    <cfRule type="cellIs" dxfId="1" priority="83" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H45:H47 E212:G212">
-    <cfRule type="cellIs" dxfId="36" priority="79" operator="lessThan">
+    <cfRule type="cellIs" dxfId="0" priority="79" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -19120,19 +19148,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgAFwAdQAwADAAMgA3AEYAcgB5AFwAdQAwADAAMgA3ACAAdABvACAAXAB1ADAAMAAyADcARAByAHkAXAB1ADAAMAAyADcALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIAVwBlAHQAIABvAHIAIABEAHIAeQAgAFoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAHcAYQByAG0AIAAvACAAYwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALwAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0ACAAYQBuAGQAIABoAGkAZwBoACAAdABlAG0AcAAgAGMAbABhAHMAcwBlAHMAIAB0AG8AIABhAGMAYwBvAG0AbQBvAGQAYQB0AGUAIABjAGwAaQBtAGEAdABlACAAcwBjAGUAbgBhAHIAaQBvAHMAIABlAHgAYwBsAHUAZABlAGQAIABiAHkAIABWAEUARQBSAEcAIABjAHIAaQB0AGUAcgBpAGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBpAHgAZQBkACAAdAB5AHAAbwAgAGkAbgAgAE0AQQBUACAAdgBhAGwAdQBlACAAZgBvAHIAIAB3AGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABjAGgAYQBuAGcAZQBkACAAMQAwACAAdABvACAAMQAxAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAG0AaQBuACAAYQBuAGQAIABtAGEAeAAgAGMAbwBsAHUAbQBuAHMAIABmAG8AcgAgAE0AQQBUACwAIABNAEEAUAAsACAAZgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgAsACAAZQBsAGUAdgBhAHQAaQBvAG4ALAAgAE0AQQBQADoAUABFAFQAIAB0AG8AIABjAGEAbABjAHUAbABhAHQAZQAgAHoAbwBuAGUAcwAgAGYAcgBvAG0AIAByAGUAYQBsACAAYwBsAGkAbQBhAHQAZQAgAGQAYQB0AGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBBAEYAIABhAGMAYwBlAHAAdABzACAAcgBhAGkAbgBmAGEAbABsACAAYQBzACAAYQAgAHAAcgBvAHgAeQAgAGYAbwByACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUAFwAIgAsACAAXAAiAE0AQQBQAFwAIgAsACAAXAAiAEYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIAXAAiACwAIABcACIARQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAHQAZQBtAHAAXAAiACwAIABcACIATQBhAHgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AaQBuACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AYQB4ACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AaQBuACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGEAeAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBpAG4AIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGEAeAAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADIAMAAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAG0AIAAtACAAZCIgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAxADAAMAAwAC4AMAAwADEALAAgADIAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQBcACIALAAgADEAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB0AGUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFQAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAUAAgAD0AIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEUAVAAgAD0AIABwAG8AdABlAG4AdABpAGEAbAAgAGUAdgBhAHAAbwB0AHIAYQBuAHMAcABpAHIAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAE0AQQBUACAAbQBpAG4AIABhAG4AZAAgAE0AQQBUACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AZQBkAGkAYQBuACAAQQBuAG4AdQBhAGwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAAoAE0AQQBUACkAXAAiACwAIABcACIATQBpAG4AIABNAEEAVABcACIALAAgAFwAIgBNAGEAeAAgAE0AQQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiIAAyADYAIABDAFwAIgAsACAAMgA2ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgAFwAIgAxADUAIAAtACAAMgA1ACAAQwBcACIALAAgADEANQAsACAAMgA1AC4AOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIiAAMQA0ACAAQwBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEANAAuADkAOQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABaAG8AbgBlAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AaQBuAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAXAB1ADAAMAAzAGUAIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAXAB1ADAAMAAzAGUAowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABkAG8AZQBzACAAbgBvAHQAIABvAGMAYwB1AHIAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAGQiowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBzACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAWQBlAHMAIAAtACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvACAALQAgAG4AbwB0ACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAZABhAHQAYQAgAHMAYwBvAHIAZQBzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFgAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAdABhACAAcwBvAHUAcgBjAGUAXAAiACwAIABcACIARABhAHQAYQAgAHMAYwBvAHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAHQAZQByAG4AYQB0AGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUAIABvAHIAIAByAGUAZwBpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAGkAbgB0AGUAbgBzAGkAdAB5ACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIABhAHAAcAByAG8AdgBlAGQAIABtAGUAdABoAG8AZABcACIALAAgADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBlAHIAaQBmAGkAZQBkACAAYwByAGUAZABlAG4AdABpAGEAbAAgAG0AYQB0AGMAaABpAG4AZwAgAEkAUwBPADEANAAwADYANwBcACIALAAgADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIAAoADMALgBEAC4AYgAuADIAKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBMAEUAQQBDAEgAXAAiACwAMAAuADIANABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AIAAzAC4ARAAuAEIAXwAxADAAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAGwAZQBhAGMAaABcACIALAAwAC4AMAAxADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADUALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACwAXAAiAEUARgBOADIATwBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5AFwAIgAsACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAA1ADkALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAXAAiACwAMAAuADAAMAA3ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABsAG8AdwAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAMgA5ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAaABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAOAAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAMAAuADAAMQA5ADkALAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsADAALgAwADAANQAzACwAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAMAAuADAAMAA2ADQALAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABjAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnACkAXAAiACwAMAAuADAAMAAzACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBDAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABzAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnACkAXAAiACwAMAAuADAAMAA1ACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBTAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAMAAuADAAMAAyADYALAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABkAHUAcABsAGkAYwBhAHQAZQAgAFwAdQAwADAAMgA3AEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcAHUAMAAwADIANwAsACAAXAB1ADAAMAAyADcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcAHUAMAAwADIANwAgAGEAbgBkACAAXAB1ADAAMAAyADcAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AG4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAdQAwADAAMgA3ACAAcgBvAHcAIAB3AGkAdABoACAAcwBhAG0AZQAgAEUARgAgAGYAbwByACAAbABvAHcAIABhAG4AZAAgAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXABuAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXABuAEkAUABDAEMAOgAgAE4AMgBPACAARQBNAEkAUwBTAEkATwBOAFMAIABGAFIATwBNACAATQBBAE4AQQBHAEUARAAgAFMATwBJAEwAUwAsACAAQQBOAEQAIABDAE8AMgAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAEwASQBNAEUAIABBAE4ARAAgAFUAUgBFAEEAIABBAFAAUABMAEkAQwBBAFQASQBPAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAFcARQBUACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAQwBoAGEAcAB0AGUAcgAgADEALAAgAHMAZQBjAHQAaQBvAG4AIAAxAC4AOAAuADIAIABMAGUAYQBjAGgAaQBuAGcALAAgAGMAbABpAG0AYQB0AGUAIABhAG4AZAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAUgBlAGYAaQBuAGUAbQBlAG4AdAAgAFYAbwBsAHUAbQBlACAANAA6ACAAQwBoAGEAcAB0AGUAcgAgADEAMQA6ACAATgAyAE8AIABFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABNAGEAbgBhAGcAZQBkACAAUwBvAGkAbABzACwAIABhAG4AZAAgAEMATwAyACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATABpAG0AZQAgAGEAbgBkACAAVQByAGUAYQAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlACAAaQByAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBwAHIAaQBuAGsAbABlAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAcgBmAGEAYwBlACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABUAGEAYgBsAGUAIABjAHIAZQBhAHQAZQBkACAAYgBhAHMAZQBkACAAbwBuACAAVgBFAEUAUgBHACAAdABlAHgAdAAgAFwAdQAwADAAMgA3AEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuAFwAdQAwADAAMgA3AFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAOgAgAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAFAAUgBQACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgAyAE8AIAAtACAATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIABcACIARQBGAFAAUgBQAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAB1ADAAMAAyADcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAdQAwADAAMgA3ACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AbwBuAHQAaABzACAAdABvACAAUwBlAGEAcwBvAG4AcwAgAE0AYQBwAHAAaQBuAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AbgB0AGgAXAAiACwAIABcACIAUwBlAGEAcwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAYQBuAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBiAHIAdQBhAHIAeQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAHIAYwBoAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHAAcgBpAGwAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQB5AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbgBlAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbAB5AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAZwB1AHMAdABcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAHAAdABlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AYwB0AG8AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB2AGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGMAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAbgB1AHIAZQAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAIAATICAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAegBvAG4AZQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA4AC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAyACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAIAAoALoAQwApAFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAUwBsAHUAcgByAHkAIAAoAHcAaQB0AGgAbwB1AHQAIABuAGEAdAB1AHIAYQBsACAAYwByAHUAcwB0ACkAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAGIAKQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABTAHQAbwByAGEAZwBlACAAXAB1ADAAMAAzAGMAMQAgAG0AbwBuAHQAaABcACIALAAgAFwAIgBEAGUAZQBwACAATABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAE0AYQBuAHUAcgBlACAAKAB3AGkAdABoAC8AdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACkAXAAiACwAIABcACIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAaQBuAHQAbwAgAHAAZQBsAGwAZQB0AGkAegBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACwAIABSAGEAbgBnAGUAIABhAG4AZAAgAFAAYQBkAGQAbwBjAGsAIAAoAGMAKQAoAGQAKQBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAXAAiAGQiMQAwAFwAIgAsACAAMAAuADYANgAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMQAsACAAMAAuADYAOAAsACAAMAAuADEALAAgADAALgAxADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAyACwAIAAwAC4ANwAsACAAMAAuADEALAAgADAALgAxADMALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAzACwAIAAwAC4ANwAxACwAIAAwAC4AMQAsACAAMAAuADEANAAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADQALAAgADAALgA3ADMALAAgADAALgAxACwAIAAwAC4AMQA1ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADUALAAgADAALgA3ADQALAAgADAALgAxACwAIAAwAC4AMQA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA2ACwAIAAwAC4ANwA1ACwAIAAwAC4AMQAsACAAMAAuADEAOAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANwAsACAAMAAuADcANgAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA4ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIAMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOQAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADAALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA2ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAxACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIAOQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMgAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAzADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADMALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA0ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANQAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANgAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADQALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANwAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANAA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIABcACIAZSIyADgAXAAiACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwBcACIALAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZABcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgAgAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAcgBvAHcAIABvAGYAIABOAEkAUgAgAE0ATQBBACAAZABlAGYAaQBuAGkAdABpAG8AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuACAARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AFAAbwB1AGwAdAByAHkAIAB3AGkAdABoACAAYQBuAGQAIAB3AGkAdABoAG8AdQB0ACAAbABpAHQAdABlAHIAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABzAGUAcABhAHIAYQB0AGUAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AE0AQQBUACAAcgBhAHcAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHQAbwAgAGEAbABsAG8AdwAgAGwAbwBvAGsAdQBwACAAbwBmACAAbgB1AG0AYgBlAHIAcwAuAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBuAGQAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYATgBpACAAXAB1ADAAMAAyADYAIABFAEYATgAyAE8AaQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADEALgA0AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBOAGkAIABcAHUAMAAwADIANgAgAEUARgBOADIATwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAE4AMgBPACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUATgAyAE8AOgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXABuAEcAVwBQAE4AMgBPADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBOADIATwAsACAARwBXAFAAXwBOADIATwAsAFwAbgAgACAAIAAgAEUAXwBOADIATwAgACoAIABHAFcAUABfAE4AMgBPAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AE4AMgBPAH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AE4AMgBPAH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBOADIATwBcACIALABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAATgAyAE8AXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAEMASAA0ACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUAQwBIADQAOgAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXABuAEcAVwBQAEMASAA0ADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBDAEgANAAsACAARwBXAFAAXwBDAEgANAAsAFwAbgAgACAAIAAgAEUAXwBDAEgANAAgACoAIABHAFcAUABfAEMASAA0AFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEMASAA0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AEMASAA0AH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AEMASAA0AH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAEgANABcACIALABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAAQwBIADQAXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkALABcAG4AIAAgACAAIABSAE8AVwAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAgAC0AIAAxAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACwAXABuACAAIABDAE8ATABVAE0ATgAoAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAQQByAHIAYQB5AEQAYQB0AGEALAAgAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAIABbAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAXQAsAFwAbgAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgAEkATgBEAEUAWAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABVAE4ASQBRAFUARQAoAEEAcgByAGEAeQBEAGEAdABhACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwAoACkALQBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwAKQAgACsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApACwAIAAxACwAIABDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAIABcACIAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAASQBGACgASQBTAE4AVQBNAEIARQBSACgAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgAgACAAIAAgACkALAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkALAAgADAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABbAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlAF0ALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAMQAsACAAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACkAKgAoAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlADIAKQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE8AbgBlAEMAbwBsAHUAbQBuAEEAbgBkAEgAZQBhAGQAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBmAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQAsACAAXAAiAFwAIgAsACAAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQwBlAGwAbAAsACAARABlAGwAaQBtAGkAdABlAHIALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEAXQAsACAAWwBDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgBdACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgBYAE0ATAAoAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAdQAwADAAMwBjAHQAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAIABcAHUAMAAwADIANgBcAG4AIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFMAVQBCAFMAVABJAFQAVQBUAEUAKABDAGUAbABsACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEALABcACIAXAAiACkALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABEAGUAbABpAG0AaQB0AGUAcgAsAFwAIgBcAHUAMAAwADMAYwAvAHMAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAXABuACAAIAAgACAAIAAgACAAIAApACAAXAB1ADAAMAAyADYAXABuACAAIAAgACAAIAAgACAAIABcACIAXAB1ADAAMAAzAGMALwBzAFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAC8AdABcAHUAMAAwADMAZQBcACIALABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAvAC8AcwBcACIAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAdgBnAFQAZQBtAHAALABhAHYAZwBSAGEAaQBuACwAZgByAG8AcwB0AEQAYQB5AHMALABlAGwAZQB2ACwAbQBhAHAAXwBwAGUAdAAsAFwAbgAgACAAIAAgAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACwAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkALABtAGEAeABGAHIAbwBzAHQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4AUABFAFQAQQByAHIAYQB5ACwAbQBhAHgAUABFAFQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAYwBsAGkAbQBhAHQAZQBaAG8AbgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBSAGEAaQBuACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AYQB2AGcAUgBhAGkAbgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AZgByAG8AcwB0AEQAYQB5AHMAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AG0AYQBwAF8AcABlAHQAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AG0AYQBwAF8AcABlAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABBAEsARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAGMAbABpAG0AYQB0AGUAWgBvAG4AZQBBAHIAcgBhAHkALABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgADEAXABuACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAE0AaQBuAEEAcgByAGEAeQAsACAATQBhAHgAQQByAHIAYQB5ACwAIABJAHQAZQBtAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAE0AaQBuAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBhAHgAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABJAHQAZQBtAEEAcgByAGEAeQAsACAAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAQwByAGkAdABlAHIAaQBhADEALAAgAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5ACwAIABRAHUAYQBuAHQAaQB0AHkALAAgAFsATQB1AGwAdABpAHAAbABpAGUAcgBdACwAIABbAEMAcgBpAHQAZQByAGkAYQAyAF0ALABbAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQBdACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAG0AdQBsAHQAaQBwAGwAaQBlAHIALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgATQB1AGwAdABpAHAAbABpAGUAcgApACwAMQAsAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsAFwAbgAgACAAIAAgAHEAdQBhAG4AdABpAHQAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACoATQB1AGwAdABpAHAAbABpAGUAcgAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMQApACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADIALABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAcgBpAHQAZQByAGkAYQAyACkALAAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADIAKQApACwAXABuACAAIAAgACAAUwBVAE0AUABSAE8ARABVAEMAVAAoAGMAcgBpAHQAZQByAGkAYQAxACoAYwByAGkAdABlAHIAaQBhADIAKgBxAHUAYQBuAHQAaQB0AHkAKQBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAXABuACAAIAAgACAAIAAgACAAIABBACwAUwAtADMANgA1ACwAXABuACAAIAAgACAAIAAgACAAIAB5AGEALABZAEUAQQBSACgAQQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AGIALABZAEUAQQBSACgARQApACwAXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApAFwAdQAwADAAMwBjACAAUwApACwAXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAFwAdQAwADAAMwBlACAARQApACwAXABuACAAIAAgACAAIAAgACAAIABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsACAALwAqAGgAZQBsAHAAZQByADoAIABlAG4AZAAgAGQAYQB0AGUAIABmAG8AcgAgAGEAIAByAGUAcABvAHIAdABpAG4AZwAgAHAAZQByAGkAbwBkACAAcwB0AGEAcgB0AGkAbgBnACAAYQB0ACAAYQAgAGcAaQB2AGUAbgAgAGQAYQB0AGUAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAIAAvACoAbwBuAGwAeQAgAG4AZQBlAGQAIAB0AG8AIABsAG8AbwBrACAAYgBhAGMAawAgADMANgA1ACAAZABhAHkAcwAoAG0AYQB4ACAAbwB2AGUAcgBsAGEAcAAgAHcAaQBuAGQAbwB3ACkAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYQAgAGUAbgBkAHMAIABiAGUAZgBvAHIAZQAgAFMALABpAHQAIABjAGEAbgBcAHUAMAAwADIANwB0ACAAbwB2AGUAcgBsAGEAcAA7ACAAbQBvAHYAZQAgAHQAbwAgAG4AZQB4AHQAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAXAB1ADAAMAAzAGMAUwApACwAIAAvACoAaQBmACAAdABoAGUAIABhAG4AYwBoAG8AcgAgAGYAbwByACAAeQBiACAAcwB0AGEAcgB0AHMAIABhAGYAdABlAHIAIABFACwAaQB0ACAAYwBhAG4AXAB1ADAAMAAyADcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABwAHIAZQB2AGkAbwB1AHMAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAXAB1ADAAMAAzAGUARQApACwAXABuACAAIAAgACAAIAAgACAAIABuACwATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAcgBzACwAUwBFAFEAVQBFAE4AQwBFACgAbgAsADEALABmAGkAcgBzAHQAWQBlAGEAcgAsADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMALABEAEEAVABFACgAeQByAHMALABtACwAZAApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzACwATQBBAFAAKABzAHQAYQByAHQAcwAsAFAAZQByAGkAbwBkAEUAbgBkACkALABcAG4AIAAgACAAIAAgACAAIAAgAHQAYQBnACwASQBGACgAcwB0AGEAcgB0AHMAPQBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXAAiACAAKABUAGgAaQBzACAAcgBlAHAAbwByAHQAaQBuAGcAIABjAHkAYwBsAGUAKQBcACIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzAFQAZQB4AHQALABUAEUAWABUACgAcwB0AGEAcgB0AHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzAFQAZQB4AHQALABUAEUAWABUACgAZQBuAGQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAG4APQAwACwAXAAiAFwAIgAsAEgAUwBUAEEAQwBLACgAcwB0AGEAcgB0AHMAVABlAHgAdAAgAFwAdQAwADAAMgA2ACAAXAAiACAAdABvACAAXAAiACAAXAB1ADAAMAAyADYAIABlAG4AZABzAFQAZQB4AHQAIABcAHUAMAAwADIANgAgAHQAYQBnACkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQBcAG4APQBMAEEATQBCAEQAQQAoAEYAdQBuAGMAdABpAG8AbgAsACAAVABFAFgAVABCAEUARgBPAFIARQAoAEYATwBSAE0AVQBMAEEAVABFAFgAVAAoAEYAdQBuAGMAdABpAG8AbgApACwAIABcACIAKABcACIAKQApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBBAHIAcgBhAHkALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5ACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkALABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAA9AFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABJAEYAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACAAPQAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALAAgAFwAIgBBAG4AeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5AD0AUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZABBAHIAcgBhAHkAPQBJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkAPQBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQAIAArACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAFwAdQAwADAAMwBlADAALAAgADEALAAgADAAKQBcAG4AIAAgACAAIAApACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsAFwAbgAgACAAIAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAdQAwADAAMgA3AFwAIgAgAFwAdQAwADAAMgA2ACAAcwBoACAAXAB1ADAAMAAyADYAIABcACIAXAB1ADAAMAAyADcAIQBcACIAIABcAHUAMAAwADIANgAgAGEAZABkAHIAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsARABpAGYAZgBlAHIAZQBuAHQAUwBoAGUAZQB0AFwAbgA9AEwAQQBNAEIARABBACgAVABhAHIAZwBlAHQAQwBlAGwAbAAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABzAGgALAAgAFQARQBYAFQAQQBGAFQARQBSACgAQwBFAEwATAAoAFwAIgBmAGkAbABlAG4AYQBtAGUAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALAAgAFwAIgBdAFwAIgApACwAXABuACAAIAAgACAAYQBkAGQAcgAsACAAQwBFAEwATAAoAFwAIgBhAGQAZAByAGUAcwBzAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAXABuACAAIAAgACAAXAAiACMAXAAiACAAXAB1ADAAMAAyADYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAxAF8AMgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADEALAAgADIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAzAF8ANABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADMALAAgADQAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBHAGUAdABNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAATQBNAFMALAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFwAbgAgACAAIAAgACAAIAAgACAATQBFAEQASQBBAE4AKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFUATgBEACgAVABlAG0AcABlAHIAYQB0AHUAcgBlACwAIAAwACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEkATgAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0AQQBYACgAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAE0ATQBTACwAIABNAE0AUwBBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUgBlAHMAdQBsAHQAcwBJAHQAZQBtAEYAcgBvAG0ARQBxAHUAYQB0AGkAbwBuAFQAaQB0AGwAZQBBAG4AZABTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAaQB0AGwAZQBDAGUAbABsACwAIABTAG8AdQByAGMAZQBDAGUAbABsACwAXABuACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAEwARQBGAFQAKABTAG8AdQByAGMAZQBDAGUAbABsACwAIABGAEkATgBEACgAXAAiACwAXAAiACwAIABTAG8AdQByAGMAZQBDAGUAbABsACkAIAAtADEAKQAsACAAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFwAIgAsACAAXAAiAFwAIgApACAAXAB1ADAAMAAyADYAIABcACIAIABcACIAIABcAHUAMAAwADIANgAgAFQAaQB0AGwAZQBDAGUAbABsAFwAbgApADsAIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ARgB1AGUAbAAgAHMAYwBvAHAAZQAgADEAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAALQAgAFMAdABhAHQAaQBvAG4AYQByAHkAIABnAGEAcwBlAG8AdQBzACAAZgB1AGUAbABzAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8AVABpAHQAbABlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIARgB1AGUAbAAgAHMAYwBvAHAAZQAgADEAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAALQAgAFMAdABhAHQAaQBvAG4AYQByAHkAIABnAGEAcwBlAG8AdQBzACAAZgB1AGUAbABzAFwAIgApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBEAGkAcgBlAGMAdAAgACgAUwBjAG8AcABlACAAMQApACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAdABoAGUAIABjAG8AbgBzAHUAbQBwAHQAaQBvAG4AIABvAGYAIABnAGEAcwBlAG8AdQBzACAAZgB1AGUAbABzACAAaQBuAGMAbAB1AGQAaQBuAGcAIABsAGkAcQB1AGUAZgBpAGUAZAAgAG4AYQB0AHUAcgBhAGwAIABnAGEAcwAgACAAXAAiACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAE4AYQB0AGkAbwBuAGEAbAAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABBAGMAYwBvAHUAbgB0AHMAIABGAGEAYwB0AG8AcgBzACAAMgAwADIANQAgAC0AIABUAGEAYgBsAGUAIAA1AFwAIgApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAOQAsACAANwAsAFwAbgAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBGAHUAZQBsACAAYwBvAG0AYgB1AHMAdABlAGQAXAAiACwAIABcACIARQBuAGUAcgBnAHkAIABDAG8AbgB0AGUAbgB0ACAARgBhAGMAdABvAHIAIAAoAEcASgAgAHAAZQByACAAdQBuAGkAdAAgAG8AZgAgAGYAdQBlAGwAKQBcACIALAAgAFwAIgBGAHUAZQBsACAAdQBuAGkAdABcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAxACAARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAIAAoAGsAZwAgAEMATwAyACAALQAgAGUAIAAvACAARwBKACkAIABDAE8AMgBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAxACAARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAIAAoAGsAZwAgAEMATwAyACAALQAgAGUAIAAvACAARwBKACkAIABDAEgANABcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAxACAARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAIAAoAGsAZwAgAEMATwAyACAALQAgAGUAIAAvACAARwBKACkAIABOADIATwBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAxACAARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAIAAoAGsAZwAgAEMATwAyACAALQAgAGUAIAAvACAARwBKACkAIABDAG8AbQBiAGkAbgBlAGQAIABnAGEAcwBlAHMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIATgBhAHQAdQByAGEAbAAgAGcAYQBzACAAZABpAHMAdAByAGkAYgB1AHQAZQBkACAAaQBuACAAYQAgAHAAaQBwAGUAbABpAG4AZQBcACIALAAgADAALgAwADMAOQAzACwAIABcACIAbQAzAFwAIgAsACAANQAxAC4ANAAsACAAMAAuADEALAAgADAALgAwADMALAAgADUAMQAuADUAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBhAGwAIABzAGUAYQBtACAAbQBlAHQAaABhAG4AZQAgAHQAaABhAHQAIABpAHMAIABjAGEAcAB0AHUAcgBlAGQAIABmAG8AcgAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AXAAiACwAIAAwAC4AMAAzADcANwAsACAAXAAiAG0AMwBcACIALAAgADUAMQAuADQALAAgADAALgAyACwAIAAwAC4AMAAzACwAIAA1ADEALgA2ADMAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AYQBsACAAbQBpAG4AZQAgAHcAYQBzAHQAZQAgAGcAYQBzACAAdABoAGEAdAAgAGkAcwAgAGMAYQBwAHQAdQByAGUAZAAgAGYAbwByACAAYwBvAG0AYgB1AHMAdABpAG8AbgBcACIALAAgADAALgAwADMANwA3ACwAIABcACIAbQAzAFwAIgAsACAANQAxAC4AOQAsACAANAAuADYALAAgADAALgAzACwAIAA1ADYALgA4ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBvAG0AcAByAGUAcwBzAGUAZAAgAG4AYQB0AHUAcgBhAGwAIABnAGEAcwAoAHIAZQB2AGUAcgB0AGkAbgBnACAAdABvACAAcwB0AGEAbgBkAGEAcgBkACAAYwBvAG4AZABpAHQAaQBvAG4AcwApAFwAIgAsACAAMAAuADAAMwA5ADMALAAgAFwAIgBtADMAXAAiACwAIAA1ADEALgA0ACwAIAAwAC4AMQAsACAAMAAuADAAMwAsACAANQAxAC4ANQAzADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVQBuAHAAcgBvAGMAZQBzAHMAZQBkACAAbgBhAHQAdQByAGEAbAAgAGcAYQBzAFwAIgAsACAAMAAuADAAMwA5ADMALAAgAFwAIgBtADMAXAAiACwAIAA1ADEALgA0ACwAIAAwAC4AMQAsACAAMAAuADAAMwAsACAANQAxAC4ANQAzADsAXABuACAAIAAgACAAIAAgACAAIABcACIARQB0AGgAYQBuAGUAXAAiACwAIAAwAC4AMAA2ADIAOQAsACAAXAAiAG0AMwBcACIALAAgADUANgAuADUALAAgADAALgAwADMALAAgADAALgAwADMALAAgADUANgAuADUANgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBrAGUAIABvAHYAZQBuACAAZwBhAHMAXAAiACwAIAAwAC4AMAAxADgAMQAsACAAXAAiAG0AMwBcACIALAAgADMANwAuADAALAAgADAALgAwADMALAAgADAALgAwADUALAAgADMANwAuADAAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEIAbABhAHMAdAAgAGYAdQByAG4AYQBjAGUAIABnAGEAcwBcACIALAAgADAALgAwADAANAAwACwAIABcACIAbQAzAFwAIgAsACAAMgAzADQALgAwACwAIAAwAC4AMAAzACwAIAAwAC4AMAAyACwAIAAyADMANAAuADAANQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFQAbwB3AG4AIABnAGEAcwBcACIALAAgADAALgAwADMAOQAwACwAIABcACIAbQAzAFwAIgAsACAANgAwAC4AMgAsACAAMAAuADAANAAsACAAMAAuADAAMwAsACAANgAwAC4AMgA3ADsAXABuACAAIAAgACAAIAAgACAAIABcACIATABpAHEAdQBlAGYAaQBlAGQAIABuAGEAdAB1AHIAYQBsACAAZwBhAHMAXAAiACwAIAAyADUALgAzACwAIABcACIAawBMAFwAIgAsACAANQAxAC4ANAAsACAAMAAuADEALAAgADAALgAwADMALAAgADUAMQAuADUAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEcAYQBzAGUAbwB1AHMAIABmAG8AcwBzAGkAbAAgAGYAdQBlAGwAcwAgAG8AdABoAGUAcgAgAHQAaABhAG4AIAB0AGgAbwBzAGUAIABtAGUAbgB0AGkAbwBuAGUAZAAgAGkAbgAgAHQAaABlACAAaQB0AGUAbQBzACAAYQBiAG8AdgBlAFwAIgAsACAAMAAuADAAMwA5ADAALAAgAFwAIgBtADMAXAAiACwAIAA1ADEALgA0ACwAIAAwAC4AMQAsACAAMAAuADAAMwAsACAANQAxAC4ANQAzADsAXABuACAAIAAgACAAIAAgACAAIABcACIATABhAG4AZABmAGkAbABsACAAYgBpAG8AZwBhAHMAIAB0AGgAYQB0ACAAaQBzACAAYwBhAHAAdAB1AHIAZQBkACAAZgBvAHIAIABjAG8AbQBiAHUAcwB0AGkAbwBuACAAKABtAGUAdABoAGEAbgBlACAAbwBuAGwAeQApAFwAIgAsACAAMAAuADAAMwA3ADcALAAgAFwAIgBtADMAXAAiACwAIAAwAC4AMAAsACAANgAuADQALAAgADAALgAwADMALAAgADYALgA0ADMAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAGwAdQBkAGcAZQAgAGIAaQBvAGcAYQBzACAAdABoAGEAdAAgAGkAcwAgAGMAYQBwAHQAdQByAGUAZAAgAGYAbwByACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgACgAbQBlAHQAaABhAG4AZQAgAG8AbgBsAHkAKQBcACIALAAgADAALgAwADMANwA3ACwAIABcACIAbQAzAFwAIgAsACAAMAAuADAALAAgADYALgA0ACwAIAAwAC4AMAAzACwAIAA2AC4ANAAzADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQQAgAGIAaQBvAGcAYQBzACAAdABoAGEAdAAgAGkAcwAgAGMAYQBwAHQAdQByAGUAZAAgAGYAbwByACAAYwBvAG0AYgB1AHMAdABpAG8AbgAsACAAbwB0AGgAZQByACAAdABoAGEAbgAgAHQAaABvAHMAZQAgAG0AZQBuAHQAaQBvAG4AZQBkACAAaQBuACAAdABoAGUAIABpAHQAZQBtAHMAIABhAGIAbwB2AGUAXAAiACwAIAAwAC4AMAAzADcAMAAsACAAXAAiAG0AMwBcACIALAAgADAALgAwACwAIAA2AC4ANAAsACAAMAAuADAAMwAsACAANgAuADQAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEIAaQBvAG0AZQB0AGgAYQBuAGUAXAAiACwAIAAwAC4AMAAzADkAMwAsACAAXAAiAG0AMwBcACIALAAgADAALgAwACwAIAAwAC4AMQAsACAAMAAuADAAMwAsACAAMAAuADEAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAeQBkAHIAbwBnAGUAbgBcACIALAAgADAALgAwADEAMgAyACwAIABcACIAbQAzAFwAIgAsACAAMAAuADAALAAgADAALgAwACwAIAAwAC4ANQAsACAAMAAuADUAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBOAGEAdAB1AHIAYQBsACAAZwBhAHMAIABkAGkAcwB0AHIAaQBiAHUAdABlAGQAIABpAG4AIABhACAAcABpAHAAZQBsAGkAbgBlACAALQAgAEcAaQBnAGEAagBvAHUAbABlAHMAXAAiACwAIAAxACwAIABcACIARwBKAFwAIgAsACAANQAxAC4ANAAsACAAMAAuADEALAAgADAALgAwADMALAAgADUAMQAuADUAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFQAbwB3AG4AIABnAGEAcwAgAC0AIABHAGkAZwBhAGoAbwB1AGwAZQBzAFwAIgAsACAAMQAsACAAXAAiAEcASgBcACIALAAgADYAMAAuADIALAAgADAALgAwADQALAAgADAALgAwADMALAAgADYAMAAuADIANwBcAG4AIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgApACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAFwAdQAwADAAMgA3AE4AYQB0AHUAcgBhAGwAIABnAGEAcwAgAGQAaQBzAHQAcgBpAGIAdQB0AGUAZAAgAGkAbgAgAGEAIABwAGkAcABlAGwAaQBuAGUAIAAtACAARwBpAGcAYQBqAG8AdQBsAGUAcwBcAHUAMAAwADIANwAgAGEAbgBkACAAXAB1ADAAMAAyADcAVABvAHcAbgAgAGcAYQBzACAALQAgAEcAaQBnAGEAagBvAHUAbABlAHMAXAB1ADAAMAAyADcAIAB3AGUAcgBlACAAYQBkAGQAZQBkACwAIABlAGEAYwBoACAAdwBpAHQAaAAgAGEAbgAgAGUAbgBlAHIAZwB5ACAAYwBvAG4AdABlAG4AdAAgAGYAYQBjAHQAbwByACAAbwBmACAAMQAgAEcASgAgAHAAZQByACAAdQBuAGkAdAAgAG8AZgAgAGYAdQBlAGwALgAgAFQAaABpAHMAIABpAHMAIABmAG8AcgAgAHUAcwBlAHIAcwAgAHcAaABvACAAaABhAHYAZQAgAGYAdQBlAGwAIABjAG8AbgBzAHUAbQBwAHQAaQBvAG4AIABkAGEAdABhACAAaQBuACAARwBKACAAcgBhAHQAaABlAHIAIAB0AGgAYQBuACAAbQAzAC4AXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ARgB1AGUAbAAgAHMAYwBvAHAAZQAgADMAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAALQAgAFMAdABhAHQAaQBvAG4AYQByAHkAIABnAGEAcwBlAG8AdQBzACAAZgB1AGUAbABzAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8AVABpAHQAbABlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIARgB1AGUAbAAgAHMAYwBvAHAAZQAgADMAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAALQAgAFMAdABhAHQAaQBvAG4AYQByAHkAIABnAGEAcwBlAG8AdQBzACAAZgB1AGUAbABzAFwAIgApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBJAG4AZABpAHIAZQBjAHQAIAAoAFMAYwBvAHAAZQAgADMAKQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAHQAaABlACAAYwBvAG4AcwB1AG0AcAB0AGkAbwBuACAAbwBmACAAbgBhAHQAdQByAGEAbAAgAGcAYQBzAC4AXAAiACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAE4AYQB0AGkAbwBuAGEAbAAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABBAGMAYwBvAHUAbgB0AHMAIABGAGEAYwB0AG8AcgBzACAAMgAwADIANQAgAC0AIABUAGEAYgBsAGUAIAA2AFwAIgApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALABcAG4AIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIABcACIAUwB0AGEAdABlACAAbwByACAAdABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAUwBjAG8AcABlACAAMwAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByAHMAIABmAG8AcgAgAE4AYQB0AHUAcgBhAGwAIABHAGEAcwAgACgAawBnACAAQwBPADIAIAAtACAAZQAgAC8AIABHAEoAKQAgAE0AZQB0AHIAbwBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAzACAARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAcwAgAGYAbwByACAATgBhAHQAdQByAGEAbAAgAEcAYQBzACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAATgBvAG4AIAAtACAATQBlAHQAcgBvAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE4AZQB3ACAAUwBvAHUAdABoACAAVwBhAGwAZQBzAFwAIgAsACAAMQAzAC4AMQAsACAAMQA0AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEEAQwBUAFwAIgAsACAAMQAzAC4AMQAsACAAMQA0AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgADQALgAwACwAIAA0AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIAA4AC4AOAAsACAANwAuADkAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAG8AdQB0AGgAIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgADEAMAAuADcALAAgADEAMAAuADYAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIAA0AC4AMQAsACAANAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBUAGEAcwBtAGEAbgBpAGEAXAAiACwAIAA0AC4AMAAsACAANAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AcgB0AGgAZQByAG4AIABUAGUAcgByAGkAdABvAHIAeQBcACIALAAgADQALgAxACwAIAA0AC4AMABcAG4AIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgApACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAE4AUwBXACAAYQBuAGQAIABBAEMAVAAgAHMAcABsAGkAdAAgAGkAbgB0AG8AIABzAGUAcABhAHIAYQB0AGUAIAByAG8AdwBzAC4AIABcAHUAMAAwADIANwBDAFwAdQAwADAAMgA3ACAAVgBhAGwAdQBlAHMAIABmAG8AcgAgAFQAYQBzAG0AYQBuAGkAYQAgAGEAbgBkACAATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAIAByAGUAcABsAGEAYwBlAGQAIAB3AGkAdABoACAAdABoAG8AcwBlACAAZgBvAHIAIABWAGkAYwB0AG8AcgBpAGEAIABhAG4AZAAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAHIAZQBzAHAAZQBjAHQAaQB2AGUAbAB5AC4AIAAoAFMAZQBlACAAYQBwAHAAZQBuAGQAaQBjAGUAcwApAFwAIgApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBBAHAAcABlAG4AZABpAGMAZQBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMgAsACAAMgAsAFwAbgAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAtAFwAIgAsACAAXAAiAEEAcwAgAFMAYwBvAHAAZQAgADMAIABmAGEAYwB0AG8AcgBzACAAYQByAGUAIABjAGEAbABjAHUAbABhAHQAZQBkACAAYQB0ACAAdABoAGUAIABwAG8AaQBuAHQAIAB3AGgAZQByAGUAIABuAGEAdAB1AHIAYQBsACAAZwBhAHMAIABpAHMAIABkAGUAbABpAHYAZQByAGUAZAAgAHQAbwAgAGUAbgBkACAAdQBzAGUAcgBzACwAIABpAHQAIABpAHMAIABuAGUAYwBlAHMAcwBhAHIAeQAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAYwBvAG4AcwB1AG0AcAB0AGkAbwBuACAAYQB0ACAAZQBhAGMAaAAgAG8AZgAgAHQAaABlACAAbABvAGEAZAAgAGMAZQBuAHQAcgBlAHMALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBHAGEAcwAgAHIAZQBhAGMAaABlAHMAIABlAG4AZAAgAHUAcwBlAHIAcwAgAGUAaQB0AGgAZQByACAAZgByAG8AbQAgAHQAaABlACAAbQBlAHQAcgBvACAAZABpAHMAdAByAGkAYgB1AHQAaQBvAG4AIABuAGUAdAB3AG8AcgBrAHMAIABvAHIAIABkAGkAcgBlAGMAdAAgAGYAcgBvAG0AIAB0AGgAZQAgAGgAaQBnAGgAIAAtACAAcAByAGUAcwBzAHUAcgBlACAAZABpAHMAdAByAGkAYgB1AHQAaQBvAG4AIABwAGkAcABlAGwAaQBuAGUAcwAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAEgAbwB1AHMAZQBoAG8AbABkAHMAIABhAG4AZAAgAGMAbwBtAG0AZQByAGMAaQBhAGwAIAB1AHMAZQByAHMAIAB0AGUAbgBkACAAdABvACAAYgBlACAAcwBlAHIAdgBlAGQAIABiAHkAIAB0AGgAZQAgAGYAbwByAG0AZQByACwAIABhAG4AZAAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQAgAGcAZQBuAGUAcgBhAHQAbwByAHMAIABhAG4AZAAgAGwAYQByAGcAZQAgAGkAbgBkAHUAcwB0AHIAaQBhAGwAIABwAGwAYQBuAHQAcwAgAGYAcgBvAG0AIAB0AGgAZQAgAGwAYQB0AHQAZQByAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIALQBcACIALAAgAFwAIgBNAGUAdAByAG8AIABpAHMAIABkAGUAZgBpAG4AZQBkACAAYQBzACAAbABvAGMAYQB0AGUAZAAgAG8AbgAgAG8AcgAgAGUAYQBzAHQAIABvAGYAIAB0AGgAZQAgAGQAaQB2AGkAZABpAG4AZwAgAHIAYQBuAGcAZQAgAGkAbgAgAE4AUwBXACwAIABpAG4AYwBsAHUAZABpAG4AZwAgAEMAYQBuAGIAZQByAHIAYQAgAGEAbgBkACAAUQB1AGUAYQBuAGIAZQB5AGEAbgAsACAATQBlAGwAYgBvAHUAcgBuAGUALAAgAEIAcgBpAHMAYgBhAG4AZQAsACAAQQBkAGUAbABhAGkAZABlACAAbwByACAAUABlAHIAdABoAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIATwB0AGgAZQByAHcAaQBzAGUALAAgAHQAaABlACAAbgBvAG4AIAAtACAAbQBlAHQAcgBvACAAZgBhAGMAdABvAHIAIABzAGgAbwB1AGwAZAAgAGIAZQAgAHUAcwBlAGQALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAtAFwAIgAsACAAXAAiAEYAYQBjAHQAbwByAHMAIABhAHIAZQAgAGMAYQBsAGMAdQBsAGEAdABlAGQAIABmAG8AcgAgAGEAbABsACAAbgBhAHQAdQByAGEAbAAgAGcAYQBzACAAZABpAHMAdAByAGkAYgB1AHQAZQBkACAAaQBuACAAYQAgAHAAaQBwAGUAbABpAG4AZQAgAHcAaABpAGMAaAAgAG0AYQB5ACAAaQBuAGMAbAB1AGQAZQAgAGMAbwBhAGwAIABzAGUAYQBtACAAbQBlAHQAaABhAG4AZQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAC0AXAAiACwAIABcACIAVABhAGIAbABlACAANgAgAGkAcwAgAG4AbwB0ACAAYQBwAHAAbABpAGMAYQBiAGwAZQAgAHQAbwAgAGUAdABoAGEAbgBlAC4AIABTAGUAZQAgAFQAYQBiAGwAZQAgADcAIABJAG4AZABpAHIAZQBjAHQAIAAoAFMAYwBvAHAAZQAgADMAKQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHQAaABlACAAYwBvAG4AcwB1AG0AcAB0AGkAbwBuACAAbwBmACAAZQB0AGgAYQBuAGUALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAtAFwAIgAsACAAXAAiAEMAIAA9ACAAQwBvAG4AZgBpAGQAZQBuAHQAaQBhAGwALgAgAFMAYwBvAHAAZQAgADMAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABUAGEAcwBtAGEAbgBpAGEAIABhAG4AZAAgAHQAaABlACAATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAIABhAHIAZQAgAG4AbwB0ACAAYQB2AGEAaQBsAGEAYgBsAGUAIABkAHUAZQAgAHQAbwAgAGMAbwBuAGYAaQBkAGUAbgB0AGkAYQBsAGkAdAB5ACAAYwBvAG4AcwB0AHIAYQBpAG4AdABzACAAdABoAGEAdAAgAGEAcgBpAHMAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBmAHIAbwBtACAAdABoAGUAIAB1AHMAZQAgAG8AZgAgAGEAIABsAGkAbQBpAHQAZQBkACAAbgB1AG0AYgBlAHIAIABvAGYAIABOAEcARQBSACAAZABhAHQAYQAgAGkAbgBwAHUAdABzAC4AIABJAHQAIABpAHMAIABzAHUAZwBnAGUAcwB0AGUAZAAgAHQAaABhAHQAIABmAG8AcgAgAFQAYQBzAG0AYQBuAGkAYQAgAHQAaABlACAAdQBzAGUAIABvAGYAIAB0AGgAZQAgAFYAaQBjAHQAbwByAGkAYQBuACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGkAcwAgAGEAcABwAHIAbwBwAHIAaQBhAHQAZQAsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAHcAaABpAGwAZQAgAGYAbwByACAATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAIAB0AGgAZQAgAHUAcwBlACAAbwBmACAAdABoAGUAIABXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABpAHMAIABhAHAAcAByAG8AcAByAGkAYQB0AGUALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAtAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADMAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZABvACAAbgBvAHQAIABpAG4AYwBsAHUAZABlACAAZgB1AGcAaQB0AGkAdgBlACAAZQBtAGkAcwBzAGkAbwBuACAAbABlAGEAawBhAGcAZQAgAGYAcgBvAG0AIABsAG8AdwAgAHAAcgBlAHMAcwB1AHIAZQAgAG4AYQB0AHUAcgBhAGwAIABnAGEAcwAgAGQAaQBzAHQAcgBpAGIAdQB0AGkAbwBuACAAcABpAHAAZQBsAGkAbgBlACAAbgBlAHQAdwBvAHIAawBzACAAdwBoAGkAbABlACAAdABoAG8AcwBlACAAZgByAG8AbQAgAGgAaQBnAGgAIABwAHIAZQBzAHMAdQByAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAZwBhAHMAIABuAGUAdAB3AG8AcgBrAHMAIABhAHIAZQAgAGMAbwBuAHMAaQBkAGUAcgBlAGQAIABuAGUAZwBsAGkAZwBpAGIAbABlAC4AXAAiAFwAbgAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACkAKQApADsAXABuAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBGAHUAZQBsACAAcwBjAG8AcABlACAAMQAgAGEAbgBkACAAMwAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIAAtACAAUwB0AGEAdABpAG8AbgBhAHIAeQAgAGwAaQBxAHUAaQBkACAAZgB1AGUAbABzAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBMAGkAcQB1AGkAZABfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEYAdQBlAGwAIABzAGMAbwBwAGUAIAAxACAAYQBuAGQAIAAzACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAC0AIABTAHQAYQB0AGkAbwBuAGEAcgB5ACAAbABpAHEAdQBpAGQAIABmAHUAZQBsAHMAXAAiACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkATABpAHEAdQBpAGQAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBEAGkAcgBlAGMAdAAgACgAUwBjAG8AcABlACAAMQApACAAYQBuAGQAIABpAG4AZABpAHIAZQBjAHQAIAAoAHMAYwBvAHAAZQAgADMAKQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAHQAaABlACAAYwBvAG4AcwB1AG0AcAB0AGkAbwBuACAAbwBmACAAbABpAHEAdQBpAGQAIABmAHUAZQBsAHMALAAgAGkAbgBjAGwAdQBkAGkAbgBnACAAYwBlAHIAdABhAGkAbgAgAHAAZQB0AHIAbwBsAGUAdQBtACAAYgBhAHMAZQBkACAAcAByAG8AZAB1AGMAdABzACAAZgBvAHIAIABzAHQAYQB0AGkAbwBuAGEAcgB5ACAAZQBuAGUAcgBnAHkAIABwAHUAcgBwAG8AcwBlAHMALgBcACIAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBMAGkAcQB1AGkAZABfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAE4AYQB0AGkAbwBuAGEAbAAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABBAGMAYwBvAHUAbgB0AHMAIABGAGEAYwB0AG8AcgBzACAAMgAwADIANQAgAC0AIABUAGEAYgBsAGUAIAA4AFwAIgApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEwAaQBxAHUAaQBkAF8ARABhAHQAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyADUALAAgADgALABcAG4AIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIABcACIARgB1AGUAbAAgAGMAbwBtAGIAdQBzAHQAZQBkAFwAIgAsACAAXAAiAEUAbgBlAHIAZwB5ACAAQwBvAG4AdABlAG4AdAAgAEYAYQBjAHQAbwByACAAKABHAEoAIABwAGUAcgAgAHUAbgBpAHQAIABvAGYAIABmAHUAZQBsACkAXAAiACwAIABcACIARgB1AGUAbAAgAHUAbgBpAHQAXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAAQwBPADIAXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAAQwBIADQAXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAATgAyAE8AXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAAQwBvAG0AYgBpAG4AZQBkACAAZwBhAHMAZQBzAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADMAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgAgACgAawBnACAAQwBPADIAIAAtACAAZQAgAC8AIABHAEoAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAdAByAG8AbABlAHUAbQAgAGIAYQBzAGUAZAAgAG8AaQBsAHMAIAAoAG8AdABoAGUAcgAgAHQAaABhAG4AIABwAGUAdAByAG8AbABlAHUAbQAgAGIAYQBzAGUAZAAgAG8AaQBsACAAdQBzAGUAZAAgAGEAcwAgAGYAdQBlAGwAKQAsACAAZQAuAGcALgAgAGwAdQBiAHIAaQBjAGEAbgB0AHMAXAAiACwAIAAzADgALgA4ACwAIABcACIAawBsAFwAIgAsACAAMQAzAC4AOQAsACAAMAAuADAALAAgADAALgAwACwAIAAxADMALgA5ACwAIAAxADgALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUABlAHQAcgBvAGwAZQB1AG0AIABiAGEAcwBlAGQAIABnAHIAZQBhAHMAZQBzAFwAIgAsACAAMwA4AC4AOAAsACAAXAAiAGsAbABcACIALAAgADMALgA1ACwAIAAwAC4AMAAsACAAMAAuADAALAAgADMALgA1ACwAIAAxADgALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwByAHUAZABlACAAbwBpAGwAIABpAG4AYwBsAHUAZABpAG4AZwAgAGMAcgB1AGQAZQAgAG8AaQBsACAAYwBvAG4AZABlAG4AcwBhAHQAZQBzAFwAIgAsACAANAA1AC4AMwAsACAAXAAiAHQAXAAiACwAIAA2ADkALgA2ACwAIAAwAC4AMAA4ACwAIAAwAC4AMgAsACAANgA5AC4AOAA4ACwAIABcACIATgBFAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAG4AYQB0AHUAcgBhAGwAIABnAGEAcwAgAGwAaQBxAHUAaQBkAHMAXAAiACwAIAA0ADYALgA1ACwAIABcACIAdABcACIALAAgADYAMQAuADAALAAgADAALgAwADgALAAgADAALgAyACwAIAA2ADEALgAyADgALAAgAFwAIgBOAEUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQQB1AHQAbwBtAG8AdABpAHYAZQAgAGcAYQBzAG8AbABpAG4AZQAgAC8AIABwAGUAdAByAG8AbAAgACgAbwB0AGgAZQByACAAdABoAGEAbgAgAGYAbwByACAAdQBzAGUAIABhAHMAIABmAHUAZQBsACAAaQBuACAAYQBuACAAYQBpAHIAYwByAGEAZgB0ACkAXAAiACwAIAAzADQALgAyACwAIABcACIAawBMAFwAIgAsACAANgA3AC4ANAAsACAAMAAuADIALAAgADAALgAyACwAIAA2ADcALgA4ADAALAAgADEANwAuADIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAHYAaQBhAHQAaQBvAG4AIABnAGEAcwBvAGwAaQBuAGUAXAAiACwAIAAzADMALgAxACwAIABcACIAawBMAFwAIgAsACAANgA3ACwAIAAwAC4AMgAsACAAMAAuADIALAAgADYANwAuADQAMAAsACAAMQA4AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEsAZQByAG8AcwBlAG4AZQAgACgAbwB0AGgAZQByACAAdABoAGEAbgAgAGYAbwByACAAdQBzAGUAIABhAHMAIABmAHUAZQBsACAAaQBuACAAYQBuACAAYQBpAHIAYwByAGEAZgB0ACkAXAAiACwAIAAzADcALgA1ACwAIABcACIAawBMAFwAIgAsACAANgA4AC4AOQAsACAAMAAuADAAMQAsACAAMAAuADIALAAgADYAOQAuADEAMQAsACAAMQA4AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEEAdgBpAGEAdABpAG8AbgAgAHQAdQByAGIAaQBuAGUAIABmAHUAZQBsACAALwAgAGsAZQByAG8AcwBlAG4AZQBcACIALAAgADMANgAuADgALAAgAFwAIgBrAEwAXAAiACwAIAA2ADkALgA2ACwAIAAwAC4AMAAyACwAIAAwAC4AMgAsACAANgA5AC4AOAAyACwAIAAxADgALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABlAGEAdABpAG4AZwAgAG8AaQBsAFwAIgAsACAAMwA3AC4AMwAsACAAXAAiAGsATABcACIALAAgADYAOQAuADUALAAgADAALgAwADMALAAgADAALgAyACwAIAA2ADkALgA3ADMALAAgADEAOAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBEAGkAZQBzAGUAbAAgAG8AaQBsAFwAIgAsACAAMwA4AC4ANgAsACAAXAAiAGsATABcACIALAAgADYAOQAuADkALAAgADAALgAxACwAIAAwAC4AMgAsACAANwAwAC4AMgAwACwAIAAxADcALgAzADsAXABuACAAIAAgACAAIAAgACAAIABcACIARgB1AGUAbAAgAG8AaQBsAFwAIgAsACAAMwA5AC4ANwAsACAAXAAiAGsATABcACIALAAgADcAMwAuADYALAAgADAALgAwADQALAAgADAALgAyACwAIAA3ADMALgA4ADQALAAgADEAOAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBMAGkAcQB1AGUAZgBpAGUAZAAgAGEAcgBvAG0AYQB0AGkAYwAgAGgAeQBkAHIAbwBjAGEAcgBiAG8AbgBzAFwAIgAsACAAMwA0AC4ANAAsACAAXAAiAGsATABcACIALAAgADYAOQAuADcALAAgADAALgAwADMALAAgADAALgAyACwAIAA2ADkALgA5ADMALAAgADEAOAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAG8AbAB2AGUAbgB0AHMAOgAgAG0AaQBuAGUAcgBhAGwAIAB0AHUAcgBwAGUAbgB0AGkAbgBlACAAbwByACAAdwBoAGkAdABlACAAcwBwAGkAcgBpAHQAcwBcACIALAAgADMANAAuADQALAAgAFwAIgBrAEwAXAAiACwAIAA2ADkALgA3ACwAIAAwAC4AMAAzACwAIAAwAC4AMgAsACAANgA5AC4AOQAzACwAIAAxADgALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIATABpAHEAdQBlAGYAaQBlAGQAIABwAGUAdAByAG8AbABlAHUAbQAgAGcAYQBzACAAKABMAFAARwApAFwAIgAsACAAMgA1AC4ANwAsACAAXAAiAGsATABcACIALAAgADYAMAAuADIALAAgADAALgAyACwAIAAwAC4AMgAsACAANgAwAC4ANgAwACwAIAAyADAALgAyADsAXABuACAAIAAgACAAIAAgACAAIABcACIATgBhAHAAaAB0AGgAYQBcACIALAAgADMAMQAuADQALAAgAFwAIgBrAEwAXAAiACwAIAA2ADkALgA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxACwAIAA2ADkALgA4ADIALAAgADEAOAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAdAByAG8AbABlAHUAbQAgAGMAbwBrAGUAXAAiACwAIAAzADQALgAyACwAIABcACIAdABcACIALAAgADkAMgAuADYALAAgADAALgAwADgALAAgADAALgAyACwAIAA5ADIALgA4ADgALAAgADEAOAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAGUAZgBpAG4AZQByAHkAIABnAGEAcwAgAGEAbgBkACAAbABpAHEAdQBpAGQAcwBcACIALAAgADQAMgAuADkALAAgAFwAIgB0AFwAIgAsACAANQA0AC4ANwAsACAAMAAuADAAMwAsACAAMAAuADAAMwAsACAANQA0AC4ANwA2ACwAIAAxADgALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgBlAGYAaQBuAGUAcgB5ACAAYwBvAGsAZQBcACIALAAgADMANAAuADIALAAgAFwAIgB0AFwAIgAsACAAOQAyAC4ANgAsACAAMAAuADAAOAAsACAAMAAuADIALAAgADkAMgAuADgAOAAsACAAMQA4AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFAAZQB0AHIAbwBsAGUAdQBtACAAYgBhAHMAZQBkACAAcAByAG8AZAB1AGMAdABzACAAbwB0AGgAZQByACAAdABoAGEAbgAgAG0AZQBuAHQAaQBvAG4AZQBkACAAaQBuACAAdABoAGUAIABpAHQAZQBtAHMAIABhAGIAbwB2AGUAXAAiACwAIAAzADQALgA0ACwAIABcACIAawBMAFwAIgAsACAANgA5AC4AOAAsACAAMAAuADAAMgAsACAAMAAuADEALAAgADYAOQAuADkAMgAsACAAMQA4AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEIAaQBvAGQAaQBlAHMAZQBsAFwAIgAsACAAMwA0AC4ANgAsACAAXAAiAGsATABcACIALAAgADAALgAwACwAIAAwAC4AMAA4ACwAIAAwAC4AMgAsACAAMAAuADIAOAAsACAAXAAiAE4ARQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBFAHQAaABhAG4AbwBsACAAZgBvAHIAIAB1AHMAZQAgAGEAcwAgAGEAIABmAHUAZQBsACAAaQBuACAAYQBuACAAaQBuAHQAZQByAG4AYQBsACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgAGUAbgBnAGkAbgBlAFwAIgAsACAAMgAzAC4ANAAsACAAXAAiAGsATABcACIALAAgADAALgAwACwAIAAwAC4AMAA4ACwAIAAwAC4AMgAsACAAMAAuADIAOAAsACAAXAAiAE4ARQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBCAGkAbwBmAHUAZQBsAHMAIABvAHQAaABlAHIAIAB0AGgAYQBuACAAdABoAG8AcwBlACAAbQBlAG4AdABpAG8AbgBlAGQAIABpAG4AIAB0AGgAZQAgAGkAdABlAG0AcwAgAGEAYgBvAHYAZQAgAGEAbgBkACAAYgBlAGwAbwB3AFwAIgAsACAAMgAzAC4ANAAsACAAXAAiAGsATABcACIALAAgADAALgAwACwAIAAwAC4AMAA4ACwAIAAwAC4AMgAsACAAMAAuADIAOAAsACAAXAAiAE4ARQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAGUAbgBlAHcAYQBiAGwAZQAgAGEAdgBpAGEAdABpAG8AbgAgAGsAZQByAG8AcwBlAG4AZQBcACIALAAgADMANgAuADgALAAgAFwAIgBrAEwAXAAiACwAIAAwAC4AMAAsACAAMAAuADAAMgAsACAAMAAuADIALAAgADAALgAyADIALAAgAFwAIgBOAEUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgBlAG4AZQB3AGEAYgBsAGUAIABkAGkAZQBzAGUAbABcACIALAAgADMAOAAuADYALAAgAFwAIgBrAEwAXAAiACwAIAAwAC4AMAAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMwAwACwAIABcACIATgBFAFwAIgBcAG4AIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgApACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkATABpAHEAdQBpAGQAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAXAB1ADAAMAAyADcATgBFAFwAdQAwADAAMgA3ACAAdgBhAGwAdQBlAHMAIAByAGUAdAB1AHIAbgBlAGQAIABhAHMAIAB6AGUAcgBvACAAZgBvAHIAIABjAGEAbABjAHUAbABhAHQAaQBvAG4AcwAuAFwAIgApADsAXABuAFwAbgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAEYAdQBlAGwAIABzAGMAbwBwAGUAIAAxACAAYQBuAGQAIAAzACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAC0AIABUAHIAYQBuAHMAcABvAHIAdABcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AF8AVABpAHQAbABlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIARgB1AGUAbAAgAHMAYwBvAHAAZQAgADEAIABhAG4AZAAgADMAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAALQAgAFQAcgBhAG4AcwBwAG8AcgB0AFwAIgApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBUAHIAYQBuAHMAcABvAHIAdABfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEQAaQByAGUAYwB0ACAAKABzAGMAbwBwAGUAIAAxACkAIABhAG4AZAAgAGkAbgBkAGkAcgBlAGMAdAAgACgAcwBjAG8AcABlACAAMwApACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAdABoAGUAIABjAG8AbgBzAHUAbQBwAHQAaQBvAG4AIABvAGYAIAB0AHIAYQBuAHMAcABvAHIAdAAgAGYAdQBlAGwAcwAgAGkAbgAgAGQAaQBmAGYAZQByAGUAbgB0ACAAdAByAGEAbgBzAHAAbwByAHQAIABlAHEAdQBpAHAAbQBlAG4AdABcACIAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAVAByAGEAbgBzAHAAbwByAHQAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABOAGEAdABpAG8AbgBhAGwAIABHAHIAZQBlAG4AaABvAHUAcwBlACAAQQBjAGMAbwB1AG4AdABzACAARgBhAGMAdABvAHIAcwAgADIAMAAyADUAIAAtACAAVABhAGIAbABlACAAOQBcACIAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAVAByAGEAbgBzAHAAbwByAHQAXwBEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIANgAsACAAMQAwACwAXABuACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBhAG4AcwBwAG8AcgB0ACAAdAB5AHAAZQBcACIALAAgAFwAIgBGAHUAZQBsACAAYwBvAG0AYgB1AHMAdABlAGQAXAAiACwAIABcACIARQBuAGUAcgBnAHkAIABDAG8AbgB0AGUAbgB0ACAARgBhAGMAdABvAHIAKABHAEoAIABwAGUAcgAgAHUAbgBpAHQAIABvAGYAIABmAHUAZQBsACkAXAAiACwAIABcACIARgB1AGUAbAAgAHUAbgBpAHQAXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAAQwBPADIAXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAAQwBIADQAXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAATgAyAE8AXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAAQwBvAG0AYgBpAG4AZQBkACAAZwBhAHMAZQBzAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADMAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgAgACgAawBnACAAQwBPADIAIAAtACAAZQAgAC8AIABHAEoAKQBcACIALAAgAFwAIgBTAG8AdQByAGMAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAGEAcgBzACAAYQBuAGQAIABsAGkAZwBoAHQAIABjAG8AbQBtAGUAcgBjAGkAYQBsACAAdgBlAGgAaQBjAGwAZQBzAFwAIgAsACAAXAAiAEcAYQBzAG8AbABpAG4AZQBcACIALAAgADMANAAuADIALAAgAFwAIgBrAGwAXAAiACwAIAA2ADcALgA0ACwAIAAwAC4AMAAyACwAIAAwAC4AMgAsACAANgA3AC4ANgAyACwAIAAxADcALgAyACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBhAHIAcwAgAGEAbgBkACAAbABpAGcAaAB0ACAAYwBvAG0AbQBlAHIAYwBpAGEAbAAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBEAGkAZQBzAGUAbAAgAG8AaQBsAFwAIgAsACAAMwA4AC4ANgAsACAAXAAiAGsAbABcACIALAAgADYAOQAuADkALAAgADAALgAwADEALAAgADAALgA1ACwAIAA3ADAALgA0ADEALAAgADEANwAuADMALAAgAFwAIgBOAEcAQQBGACAAMgAwADIANQA6ACAAVABhAGIAbABlACAAOQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAGEAcgBzACAAYQBuAGQAIABsAGkAZwBoAHQAIABjAG8AbQBtAGUAcgBjAGkAYQBsACAAdgBlAGgAaQBjAGwAZQBzAFwAIgAsACAAXAAiAEwAaQBxAHUAZQBmAGkAZQBkACAAcABlAHQAcgBvAGwAZQB1AG0AIABnAGEAcwAgACgATABQAEcAKQBcACIALAAgADIANgAuADIALAAgAFwAIgBrAGwAXAAiACwAIAA2ADAALgAyACwAIAAwAC4ANQAsACAAMAAuADMALAAgADYAMQAuADAAMAAsACAAMgAwAC4AMgAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAYQByAHMAIABhAG4AZAAgAGwAaQBnAGgAdAAgAGMAbwBtAG0AZQByAGMAaQBhAGwAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIARgB1AGUAbAAgAG8AaQBsAFwAIgAsACAAMwA5AC4ANwAsACAAXAAiAGsAbABcACIALAAgADcAMwAuADYALAAgADAALgAwADgALAAgADAALgA1ACwAIAA3ADQALgAxADgALAAgADEAOAAuADAALAAgAFwAIgBOAEcAQQBGACAAMgAwADIANQA6ACAAVABhAGIAbABlACAAOQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAGEAcgBzACAAYQBuAGQAIABsAGkAZwBoAHQAIABjAG8AbQBtAGUAcgBjAGkAYQBsACAAdgBlAGgAaQBjAGwAZQBzAFwAIgAsACAAXAAiAEUAdABoAGEAbgBvAGwAXAAiACwAIAAyADMALgA0ACwAIABcACIAawBsAFwAIgAsACAAMAAuADAALAAgADAALgAyACwAIAAwAC4AMgAsACAAMAAuADQALAAgAFwAIgBOAEUAXAAiACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBhAHIAcwAgAGEAbgBkACAAbABpAGcAaAB0ACAAYwBvAG0AbQBlAHIAYwBpAGEAbAAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBCAGkAbwBkAGkAZQBzAGUAbABcACIALAAgADMANAAuADYALAAgAFwAIgBrAGwAXAAiACwAIAAwAC4AMAAsACAAMAAuADgALAAgADEALgA3ACwAIAAyAC4ANQAsACAAXAAiAE4ARQBcACIALAAgAFwAIgBOAEcAQQBGACAAMgAwADIANQA6ACAAVABhAGIAbABlACAAOQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAGEAcgBzACAAYQBuAGQAIABsAGkAZwBoAHQAIABjAG8AbQBtAGUAcgBjAGkAYQBsACAAdgBlAGgAaQBjAGwAZQBzAFwAIgAsACAAXAAiAFIAZQBuAGUAdwBhAGIAbABlACAAZABpAGUAcwBlAGwAXAAiACwAIAAzADgALgA2ACwAIABcACIAawBsAFwAIgAsACAAMAAuADAALAAgADAALgAwADEALAAgADAALgA1ACwAIAAwAC4ANQAxACwAIABcACIATgBFAFwAIgAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAYQByAHMAIABhAG4AZAAgAGwAaQBnAGgAdAAgAGMAbwBtAG0AZQByAGMAaQBhAGwAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIATwB0AGgAZQByACAAYgBpAG8AZgB1AGUAbABzAFwAIgAsACAAMgAzAC4ANAAsACAAXAAiAGsAbABcACIALAAgADAALgAwACwAIAAwAC4AOAAsACAAMQAuADcALAAgADIALgA1ACwAIABcACIATgBFAFwAIgAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEwAaQBnAGgAdAAgAGQAdQB0AHkAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIAQwBvAG0AcAByAGUAcwBzAGUAZAAgAG4AYQB0AHUAcgBhAGwAIABnAGEAcwBcACIALAAgADAALgAwADMAOQAzACwAIABcACIAbQAzAFwAIgAsACAANQAxAC4ANAAsACAANwAuADMALAAgADAALgAzACwAIAA1ADkALgAwACwAIAAxADgALgAwACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIATABpAGcAaAB0ACAAZAB1AHQAeQAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBMAGkAcQB1AGUAZgBpAGUAZAAgAG4AYQB0AHUAcgBhAGwAIABnAGEAcwBcACIALAAgADIANQAuADMALAAgAFwAIgBrAGwAXAAiACwAIAA1ADEALgA0ACwAIAA3AC4AMwAsACAAMAAuADMALAAgADUAOQAuADAALAAgADEAOAAuADAALAAgAFwAIgBOAEcAQQBGACAAMgAwADIANQA6ACAAVABhAGIAbABlACAAOQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAGUAYQB2AHkAIABkAHUAdAB5ACAAdgBlAGgAaQBjAGwAZQBzAFwAIgAsACAAXAAiAEMAbwBtAHAAcgBlAHMAcwBlAGQAIABuAGEAdAB1AHIAYQBsACAAZwBhAHMAXAAiACwAIAAwAC4AMAAzADkAMwAsACAAXAAiAG0AMwBcACIALAAgADUAMQAuADQALAAgADIALgA4ACwAIAAwAC4AMwAsACAANQA0AC4ANQAsACAAMQA4AC4AMAAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAZQBhAHYAeQAgAGQAdQB0AHkAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIATABpAHEAdQBlAGYAaQBlAGQAIABuAGEAdAB1AHIAYQBsACAAZwBhAHMAXAAiACwAIAAyADUALgAzACwAIABcACIAawBsAFwAIgAsACAANQAxAC4ANAAsACAAMgAuADgALAAgADAALgAzACwAIAA1ADQALgA1ACwAIAAxADgALgAwACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABlAGEAdgB5ACAAZAB1AHQAeQAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBEAGkAZQBzAGUAbAAgAG8AaQBsACAALQAgAEUAdQByAG8AIABpAHYAIABvAHIAIABoAGkAZwBoAGUAcgBcACIALAAgADMAOAAuADYALAAgAFwAIgBrAGwAXAAiACwAIAA2ADkALgA5ACwAIAAwAC4AMAA3ACwAIAAwAC4ANAAsACAANwAwAC4AMwA3ACwAIAAxADcALgAzACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABlAGEAdgB5ACAAZAB1AHQAeQAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBEAGkAZQBzAGUAbAAgAG8AaQBsACAALQAgAEUAdQByAG8AIABpAGkAaQBcACIALAAgADMAOAAuADYALAAgAFwAIgBrAGwAXAAiACwAIAA2ADkALgA5ACwAIAAwAC4AMQAsACAAMAAuADQALAAgADcAMAAuADQALAAgADEANwAuADMALAAgAFwAIgBOAEcAQQBGACAAMgAwADIANQA6ACAAVABhAGIAbABlACAAOQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAGUAYQB2AHkAIABkAHUAdAB5ACAAdgBlAGgAaQBjAGwAZQBzAFwAIgAsACAAXAAiAEQAaQBlAHMAZQBsACAAbwBpAGwAIAAtACAARQB1AHIAbwAgAGkAXAAiACwAIAAzADgALgA2ACwAIABcACIAawBsAFwAIgAsACAANgA5AC4AOQAsACAAMAAuADIALAAgADAALgA0ACwAIAA3ADAALgA1ACwAIAAxADcALgAzACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABlAGEAdgB5ACAAZAB1AHQAeQAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBSAGUAbgBlAHcAYQBiAGwAZQAgAGQAaQBlAHMAZQBsACAAEyAgAEUAdQByAG8AIABpAHYAIABvAHIAIABoAGkAZwBoAGUAcgBcACIALAAgADMAOAAuADYALAAgAFwAIgBrAGwAXAAiACwAIAAwAC4AMAAsACAAMAAuADAANwAsACAAMAAuADQALAAgADAALgA0ADcALAAgAFwAIgBOAEUAXAAiACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABlAGEAdgB5ACAAZAB1AHQAeQAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBSAGUAbgBlAHcAYQBiAGwAZQAgAGQAaQBlAHMAZQBsACAAEyAgAEUAdQByAG8AIABpAGkAaQBcACIALAAgADMAOAAuADYALAAgAFwAIgBrAGwAXAAiACwAIAAwAC4AMAAsACAAMAAuADEALAAgADAALgA0ACwAIAAwAC4ANQAsACAAXAAiAE4ARQBcACIALAAgAFwAIgBOAEcAQQBGACAAMgAwADIANQA6ACAAVABhAGIAbABlACAAOQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAGUAYQB2AHkAIABkAHUAdAB5ACAAdgBlAGgAaQBjAGwAZQBzAFwAIgAsACAAXAAiAFIAZQBuAGUAdwBhAGIAbABlACAAZABpAGUAcwBlAGwAIAATICAARQB1AHIAbwAgAGkAXAAiACwAIAAzADgALgA2ACwAIABcACIAawBsAFwAIgAsACAAMAAuADAALAAgADAALgAyACwAIAAwAC4ANAAsACAAMAAuADYALAAgAFwAIgBOAEUAXAAiACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQQB2AGkAYQB0AGkAbwBuAFwAIgAsACAAXAAiAEcAYQBzAG8AbABpAG4AZQAgAGYAbwByACAAdQBzAGUAIABhAHMAIABmAHUAZQBsACAAaQBuACAAYQBuACAAYQBpAHIAYwByAGEAZgB0AFwAIgAsACAAMwAzAC4AMQAsACAAXAAiAGsAbABcACIALAAgADYANwAuADAALAAgADAALgAwADYALAAgADAALgA2ACwAIAA2ADcALgA2ADYALAAgADEAOAAuADAALAAgAFwAIgBOAEcAQQBGACAAMgAwADIANQA6ACAAVABhAGIAbABlACAAOQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAHYAaQBhAHQAaQBvAG4AXAAiACwAIABcACIASwBlAHIAbwBzAGUAbgBlACAAZgBvAHIAIAB1AHMAZQAgAGEAcwAgAGYAdQBlAGwAIABpAG4AIABhAG4AIABhAGkAcgBjAHIAYQBmAHQAXAAiACwAIAAzADYALgA4ACwAIABcACIAawBsAFwAIgAsACAANgA5AC4ANgAsACAAMAAuADAAMQAsACAAMAAuADYALAAgADcAMAAuADIAMQAsACAAMQA4AC4AMAAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEEAdgBpAGEAdABpAG8AbgBcACIALAAgAFwAIgBSAGUAbgBlAHcAYQBiAGwAZQAgAGEAdgBpAGEAdABpAG8AbgAgAGsAZQByAG8AcwBlAG4AZQBcACIALAAgADMANgAuADgALAAgAFwAIgBrAGwAXAAiACwAIAAwAC4AMAAsACAAMAAuADAAMQAsACAAMAAuADYALAAgADAALgA2ADEALAAgAFwAIgBOAEUAXAAiACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVgBlAHMAcwBlAGwAcwBcACIALAAgAFwAIgBHAGEAcwBvAGwAaQBuAGUAXAAiACwAIAAzADQALgAyACwAIABcACIAawBMAFwAIgAsACAANgA3AC4ANAAsACAAMQAwAC4AMQAsACAAMAAuADMALAAgAFwAIgBcACIALAAgADEANwAuADIALAAgAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4ANAAuADIALgAxAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFYAZQBzAHMAZQBsAHMAXAAiACwAIABcACIARABpAGUAcwBlAGwAIABvAGkAbABcACIALAAgADMAOAAuADYALAAgAFwAIgBrAEwAXAAiACwAIAA2ADkALgA5ACwAIAAwAC4AMgAsACAAMAAuADUALAAgAFwAIgBcACIALAAgADEANwAuADMALAAgAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4ANAAuADIALgAxAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFYAZQBzAHMAZQBsAHMAXAAiACwAIABcACIARgB1AGUAbAAgAE8AaQBsAFwAIgAsACAAMwA5AC4ANwAsACAAXAAiAGsATABcACIALAAgADcAMwAuADYALAAgADAALgAyACwAIAAwAC4ANQAsACAAXAAiAFwAIgAsACAAMQA4AC4AMAAsACAAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgA0AC4AMgAuADEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwBmAGYALQByAG8AYQBkACAAQQBnAHIAaQBjAHUAbAB0AHUAcgBlACAAYQBuAGQAIABmAG8AcgBlAHMAdAByAHkAIABlAHEAdQBpAHAAbQBlAG4AdABcACIALAAgAFwAIgBEAGkAZQBzAGUAbAAgAG8AaQBsAFwAIgAsACAAMwA4AC4ANgAsACAAXAAiAGsATABcACIALAAgADYAOQAuADkALAAgADAALgAzACwAIAAwAC4ANQAsACAAXAAiAFwAIgAsACAAMQA3AC4AMwAsACAAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgA0AC4AMgAuADEAXAAiAFwAbgAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACkAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAVAByAGEAbgBzAHAAbwByAHQAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAXAB1ADAAMAAyADcATgBFAFwAdQAwADAAMgA3ACAAdgBhAGwAdQBlAHMAIAByAGUAdAB1AHIAbgBlAGQAIABhAHMAIAB6AGUAcgBvACAAZgBvAHIAIABjAGEAbABjAHUAbABhAHQAaQBvAG4AcwAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBGAHUAZQBsACAAcwBjAG8AcABlACAAMQAgAGEAbgBkACAAMwAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIAAtACAATwBmAGYALQByAGEAZAAgAGUAcQB1AGkAcABtAGUAbgB0ACAAYQBuAGQAIAB2AGUAcwBzAGUAbABzAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAVAByAGEAbgBzAHAAbwByAHQATwBmAGYAUgBvAGEAZABfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEYAdQBlAGwAIABzAGMAbwBwAGUAIAAxACAAYQBuAGQAIAAzACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAC0AIABPAGYAZgAtAHIAbwBhAGQAIABlAHEAdQBpAHAAbQBlAG4AdAAgAGEAbgBkACAAdgBlAHMAcwBlAGwAcwBcACIAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAVAByAGEAbgBzAHAAbwByAHQATwBmAGYAUgBvAGEAZABfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEQAaQByAGUAYwB0ACAAKABzAGMAbwBwAGUAIAAxACkAIABhAG4AZAAgAGkAbgBkAGkAcgBlAGMAdAAgACgAcwBjAG8AcABlACAAMwApACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAdABoAGUAIABjAG8AbgBzAHUAbQBwAHQAaQBvAG4AIABvAGYAIABmAHUAZQBsAHMAIABpAG4AIABvAGYAZgAtAHIAbwBhAGQAIABlAHEAdQBpAHAAbQBlAG4AdAAgAGEAbgBkACAAdgBlAHMAcwBlAGwAcwBcACIAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAVAByAGEAbgBzAHAAbwByAHQATwBmAGYAUgBvAGEAZABfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADQALgAyAC4AMQBcACIAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAVAByAGEAbgBzAHAAbwByAHQATwBmAGYAUgBvAGEAZABfAEQAYQB0AGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAANwAsAFwAbgAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAYQBuAHMAcABvAHIAdAAgAHQAeQBwAGUAIAB0AFwAIgAsACAAXAAiAEYAdQBlAGwAIAB0AHkAcABlACAAcQBcACIALAAgAFwAIgBFAEMAVAByAGEAbgBzACwAcQAgACgARwBKAC8AawBMACkAXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAEMATwAyACAARQBGAFQAcgBhAG4ALAAxACwAdABxAGcAIAAoAGsAZwAgAEMATwAyAC0AZQAvAEcASgApAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAIABDAEgANAAgAEUARgBUAHIAYQBuACwAMQAsAHQAZwBnACAAKABrAGcAIABDAE8AMgAtAGUALwBHAEoAKQBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAxACAATgAyAE8AIABFAEYAVAByAGEAbgAsADEALAB0AGcAZwAgACgAawBnACAAQwBPADIALQBlAC8ARwBKACkAXAAiACwAIABcACIAUwBjAG8AcABlACAAMwAgAEUARgBUAHIAYQBuAHMALAAzACwAcQAgACgAawBnACAAQwBPADIALQBlAC8ARwBKACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVgBlAHMAcwBlAGwAXAAiACwAIABcACIAUABlAHQAcgBvAGwAXAAiACwAIAAzADQALgAyACwAIAA2ADcALgA0ACwAIAAxADAALgAxACwAIAAwAC4AMwAsACAAMQA3AC4AMgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFYAZQBzAHMAZQBsAFwAIgAsACAAXAAiAEQAaQBlAHMAZQBsAFwAIgAsACAAMwA4AC4ANgAsACAANgA5AC4AOQAsACAAMAAuADIALAAgADAALgA1ACwAIAAxADcALgAzADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVgBlAHMAcwBlAGwAXAAiACwAIABcACIARgB1AGUAbAAgAE8AaQBsAFwAIgAsACAAMwA5AC4ANwAsACAANwAzAC4ANgAsACAAMAAuADIALAAgADAALgA1ACwAIAAxADgALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwBmAGYALQByAG8AYQBkACAAQQBnAHIAaQBjAHUAbAB0AHUAcgBlACAAYQBuAGQAIABmAG8AcgBlAHMAdAByAHkAIABlAHEAdQBpAHAAbQBlAG4AdABcACIALAAgAFwAIgBEAGkAZQBzAGUAbABcACIALAAgADMAOAAuADYALAAgADYAOQAuADkALAAgADAALgAzACwAIAAwAC4ANQAsACAAMQA3AC4AMwBcAG4AIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgApACkAKQA7AFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEYAdQBlAGwAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBGAHUAZQBsAF8ARwBlAHQAVAByAGEAbgBzAHAAbwByAHQARgB1AGUAbABTAHQAcgBpAG4AZwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEMAZQBsAGwALABcAG4AIAAgACAAIABMAEUARgBUACgAQwBlAGwAbAAsACAARgBJAE4ARAAoAFwAIgAsACAAXAAiACwAQwBlAGwAbAApACAALQAxACkAXABuACkAOwBcAG4AXABuAEYAdQBlAGwAXwBHAGUAdABTAHQAYQB0AGkAbwBuAGEAcgB5AEYAdQBlAGwAUwB0AHIAaQBuAGcAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABDAGUAbABsACwAXABuACAAIAAgACAAUgBJAEcASABUACgAQwBlAGwAbAAsAEwARQBOACgAQwBlAGwAbAApAC0ARgBJAE4ARAAoAFwAIgAsACAAXAAiACwAQwBlAGwAbAApACkAXABuACkAOwBcAG4AXABuAEYAdQBlAGwAXwBUAG8AdABhAGwAQwBvAG4AcwB1AG0AcAB0AGkAbwBuAFwAbgA9ACAATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABGAHUAZQBsAEMAbwBuAHMAdQBtAHAAdABpAG8AbgBBAHIAcgBhAHkALAAgAEYAdQBlAGwAVQBzAGUAQQByAHIAYQB5ACwAIABGAHUAZQBsAFUAcwBlACwAIABGAHUAZQBsAFQAeQBwAGUAQQByAHIAYQB5ACwAIABGAHUAZQBsAFQAeQBwAGUALABcAG4AIAAgACAAIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAUwBVAE0AKABcAG4AIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABcAG4AIAAgACAAIAAgACAAIAAgAEYAdQBlAGwAQwBvAG4AcwB1AG0AcAB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgACAAIAAgACAAKABGAHUAZQBsAFQAeQBwAGUAQQByAHIAYQB5ACAAPQAgAEYAdQBlAGwAVAB5AHAAZQApACAAKgAgAFwAbgAgACAAIAAgACAAIAAgACAAKABGAHUAZQBsAFUAcwBlAEEAcgByAGEAeQAgAD0AIABGAHUAZQBsAFUAcwBlACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQAsAFwAbgAgACAAIAAgADAAXABuACAAIAApAFwAbgApADsAIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AOAA6ACAARgB1AGUAbAAgAFUAcwBlAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADgALgAxACAARgB1AGUAbAAgAFUAcwBlACAALQAgAFQAcgBhAG4AcwBwAG8AcgB0ACAAZgB1AGUAbABcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBcAG4AVgBFAEUAUgBHAF8AOABfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABRACwAIABFAEMALAAgAEUARgAsAFwAbgAgACAAIAAgACgAUQAgACoAIABFAEMAIAAqACAARQBGACkAIAAqACAAMQAwACAAXgAgAC0AIAAzAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADgAXwAxAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AVAByAGEAbgBzAHAAbwByAHQAXABuAEUAbQBpAHMAcwBpAG8AbgBzACAAZgBvAHIAIABlAGEAYwBoACAARwBIAEcAIABmAHIAbwBtACAAdABoAGUAIABjAG8AbQBiAHUAcwB0AGkAbwBuACAAbwBmACAAZgB1AGUAbABzACAAZgBvAHIAIAB0AHIAYQBuAHMAcABvAHIAdAAgAGUAbgBlAHIAZwB5ACAAcAB1AHIAcABvAHMAZQBzAFwAbgBRACAAOgAgAEEAbQBvAHUAbgB0ACAAbwBmACAAZgB1AGUAbAAgAHQAeQBwAGUAIABxACAAYwBvAG0AYgB1AHMAdABlAGQAIABmAG8AcgAgAHQAcgBhAG4AcwBwAG8AcgB0ACAAZQBuAGUAcgBnAHkAIABwAHUAcgBwAG8AcwBlAHMAIAA6ACAAawBMAFwAbgBFAEMAIAA6ACAAZQBuAGUAcgBnAHkAIABjAG8AbgB0AGUAbgB0ACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHQAcgBhAG4AcwBwAG8AcgB0ACAAZQBuAGUAcgBnAHkAIABwAHUAcgBwAG8AcwBlAHMAIAA6ACAARwBKAC8AawBMAFwAbgBFAEYAIAA6ACAAUwBjAG8AcABlACAAMQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AHIAYQBuAHMAcABvAHIAdAAgAGUAbgBlAHIAZwB5ACAAcAB1AHIAcABvAHMAZQBzACAAZgBvAHIAIABlAGEAYwBoACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzACAAOgAgAGsAZwAgAEMATwAyAGUAIAAvACAARwBKAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFwAbgBWAEUARQBSAEcAXwA4AF8AMQBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFQAcgBhAG4AcwBwAG8AcgB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFEAXwBUAHIAYQBuAHMAdABxACwAIABFAEMAXwBUAHIAYQBuAHMAcQAsACAARQBGAF8AVAByAGEAbgBzADEAdABxAGcALABcAG4AIAAgACAAIABWAEUARQBSAEcAXwA4AF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuACgAUQBfAFQAcgBhAG4AcwB0AHEALAAgAEUAQwBfAFQAcgBhAG4AcwBxACwAIABFAEYAXwBUAHIAYQBuAHMAMQB0AHEAZwApAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAFYARQBFAFIARwBfADgAXwAxAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AVAByAGEAbgBzAHAAbwByAHQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgBzACAAZgBvAHIAIABlAGEAYwBoACAARwBIAEcAIABmAHIAbwBtACAAdABoAGUAIABjAG8AbQBiAHUAcwB0AGkAbwBuACAAbwBmACAAZgB1AGUAbABzACAAZgBvAHIAIAB0AHIAYQBuAHMAcABvAHIAdAAgAGUAbgBlAHIAZwB5ACAAcAB1AHIAcABvAHMAZQBzAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA4AF8AMQBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFQAcgBhAG4AcwBwAG8AcgB0AF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AZwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOABfADEAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBUAHIAYQBuAHMAcABvAHIAdABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgAtAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADgAXwAxAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AVAByAGEAbgBzAHAAbwByAHQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAOAAuADEALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADgAXwAxAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AVAByAGEAbgBzAHAAbwByAHQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAE4AYQB0AGkAbwBuAGEAbAAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABBAGMAYwBvAHUAbgB0AHMAIABGAGEAYwB0AG8AcgBzACAAMgAwADIANQAgAC0AIAAyAC4AMwAgAEUAcwB0AGkAbQBhAHQAaQBuAGcAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIAB0AHIAYQBuAHMAcABvAHIAdAAgAGYAdQBlAGwAcwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOABfADEAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBUAHIAYQBuAHMAcABvAHIAdABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwBnAD0AXABcAHMAdQBtAFwAXABuAG8AbABpAG0AaQB0AHMAXwB0ACAAXABcAHMAdQBtAFwAXABuAG8AbABpAG0AaQB0AHMAXwBxAFwAXABsAGUAZgB0ACgAUQBfAHsAVAByAGEAbgBzACwAdABxAH0AXABcAHQAaQBtAGUAcwAgAEUAQwBfAHsAVAByAGEAbgBzACwAcQB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AFQAcgBhAG4AcwAsADEALAB0AHEAZwB9AFwAXAByAGkAZwBoAHQAKQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOABfADEAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBUAHIAYQBuAHMAcABvAHIAdABfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANwAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQBfAFQAcgBhAG4AcwB0AHEAXAAiACwAIABcACIAQQBtAG8AdQBuAHQAIABvAGYAIABmAHUAZQBsACAAdAB5AHAAZQAgAHEAIABjAG8AbQBiAHUAcwB0AGUAZAAgAGYAbwByACAAdAByAGEAbgBzAHAAbwByAHQAIABlAG4AZQByAGcAeQAgAHAAdQByAHAAbwBzAGUAcwBcACIALAAgAFwAIgBWAGEAcgBpAGUAcwAgAGIAYQBzAGUAZAAgAG8AbgAgAGYAdQBlAGwAIAB0AHkAcABlADoAIABrAEwALAAgAG0AMwAsACAARwBKAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAF8AVAByAGEAbgBzAHEAXAAiACwAIABcACIARQBuAGUAcgBnAHkAIABjAG8AbgB0AGUAbgB0ACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHQAcgBhAG4AcwBwAG8AcgB0ACAAZQBuAGUAcgBnAHkAIABwAHUAcgBwAG8AcwBlAHMAXAAiACwAIABcACIARwBKACAALwAgAHUAbgBpAHQAIABvAGYAIABmAHUAZQBsAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8AVAByAGEAbgBzADEAdABxAGcAXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AHIAYQBuAHMAcABvAHIAdAAgAGUAbgBlAHIAZwB5ACAAcAB1AHIAcABvAHMAZQBzACAAZgBvAHIAIABlAGEAYwBoACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAFwAIgAsACAAXAAiAGsAZwAgAEMATwAyAGUAIAAvACAARwBKAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAcQBcACIALAAgAFwAIgBGAHUAZQBsACAAdAB5AHAAZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBhAG4AcwBcACIALAAgAFwAIgBUAHIAYQBuAHMAcABvAHIAdAAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AXAAiACwAIABcACIAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBnAFwAIgAsACAAXAAiAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBcACIALAAgAFwAIgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEAXAAiACwAIABcACIAUwBjAG8AcABlACAAMQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA4AF8AMgBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFMAdABhAHQAaQBvAG4AYQByAHkAXABuAEUAbQBpAHMAcwBpAG8AbgBzACAAZgBvAHIAIABlAGEAYwBoACAARwBIAEcAIABmAHIAbwBtACAAdABoAGUAIABzAHQAYQB0AGkAbwBuAGEAcgB5ACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgAG8AZgAgAGYAdQBlAGwAcwBcAG4AUQAgADoAIABBAG0AbwB1AG4AdAAgAG8AZgAgAGYAdQBlAGwAIAB0AHkAcABlACAAcQAgAHUAcwBlAGQAIABmAG8AcgAgAHMAdABhAHQAaQBvAG4AYQByAHkAIABjAG8AbQBiAHUAcwB0AGkAbwBuACAAbwBwAGUAcgBhAHQAaQBvAG4AcwAgADoAIABrAEwAXABuAEUAQwAgADoAIABFAG4AZQByAGcAeQAgAGMAbwBuAHQAZQBuAHQAIABmAGEAYwB0AG8AcgAgAGYAbwByACAAcwB0AGEAdABpAG8AbgBhAHIAeQAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AIABvAHAAZQByAGEAdABpAG8AbgBzACAAOgAgAEcASgAvAGsATABcAG4ARQBGACAAOgAgAFMAYwBvAHAAZQAgADEAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAcwB0AGEAdABpAG8AbgBhAHIAeQAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AIABmAG8AcgAgAGUAYQBjAGgAIABnAHIAZQBlAG4AaABvAHUAcwBlACAAZwBhAHMAIAA6ACAAawBnACAAQwBPADIAZQAgAC8AIABHAEoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAFYARQBFAFIARwBfADgAXwAyAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AUwB0AGEAdABpAG8AbgBhAHIAeQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABRAF8AUwBDAHEALAAgAEUAQwBfAFMAQwBxACwAIABFAEYAXwBTAEMAMQBxAGcALABcAG4AIAAgACAAIABWAEUARQBSAEcAXwA4AF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuACgAUQBfAFMAQwBxACwAIABFAEMAXwBTAEMAcQAsACAARQBGAF8AUwBDADEAcQBnACkAXABuACAAIAApAFwAbgA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOABfADIAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBTAHQAYQB0AGkAbwBuAGEAcgB5AF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAGYAbwByACAAZQBhAGMAaAAgAEcASABHACAAZgByAG8AbQAgAHQAaABlACAAcwB0AGEAdABpAG8AbgBhAHIAeQAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AIABvAGYAIABmAHUAZQBsAHMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADgAXwAyAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AUwB0AGEAdABpAG8AbgBhAHIAeQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAGcAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADgAXwAyAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AUwB0AGEAdABpAG8AbgBhAHIAeQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgAtAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADgAXwAyAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AUwB0AGEAdABpAG8AbgBhAHIAeQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA4AC4AMgAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOABfADIAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBTAHQAYQB0AGkAbwBuAGEAcgB5AF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABOAGEAdABpAG8AbgBhAGwAIABHAHIAZQBlAG4AaABvAHUAcwBlACAAQQBjAGMAbwB1AG4AdABzACAARgBhAGMAdABvAHIAcwAgADIAMAAyADUAIAAtACAAMgAuADIAIABFAHMAdABpAG0AYQB0AGkAbgBnACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAcwB0AGEAdABpAG8AbgBhAHIAeQAgAGUAbgBlAHIAZwB5ACAAcwBvAHUAcgBjAGUAcwAgAC0AIABDAGEAbABjAHUAbABhAHQAaQBuAGcAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABzAHQAYQB0AGkAbwBuAGEAcgB5ACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgAG8AZgAgAGwAaQBxAHUAaQBkACAAZgB1AGUAbABzAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA4AF8AMgBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFMAdABhAHQAaQBvAG4AYQByAHkAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AZwA9AFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AdAAgAFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AcQBcAFwAbABlAGYAdAAoAFEAXwB7AFMAQwAsAHEAfQBcAFwAdABpAG0AZQBzACAARQBDAF8AewBTAEMALABxAH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAUwBDACwAMQAsAHEAZwB9AFwAXAByAGkAZwBoAHQAKQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOABfADIAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBTAHQAYQB0AGkAbwBuAGEAcgB5AF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA3ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBRAF8AUwBDAHEAXAAiACwAIABcACIAQQBtAG8AdQBuAHQAIABvAGYAIABmAHUAZQBsACAAdAB5AHAAZQAgAHEAIAB1AHMAZQBkACAAZgBvAHIAIABzAHQAYQB0AGkAbwBuAGEAcgB5ACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgAG8AcABlAHIAYQB0AGkAbwBuAHMAXAAiACwAIABcACIAVgBhAHIAaQBlAHMAIABiAGEAcwBlAGQAIABvAG4AIABmAHUAZQBsACAAdAB5AHAAZQA6ACAAawBMACwAIABtADMALAAgAEcASgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAQwBfAFMAQwBxAFwAIgAsACAAXAAiAEUAbgBlAHIAZwB5ACAAYwBvAG4AdABlAG4AdAAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABzAHQAYQB0AGkAbwBuAGEAcgB5ACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgAG8AcABlAHIAYQB0AGkAbwBuAHMAXAAiACwAIABcACIARwBKACAALwAgAHUAbgBpAHQAIABvAGYAIABmAHUAZQBsAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8AUwBDADEAcQBnAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAcwB0AGEAdABpAG8AbgBhAHIAeQAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AIABmAG8AcgAgAGUAYQBjAGgAIABnAHIAZQBlAG4AaABvAHUAcwBlACAAZwBhAHMAXAAiACwAIABcACIAawBnACAAQwBPADIAZQAgAC8AIABHAEoAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBxAFwAIgAsACAAXAAiAEYAdQBlAGwAIAB0AHkAcABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBDAFwAIgAsACAAXAAiAFMAdABhAHQAaQBvAG4AYQByAHkAIABjAG8AbQBiAHUAcwB0AGkAbwBuAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAZwBcACIALAAgAFwAIgBHAHIAZQBlAG4AaABvAHUAcwBlACAAZwBhAHMAXAAiACwAIABcACIAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAXAAiACwAIABcACIAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADkAOgAgAFIAZQBmAHIAaQBnAGUAcgBhAG4AdAAgAFUAcwBlAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADkALgAxACAAUgBlAGYAcgBpAGcAZQByAGEAbgB0ACAAVQBzAGUAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAXABuAFQAaABlACAAdABvAHQAYQBsACAAZQBtAGkAcwBzAGkAbwBuAHMAIABvAGYAIAByAGUAZgByAGkAZwBlAHIAYQBuAHQAIABsAGUAYQBrAGkAbgBnACAAZAB1AHIAaQBuAGcAIABvAHAAZQByAGEAdABpAG8AbgAgACgAbgBvAHQAIABkAHUAcgBpAG4AZwAgAGkAbgBzAHQAYQBsAGwAYQB0AGkAbwBuACAAbwByACAAZABpAHMAcABvAHMAYQBsACkAXABuAEcAVwBQAFIAIAA6ACAARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABvAGYAIAByAGUAZgByAGkAZwBlAHIAYQBuAHQAIABSACAAOgAgAEQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXABuAGMAaABhAHIAZwBlAF8AUgBhACAAOgAgAEEAbQBvAHUAbgB0ACAAbwBmACAAcgBlAGYAcgBpAGcAZQByAGEAbgB0ACAAUgAgAGMAbwBuAHQAYQBpAG4AZQBkACAAaQBuACAAYQBwAHAAbABpAGEAbgBjAGUAIABhACAAOgAgAGsAZwBcAG4AbABlAGEAawBhAGcAZQByAGEAdABlAF8AYQAgADoAIABQAHIAYwBlAG4AdABhAGcAZQAgAG8AZgAgAHQAbwB0AGEAbAAgAGMAaABhAHIAZwBlACAAbABlAGEAawBlAGQAIABmAHIAbwBtACAAYQBwAHAAbABpAGEAbgBjAGUAIABhACAAZQBhAGMAaAAgAHkAZQBhAHIAIAA6ACAAUABlAHIAYwBlAG4AdABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYwBoAGEAcgBnAGUAXwBSAGEALAAgAGwAZQBhAGsAYQBnAGUAcgBhAHQAZQBfAGEALABcAG4AIAAgACAAIAAoAGMAaABhAHIAZwBlAF8AUgBhACAAKgAgACgAbABlAGEAawBhAGcAZQByAGEAdABlAF8AYQAvADEAMAAwACkAKQAgACoAIAAxADAAIABeACAALQAgADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBHAFcAUABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8AUgAsACAARwBXAFAAXwBSACwAXABuACAAIAAgACAAKAAoAEUAXwBSACAAKgAgADEAMABeADMAKQAgACoAIABHAFcAUABfAFIAKQAgACoAIAAxADAAXgAtADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVABoAGUAIAB0AG8AdABhAGwAIABlAG0AaQBzAHMAaQBvAG4AcwAgAG8AZgAgAHIAZQBmAHIAaQBnAGUAcgBhAG4AdAAgAGwAZQBhAGsAaQBuAGcAIABkAHUAcgBpAG4AZwAgAG8AcABlAHIAYQB0AGkAbwBuACAAKABuAG8AdAAgAGQAdQByAGkAbgBnACAAaQBuAHMAdABhAGwAbABhAHQAaQBvAG4AIABvAHIAIABkAGkAcwBwAG8AcwBhAGwAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcARwBXAFAAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdAAgAGwAZQBhAGsAYQBnAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGMAbwBuAHYAZQByAHQAZQBkACAAdABvACAAQwBPADIALQBlAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAFIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAAcgBlAGYAcgBpAGcAZQByAGEAbgB0ACAAZwBhAHMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAEcAVwBQAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAC0AZQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAOQAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAE4AYQB0AGkAbwBuAGEAbAAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABBAGMAYwBvAHUAbgB0AHMAIABGAGEAYwB0AG8AcgBzACAAMgAwADIANQAgAC0AIAAzAC4AMQAgAEUAcwB0AGkAbQBhAHQAaQBuAGcAIABpAG4AZAB1AHMAdAByAGkAYQBsACAAcAByAG8AYwBlAHMAcwBlAHMAIABlAG0AaQBzAHMAaQBvAG4AcwAgAC0AIABSAGUAZgByAGkAZwBlAHIAYQBuAHQAIABsAGUAYQBrAGEAZwBlAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBfAFIAZQBhAGQAYQBiAGwAZQBFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGMAaABhAHIAZwBlAF8AUgBhACAAKgAgACgAbABlAGEAawBhAGcAZQByAGEAdABlAF8AYQAvADEAMAAwACkAIAAqACAAMQAwACAAXgAgAC0AIAAzAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwBSACAAPQAgAFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AYQAgAFwAXABsAGUAZgB0ACgAIABjAGgAYQByAGcAZQBfAHsAUgBhAH0AIABcAFwAdABpAG0AZQBzACAAXABcAGYAcgBhAGMAewBsAGUAYQBrAGEAZwBlAFwAXAAsAHIAYQB0AGUAXwBhAH0AewAxADAAMAB9ACAAXABcAHIAaQBnAGgAdAApACAAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAEcAVwBQAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAEMATwAyAGUAIAA9ACAAXABcAGwAZQBmAHQAKABFAF8AUgAgAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7ADMAfQAgAFwAXAByAGkAZwBoAHQAKQAgAFwAXAB0AGkAbQBlAHMAIABHAFcAUABfAFIAIABcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGMAaABhAHIAZwBlAF8AUgBhAFwAIgAsACAAXAAiAEEAbQBvAHUAbgB0ACAAbwBmACAAcgBlAGYAcgBpAGcAZQByAGEAbgB0ACAAUgAgAGMAbwBuAHQAYQBpAG4AZQBkACAAaQBuACAAYQBwAHAAbABpAGEAbgBjAGUAIABhAFwAIgAsACAAXAAiAGsAZwBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGwAZQBhAGsAYQBnAGUAcgBhAHQAZQBfAGEAXAAiACwAIABcACIAUAByAGMAZQBuAHQAYQBnAGUAIABvAGYAIAB0AG8AdABhAGwAIABjAGgAYQByAGcAZQAgAGwAZQBhAGsAZQBkACAAZgByAG8AbQAgAGEAcABwAGwAaQBhAG4AYwBlACAAYQAgAGUAYQBjAGgAIAB5AGUAYQByAFwAIgAsACAAXAAiAFAAZQByAGMAZQBuAHQAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBhAFwAIgAsACAAXAAiAEEAcABwAGwAaQBhAG4AYwBlACAAdAB5AHAAZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAXAAiACwAIABcACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAEcAVwBQAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAF8AUgBcACIALAAgAFwAIgBUAG8AdABhAGwAIABlAG0AaQBzAHMAaQBvAG4AcwAgAG8AZgAgAHIAZQBmAHIAaQBnAGUAcgBhAG4AdAAgAFIAXAAiACwAIABcACIAdAAgAHIAZQBmAHIAaQBnAGUAcgBhAG4AdAAgAGcAYQBzAFwAIgAsACAAXAAiAEMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAAOQAuADEALgAxACAAKAAxACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAF8AUgBcACIALAAgAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAG8AZgAgAHIAZQBmAHIAaQBnAGUAcgBhAG4AdAAgAFIAXAAiACwAIABcACIARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ATgAgAFMATwBVAFIAQwBFADoAIABBAGQAZABlAGQAIABlAHEAdQBhAHQAaQBvAG4AIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAcgBlAGYAcgBpAGcAZQByAGEAbgB0ACAAUgAgAHQAbwAgAEMATwAyAC0AZQAgAHUAcwBpAG4AZwAgAHQAaABlACAAcgBlAGYAcgBpAGcAZQByAGEAbgB0AFwAdQAwADAAMgA3AHMAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgACgARwBXAFAAKQAuAFwAIgApADsAIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAEEAcABwAGUAbgBkAGkAeAAgADIAIABHAGwAbwBiAGEAbAAgAFcAYQByAG0AaQBuAGcAIABQAG8AdABlAG4AdABpAGEAbABzADoAIABUAGEAYgBsAGUAIAAyADMAIABHAGwAbwBiAGEAbAAgAFcAYQByAG0AaQBuAGcAIABQAG8AdABlAG4AdABpAGEAbABzAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABHAFcAUABfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEcAbABvAGIAYQBsACAAVwBhAHIAbQBpAG4AZwAgAFAAbwB0AGUAbgB0AGkAYQBsAHMAXAAiACkAKQA7AFwAbgBcAG4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBDAGgAZQBtAGkAYwBhAGwARwBXAFAAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABHAFcAUABfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAE4AYQB0AGkAbwBuAGEAbAAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABBAGMAYwBvAHUAbgB0AHMAIABGAGEAYwB0AG8AcgBzACAAMgAwADIANQAgAC0AIABBAHAAcABlAG4AZABpAHgAIAAyACAALQAgAFQAYQBiAGwAZQAgADIAMwBcACIAKQApADsAXABuAFwAbgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABHAFcAUABfAEQAYQB0AGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwA5ACwAIAA1ACwAXABuACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEcAYQBzAFwAIgAsACAAXAAiAEMAaABlAG0AaQBjAGEAbAAgAGYAbwByAG0AdQBsAGEAXAAiACwAIABcACIARwBsAG8AYgBhAGwAIABXAGEAcgBtAGkAbgBnACAAUABvAHQAZQBuAHQAaQBhAGwAIAAoAEEAUgA1ACkAXAAiACwAIABcACIARwBhAHMAIAAtACAARgBDACAAbgBhAG0AZQBcACIALAAgAFwAIgBBAGQAaQB0AGkAbwBuAGEAbAAgAGQAYQB0AGEAIABzAG8AdQByAGMAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAXAAiACwAIABcACIAQwBPADIAXAAiACwAIAAxACwAIABcACIAQwBPADIAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIATQBlAHQAaABhAG4AZQBcACIALAAgAFwAIgBDAEgANABcACIALAAgADIAOAAsACAAXAAiAEMASAA0AFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAXAAiACwAIABcACIATgAyAE8AXAAiACwAIAAyADYANQAsACAAXAAiAE4AMgBPAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFMAdQBsAHAAaAB1AHIAIABoAGUAeABhAGYAbAB1AG8AcgBpAGQAZQBcACIALAAgAFwAIgBTAEYANgBcACIALAAgADIAMwA1ADAAMAAsACAAXAAiAFMARgA2AFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgARgBDAC0AMgAzACAAKABSAC0AMgAzACkAXAAiACwAIABcACIAQwBIAEYAMwBcACIALAAgACAAMQAyADQAMAAwACwAIABcACIASABGAEMALQAyADMAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABGAEMALQAzADIAIAAoAFIALQAzADIAKQBcACIALAAgAFwAIgBDAEgAMgBGADIAXAAiACwAIAA2ADcANwAsACAAXAAiAEgARgBDAC0AMwAyAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgARgBDAC0ANAAxACAAKABSAC0ANAAxACkAXAAiACwAIABcACIAQwBIADMARgBcACIALAAgACAAMQAxADYALAAgAFwAIgBIAEYAQwAtADQAMQBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAEYAQwAtADQAMwAtADEAMABtAGUAZQAgACgAUgAtADQAMwAxADAAbQBlAGUAKQBcACIALAAgAFwAIgBDADUASAAyAEYAMQAwAFwAIgAsACAAMQA2ADUAMAAsACAAXAAiAEgARgBDAC0ANAAzAC0AMQAwAG0AZQBlAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgARgBDAC0AMQAyADUAIAAoAFIALQAxADIANQApAFwAIgAsACAAXAAiAEMAMgBIAEYANQBcACIALAAgACAAMwAxADcAMAAsACAAXAAiAEgARgBDAC0AMQAyADUAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABGAEMALQAxADMANAAgACgAUgAtADEAMwA0ACkAXAAiACwAIABcACIAQwAyAEgAMgBGADQAIAAoAEMASABGADIAQwBIAEYAMgApAFwAIgAsACAAIAAxADEAMgAwACwAIABcACIASABGAEMALQAxADMANABcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAEYAQwAtADEAMwA0AGEAIAAoAFIALQAxADMANABhACkAXAAiACwAIABcACIAQwAyAEgAMgBGADQAIAAoAEMASAAyAEYAQwBGADMAKQBcACIALAAgADEAMwAwADAALAAgAFwAIgBIAEYAQwAtADEAMwA0AGEAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABGAEMALQAxADQAMwAgACgAUgAtADEANAAzACkAXAAiACwAIABcACIAQwAyAEgAMwBGADMAIAAoAEMASABGADIAQwBIADIARgApAFwAIgAsACAAMwAyADgALAAgAFwAIgBIAEYAQwAtADEANAAzAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgARgBDAC0AMQA0ADMAYQAgACgAUgAtADEANAAzAGEAKQBcACIALAAgAFwAIgBDADIASAAzAEYAMwAgACgAQwBGADMAQwBIADMAKQBcACIALAAgADQAOAAwADAALAAgAFwAIgBIAEYAQwAtADEANAAzAGEAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABGAEMALQAxADUAMgBhACAAKABSAC0AMQA1ADIAYQApAFwAIgAsACAAXAAiAEMAMgBIADQARgAyACAAKABDAEgAMwBDAEgARgAyACkAXAAiACwAIAAxADMAOAAsACAAXAAiAEgARgBDAC0AMQA1ADIAYQBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAEYAQwAtADIAMgA3AGUAYQAgACgAUgAtADIAMgA3AGUAYQApAFwAIgAsACAAXAAiAEMAMwBIAEYANwBcACIALAAgADMAMwA1ADAALAAgAFwAIgBIAEYAQwAtADIAMgA3AGUAYQBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAEYAQwAtADIAMwA2AGYAYQAgACgAUgAtADIAMwA2AGYAYQApAFwAIgAsACAAXAAiAEMAMwBIADIARgA2AFwAIgAsACAAOAAwADYAMAAsACAAXAAiAEgARgBDAC0AMgAzADYAZgBhAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgARgBDAC0AMgA0ADUAYwBhACAAKABSAC0AMgA0ADUAYwBhACkAXAAiACwAIABcACIAQwAzAEgAMwBGADUAXAAiACwAIAA3ADEANgAsACAAXAAiAEgARgBDAC0AMgA0ADUAYwBhAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgARgBDAC0AMgA0ADUAZgBhACAAKABSAC0AMgA0ADUAZgBhACkAXAAiACwAIABcACIAQwBIAEYAMgBDAEgAMgBDAEYAMwBcACIALAAgADgANQA4ACwAIABcACIASABGAEMALQAyADQANQBmAGEAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABGAEMALQAzADYANQBtAGYAYwAgACgAUgAtADMANgA1AG0AZgBjACkAXAAiACwAIABcACIAQwBIADMAQwBGADIAQwBIADIAQwBGADMAXAAiACwAIAA4ADAANAAsACAAXAAiAEgARgBDAC0AMwA2ADUAbQBmAGMAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABDAEYAQwAtADIAMgAgACgAUgAtADIAMgApAFwAIgAsACAAXAAiAEMASABDAGwARgAyAFwAIgAsACAAMQA3ADYAMAAsACAAXAAiAEgAQwBGAEMALQAyADIAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABDAEYAQwAtADEAMgAzACAAKABSAC0AMQAyADMAKQBcACIALAAgAFwAIgBDAEgAQwBsADIAMgBDAEYAMwBcACIALAAgADcAOQAsACAAXAAiAEgAQwBGAEMALQAxADIAMwBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAEMARgBDAC0AMQAyADQAIAAoAFIALQAxADIANAApAFwAIgAsACAAXAAiAEMASABDAGwARgBDAEYAMwBcACIALAAgADUAMgA3ACwAIABcACIASABDAEYAQwAtADEAMgA0AFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAQwBGAEMALQAxADQAMQBiACAAKABSAC0AMQA0ADEAYgApAFwAIgAsACAAXAAiAEMASAAzAEMAQwBsADIARgBcACIALAAgADcAOAAyACwAIABcACIASABDAEYAQwAtADEANAAxAGIAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABDAEYAQwAtADEANAAyAGIAIAAoAFIALQAxADQAMgBiACkAXAAiACwAIABcACIAQwBIADIAQwBDAGwARgAyAFwAIgAsACAAMQA5ADgAMAAsACAAXAAiAEgAQwBGAEMALQAxADQAMgBiAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAQwBGAEMALQAyADIANQBjAGEAIAAoAFIALQAyADIANQBjAGEAKQBcACIALAAgAFwAIgBDAEgAQwBsADIAQwBGADIAQwBGADMAXAAiACwAIAAxADIANwAsACAAXAAiAEgAQwBGAEMALQAyADIANQBjAGEAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABDAEYAQwAtADIAMgA1AGMAYgAgACgAUgAtADIAMgA1AGMAYgApAFwAIgAsACAAXAAiAEMASABDAGwARgBDAEYAMgBDAEMASQBGADIAXAAiACwAIAA1ADIANQAsACAAXAAiAEgAQwBGAEMALQAyADIANQBjAGIAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUABGAEMALQAxADQAIABQAGUAcgBmAGwAdQBvAHIAbwBtAGUAdABoAGEAbgBlACAAKAB0AGUAdAByAGEAZgBsAHUAbwByAG8AbQBlAHQAaABhAG4AZQApAFwAIgAsACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAAsACAAXAAiAFAARgBDAC0AMQA0AFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFAARgBDAC0AMQAxADYAIABQAGUAcgBmAGwAdQBvAHIAbwBlAHQAaABhAG4AZQAgACgAaABlAHgAYQBmAGwAdQBvAHIAbwBlAHQAaABhAG4AZQApAFwAIgAsACAAXAAiAEMAMgBGADYAXAAiACwAIAAxADEAMQAwADAALAAgAFwAIgBQAEYAQwAtADEAMQA2AFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFAARgBDAC0AMgAxADgAIABQAGUAcgBmAGwAdQBvAHIAbwBwAHIAbwBwAGEAbgBlAFwAIgAsACAAXAAiAEMAMwBGADgAXAAiACwAIAA4ADkAMAAwACwAIABcACIAUABGAEMALQAyADEAOABcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAEYAQwAtADMAMQAtADEAMAAgAFAAZQByAGYAbAB1AG8AcgBvAGIAdQB0AGEAbgBlAFwAIgAsACAAXAAiAEMANABGADEAMABcACIALAAgADkAMgAwADAALAAgAFwAIgBQAEYAQwAtADMAMQAtADEAMABcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAEYAQwAtADMAMQA4ACAAUABlAHIAZgBsAHUAbwByAG8AYwB5AGMAbABvAGIAdQB0AGEAbgBlAFwAIgAsACAAXAAiAGMALQBDADQARgA4AFwAIgAsACAAOQA1ADQAMAAsACAAXAAiAFAARgBDAC0AMwAxADgAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUABGAEMALQA0ADEALQAxADIAIABQAGUAcgBmAGwAdQBvAHIAbwBwAGUAbgB0AGEAbgBlAFwAIgAsACAAXAAiAEMANQBGADEAMgBcACIALAAgADgANQA1ADAALAAgAFwAIgBQAEYAQwAtADQAMQAtADEAMgBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAEYAQwAtADUAMQAtADEANAAgAFAAZQByAGYAbAB1AG8AcgBvAGgAZQB4AGEAbgBlAFwAIgAsACAAXAAiAEMANgBGADEANABcACIALAAgADcAOQAxADAALAAgAFwAIgBQAEYAQwAtADUAMQAtADEANABcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAEYAQwAtADkAMQAtADEAOAAgAFAAZQByAGYAbAB1AG4AYQBmAGUAbgBlAFwAIgAsACAAXAAiAEMAMQAwAEYAMQA4AFwAIgAsACAANwAxADkAMAAsACAAXAAiAFAARgBDAC0AOQAxAC0AMQA4AFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMARgBDAC0AMQAyAFwAIgAsACAAXAAiAEMAQwBsADIARgAyAFwAIgAsACAAMQAwADIAMAAwACwAIABcACIAQwBGAEMALQAxADIAXAAiACwAIABcACIASQBQAEMAQwAgAEcAbABvAGIAYQBsACAAVwBhAHIAbQBpAG4AZwAgAFAAbwB0AGUAbgB0AGkAYQBsACAAVgBhAGwAdQBlAHMAIAB2ADIALgAwACAALQAgACgAQQBSADUAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAEYAQwAtADEAMwBcACIALAAgAFwAIgBDAEMAbABGADMAXAAiACwAIAAxADMAOQAwADAALAAgAFwAIgBDAEYAQwAtADEAMwBcACIALAAgAFwAIgBJAFAAQwBDACAARwBsAG8AYgBhAGwAIABXAGEAcgBtAGkAbgBnACAAUABvAHQAZQBuAHQAaQBhAGwAIABWAGEAbAB1AGUAcwAgAHYAMgAuADAAIAAtACAAKABBAFIANQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMARgBDAC0AMQAxADQAXAAiACwAIABcACIAQwBDAGwARgAyAEMAQwBsAEYAMgBcACIALAAgADgANQA5ADAALAAgAFwAIgBDAEYAQwAtADEAMQA0AFwAIgAsACAAXAAiAEkAUABDAEMAIABHAGwAbwBiAGEAbAAgAFcAYQByAG0AaQBuAGcAIABQAG8AdABlAG4AdABpAGEAbAAgAFYAYQBsAHUAZQBzACAAdgAyAC4AMAAgAC0AIAAoAEEAUgA1ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBGAEMALQAxADEANQBcACIALAAgAFwAIgBDAEMAbABGADIAQwBGADMAXAAiACwAIAA3ADYANwAwACwAIABcACIAQwBGAEMALQAxADEANQBcACIALAAgAFwAIgBJAFAAQwBDACAARwBsAG8AYgBhAGwAIABXAGEAcgBtAGkAbgBnACAAUABvAHQAZQBuAHQAaQBhAGwAIABWAGEAbAB1AGUAcwAgAHYAMgAuADAAIAAtACAAKABBAFIANQApAFwAIgBcAG4AIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgApACkAKQA7AFwAbgBcAG4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBDAGgAZQBtAGkAYwBhAGwARwBXAFAAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABcAHUAMAAwADIANwBHAEEAUwAgAC0AIABGAEMAIABuAGEAbQBlAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AIAB3AGkAdABoACAAdAByAHUAbgBjAGEAdABlAGQAIABnAGEAcwAgAG4AYQBtAGUAIAB0AG8AIABhAGwAbABvAHcAIABtAGEAdABjAGgAaQBuAGcAIAB3AGkAdABoACAAbwB0AGgAZQByACAAdABhAGIAbABlAHMALgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAGcAYQBzAGUAcwAgAGYAcgBvAG0AIABJAFAAQwBDACAARwBsAG8AYgBhAGwAIABXAGEAcgBtAGkAbgBnACAAUABvAHQAZQBuAHQAaQBhAGwAIABWAGEAbAB1AGUAcwAgAHYAMgAuADAAIAAtACAAKABBAFIANQApAC4AIABBAGQAZABlAGQAIABcAHUAMAAwADIANwBBAGQAZABpAHQAaQBvAG4AYQBsACAAZABhAHQAYQAgAHMAbwB1AHIAYwBlAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4ALgBcACIAKQApADsAXABuAFwAbgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAEEAcABwAGUAbgBkAGkAeAAgADIAIABHAGwAbwBiAGEAbAAgAFcAYQByAG0AaQBuAGcAIABQAG8AdABlAG4AdABpAGEAbABzADoAIABCAGwAZQBuAGQAZQBkACAAcgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AQwBoAGUAbQBpAGMAYQBsAEIAbABlAG4AZABzAF8AVABpAHQAbABlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAQgBsAGUAbgBkAGUAZAAgAHIAZQBmAHIAaQBnAGUAcgBhAG4AdABzACAAKABtAGEAbgB5ACAAYwBvAG4AdABhAGkAbgBpAG4AZwAgAEgARgBDAFMAIABhAG4AZAAvAG8AcgAgAFAARgBDAFMAKQBcACIAKQApADsAXABuAFwAbgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABCAGwAZQBuAGQAcwBfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AQwBoAGUAbQBpAGMAYQBsAEIAbABlAG4AZABzAF8AUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAEEAYwBjAG8AdQBuAHQAcwAgAEYAYQBjAHQAbwByAHMAIAAyADAAMgA1ACAALQAgAEEAcABwAGUAbgBkAGkAeAAgADIAIAAtACAAVABhAGIAbABlACAAMgA0AFwAIgApACkAOwBcAG4AXABuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AQwBoAGUAbQBpAGMAYQBsAEIAbABlAG4AZABzAF8ARABhAHQAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ADEALAAgADMALABcAG4AIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIABcACIAQgBsAGUAbgBkAFwAIgAsACAAXAAiAEMAbwBuAHMAdABpAHQAdQBlAG4AdABzAFwAIgAsACAAXAAiAEMAbwBtAHAAbwBzAGkAdABpAG8AbgAgACgAJQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADAAMABcACIALAAgAFwAIgBDAEYAQwAtADEAMgAvAEMARgBDAC0AMQAxADQAXAAiACwAIABcACIAUgAtADQAMAAwACAAYwBhAG4AIABoAGEAdgBlACAAdgBhAHIAaQBvAHUAcwAgAHAAcgBvAHAAbwByAHQAaQBvAG4AcwAgAG8AZgAgAEMARgBDAC0AMQAyACAAYQBuAGQAIABDAEYAQwAtADEAMQA0AC4AIABUAGgAZQAgAGUAeABhAGMAdAAgAGMAbwBtAHAAbwBzAGkAdABpAG8AbgAgAG4AZQBlAGQAcwAgAHQAbwAgAGIAZQAgAHMAcABlAGMAaQBmAGkAZQBkACwAIABlAC4AZwAuACwAIABSAC0ANAAwADAAIAAoADYAMAAvADQAMAApAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMAAxAEEAXAAiACwAIABcACIASABDAEYAQwAtADIAMgAvAEgARgBDAC0AMQA1ADIAYQAvAEgAQwBGAEMALQAxADIANABcACIALAAgAFwAIgAoADUAMwAuADAALwAxADMALgAwAC8AMwA0AC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADAAMQBCAFwAIgAsACAAXAAiAEgAQwBGAEMALQAyADIALwBIAEYAQwAtADEANQAyAGEALwBIAEMARgBDAC0AMQAyADQAXAAiACwAIABcACIAKAA2ADEALgAwAC8AMQAxAC4AMAAvADIAOAAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAwADEAQwBcACIALAAgAFwAIgBIAEMARgBDAC0AMgAyAC8ASABGAEMALQAxADUAMgBhAC8ASABDAEYAQwAtADEAMgA0AFwAIgAsACAAXAAiACgAMwAzAC4AMAAvADEANQAuADAALwA1ADIALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMAAyAEEAXAAiACwAIABcACIASABGAEMALQAxADIANQAvAEgAQwAtADIAOQAwAC8ASABDAEYAQwAtADIAMgBcACIALAAgAFwAIgAoADYAMAAuADAALwAyAC4AMAAvADMAOAAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAwADIAQgBcACIALAAgAFwAIgBIAEYAQwAtADEAMgA1AC8ASABDAC0AMgA5ADAALwBIAEMARgBDAC0AMgAyAFwAIgAsACAAXAAiACgAMwA4AC4AMAAvADIALgAwAC8ANgAwAC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADAAMwBBAFwAIgAsACAAXAAiAEgAQwAtADIAOQAwAC8ASABDAEYAQwAtADIAMgAvAFAARgBDAC0AMgAxADgAXAAiACwAIABcACIAKAA1AC4AMAAvADcANQAuADAALwAyADAALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMAAzAEIAXAAiACwAIABcACIASABDAC0AMgA5ADAALwBIAEMARgBDAC0AMgAyAC8AUABGAEMALQAyADEAOABcACIALAAgAFwAIgAoADUALgAwAC8ANQA2AC4AMAAvADMAOQAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAwADQAQQBcACIALAAgAFwAIgBIAEYAQwAtADEAMgA1AC8ASABGAEMALQAxADQAMwBhAC8ASABGAEMALQAxADMANABhAFwAIgAsACAAXAAiACgANAA0AC4AMAAvADUAMgAuADAALwA0AC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADAANQBBAFwAIgAsACAAXAAiAEgAQwBGAEMALQAyADIALwAgAEgARgBDAC0AMQA1ADIAYQAvAEgAQwBGAEMALQAxADQAMgBiAC8AUABGAEMALQAzADEAOABcACIALAAgAFwAIgAoADQANQAuADAALwA3AC4AMAAvADUALgA1AC8ANAAyAC4ANQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADAANgBBAFwAIgAsACAAXAAiAEgAQwBGAEMALQAyADIALwBIAEMALQA2ADAAMABhAC8ASABDAEYAQwAtADEANAAyAGIAXAAiACwAIABcACIAKAA1ADUALgAwAC8AMQA0AC4AMAAvADQAMQAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAwADcAQQBcACIALAAgAFwAIgBIAEYAQwAtADMAMgAvAEgARgBDAC0AMQAyADUALwBIAEYAQwAtADEAMwA0AGEAXAAiACwAIABcACIAKAAyADAALgAwAC8ANAAwAC4AMAAvADQAMAAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAwADcAQgBcACIALAAgAFwAIgBIAEYAQwAtADMAMgAvAEgARgBDAC0AMQAyADUALwBIAEYAQwAtADEAMwA0AGEAXAAiACwAIABcACIAKAAxADAALgAwAC8ANwAwAC4AMAAvADIAMAAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAwADcAQwBcACIALAAgAFwAIgBIAEYAQwAtADMAMgAvAEgARgBDAC0AMQAyADUALwBIAEYAQwAtADEAMwA0AGEAXAAiACwAIABcACIAKAAyADMALgAwAC8AMgA1AC4AMAAvADUAMgAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAwADcARABcACIALAAgAFwAIgBIAEYAQwAtADMAMgAvAEgARgBDAC0AMQAyADUALwBIAEYAQwAtADEAMwA0AGEAXAAiACwAIABcACIAKAAxADUALgAwAC8AMQA1AC4AMAAvADcAMAAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAwADcARQBcACIALAAgAFwAIgBIAEYAQwAtADMAMgAvAEgARgBDAC0AMQAyADUALwBIAEYAQwAtADEAMwA0AGEAXAAiACwAIABcACIAKAAyADUALgAwAC8AMQA1AC4AMAAvADYAMAAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAwADgAQQBcACIALAAgAFwAIgBIAEYAQwAtADEAMgA1AC8ASABGAEMALQAxADQAMwBhAC8ASABDAEYAQwAtADIAMgBcACIALAAgAFwAIgAoADcALgAwAC8ANAA2AC4AMAAvADQANwAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAwADkAQQBcACIALAAgAFwAIgBIAEMARgBDAC0AMgAyAC8ASABDAEYAQwAtADEAMgA0AC8ASABDAEYAQwAtADEANAAyAGIAXAAiACwAIABcACIAKAA2ADAALgAwAC8AMgA1AC4AMAAvADEANQAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAwADkAQgBcACIALAAgAFwAIgBIAEMARgBDAC0AMgAyAC8ASABDAEYAQwAtADEAMgA0AC8ASABDAEYAQwAtADEANAAyAGIAXAAiACwAIABcACIAKAA2ADUALgAwAC8AMgA1AC4AMAAvADEAMAAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAxADAAQQBcACIALAAgAFwAIgBIAEYAQwAtADMAMgAvAEgARgBDAC0AMQAyADUAXAAiACwAIABcACIAKAA1ADAALgAwAC8ANQAwAC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADEAMABCAFwAIgAsACAAXAAiAEgARgBDAC0AMwAyAC8ASABGAEMALQAxADIANQBcACIALAAgAFwAIgAoADQANQAuADAALwA1ADUALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMQAxAEEAXAAiACwAIABcACIASABDAC0AMQAyADcAMAAvAEgAQwBGAEMALQAyADIALwBIAEYAQwAtADEANQAyAGEAXAAiACwAIABcACIAKAAxAC4ANQAvADgANwAuADUALwAxADEALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMQAxAEIAXAAiACwAIABcACIASABDAC0AMQAyADcAMAAvAEgAQwBGAEMALQAyADIALwBIAEYAQwAtADEANQAyAGEAXAAiACwAIABcACIAKAAzAC4AMAAvADkANAAuADAALwAzAC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADEAMQBDAFwAIgAsACAAXAAiAEgAQwAtADEAMgA3ADAALwBIAEMARgBDAC0AMgAyAC8ASABGAEMALQAxADUAMgBhAFwAIgAsACAAXAAiACgAMwAuADAALwA5ADUALgA1AC8AMQAuADUAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAxADIAQQBcACIALAAgAFwAIgBIAEMARgBDAC0AMgAyAC8AUABGAEMALQAyADEAOAAvAEgAQwBGAEMALQAxADQAMgBiAFwAIgAsACAAXAAiACgANwAwAC4AMAAvADUALgAwAC8AMgA1AC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADEAMwBBAFwAIgAsACAAXAAiAFAARgBDAC0AMgAxADgALwBIAEYAQwAtADEAMwA0AGEALwBIAEMALQA2ADAAMABhAFwAIgAsACAAXAAiACgAOQAuADAALwA4ADgALgAwAC8AMwAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAxADQAQQBcACIALAAgAFwAIgBIAEMARgBDAC0AMgAyAC8ASABDAEYAQwAtADEAMgA0AC8ASABDAC0ANgAwADAAYQAvAEgAQwBGAEMALQAxADQAMgBiAFwAIgAsACAAXAAiACgANQAxAC4AMAAvADIAOAAuADUALwA0AC4AMAAvADEANgAuADUAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAxADQAQgBcACIALAAgAFwAIgBIAEMARgBDAC0AMgAyAC8ASABDAEYAQwAtADEAMgA0AC8ASABDAC0ANgAwADAAYQAvAEgAQwBGAEMALQAxADQAMgBiAFwAIgAsACAAXAAiACgANQAwAC4AMAAvADMAOQAuADAALwAxAC4ANQAvADkALgA1ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMQA1AEEAXAAiACwAIABcACIASABDAEYAQwAtADIAMgAvAEgARgBDAC0AMQA1ADIAYQBcACIALAAgAFwAIgAoADgAMgAuADAALwAxADgALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMQA1AEIAXAAiACwAIABcACIASABDAEYAQwAtADIAMgAvAEgARgBDAC0AMQA1ADIAYQBcACIALAAgAFwAIgAoADIANQAuADAALwA3ADUALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMQA2AEEAXAAiACwAIABcACIASABGAEMALQAxADMANABhAC8ASABDAEYAQwAtADEAMgA0AC8ASABDAC0ANgAwADAAXAAiACwAIABcACIAKAA1ADkALgAwAC8AMwA5AC4ANQAvADEALgA1ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMQA3AEEAXAAiACwAIABcACIASABGAEMALQAxADIANQAvAEgARgBDAC0AMQAzADQAYQAvAEgAQwAtADYAMAAwAFwAIgAsACAAXAAiACgANAA2AC4ANgAvADUAMAAuADAALwAzAC4ANAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADEAOABBAFwAIgAsACAAXAAiAEgAQwAtADIAOQAwAC8ASABDAEYAQwAtADIAMgAvAEgARgBDAC0AMQA1ADIAYQBcACIALAAgAFwAIgAoADEALgA1AC8AOQA2AC4AMAAvADIALgA1ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMQA5AEEAXAAiACwAIABcACIASABGAEMALQAxADIANQAvAEgARgBDAC0AMQAzADQAYQAvAEgARQAtAEUAMQA3ADAAXAAiACwAIABcACIAKAA3ADcALgAwAC8AMQA5AC4AMAAvADQALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMgAwAEEAXAAiACwAIABcACIASABGAEMALQAxADMANABhAC8ASABDAEYAQwAtADEANAAyAGIAXAAiACwAIABcACIAKAA4ADgALgAwAC8AMQAyAC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADIAMQBBAFwAIgAsACAAXAAiAEgARgBDAC0AMQAyADUALwBIAEYAQwAtADEAMwA0AGEAXAAiACwAIABcACIAKAA1ADgALgAwAC8ANAAyAC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADIAMgBBAFwAIgAsACAAXAAiAEgARgBDAC0AMQAyADUALwBIAEYAQwAtADEAMwA0AGEALwBIAEMALQA2ADAAMABhAFwAIgAsACAAXAAiACgAOAA1AC4AMQAvADEAMQAuADUALwAzAC4ANAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADIAMgBCAFwAIgAsACAAXAAiAEgARgBDAC0AMQAyADUALwBIAEYAQwAtADEAMwA0AGEALwBIAEMALQA2ADAAMABhAFwAIgAsACAAXAAiACgANQA1AC4AMAAvADQAMgAuADAALwAzAC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADIAMgBDAFwAIgAsACAAXAAiAEgARgBDAC0AMQAyADUALwBIAEYAQwAtADEAMwA0AGEALwBIAEMALQA2ADAAMABhAFwAIgAsACAAXAAiACgAOAAyAC4AMAAvADEANQAuADAALwAzAC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA1ADAAMABcACIALAAgAFwAIgBDAEYAQwAtADEAMgAvAEgARgBDAC0AMQA1ADIAYQBcACIALAAgAFwAIgAoADcAMwAuADgALwAyADYALgAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADUAMAAxAFwAIgAsACAAXAAiAEgAQwBGAEMALQAyADIALwBDAEYAQwAtADEAMgBcACIALAAgAFwAIgAoADcANQAuADAALwAyADUALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADUAMAAyAFwAIgAsACAAXAAiAEgAQwBGAEMALQAyADIALwBDAEYAQwAtADEAMQA1AFwAIgAsACAAXAAiACgANAA4AC4AOAAvADUAMQAuADIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANQAwADMAXAAiACwAIABcACIASABGAEMALQAyADMALwBDAEYAQwAtADEAMwBcACIALAAgAFwAIgAoADQAMAAuADEALwA1ADkALgA5ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADUAMAA0AFwAIgAsACAAXAAiAEgARgBDAC0AMwAyAC8AQwBGAEMALQAxADEANQBcACIALAAgAFwAIgAoADQAOAAuADIALwA1ADEALgA4ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADUAMAA1AFwAIgAsACAAXAAiAEMARgBDAC0AMQAyAC8ASABDAEYAQwAtADMAMQBcACIALAAgAFwAIgAoADcAOAAuADAALwAyADIALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADUAMAA2AFwAIgAsACAAXAAiAEMARgBDAC0AMwAxAC8AQwBGAEMALQAxADEANABcACIALAAgAFwAIgAoADUANQAuADEALwA0ADQALgA5ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADUAMAA3AEEAXAAiACwAIABcACIASABGAEMALQAxADIANQAvAEgARgBDAC0AMQA0ADMAYQBcACIALAAgAFwAIgAoADUAMAAuADAALwA1ADAALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADUAMAA4AEEAXAAiACwAIABcACIASABGAEMALQAyADMALwBQAEYAQwAtADEAMQA2AFwAIgAsACAAXAAiACgAMwA5AC4AMAAvADYAMQAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANQAwADgAQgBcACIALAAgAFwAIgBIAEYAQwAtADIAMwAvAFAARgBDAC0AMQAxADYAXAAiACwAIABcACIAKAA0ADYALgAwAC8ANQA0AC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA1ADAAOQBBAFwAIgAsACAAXAAiAEgAQwBGAEMALQAyADIALwBQAEYAQwAtADIAMQA4AFwAIgAsACAAXAAiACgANAA0AC4AMAAvADUANgAuADAAKQBcACIAXABuACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AKQApACkAOwBcAG4AXABuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AQwBoAGUAbQBpAGMAYQBsAEIAbABlAG4AZABzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAARgBpAHgAZQBkACAAdAB5AHAAbwAgAC0AIABjAGgAYQBuAGcAZQBkACAASABDADYAMAAwAGEAIAB0AG8AIABIAEMALQA2ADAAMABhACAAZgBvAHIAIABiAGwAZQBuAGQAIABSAC0ANAAxADQAQgAuACAARgBpAHgAZQBkACAAdAB5AHAAbwAgAGYAbwByACAAYgBsAGUAbgBkACAAUgAtADQAMAA1AEEAIAAtACAAQwBoAGEAbgBnAGUAZAAgAEgAQwBGAEMAMQA0ADIAYgAgAHQAbwAgAEgAQwBGAEMALQAxADQAMgBiAC4AXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ATABlAGEAawBhAGcAZQAgAHIAYQB0AGUAcwAgAGYAbwByACAAYwBvAG0AbQBvAG4AIAByAGUAZgByAGkAZwBlAHIAYQB0AGkAbwBuACAAYQBuAGQAIABhAGkAcgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBMAGUAYQBrAGEAZwBlAFIAYQB0AGUAcwBfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEkAbgBkAGkAYwBhAHQAaQB2AGUAIABsAGUAYQBrAGEAZwBlACAAcgBhAHQAZQBzACAAZgBvAHIAIABjAG8AbQBtAG8AbgAgAHIAZQBmAHIAaQBnAGUAcgBhAHQAaQBvAG4AIABhAG4AZAAgAGEAaQByACAALQAgAGMAbwBuAGQAaQB0AGkAbwBuAGkAbgBnACAAZQBxAHUAaQBwAG0AZQBuAHQAXAAiACkAKQA7AFwAbgBcAG4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBMAGUAYQBrAGEAZwBlAFIAYQB0AGUAcwBfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ATABlAGEAawBhAGcAZQBSAGEAdABlAHMAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABOAGEAdABpAG8AbgBhAGwAIABHAHIAZQBlAG4AaABvAHUAcwBlACAAQQBjAGMAbwB1AG4AdABzACAARgBhAGMAdABvAHIAcwAgADIAMAAyADUAIAAtACAAVABhAGIAbABlACAAMQAwAFwAIgApACkAOwBcAG4AXABuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ATABlAGEAawBhAGcAZQBSAGEAdABlAHMAXwBEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADgAMQAsACAAMgAsAFwAbgAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwBkAHUAYwB0AFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAbABlAGEAawBhAGcAZQAgAHIAYQB0AGUAIAAoACUAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBEAG8AbQBlAHMAdABpAGMAIAByAGUAZgByAGkAZwBlAHIAYQB0AG8AcgBzAFwAIgAsACAAMQAuADcAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAYQBuAHMAcABvAHIAdAAgAHIAZQBmAHIAaQBnAGUAcgBhAHQAaQBvAG4AXAAiACwAIAAxADUALgA3ADsAXABuACAAIAAgACAAIAAgACAAIABcACIARABvAG0AZQBzAHQAaQBjACAAQQAvAEMAIABwAG8AcgB0AGEAYgBsAGUAXAAiACwAIAAyAC4ANQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEQAbwBtAGUAcwB0AGkAYwAgAEEALwBDACAAcwBwAGwAaQB0AFwAIgAsACAAMwAuADUAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBEAG8AbQBlAHMAdABpAGMAIABBAC8AQwAgAHAAYQBjAGsAYQBnAGUAZABcACIALAAgADIALgA1ADsAXABuACAAIAAgACAAIAAgACAAIABcACIATABpAGcAaAB0ACAAdgBlAGgAaQBjAGwAZQAgAEEALwBDAFwAIgAsACAANgAuADcAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAGUAYQB2AHkAIAB2AGUAaABpAGMAbABlACAAQQAvAEMAXAAiACwAIAAxADAALgA4AFwAbgAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACkAKQApADsAXABuAFwAbgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEwAZQBhAGsAYQBnAGUAUgBhAHQAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBDAGEAbABjAHUAbABhAHQAZQBCAGwAZQBuAGQARwBXAFAAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAEMAbwBuAHMAdABpAHQAdQBlAG4AdABGAGEAYwB0AGkAbwBuADEALAAgAEMAbwBuAHMAdABpAHQAdQBlAG4AdABHAFcAUAAxACwAIABcAG4AIAAgAEMAbwBuAHMAdABpAHQAdQBlAG4AdABGAGEAYwB0AGkAbwBuADIALAAgAEMAbwBuAHMAdABpAHQAdQBlAG4AdABHAFcAUAAyACwAIABcAG4AIAAgAEMAbwBuAHMAdABpAHQAdQBlAG4AdABGAGEAYwB0AGkAbwBuADMALAAgAEMAbwBuAHMAdABpAHQAdQBlAG4AdABHAFcAUAAzACwAIABcAG4AIAAgAEMAbwBuAHMAdABpAHQAdQBlAG4AdABGAGEAYwB0AGkAbwBuADQALAAgAEMAbwBuAHMAdABpAHQAdQBlAG4AdABHAFcAUAA0ACwAXABuACAAIAAoAEMAbwBuAHMAdABpAHQAdQBlAG4AdABGAGEAYwB0AGkAbwBuADEAIAAqACAAQwBvAG4AcwB0AGkAdAB1AGUAbgB0AEcAVwBQADEAKQAgACsAXABuACAAIAAoAEMAbwBuAHMAdABpAHQAdQBlAG4AdABGAGEAYwB0AGkAbwBuADIAIAAqACAAQwBvAG4AcwB0AGkAdAB1AGUAbgB0AEcAVwBQADIAKQAgACsAXABuACAAIAAoAEMAbwBuAHMAdABpAHQAdQBlAG4AdABGAGEAYwB0AGkAbwBuADMAIAAqACAAQwBvAG4AcwB0AGkAdAB1AGUAbgB0AEcAVwBQADMAKQAgACsAXABuACAAIAAoAEMAbwBuAHMAdABpAHQAdQBlAG4AdABGAGEAYwB0AGkAbwBuADQAIAAqACAAQwBvAG4AcwB0AGkAdAB1AGUAbgB0AEcAVwBQADQAKQBcAG4AKQA7ACIAfQBdACwAIgBwAHIAbwBqAGUAYwB0AE4AYQBtAGUAcwAiADoAWwAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATwBuAGUAQwBvAGwAdQBtAG4AQQBuAGQASABlAGEAZABlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABOADIATwBFAEYARgByAG8AbQBQAHIAbwBkAEkAcgByAGkAZwBhAHQAaQBvAG4AUgBhAGkAbgBmAGEAbABsACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBDAG8AbgB2AGUAcgB0AFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAFQAbwBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBUAGkAdABsAGUAIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADEARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8ARABlAHMAYwByAGkAcAB0AGkAbwBuACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAEQAYQB0AGEAIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADEARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8AVABpAHQAbABlACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBTAG8AdQByAGMAZQAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBEAGEAdABhACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBMAGkAcQB1AGkAZABfAFQAaQB0AGwAZQAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEwAaQBxAHUAaQBkAF8ARABlAHMAYwByAGkAcAB0AGkAbwBuACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkATABpAHEAdQBpAGQAXwBTAG8AdQByAGMAZQAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEwAaQBxAHUAaQBkAF8ARABhAHQAYQAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEwAaQBxAHUAaQBkAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAVAByAGEAbgBzAHAAbwByAHQAXwBUAGkAdABsAGUAIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAVAByAGEAbgBzAHAAbwByAHQAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAVAByAGEAbgBzAHAAbwByAHQAXwBTAG8AdQByAGMAZQAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBUAHIAYQBuAHMAcABvAHIAdABfAEQAYQB0AGEAIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAVAByAGEAbgBzAHAAbwByAHQAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBUAHIAYQBuAHMAcABvAHIAdABPAGYAZgBSAG8AYQBkAF8AVABpAHQAbABlACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AE8AZgBmAFIAbwBhAGQAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAVAByAGEAbgBzAHAAbwByAHQATwBmAGYAUgBvAGEAZABfAFMAbwB1AHIAYwBlACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AE8AZgBmAFIAbwBhAGQAXwBEAGEAdABhACIALAAiAEYAdQBlAGwAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBGAHUAZQBsAF8ARwBlAHQAVAByAGEAbgBzAHAAbwByAHQARgB1AGUAbABTAHQAcgBpAG4AZwAiACwAIgBGAHUAZQBsAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4ARgB1AGUAbABfAEcAZQB0AFMAdABhAHQAaQBvAG4AYQByAHkARgB1AGUAbABTAHQAcgBpAG4AZwAiACwAIgBGAHUAZQBsAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4ARgB1AGUAbABfAFQAbwB0AGEAbABDAG8AbgBzAHUAbQBwAHQAaQBvAG4AIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AMQBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFQAcgBhAG4AcwBwAG8AcgB0ACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwAxAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AVAByAGEAbgBzAHAAbwByAHQAXwBUAGkAdABsAGUAIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfADEAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBUAHIAYQBuAHMAcABvAHIAdABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AMQBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFQAcgBhAG4AcwBwAG8AcgB0AF8AVQBuAGkAdAAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AMQBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFQAcgBhAG4AcwBwAG8AcgB0AF8AUwBvAHUAcgBjAGUAIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfADEAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBUAHIAYQBuAHMAcABvAHIAdABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwAxAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AVAByAGEAbgBzAHAAbwByAHQAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwAxAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AVAByAGEAbgBzAHAAbwByAHQAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AMgBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFMAdABhAHQAaQBvAG4AYQByAHkAIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfADIAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBTAHQAYQB0AGkAbwBuAGEAcgB5AF8AVABpAHQAbABlACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwAyAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AUwB0AGEAdABpAG8AbgBhAHIAeQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AMgBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFMAdABhAHQAaQBvAG4AYQByAHkAXwBVAG4AaQB0ACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwAyAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AUwB0AGEAdABpAG8AbgBhAHIAeQBfAFMAbwB1AHIAYwBlACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwAyAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AUwB0AGEAdABpAG8AbgBhAHIAeQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwAyAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AUwB0AGEAdABpAG8AbgBhAHIAeQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfADIAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBTAHQAYQB0AGkAbwBuAGEAcgB5AF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfAFgAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4ARwBlAG4AZQByAGkAYwAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AWABfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBHAGUAbgBlAHIAaQBjAF8AVABpAHQAbABlACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwBYAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAEcAZQBuAGUAcgBpAGMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfAFgAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4ARwBlAG4AZQByAGkAYwBfAFUAbgBpAHQAIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfAFgAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4ARwBlAG4AZQByAGkAYwBfAFMAbwB1AHIAYwBlACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwBYAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAEcAZQBuAGUAcgBpAGMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AWABfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBHAGUAbgBlAHIAaQBjAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AWABfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBHAGUAbgBlAHIAaQBjAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfAFgAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4ARwBlAG4AZQByAGkAYwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcARwBXAFAAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAF8AVABpAHQAbABlACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBHAFcAUABfAFQAaQB0AGwAZQAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBfAFUAbgBpAHQAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAEcAVwBQAF8AVQBuAGkAdAAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAXwBTAG8AdQByAGMAZQAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcARwBXAFAAXwBTAG8AdQByAGMAZQAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAXwBSAGUAYQBkAGEAYgBsAGUARQBxAHUAYQB0AGkAbwBuACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAEcAVwBQAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcARwBXAFAAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABHAFcAUABfAFQAaQB0AGwAZQAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABHAFcAUABfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABHAFcAUABfAFMAbwB1AHIAYwBlACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AQwBoAGUAbQBpAGMAYQBsAEcAVwBQAF8ARABhAHQAYQAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABHAFcAUABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AQwBoAGUAbQBpAGMAYQBsAEIAbABlAG4AZABzAF8AVABpAHQAbABlACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AQwBoAGUAbQBpAGMAYQBsAEIAbABlAG4AZABzAF8ARABlAHMAYwByAGkAcAB0AGkAbwBuACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AQwBoAGUAbQBpAGMAYQBsAEIAbABlAG4AZABzAF8AUwBvAHUAcgBjAGUAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBDAGgAZQBtAGkAYwBhAGwAQgBsAGUAbgBkAHMAXwBEAGEAdABhACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AQwBoAGUAbQBpAGMAYQBsAEIAbABlAG4AZABzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBMAGUAYQBrAGEAZwBlAFIAYQB0AGUAcwBfAFQAaQB0AGwAZQAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEwAZQBhAGsAYQBnAGUAUgBhAHQAZQBzAF8ARABlAHMAYwByAGkAcAB0AGkAbwBuACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ATABlAGEAawBhAGcAZQBSAGEAdABlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEwAZQBhAGsAYQBnAGUAUgBhAHQAZQBzAF8ARABhAHQAYQAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEwAZQBhAGsAYQBnAGUAUgBhAHQAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAYQBsAGMAdQBsAGEAdABlAEIAbABlAG4AZABHAFcAUAAiAF0ALAAiAGwAbwBjAGEAbABlACIAOgB7ACIAbABpAHMAdABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHIAbwB3AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAYwBvAGwAdQBtAG4AUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHQAaABvAHUAcwBhAG4AZABzAFAAbwBzAGkAdABpAG8AbgBzACIAOgBbADMAXQAsACIAZABlAGMAaQBtAGEAbABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAuACIALAAiAGQAYQB0AGUATwByAGQAZQByACIAOgAiAEQATQBZACIALAAiAGMAdQByAHIAZQBuAGMAeQBTAHkAbQBiAG8AbAAiADoAIgAkACIALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwATABlAGEAZAAiADoAdAByAHUAZQAsACIAaQBzAEMAdQByAHIAZQBuAGMAeQBTAGUAcABCAHkAUwBwAGEAYwBlACIAOgBmAGEAbABzAGUALAAiAHIAbwB3AEwAZQB0AHQAZQByACIAOgAiAFIAIgAsACIAYwBvAGwAdQBtAG4ATABlAHQAdABlAHIAIgA6ACIAQwAiACwAIgByAGMATABlAGYAdABCAHIAYQBjAGsAZQB0ACIAOgAiAFsAIgAsACIAcgBjAFIAaQBnAGgAdABCAHIAYQBjAGsAZQB0ACIAOgAiAF0AIgAsACIAcwB0AGEAdABlAG0AZQBuAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIAOwAiACwAIgBsAG8AYwBhAGwAZQBOAGEAbQBlACIAOgAiAGUAbgAtAHUAcwAiAH0AfQA=</AFEJSONBlob>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
@@ -19141,6 +19156,19 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgAFwAdQAwADAAMgA3AEYAcgB5AFwAdQAwADAAMgA3ACAAdABvACAAXAB1ADAAMAAyADcARAByAHkAXAB1ADAAMAAyADcALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIAVwBlAHQAIABvAHIAIABEAHIAeQAgAFoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAHcAYQByAG0AIAAvACAAYwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALwAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0ACAAYQBuAGQAIABoAGkAZwBoACAAdABlAG0AcAAgAGMAbABhAHMAcwBlAHMAIAB0AG8AIABhAGMAYwBvAG0AbQBvAGQAYQB0AGUAIABjAGwAaQBtAGEAdABlACAAcwBjAGUAbgBhAHIAaQBvAHMAIABlAHgAYwBsAHUAZABlAGQAIABiAHkAIABWAEUARQBSAEcAIABjAHIAaQB0AGUAcgBpAGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBpAHgAZQBkACAAdAB5AHAAbwAgAGkAbgAgAE0AQQBUACAAdgBhAGwAdQBlACAAZgBvAHIAIAB3AGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABjAGgAYQBuAGcAZQBkACAAMQAwACAAdABvACAAMQAxAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAG0AaQBuACAAYQBuAGQAIABtAGEAeAAgAGMAbwBsAHUAbQBuAHMAIABmAG8AcgAgAE0AQQBUACwAIABNAEEAUAAsACAAZgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgAsACAAZQBsAGUAdgBhAHQAaQBvAG4ALAAgAE0AQQBQADoAUABFAFQAIAB0AG8AIABjAGEAbABjAHUAbABhAHQAZQAgAHoAbwBuAGUAcwAgAGYAcgBvAG0AIAByAGUAYQBsACAAYwBsAGkAbQBhAHQAZQAgAGQAYQB0AGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBBAEYAIABhAGMAYwBlAHAAdABzACAAcgBhAGkAbgBmAGEAbABsACAAYQBzACAAYQAgAHAAcgBvAHgAeQAgAGYAbwByACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUAFwAIgAsACAAXAAiAE0AQQBQAFwAIgAsACAAXAAiAEYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIAXAAiACwAIABcACIARQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAHQAZQBtAHAAXAAiACwAIABcACIATQBhAHgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AaQBuACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AYQB4ACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AaQBuACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGEAeAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBpAG4AIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGEAeAAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADIAMAAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAG0AIAAtACAAZCIgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAxADAAMAAwAC4AMAAwADEALAAgADIAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQBcACIALAAgADEAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB0AGUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFQAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAUAAgAD0AIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEUAVAAgAD0AIABwAG8AdABlAG4AdABpAGEAbAAgAGUAdgBhAHAAbwB0AHIAYQBuAHMAcABpAHIAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAE0AQQBUACAAbQBpAG4AIABhAG4AZAAgAE0AQQBUACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AZQBkAGkAYQBuACAAQQBuAG4AdQBhAGwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAAoAE0AQQBUACkAXAAiACwAIABcACIATQBpAG4AIABNAEEAVABcACIALAAgAFwAIgBNAGEAeAAgAE0AQQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiIAAyADYAIABDAFwAIgAsACAAMgA2ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgAFwAIgAxADUAIAAtACAAMgA1ACAAQwBcACIALAAgADEANQAsACAAMgA1AC4AOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIiAAMQA0ACAAQwBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEANAAuADkAOQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABaAG8AbgBlAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AaQBuAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAXAB1ADAAMAAzAGUAIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAXAB1ADAAMAAzAGUAowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABkAG8AZQBzACAAbgBvAHQAIABvAGMAYwB1AHIAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAGQiowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBzACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAWQBlAHMAIAAtACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvACAALQAgAG4AbwB0ACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAZABhAHQAYQAgAHMAYwBvAHIAZQBzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFgAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAdABhACAAcwBvAHUAcgBjAGUAXAAiACwAIABcACIARABhAHQAYQAgAHMAYwBvAHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAHQAZQByAG4AYQB0AGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUAIABvAHIAIAByAGUAZwBpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAGkAbgB0AGUAbgBzAGkAdAB5ACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIABhAHAAcAByAG8AdgBlAGQAIABtAGUAdABoAG8AZABcACIALAAgADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBlAHIAaQBmAGkAZQBkACAAYwByAGUAZABlAG4AdABpAGEAbAAgAG0AYQB0AGMAaABpAG4AZwAgAEkAUwBPADEANAAwADYANwBcACIALAAgADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIAAoADMALgBEAC4AYgAuADIAKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBMAEUAQQBDAEgAXAAiACwAMAAuADIANABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AIAAzAC4ARAAuAEIAXwAxADAAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAGwAZQBhAGMAaABcACIALAAwAC4AMAAxADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADUALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACwAXAAiAEUARgBOADIATwBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5AFwAIgAsACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAA1ADkALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAXAAiACwAMAAuADAAMAA3ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABsAG8AdwAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAMgA5ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAaABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAOAAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAMAAuADAAMQA5ADkALAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsADAALgAwADAANQAzACwAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAMAAuADAAMAA2ADQALAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABjAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnACkAXAAiACwAMAAuADAAMAAzACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBDAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABzAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnACkAXAAiACwAMAAuADAAMAA1ACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBTAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAMAAuADAAMAAyADYALAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABkAHUAcABsAGkAYwBhAHQAZQAgAFwAdQAwADAAMgA3AEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcAHUAMAAwADIANwAsACAAXAB1ADAAMAAyADcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcAHUAMAAwADIANwAgAGEAbgBkACAAXAB1ADAAMAAyADcAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AG4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAdQAwADAAMgA3ACAAcgBvAHcAIAB3AGkAdABoACAAcwBhAG0AZQAgAEUARgAgAGYAbwByACAAbABvAHcAIABhAG4AZAAgAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXABuAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXABuAEkAUABDAEMAOgAgAE4AMgBPACAARQBNAEkAUwBTAEkATwBOAFMAIABGAFIATwBNACAATQBBAE4AQQBHAEUARAAgAFMATwBJAEwAUwAsACAAQQBOAEQAIABDAE8AMgAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAEwASQBNAEUAIABBAE4ARAAgAFUAUgBFAEEAIABBAFAAUABMAEkAQwBBAFQASQBPAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAFcARQBUACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAQwBoAGEAcAB0AGUAcgAgADEALAAgAHMAZQBjAHQAaQBvAG4AIAAxAC4AOAAuADIAIABMAGUAYQBjAGgAaQBuAGcALAAgAGMAbABpAG0AYQB0AGUAIABhAG4AZAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAUgBlAGYAaQBuAGUAbQBlAG4AdAAgAFYAbwBsAHUAbQBlACAANAA6ACAAQwBoAGEAcAB0AGUAcgAgADEAMQA6ACAATgAyAE8AIABFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABNAGEAbgBhAGcAZQBkACAAUwBvAGkAbABzACwAIABhAG4AZAAgAEMATwAyACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATABpAG0AZQAgAGEAbgBkACAAVQByAGUAYQAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlACAAaQByAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBwAHIAaQBuAGsAbABlAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAcgBmAGEAYwBlACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABUAGEAYgBsAGUAIABjAHIAZQBhAHQAZQBkACAAYgBhAHMAZQBkACAAbwBuACAAVgBFAEUAUgBHACAAdABlAHgAdAAgAFwAdQAwADAAMgA3AEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuAFwAdQAwADAAMgA3AFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAOgAgAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAFAAUgBQACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgAyAE8AIAAtACAATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIABcACIARQBGAFAAUgBQAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAB1ADAAMAAyADcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAdQAwADAAMgA3ACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AbwBuAHQAaABzACAAdABvACAAUwBlAGEAcwBvAG4AcwAgAE0AYQBwAHAAaQBuAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AbgB0AGgAXAAiACwAIABcACIAUwBlAGEAcwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAYQBuAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBiAHIAdQBhAHIAeQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAHIAYwBoAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHAAcgBpAGwAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQB5AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbgBlAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbAB5AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAZwB1AHMAdABcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAHAAdABlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AYwB0AG8AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB2AGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGMAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAbgB1AHIAZQAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAIAATICAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAegBvAG4AZQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA4AC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAyACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAIAAoALoAQwApAFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAUwBsAHUAcgByAHkAIAAoAHcAaQB0AGgAbwB1AHQAIABuAGEAdAB1AHIAYQBsACAAYwByAHUAcwB0ACkAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAGIAKQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABTAHQAbwByAGEAZwBlACAAXAB1ADAAMAAzAGMAMQAgAG0AbwBuAHQAaABcACIALAAgAFwAIgBEAGUAZQBwACAATABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAE0AYQBuAHUAcgBlACAAKAB3AGkAdABoAC8AdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACkAXAAiACwAIABcACIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAaQBuAHQAbwAgAHAAZQBsAGwAZQB0AGkAegBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACwAIABSAGEAbgBnAGUAIABhAG4AZAAgAFAAYQBkAGQAbwBjAGsAIAAoAGMAKQAoAGQAKQBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAXAAiAGQiMQAwAFwAIgAsACAAMAAuADYANgAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMQAsACAAMAAuADYAOAAsACAAMAAuADEALAAgADAALgAxADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAyACwAIAAwAC4ANwAsACAAMAAuADEALAAgADAALgAxADMALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAzACwAIAAwAC4ANwAxACwAIAAwAC4AMQAsACAAMAAuADEANAAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADQALAAgADAALgA3ADMALAAgADAALgAxACwAIAAwAC4AMQA1ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADUALAAgADAALgA3ADQALAAgADAALgAxACwAIAAwAC4AMQA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA2ACwAIAAwAC4ANwA1ACwAIAAwAC4AMQAsACAAMAAuADEAOAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANwAsACAAMAAuADcANgAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA4ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIAMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOQAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADAALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA2ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAxACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIAOQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMgAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAzADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADMALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA0ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANQAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANgAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADQALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANwAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANAA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIABcACIAZSIyADgAXAAiACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwBcACIALAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZABcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgAgAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAcgBvAHcAIABvAGYAIABOAEkAUgAgAE0ATQBBACAAZABlAGYAaQBuAGkAdABpAG8AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuACAARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AFAAbwB1AGwAdAByAHkAIAB3AGkAdABoACAAYQBuAGQAIAB3AGkAdABoAG8AdQB0ACAAbABpAHQAdABlAHIAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABzAGUAcABhAHIAYQB0AGUAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AE0AQQBUACAAcgBhAHcAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHQAbwAgAGEAbABsAG8AdwAgAGwAbwBvAGsAdQBwACAAbwBmACAAbgB1AG0AYgBlAHIAcwAuAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBuAGQAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYATgBpACAAXAB1ADAAMAAyADYAIABFAEYATgAyAE8AaQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADEALgA0AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBOAGkAIABcAHUAMAAwADIANgAgAEUARgBOADIATwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAE4AMgBPACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUATgAyAE8AOgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXABuAEcAVwBQAE4AMgBPADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBOADIATwAsACAARwBXAFAAXwBOADIATwAsAFwAbgAgACAAIAAgAEUAXwBOADIATwAgACoAIABHAFcAUABfAE4AMgBPAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AE4AMgBPAH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AE4AMgBPAH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBOADIATwBcACIALABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAATgAyAE8AXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAEMASAA0ACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUAQwBIADQAOgAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXABuAEcAVwBQAEMASAA0ADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBDAEgANAAsACAARwBXAFAAXwBDAEgANAAsAFwAbgAgACAAIAAgAEUAXwBDAEgANAAgACoAIABHAFcAUABfAEMASAA0AFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEMASAA0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AEMASAA0AH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AEMASAA0AH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAEgANABcACIALABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAAQwBIADQAXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkALABcAG4AIAAgACAAIABSAE8AVwAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAgAC0AIAAxAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACwAXABuACAAIABDAE8ATABVAE0ATgAoAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAQQByAHIAYQB5AEQAYQB0AGEALAAgAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAIABbAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAXQAsAFwAbgAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgAEkATgBEAEUAWAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABVAE4ASQBRAFUARQAoAEEAcgByAGEAeQBEAGEAdABhACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwAoACkALQBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwAKQAgACsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApACwAIAAxACwAIABDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAIABcACIAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAASQBGACgASQBTAE4AVQBNAEIARQBSACgAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgAgACAAIAAgACkALAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkALAAgADAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABbAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlAF0ALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAMQAsACAAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACkAKgAoAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlADIAKQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE8AbgBlAEMAbwBsAHUAbQBuAEEAbgBkAEgAZQBhAGQAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBmAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQAsACAAXAAiAFwAIgAsACAAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQwBlAGwAbAAsACAARABlAGwAaQBtAGkAdABlAHIALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEAXQAsACAAWwBDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgBdACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgBYAE0ATAAoAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAdQAwADAAMwBjAHQAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAIABcAHUAMAAwADIANgBcAG4AIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFMAVQBCAFMAVABJAFQAVQBUAEUAKABDAGUAbABsACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEALABcACIAXAAiACkALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABEAGUAbABpAG0AaQB0AGUAcgAsAFwAIgBcAHUAMAAwADMAYwAvAHMAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAXABuACAAIAAgACAAIAAgACAAIAApACAAXAB1ADAAMAAyADYAXABuACAAIAAgACAAIAAgACAAIABcACIAXAB1ADAAMAAzAGMALwBzAFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAC8AdABcAHUAMAAwADMAZQBcACIALABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAvAC8AcwBcACIAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAdgBnAFQAZQBtAHAALABhAHYAZwBSAGEAaQBuACwAZgByAG8AcwB0AEQAYQB5AHMALABlAGwAZQB2ACwAbQBhAHAAXwBwAGUAdAAsAFwAbgAgACAAIAAgAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACwAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkALABtAGEAeABGAHIAbwBzAHQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4AUABFAFQAQQByAHIAYQB5ACwAbQBhAHgAUABFAFQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAYwBsAGkAbQBhAHQAZQBaAG8AbgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBSAGEAaQBuACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AYQB2AGcAUgBhAGkAbgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AZgByAG8AcwB0AEQAYQB5AHMAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AG0AYQBwAF8AcABlAHQAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AG0AYQBwAF8AcABlAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABBAEsARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAGMAbABpAG0AYQB0AGUAWgBvAG4AZQBBAHIAcgBhAHkALABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgADEAXABuACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAE0AaQBuAEEAcgByAGEAeQAsACAATQBhAHgAQQByAHIAYQB5ACwAIABJAHQAZQBtAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAE0AaQBuAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBhAHgAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABJAHQAZQBtAEEAcgByAGEAeQAsACAAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAQwByAGkAdABlAHIAaQBhADEALAAgAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5ACwAIABRAHUAYQBuAHQAaQB0AHkALAAgAFsATQB1AGwAdABpAHAAbABpAGUAcgBdACwAIABbAEMAcgBpAHQAZQByAGkAYQAyAF0ALABbAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQBdACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAG0AdQBsAHQAaQBwAGwAaQBlAHIALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgATQB1AGwAdABpAHAAbABpAGUAcgApACwAMQAsAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsAFwAbgAgACAAIAAgAHEAdQBhAG4AdABpAHQAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACoATQB1AGwAdABpAHAAbABpAGUAcgAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMQApACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADIALABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAcgBpAHQAZQByAGkAYQAyACkALAAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADIAKQApACwAXABuACAAIAAgACAAUwBVAE0AUABSAE8ARABVAEMAVAAoAGMAcgBpAHQAZQByAGkAYQAxACoAYwByAGkAdABlAHIAaQBhADIAKgBxAHUAYQBuAHQAaQB0AHkAKQBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAXABuACAAIAAgACAAIAAgACAAIABBACwAUwAtADMANgA1ACwAXABuACAAIAAgACAAIAAgACAAIAB5AGEALABZAEUAQQBSACgAQQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AGIALABZAEUAQQBSACgARQApACwAXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApAFwAdQAwADAAMwBjACAAUwApACwAXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAFwAdQAwADAAMwBlACAARQApACwAXABuACAAIAAgACAAIAAgACAAIABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsACAALwAqAGgAZQBsAHAAZQByADoAIABlAG4AZAAgAGQAYQB0AGUAIABmAG8AcgAgAGEAIAByAGUAcABvAHIAdABpAG4AZwAgAHAAZQByAGkAbwBkACAAcwB0AGEAcgB0AGkAbgBnACAAYQB0ACAAYQAgAGcAaQB2AGUAbgAgAGQAYQB0AGUAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAIAAvACoAbwBuAGwAeQAgAG4AZQBlAGQAIAB0AG8AIABsAG8AbwBrACAAYgBhAGMAawAgADMANgA1ACAAZABhAHkAcwAoAG0AYQB4ACAAbwB2AGUAcgBsAGEAcAAgAHcAaQBuAGQAbwB3ACkAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYQAgAGUAbgBkAHMAIABiAGUAZgBvAHIAZQAgAFMALABpAHQAIABjAGEAbgBcAHUAMAAwADIANwB0ACAAbwB2AGUAcgBsAGEAcAA7ACAAbQBvAHYAZQAgAHQAbwAgAG4AZQB4AHQAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAXAB1ADAAMAAzAGMAUwApACwAIAAvACoAaQBmACAAdABoAGUAIABhAG4AYwBoAG8AcgAgAGYAbwByACAAeQBiACAAcwB0AGEAcgB0AHMAIABhAGYAdABlAHIAIABFACwAaQB0ACAAYwBhAG4AXAB1ADAAMAAyADcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABwAHIAZQB2AGkAbwB1AHMAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAXAB1ADAAMAAzAGUARQApACwAXABuACAAIAAgACAAIAAgACAAIABuACwATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAcgBzACwAUwBFAFEAVQBFAE4AQwBFACgAbgAsADEALABmAGkAcgBzAHQAWQBlAGEAcgAsADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMALABEAEEAVABFACgAeQByAHMALABtACwAZAApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzACwATQBBAFAAKABzAHQAYQByAHQAcwAsAFAAZQByAGkAbwBkAEUAbgBkACkALABcAG4AIAAgACAAIAAgACAAIAAgAHQAYQBnACwASQBGACgAcwB0AGEAcgB0AHMAPQBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXAAiACAAKABUAGgAaQBzACAAcgBlAHAAbwByAHQAaQBuAGcAIABjAHkAYwBsAGUAKQBcACIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzAFQAZQB4AHQALABUAEUAWABUACgAcwB0AGEAcgB0AHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzAFQAZQB4AHQALABUAEUAWABUACgAZQBuAGQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAG4APQAwACwAXAAiAFwAIgAsAEgAUwBUAEEAQwBLACgAcwB0AGEAcgB0AHMAVABlAHgAdAAgAFwAdQAwADAAMgA2ACAAXAAiACAAdABvACAAXAAiACAAXAB1ADAAMAAyADYAIABlAG4AZABzAFQAZQB4AHQAIABcAHUAMAAwADIANgAgAHQAYQBnACkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQBcAG4APQBMAEEATQBCAEQAQQAoAEYAdQBuAGMAdABpAG8AbgAsACAAVABFAFgAVABCAEUARgBPAFIARQAoAEYATwBSAE0AVQBMAEEAVABFAFgAVAAoAEYAdQBuAGMAdABpAG8AbgApACwAIABcACIAKABcACIAKQApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBBAHIAcgBhAHkALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5ACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkALABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAA9AFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABJAEYAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACAAPQAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALAAgAFwAIgBBAG4AeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5AD0AUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZABBAHIAcgBhAHkAPQBJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkAPQBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQAIAArACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAFwAdQAwADAAMwBlADAALAAgADEALAAgADAAKQBcAG4AIAAgACAAIAApACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsAFwAbgAgACAAIAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAdQAwADAAMgA3AFwAIgAgAFwAdQAwADAAMgA2ACAAcwBoACAAXAB1ADAAMAAyADYAIABcACIAXAB1ADAAMAAyADcAIQBcACIAIABcAHUAMAAwADIANgAgAGEAZABkAHIAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsARABpAGYAZgBlAHIAZQBuAHQAUwBoAGUAZQB0AFwAbgA9AEwAQQBNAEIARABBACgAVABhAHIAZwBlAHQAQwBlAGwAbAAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABzAGgALAAgAFQARQBYAFQAQQBGAFQARQBSACgAQwBFAEwATAAoAFwAIgBmAGkAbABlAG4AYQBtAGUAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALAAgAFwAIgBdAFwAIgApACwAXABuACAAIAAgACAAYQBkAGQAcgAsACAAQwBFAEwATAAoAFwAIgBhAGQAZAByAGUAcwBzAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAXABuACAAIAAgACAAXAAiACMAXAAiACAAXAB1ADAAMAAyADYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAxAF8AMgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADEALAAgADIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAzAF8ANABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADMALAAgADQAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBHAGUAdABNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAATQBNAFMALAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFwAbgAgACAAIAAgACAAIAAgACAATQBFAEQASQBBAE4AKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFUATgBEACgAVABlAG0AcABlAHIAYQB0AHUAcgBlACwAIAAwACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEkATgAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0AQQBYACgAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAE0ATQBTACwAIABNAE0AUwBBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUgBlAHMAdQBsAHQAcwBJAHQAZQBtAEYAcgBvAG0ARQBxAHUAYQB0AGkAbwBuAFQAaQB0AGwAZQBBAG4AZABTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAaQB0AGwAZQBDAGUAbABsACwAIABTAG8AdQByAGMAZQBDAGUAbABsACwAXABuACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAEwARQBGAFQAKABTAG8AdQByAGMAZQBDAGUAbABsACwAIABGAEkATgBEACgAXAAiACwAXAAiACwAIABTAG8AdQByAGMAZQBDAGUAbABsACkAIAAtADEAKQAsACAAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFwAIgAsACAAXAAiAFwAIgApACAAXAB1ADAAMAAyADYAIABcACIAIABcACIAIABcAHUAMAAwADIANgAgAFQAaQB0AGwAZQBDAGUAbABsAFwAbgApADsAIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ARgB1AGUAbAAgAHMAYwBvAHAAZQAgADEAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAALQAgAFMAdABhAHQAaQBvAG4AYQByAHkAIABnAGEAcwBlAG8AdQBzACAAZgB1AGUAbABzAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8AVABpAHQAbABlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIARgB1AGUAbAAgAHMAYwBvAHAAZQAgADEAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAALQAgAFMAdABhAHQAaQBvAG4AYQByAHkAIABnAGEAcwBlAG8AdQBzACAAZgB1AGUAbABzAFwAIgApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBEAGkAcgBlAGMAdAAgACgAUwBjAG8AcABlACAAMQApACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAdABoAGUAIABjAG8AbgBzAHUAbQBwAHQAaQBvAG4AIABvAGYAIABnAGEAcwBlAG8AdQBzACAAZgB1AGUAbABzACAAaQBuAGMAbAB1AGQAaQBuAGcAIABsAGkAcQB1AGUAZgBpAGUAZAAgAG4AYQB0AHUAcgBhAGwAIABnAGEAcwAgACAAXAAiACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAE4AYQB0AGkAbwBuAGEAbAAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABBAGMAYwBvAHUAbgB0AHMAIABGAGEAYwB0AG8AcgBzACAAMgAwADIANQAgAC0AIABUAGEAYgBsAGUAIAA1AFwAIgApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAOQAsACAANwAsAFwAbgAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBGAHUAZQBsACAAYwBvAG0AYgB1AHMAdABlAGQAXAAiACwAIABcACIARQBuAGUAcgBnAHkAIABDAG8AbgB0AGUAbgB0ACAARgBhAGMAdABvAHIAIAAoAEcASgAgAHAAZQByACAAdQBuAGkAdAAgAG8AZgAgAGYAdQBlAGwAKQBcACIALAAgAFwAIgBGAHUAZQBsACAAdQBuAGkAdABcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAxACAARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAIAAoAGsAZwAgAEMATwAyACAALQAgAGUAIAAvACAARwBKACkAIABDAE8AMgBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAxACAARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAIAAoAGsAZwAgAEMATwAyACAALQAgAGUAIAAvACAARwBKACkAIABDAEgANABcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAxACAARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAIAAoAGsAZwAgAEMATwAyACAALQAgAGUAIAAvACAARwBKACkAIABOADIATwBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAxACAARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAIAAoAGsAZwAgAEMATwAyACAALQAgAGUAIAAvACAARwBKACkAIABDAG8AbQBiAGkAbgBlAGQAIABnAGEAcwBlAHMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIATgBhAHQAdQByAGEAbAAgAGcAYQBzACAAZABpAHMAdAByAGkAYgB1AHQAZQBkACAAaQBuACAAYQAgAHAAaQBwAGUAbABpAG4AZQBcACIALAAgADAALgAwADMAOQAzACwAIABcACIAbQAzAFwAIgAsACAANQAxAC4ANAAsACAAMAAuADEALAAgADAALgAwADMALAAgADUAMQAuADUAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBhAGwAIABzAGUAYQBtACAAbQBlAHQAaABhAG4AZQAgAHQAaABhAHQAIABpAHMAIABjAGEAcAB0AHUAcgBlAGQAIABmAG8AcgAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AXAAiACwAIAAwAC4AMAAzADcANwAsACAAXAAiAG0AMwBcACIALAAgADUAMQAuADQALAAgADAALgAyACwAIAAwAC4AMAAzACwAIAA1ADEALgA2ADMAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AYQBsACAAbQBpAG4AZQAgAHcAYQBzAHQAZQAgAGcAYQBzACAAdABoAGEAdAAgAGkAcwAgAGMAYQBwAHQAdQByAGUAZAAgAGYAbwByACAAYwBvAG0AYgB1AHMAdABpAG8AbgBcACIALAAgADAALgAwADMANwA3ACwAIABcACIAbQAzAFwAIgAsACAANQAxAC4AOQAsACAANAAuADYALAAgADAALgAzACwAIAA1ADYALgA4ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBvAG0AcAByAGUAcwBzAGUAZAAgAG4AYQB0AHUAcgBhAGwAIABnAGEAcwAoAHIAZQB2AGUAcgB0AGkAbgBnACAAdABvACAAcwB0AGEAbgBkAGEAcgBkACAAYwBvAG4AZABpAHQAaQBvAG4AcwApAFwAIgAsACAAMAAuADAAMwA5ADMALAAgAFwAIgBtADMAXAAiACwAIAA1ADEALgA0ACwAIAAwAC4AMQAsACAAMAAuADAAMwAsACAANQAxAC4ANQAzADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVQBuAHAAcgBvAGMAZQBzAHMAZQBkACAAbgBhAHQAdQByAGEAbAAgAGcAYQBzAFwAIgAsACAAMAAuADAAMwA5ADMALAAgAFwAIgBtADMAXAAiACwAIAA1ADEALgA0ACwAIAAwAC4AMQAsACAAMAAuADAAMwAsACAANQAxAC4ANQAzADsAXABuACAAIAAgACAAIAAgACAAIABcACIARQB0AGgAYQBuAGUAXAAiACwAIAAwAC4AMAA2ADIAOQAsACAAXAAiAG0AMwBcACIALAAgADUANgAuADUALAAgADAALgAwADMALAAgADAALgAwADMALAAgADUANgAuADUANgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBrAGUAIABvAHYAZQBuACAAZwBhAHMAXAAiACwAIAAwAC4AMAAxADgAMQAsACAAXAAiAG0AMwBcACIALAAgADMANwAuADAALAAgADAALgAwADMALAAgADAALgAwADUALAAgADMANwAuADAAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEIAbABhAHMAdAAgAGYAdQByAG4AYQBjAGUAIABnAGEAcwBcACIALAAgADAALgAwADAANAAwACwAIABcACIAbQAzAFwAIgAsACAAMgAzADQALgAwACwAIAAwAC4AMAAzACwAIAAwAC4AMAAyACwAIAAyADMANAAuADAANQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFQAbwB3AG4AIABnAGEAcwBcACIALAAgADAALgAwADMAOQAwACwAIABcACIAbQAzAFwAIgAsACAANgAwAC4AMgAsACAAMAAuADAANAAsACAAMAAuADAAMwAsACAANgAwAC4AMgA3ADsAXABuACAAIAAgACAAIAAgACAAIABcACIATABpAHEAdQBlAGYAaQBlAGQAIABuAGEAdAB1AHIAYQBsACAAZwBhAHMAXAAiACwAIAAyADUALgAzACwAIABcACIAawBMAFwAIgAsACAANQAxAC4ANAAsACAAMAAuADEALAAgADAALgAwADMALAAgADUAMQAuADUAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEcAYQBzAGUAbwB1AHMAIABmAG8AcwBzAGkAbAAgAGYAdQBlAGwAcwAgAG8AdABoAGUAcgAgAHQAaABhAG4AIAB0AGgAbwBzAGUAIABtAGUAbgB0AGkAbwBuAGUAZAAgAGkAbgAgAHQAaABlACAAaQB0AGUAbQBzACAAYQBiAG8AdgBlAFwAIgAsACAAMAAuADAAMwA5ADAALAAgAFwAIgBtADMAXAAiACwAIAA1ADEALgA0ACwAIAAwAC4AMQAsACAAMAAuADAAMwAsACAANQAxAC4ANQAzADsAXABuACAAIAAgACAAIAAgACAAIABcACIATABhAG4AZABmAGkAbABsACAAYgBpAG8AZwBhAHMAIAB0AGgAYQB0ACAAaQBzACAAYwBhAHAAdAB1AHIAZQBkACAAZgBvAHIAIABjAG8AbQBiAHUAcwB0AGkAbwBuACAAKABtAGUAdABoAGEAbgBlACAAbwBuAGwAeQApAFwAIgAsACAAMAAuADAAMwA3ADcALAAgAFwAIgBtADMAXAAiACwAIAAwAC4AMAAsACAANgAuADQALAAgADAALgAwADMALAAgADYALgA0ADMAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAGwAdQBkAGcAZQAgAGIAaQBvAGcAYQBzACAAdABoAGEAdAAgAGkAcwAgAGMAYQBwAHQAdQByAGUAZAAgAGYAbwByACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgACgAbQBlAHQAaABhAG4AZQAgAG8AbgBsAHkAKQBcACIALAAgADAALgAwADMANwA3ACwAIABcACIAbQAzAFwAIgAsACAAMAAuADAALAAgADYALgA0ACwAIAAwAC4AMAAzACwAIAA2AC4ANAAzADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQQAgAGIAaQBvAGcAYQBzACAAdABoAGEAdAAgAGkAcwAgAGMAYQBwAHQAdQByAGUAZAAgAGYAbwByACAAYwBvAG0AYgB1AHMAdABpAG8AbgAsACAAbwB0AGgAZQByACAAdABoAGEAbgAgAHQAaABvAHMAZQAgAG0AZQBuAHQAaQBvAG4AZQBkACAAaQBuACAAdABoAGUAIABpAHQAZQBtAHMAIABhAGIAbwB2AGUAXAAiACwAIAAwAC4AMAAzADcAMAAsACAAXAAiAG0AMwBcACIALAAgADAALgAwACwAIAA2AC4ANAAsACAAMAAuADAAMwAsACAANgAuADQAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEIAaQBvAG0AZQB0AGgAYQBuAGUAXAAiACwAIAAwAC4AMAAzADkAMwAsACAAXAAiAG0AMwBcACIALAAgADAALgAwACwAIAAwAC4AMQAsACAAMAAuADAAMwAsACAAMAAuADEAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAeQBkAHIAbwBnAGUAbgBcACIALAAgADAALgAwADEAMgAyACwAIABcACIAbQAzAFwAIgAsACAAMAAuADAALAAgADAALgAwACwAIAAwAC4ANQAsACAAMAAuADUAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBOAGEAdAB1AHIAYQBsACAAZwBhAHMAIABkAGkAcwB0AHIAaQBiAHUAdABlAGQAIABpAG4AIABhACAAcABpAHAAZQBsAGkAbgBlACAALQAgAEcAaQBnAGEAagBvAHUAbABlAHMAXAAiACwAIAAxACwAIABcACIARwBKAFwAIgAsACAANQAxAC4ANAAsACAAMAAuADEALAAgADAALgAwADMALAAgADUAMQAuADUAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFQAbwB3AG4AIABnAGEAcwAgAC0AIABHAGkAZwBhAGoAbwB1AGwAZQBzAFwAIgAsACAAMQAsACAAXAAiAEcASgBcACIALAAgADYAMAAuADIALAAgADAALgAwADQALAAgADAALgAwADMALAAgADYAMAAuADIANwBcAG4AIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgApACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAFwAdQAwADAAMgA3AE4AYQB0AHUAcgBhAGwAIABnAGEAcwAgAGQAaQBzAHQAcgBpAGIAdQB0AGUAZAAgAGkAbgAgAGEAIABwAGkAcABlAGwAaQBuAGUAIAAtACAARwBpAGcAYQBqAG8AdQBsAGUAcwBcAHUAMAAwADIANwAgAGEAbgBkACAAXAB1ADAAMAAyADcAVABvAHcAbgAgAGcAYQBzACAALQAgAEcAaQBnAGEAagBvAHUAbABlAHMAXAB1ADAAMAAyADcAIAB3AGUAcgBlACAAYQBkAGQAZQBkACwAIABlAGEAYwBoACAAdwBpAHQAaAAgAGEAbgAgAGUAbgBlAHIAZwB5ACAAYwBvAG4AdABlAG4AdAAgAGYAYQBjAHQAbwByACAAbwBmACAAMQAgAEcASgAgAHAAZQByACAAdQBuAGkAdAAgAG8AZgAgAGYAdQBlAGwALgAgAFQAaABpAHMAIABpAHMAIABmAG8AcgAgAHUAcwBlAHIAcwAgAHcAaABvACAAaABhAHYAZQAgAGYAdQBlAGwAIABjAG8AbgBzAHUAbQBwAHQAaQBvAG4AIABkAGEAdABhACAAaQBuACAARwBKACAAcgBhAHQAaABlAHIAIAB0AGgAYQBuACAAbQAzAC4AXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ARgB1AGUAbAAgAHMAYwBvAHAAZQAgADMAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAALQAgAFMAdABhAHQAaQBvAG4AYQByAHkAIABnAGEAcwBlAG8AdQBzACAAZgB1AGUAbABzAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8AVABpAHQAbABlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIARgB1AGUAbAAgAHMAYwBvAHAAZQAgADMAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAALQAgAFMAdABhAHQAaQBvAG4AYQByAHkAIABnAGEAcwBlAG8AdQBzACAAZgB1AGUAbABzAFwAIgApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBJAG4AZABpAHIAZQBjAHQAIAAoAFMAYwBvAHAAZQAgADMAKQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAHQAaABlACAAYwBvAG4AcwB1AG0AcAB0AGkAbwBuACAAbwBmACAAbgBhAHQAdQByAGEAbAAgAGcAYQBzAC4AXAAiACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAE4AYQB0AGkAbwBuAGEAbAAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABBAGMAYwBvAHUAbgB0AHMAIABGAGEAYwB0AG8AcgBzACAAMgAwADIANQAgAC0AIABUAGEAYgBsAGUAIAA2AFwAIgApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALABcAG4AIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIABcACIAUwB0AGEAdABlACAAbwByACAAdABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAUwBjAG8AcABlACAAMwAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByAHMAIABmAG8AcgAgAE4AYQB0AHUAcgBhAGwAIABHAGEAcwAgACgAawBnACAAQwBPADIAIAAtACAAZQAgAC8AIABHAEoAKQAgAE0AZQB0AHIAbwBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAzACAARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAcwAgAGYAbwByACAATgBhAHQAdQByAGEAbAAgAEcAYQBzACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAATgBvAG4AIAAtACAATQBlAHQAcgBvAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE4AZQB3ACAAUwBvAHUAdABoACAAVwBhAGwAZQBzAFwAIgAsACAAMQAzAC4AMQAsACAAMQA0AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEEAQwBUAFwAIgAsACAAMQAzAC4AMQAsACAAMQA0AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgADQALgAwACwAIAA0AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIAA4AC4AOAAsACAANwAuADkAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAG8AdQB0AGgAIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgADEAMAAuADcALAAgADEAMAAuADYAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIAA0AC4AMQAsACAANAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBUAGEAcwBtAGEAbgBpAGEAXAAiACwAIAA0AC4AMAAsACAANAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AcgB0AGgAZQByAG4AIABUAGUAcgByAGkAdABvAHIAeQBcACIALAAgADQALgAxACwAIAA0AC4AMABcAG4AIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgApACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAE4AUwBXACAAYQBuAGQAIABBAEMAVAAgAHMAcABsAGkAdAAgAGkAbgB0AG8AIABzAGUAcABhAHIAYQB0AGUAIAByAG8AdwBzAC4AIABcAHUAMAAwADIANwBDAFwAdQAwADAAMgA3ACAAVgBhAGwAdQBlAHMAIABmAG8AcgAgAFQAYQBzAG0AYQBuAGkAYQAgAGEAbgBkACAATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAIAByAGUAcABsAGEAYwBlAGQAIAB3AGkAdABoACAAdABoAG8AcwBlACAAZgBvAHIAIABWAGkAYwB0AG8AcgBpAGEAIABhAG4AZAAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAHIAZQBzAHAAZQBjAHQAaQB2AGUAbAB5AC4AIAAoAFMAZQBlACAAYQBwAHAAZQBuAGQAaQBjAGUAcwApAFwAIgApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBBAHAAcABlAG4AZABpAGMAZQBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMgAsACAAMgAsAFwAbgAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAtAFwAIgAsACAAXAAiAEEAcwAgAFMAYwBvAHAAZQAgADMAIABmAGEAYwB0AG8AcgBzACAAYQByAGUAIABjAGEAbABjAHUAbABhAHQAZQBkACAAYQB0ACAAdABoAGUAIABwAG8AaQBuAHQAIAB3AGgAZQByAGUAIABuAGEAdAB1AHIAYQBsACAAZwBhAHMAIABpAHMAIABkAGUAbABpAHYAZQByAGUAZAAgAHQAbwAgAGUAbgBkACAAdQBzAGUAcgBzACwAIABpAHQAIABpAHMAIABuAGUAYwBlAHMAcwBhAHIAeQAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAYwBvAG4AcwB1AG0AcAB0AGkAbwBuACAAYQB0ACAAZQBhAGMAaAAgAG8AZgAgAHQAaABlACAAbABvAGEAZAAgAGMAZQBuAHQAcgBlAHMALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBHAGEAcwAgAHIAZQBhAGMAaABlAHMAIABlAG4AZAAgAHUAcwBlAHIAcwAgAGUAaQB0AGgAZQByACAAZgByAG8AbQAgAHQAaABlACAAbQBlAHQAcgBvACAAZABpAHMAdAByAGkAYgB1AHQAaQBvAG4AIABuAGUAdAB3AG8AcgBrAHMAIABvAHIAIABkAGkAcgBlAGMAdAAgAGYAcgBvAG0AIAB0AGgAZQAgAGgAaQBnAGgAIAAtACAAcAByAGUAcwBzAHUAcgBlACAAZABpAHMAdAByAGkAYgB1AHQAaQBvAG4AIABwAGkAcABlAGwAaQBuAGUAcwAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAEgAbwB1AHMAZQBoAG8AbABkAHMAIABhAG4AZAAgAGMAbwBtAG0AZQByAGMAaQBhAGwAIAB1AHMAZQByAHMAIAB0AGUAbgBkACAAdABvACAAYgBlACAAcwBlAHIAdgBlAGQAIABiAHkAIAB0AGgAZQAgAGYAbwByAG0AZQByACwAIABhAG4AZAAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQAgAGcAZQBuAGUAcgBhAHQAbwByAHMAIABhAG4AZAAgAGwAYQByAGcAZQAgAGkAbgBkAHUAcwB0AHIAaQBhAGwAIABwAGwAYQBuAHQAcwAgAGYAcgBvAG0AIAB0AGgAZQAgAGwAYQB0AHQAZQByAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIALQBcACIALAAgAFwAIgBNAGUAdAByAG8AIABpAHMAIABkAGUAZgBpAG4AZQBkACAAYQBzACAAbABvAGMAYQB0AGUAZAAgAG8AbgAgAG8AcgAgAGUAYQBzAHQAIABvAGYAIAB0AGgAZQAgAGQAaQB2AGkAZABpAG4AZwAgAHIAYQBuAGcAZQAgAGkAbgAgAE4AUwBXACwAIABpAG4AYwBsAHUAZABpAG4AZwAgAEMAYQBuAGIAZQByAHIAYQAgAGEAbgBkACAAUQB1AGUAYQBuAGIAZQB5AGEAbgAsACAATQBlAGwAYgBvAHUAcgBuAGUALAAgAEIAcgBpAHMAYgBhAG4AZQAsACAAQQBkAGUAbABhAGkAZABlACAAbwByACAAUABlAHIAdABoAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIATwB0AGgAZQByAHcAaQBzAGUALAAgAHQAaABlACAAbgBvAG4AIAAtACAAbQBlAHQAcgBvACAAZgBhAGMAdABvAHIAIABzAGgAbwB1AGwAZAAgAGIAZQAgAHUAcwBlAGQALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAtAFwAIgAsACAAXAAiAEYAYQBjAHQAbwByAHMAIABhAHIAZQAgAGMAYQBsAGMAdQBsAGEAdABlAGQAIABmAG8AcgAgAGEAbABsACAAbgBhAHQAdQByAGEAbAAgAGcAYQBzACAAZABpAHMAdAByAGkAYgB1AHQAZQBkACAAaQBuACAAYQAgAHAAaQBwAGUAbABpAG4AZQAgAHcAaABpAGMAaAAgAG0AYQB5ACAAaQBuAGMAbAB1AGQAZQAgAGMAbwBhAGwAIABzAGUAYQBtACAAbQBlAHQAaABhAG4AZQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAC0AXAAiACwAIABcACIAVABhAGIAbABlACAANgAgAGkAcwAgAG4AbwB0ACAAYQBwAHAAbABpAGMAYQBiAGwAZQAgAHQAbwAgAGUAdABoAGEAbgBlAC4AIABTAGUAZQAgAFQAYQBiAGwAZQAgADcAIABJAG4AZABpAHIAZQBjAHQAIAAoAFMAYwBvAHAAZQAgADMAKQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHQAaABlACAAYwBvAG4AcwB1AG0AcAB0AGkAbwBuACAAbwBmACAAZQB0AGgAYQBuAGUALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAtAFwAIgAsACAAXAAiAEMAIAA9ACAAQwBvAG4AZgBpAGQAZQBuAHQAaQBhAGwALgAgAFMAYwBvAHAAZQAgADMAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABUAGEAcwBtAGEAbgBpAGEAIABhAG4AZAAgAHQAaABlACAATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAIABhAHIAZQAgAG4AbwB0ACAAYQB2AGEAaQBsAGEAYgBsAGUAIABkAHUAZQAgAHQAbwAgAGMAbwBuAGYAaQBkAGUAbgB0AGkAYQBsAGkAdAB5ACAAYwBvAG4AcwB0AHIAYQBpAG4AdABzACAAdABoAGEAdAAgAGEAcgBpAHMAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBmAHIAbwBtACAAdABoAGUAIAB1AHMAZQAgAG8AZgAgAGEAIABsAGkAbQBpAHQAZQBkACAAbgB1AG0AYgBlAHIAIABvAGYAIABOAEcARQBSACAAZABhAHQAYQAgAGkAbgBwAHUAdABzAC4AIABJAHQAIABpAHMAIABzAHUAZwBnAGUAcwB0AGUAZAAgAHQAaABhAHQAIABmAG8AcgAgAFQAYQBzAG0AYQBuAGkAYQAgAHQAaABlACAAdQBzAGUAIABvAGYAIAB0AGgAZQAgAFYAaQBjAHQAbwByAGkAYQBuACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGkAcwAgAGEAcABwAHIAbwBwAHIAaQBhAHQAZQAsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAHcAaABpAGwAZQAgAGYAbwByACAATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAIAB0AGgAZQAgAHUAcwBlACAAbwBmACAAdABoAGUAIABXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABpAHMAIABhAHAAcAByAG8AcAByAGkAYQB0AGUALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAtAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADMAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZABvACAAbgBvAHQAIABpAG4AYwBsAHUAZABlACAAZgB1AGcAaQB0AGkAdgBlACAAZQBtAGkAcwBzAGkAbwBuACAAbABlAGEAawBhAGcAZQAgAGYAcgBvAG0AIABsAG8AdwAgAHAAcgBlAHMAcwB1AHIAZQAgAG4AYQB0AHUAcgBhAGwAIABnAGEAcwAgAGQAaQBzAHQAcgBpAGIAdQB0AGkAbwBuACAAcABpAHAAZQBsAGkAbgBlACAAbgBlAHQAdwBvAHIAawBzACAAdwBoAGkAbABlACAAdABoAG8AcwBlACAAZgByAG8AbQAgAGgAaQBnAGgAIABwAHIAZQBzAHMAdQByAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAZwBhAHMAIABuAGUAdAB3AG8AcgBrAHMAIABhAHIAZQAgAGMAbwBuAHMAaQBkAGUAcgBlAGQAIABuAGUAZwBsAGkAZwBpAGIAbABlAC4AXAAiAFwAbgAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACkAKQApADsAXABuAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBGAHUAZQBsACAAcwBjAG8AcABlACAAMQAgAGEAbgBkACAAMwAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIAAtACAAUwB0AGEAdABpAG8AbgBhAHIAeQAgAGwAaQBxAHUAaQBkACAAZgB1AGUAbABzAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBMAGkAcQB1AGkAZABfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEYAdQBlAGwAIABzAGMAbwBwAGUAIAAxACAAYQBuAGQAIAAzACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAC0AIABTAHQAYQB0AGkAbwBuAGEAcgB5ACAAbABpAHEAdQBpAGQAIABmAHUAZQBsAHMAXAAiACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkATABpAHEAdQBpAGQAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBEAGkAcgBlAGMAdAAgACgAUwBjAG8AcABlACAAMQApACAAYQBuAGQAIABpAG4AZABpAHIAZQBjAHQAIAAoAHMAYwBvAHAAZQAgADMAKQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAHQAaABlACAAYwBvAG4AcwB1AG0AcAB0AGkAbwBuACAAbwBmACAAbABpAHEAdQBpAGQAIABmAHUAZQBsAHMALAAgAGkAbgBjAGwAdQBkAGkAbgBnACAAYwBlAHIAdABhAGkAbgAgAHAAZQB0AHIAbwBsAGUAdQBtACAAYgBhAHMAZQBkACAAcAByAG8AZAB1AGMAdABzACAAZgBvAHIAIABzAHQAYQB0AGkAbwBuAGEAcgB5ACAAZQBuAGUAcgBnAHkAIABwAHUAcgBwAG8AcwBlAHMALgBcACIAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBMAGkAcQB1AGkAZABfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAE4AYQB0AGkAbwBuAGEAbAAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABBAGMAYwBvAHUAbgB0AHMAIABGAGEAYwB0AG8AcgBzACAAMgAwADIANQAgAC0AIABUAGEAYgBsAGUAIAA4AFwAIgApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEwAaQBxAHUAaQBkAF8ARABhAHQAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyADUALAAgADgALABcAG4AIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIABcACIARgB1AGUAbAAgAGMAbwBtAGIAdQBzAHQAZQBkAFwAIgAsACAAXAAiAEUAbgBlAHIAZwB5ACAAQwBvAG4AdABlAG4AdAAgAEYAYQBjAHQAbwByACAAKABHAEoAIABwAGUAcgAgAHUAbgBpAHQAIABvAGYAIABmAHUAZQBsACkAXAAiACwAIABcACIARgB1AGUAbAAgAHUAbgBpAHQAXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAAQwBPADIAXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAAQwBIADQAXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAATgAyAE8AXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAAQwBvAG0AYgBpAG4AZQBkACAAZwBhAHMAZQBzAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADMAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgAgACgAawBnACAAQwBPADIAIAAtACAAZQAgAC8AIABHAEoAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAdAByAG8AbABlAHUAbQAgAGIAYQBzAGUAZAAgAG8AaQBsAHMAIAAoAG8AdABoAGUAcgAgAHQAaABhAG4AIABwAGUAdAByAG8AbABlAHUAbQAgAGIAYQBzAGUAZAAgAG8AaQBsACAAdQBzAGUAZAAgAGEAcwAgAGYAdQBlAGwAKQAsACAAZQAuAGcALgAgAGwAdQBiAHIAaQBjAGEAbgB0AHMAXAAiACwAIAAzADgALgA4ACwAIABcACIAawBsAFwAIgAsACAAMQAzAC4AOQAsACAAMAAuADAALAAgADAALgAwACwAIAAxADMALgA5ACwAIAAxADgALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUABlAHQAcgBvAGwAZQB1AG0AIABiAGEAcwBlAGQAIABnAHIAZQBhAHMAZQBzAFwAIgAsACAAMwA4AC4AOAAsACAAXAAiAGsAbABcACIALAAgADMALgA1ACwAIAAwAC4AMAAsACAAMAAuADAALAAgADMALgA1ACwAIAAxADgALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwByAHUAZABlACAAbwBpAGwAIABpAG4AYwBsAHUAZABpAG4AZwAgAGMAcgB1AGQAZQAgAG8AaQBsACAAYwBvAG4AZABlAG4AcwBhAHQAZQBzAFwAIgAsACAANAA1AC4AMwAsACAAXAAiAHQAXAAiACwAIAA2ADkALgA2ACwAIAAwAC4AMAA4ACwAIAAwAC4AMgAsACAANgA5AC4AOAA4ACwAIABcACIATgBFAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAG4AYQB0AHUAcgBhAGwAIABnAGEAcwAgAGwAaQBxAHUAaQBkAHMAXAAiACwAIAA0ADYALgA1ACwAIABcACIAdABcACIALAAgADYAMQAuADAALAAgADAALgAwADgALAAgADAALgAyACwAIAA2ADEALgAyADgALAAgAFwAIgBOAEUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQQB1AHQAbwBtAG8AdABpAHYAZQAgAGcAYQBzAG8AbABpAG4AZQAgAC8AIABwAGUAdAByAG8AbAAgACgAbwB0AGgAZQByACAAdABoAGEAbgAgAGYAbwByACAAdQBzAGUAIABhAHMAIABmAHUAZQBsACAAaQBuACAAYQBuACAAYQBpAHIAYwByAGEAZgB0ACkAXAAiACwAIAAzADQALgAyACwAIABcACIAawBMAFwAIgAsACAANgA3AC4ANAAsACAAMAAuADIALAAgADAALgAyACwAIAA2ADcALgA4ADAALAAgADEANwAuADIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAHYAaQBhAHQAaQBvAG4AIABnAGEAcwBvAGwAaQBuAGUAXAAiACwAIAAzADMALgAxACwAIABcACIAawBMAFwAIgAsACAANgA3ACwAIAAwAC4AMgAsACAAMAAuADIALAAgADYANwAuADQAMAAsACAAMQA4AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEsAZQByAG8AcwBlAG4AZQAgACgAbwB0AGgAZQByACAAdABoAGEAbgAgAGYAbwByACAAdQBzAGUAIABhAHMAIABmAHUAZQBsACAAaQBuACAAYQBuACAAYQBpAHIAYwByAGEAZgB0ACkAXAAiACwAIAAzADcALgA1ACwAIABcACIAawBMAFwAIgAsACAANgA4AC4AOQAsACAAMAAuADAAMQAsACAAMAAuADIALAAgADYAOQAuADEAMQAsACAAMQA4AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEEAdgBpAGEAdABpAG8AbgAgAHQAdQByAGIAaQBuAGUAIABmAHUAZQBsACAALwAgAGsAZQByAG8AcwBlAG4AZQBcACIALAAgADMANgAuADgALAAgAFwAIgBrAEwAXAAiACwAIAA2ADkALgA2ACwAIAAwAC4AMAAyACwAIAAwAC4AMgAsACAANgA5AC4AOAAyACwAIAAxADgALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABlAGEAdABpAG4AZwAgAG8AaQBsAFwAIgAsACAAMwA3AC4AMwAsACAAXAAiAGsATABcACIALAAgADYAOQAuADUALAAgADAALgAwADMALAAgADAALgAyACwAIAA2ADkALgA3ADMALAAgADEAOAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBEAGkAZQBzAGUAbAAgAG8AaQBsAFwAIgAsACAAMwA4AC4ANgAsACAAXAAiAGsATABcACIALAAgADYAOQAuADkALAAgADAALgAxACwAIAAwAC4AMgAsACAANwAwAC4AMgAwACwAIAAxADcALgAzADsAXABuACAAIAAgACAAIAAgACAAIABcACIARgB1AGUAbAAgAG8AaQBsAFwAIgAsACAAMwA5AC4ANwAsACAAXAAiAGsATABcACIALAAgADcAMwAuADYALAAgADAALgAwADQALAAgADAALgAyACwAIAA3ADMALgA4ADQALAAgADEAOAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBMAGkAcQB1AGUAZgBpAGUAZAAgAGEAcgBvAG0AYQB0AGkAYwAgAGgAeQBkAHIAbwBjAGEAcgBiAG8AbgBzAFwAIgAsACAAMwA0AC4ANAAsACAAXAAiAGsATABcACIALAAgADYAOQAuADcALAAgADAALgAwADMALAAgADAALgAyACwAIAA2ADkALgA5ADMALAAgADEAOAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAG8AbAB2AGUAbgB0AHMAOgAgAG0AaQBuAGUAcgBhAGwAIAB0AHUAcgBwAGUAbgB0AGkAbgBlACAAbwByACAAdwBoAGkAdABlACAAcwBwAGkAcgBpAHQAcwBcACIALAAgADMANAAuADQALAAgAFwAIgBrAEwAXAAiACwAIAA2ADkALgA3ACwAIAAwAC4AMAAzACwAIAAwAC4AMgAsACAANgA5AC4AOQAzACwAIAAxADgALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIATABpAHEAdQBlAGYAaQBlAGQAIABwAGUAdAByAG8AbABlAHUAbQAgAGcAYQBzACAAKABMAFAARwApAFwAIgAsACAAMgA1AC4ANwAsACAAXAAiAGsATABcACIALAAgADYAMAAuADIALAAgADAALgAyACwAIAAwAC4AMgAsACAANgAwAC4ANgAwACwAIAAyADAALgAyADsAXABuACAAIAAgACAAIAAgACAAIABcACIATgBhAHAAaAB0AGgAYQBcACIALAAgADMAMQAuADQALAAgAFwAIgBrAEwAXAAiACwAIAA2ADkALgA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxACwAIAA2ADkALgA4ADIALAAgADEAOAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAdAByAG8AbABlAHUAbQAgAGMAbwBrAGUAXAAiACwAIAAzADQALgAyACwAIABcACIAdABcACIALAAgADkAMgAuADYALAAgADAALgAwADgALAAgADAALgAyACwAIAA5ADIALgA4ADgALAAgADEAOAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAGUAZgBpAG4AZQByAHkAIABnAGEAcwAgAGEAbgBkACAAbABpAHEAdQBpAGQAcwBcACIALAAgADQAMgAuADkALAAgAFwAIgB0AFwAIgAsACAANQA0AC4ANwAsACAAMAAuADAAMwAsACAAMAAuADAAMwAsACAANQA0AC4ANwA2ACwAIAAxADgALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgBlAGYAaQBuAGUAcgB5ACAAYwBvAGsAZQBcACIALAAgADMANAAuADIALAAgAFwAIgB0AFwAIgAsACAAOQAyAC4ANgAsACAAMAAuADAAOAAsACAAMAAuADIALAAgADkAMgAuADgAOAAsACAAMQA4AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFAAZQB0AHIAbwBsAGUAdQBtACAAYgBhAHMAZQBkACAAcAByAG8AZAB1AGMAdABzACAAbwB0AGgAZQByACAAdABoAGEAbgAgAG0AZQBuAHQAaQBvAG4AZQBkACAAaQBuACAAdABoAGUAIABpAHQAZQBtAHMAIABhAGIAbwB2AGUAXAAiACwAIAAzADQALgA0ACwAIABcACIAawBMAFwAIgAsACAANgA5AC4AOAAsACAAMAAuADAAMgAsACAAMAAuADEALAAgADYAOQAuADkAMgAsACAAMQA4AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEIAaQBvAGQAaQBlAHMAZQBsAFwAIgAsACAAMwA0AC4ANgAsACAAXAAiAGsATABcACIALAAgADAALgAwACwAIAAwAC4AMAA4ACwAIAAwAC4AMgAsACAAMAAuADIAOAAsACAAXAAiAE4ARQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBFAHQAaABhAG4AbwBsACAAZgBvAHIAIAB1AHMAZQAgAGEAcwAgAGEAIABmAHUAZQBsACAAaQBuACAAYQBuACAAaQBuAHQAZQByAG4AYQBsACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgAGUAbgBnAGkAbgBlAFwAIgAsACAAMgAzAC4ANAAsACAAXAAiAGsATABcACIALAAgADAALgAwACwAIAAwAC4AMAA4ACwAIAAwAC4AMgAsACAAMAAuADIAOAAsACAAXAAiAE4ARQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBCAGkAbwBmAHUAZQBsAHMAIABvAHQAaABlAHIAIAB0AGgAYQBuACAAdABoAG8AcwBlACAAbQBlAG4AdABpAG8AbgBlAGQAIABpAG4AIAB0AGgAZQAgAGkAdABlAG0AcwAgAGEAYgBvAHYAZQAgAGEAbgBkACAAYgBlAGwAbwB3AFwAIgAsACAAMgAzAC4ANAAsACAAXAAiAGsATABcACIALAAgADAALgAwACwAIAAwAC4AMAA4ACwAIAAwAC4AMgAsACAAMAAuADIAOAAsACAAXAAiAE4ARQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAGUAbgBlAHcAYQBiAGwAZQAgAGEAdgBpAGEAdABpAG8AbgAgAGsAZQByAG8AcwBlAG4AZQBcACIALAAgADMANgAuADgALAAgAFwAIgBrAEwAXAAiACwAIAAwAC4AMAAsACAAMAAuADAAMgAsACAAMAAuADIALAAgADAALgAyADIALAAgAFwAIgBOAEUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgBlAG4AZQB3AGEAYgBsAGUAIABkAGkAZQBzAGUAbABcACIALAAgADMAOAAuADYALAAgAFwAIgBrAEwAXAAiACwAIAAwAC4AMAAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMwAwACwAIABcACIATgBFAFwAIgBcAG4AIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgApACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkATABpAHEAdQBpAGQAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAXAB1ADAAMAAyADcATgBFAFwAdQAwADAAMgA3ACAAdgBhAGwAdQBlAHMAIAByAGUAdAB1AHIAbgBlAGQAIABhAHMAIAB6AGUAcgBvACAAZgBvAHIAIABjAGEAbABjAHUAbABhAHQAaQBvAG4AcwAuAFwAIgApADsAXABuAFwAbgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAEYAdQBlAGwAIABzAGMAbwBwAGUAIAAxACAAYQBuAGQAIAAzACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAC0AIABUAHIAYQBuAHMAcABvAHIAdABcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AF8AVABpAHQAbABlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIARgB1AGUAbAAgAHMAYwBvAHAAZQAgADEAIABhAG4AZAAgADMAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAALQAgAFQAcgBhAG4AcwBwAG8AcgB0AFwAIgApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBUAHIAYQBuAHMAcABvAHIAdABfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEQAaQByAGUAYwB0ACAAKABzAGMAbwBwAGUAIAAxACkAIABhAG4AZAAgAGkAbgBkAGkAcgBlAGMAdAAgACgAcwBjAG8AcABlACAAMwApACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAdABoAGUAIABjAG8AbgBzAHUAbQBwAHQAaQBvAG4AIABvAGYAIAB0AHIAYQBuAHMAcABvAHIAdAAgAGYAdQBlAGwAcwAgAGkAbgAgAGQAaQBmAGYAZQByAGUAbgB0ACAAdAByAGEAbgBzAHAAbwByAHQAIABlAHEAdQBpAHAAbQBlAG4AdABcACIAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAVAByAGEAbgBzAHAAbwByAHQAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABOAGEAdABpAG8AbgBhAGwAIABHAHIAZQBlAG4AaABvAHUAcwBlACAAQQBjAGMAbwB1AG4AdABzACAARgBhAGMAdABvAHIAcwAgADIAMAAyADUAIAAtACAAVABhAGIAbABlACAAOQBcACIAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAVAByAGEAbgBzAHAAbwByAHQAXwBEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIANgAsACAAMQAwACwAXABuACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBhAG4AcwBwAG8AcgB0ACAAdAB5AHAAZQBcACIALAAgAFwAIgBGAHUAZQBsACAAYwBvAG0AYgB1AHMAdABlAGQAXAAiACwAIABcACIARQBuAGUAcgBnAHkAIABDAG8AbgB0AGUAbgB0ACAARgBhAGMAdABvAHIAKABHAEoAIABwAGUAcgAgAHUAbgBpAHQAIABvAGYAIABmAHUAZQBsACkAXAAiACwAIABcACIARgB1AGUAbAAgAHUAbgBpAHQAXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAAQwBPADIAXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAAQwBIADQAXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAATgAyAE8AXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAAQwBvAG0AYgBpAG4AZQBkACAAZwBhAHMAZQBzAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADMAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgAgACgAawBnACAAQwBPADIAIAAtACAAZQAgAC8AIABHAEoAKQBcACIALAAgAFwAIgBTAG8AdQByAGMAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAGEAcgBzACAAYQBuAGQAIABsAGkAZwBoAHQAIABjAG8AbQBtAGUAcgBjAGkAYQBsACAAdgBlAGgAaQBjAGwAZQBzAFwAIgAsACAAXAAiAEcAYQBzAG8AbABpAG4AZQBcACIALAAgADMANAAuADIALAAgAFwAIgBrAGwAXAAiACwAIAA2ADcALgA0ACwAIAAwAC4AMAAyACwAIAAwAC4AMgAsACAANgA3AC4ANgAyACwAIAAxADcALgAyACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBhAHIAcwAgAGEAbgBkACAAbABpAGcAaAB0ACAAYwBvAG0AbQBlAHIAYwBpAGEAbAAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBEAGkAZQBzAGUAbAAgAG8AaQBsAFwAIgAsACAAMwA4AC4ANgAsACAAXAAiAGsAbABcACIALAAgADYAOQAuADkALAAgADAALgAwADEALAAgADAALgA1ACwAIAA3ADAALgA0ADEALAAgADEANwAuADMALAAgAFwAIgBOAEcAQQBGACAAMgAwADIANQA6ACAAVABhAGIAbABlACAAOQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAGEAcgBzACAAYQBuAGQAIABsAGkAZwBoAHQAIABjAG8AbQBtAGUAcgBjAGkAYQBsACAAdgBlAGgAaQBjAGwAZQBzAFwAIgAsACAAXAAiAEwAaQBxAHUAZQBmAGkAZQBkACAAcABlAHQAcgBvAGwAZQB1AG0AIABnAGEAcwAgACgATABQAEcAKQBcACIALAAgADIANgAuADIALAAgAFwAIgBrAGwAXAAiACwAIAA2ADAALgAyACwAIAAwAC4ANQAsACAAMAAuADMALAAgADYAMQAuADAAMAAsACAAMgAwAC4AMgAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAYQByAHMAIABhAG4AZAAgAGwAaQBnAGgAdAAgAGMAbwBtAG0AZQByAGMAaQBhAGwAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIARgB1AGUAbAAgAG8AaQBsAFwAIgAsACAAMwA5AC4ANwAsACAAXAAiAGsAbABcACIALAAgADcAMwAuADYALAAgADAALgAwADgALAAgADAALgA1ACwAIAA3ADQALgAxADgALAAgADEAOAAuADAALAAgAFwAIgBOAEcAQQBGACAAMgAwADIANQA6ACAAVABhAGIAbABlACAAOQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAGEAcgBzACAAYQBuAGQAIABsAGkAZwBoAHQAIABjAG8AbQBtAGUAcgBjAGkAYQBsACAAdgBlAGgAaQBjAGwAZQBzAFwAIgAsACAAXAAiAEUAdABoAGEAbgBvAGwAXAAiACwAIAAyADMALgA0ACwAIABcACIAawBsAFwAIgAsACAAMAAuADAALAAgADAALgAyACwAIAAwAC4AMgAsACAAMAAuADQALAAgAFwAIgBOAEUAXAAiACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBhAHIAcwAgAGEAbgBkACAAbABpAGcAaAB0ACAAYwBvAG0AbQBlAHIAYwBpAGEAbAAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBCAGkAbwBkAGkAZQBzAGUAbABcACIALAAgADMANAAuADYALAAgAFwAIgBrAGwAXAAiACwAIAAwAC4AMAAsACAAMAAuADgALAAgADEALgA3ACwAIAAyAC4ANQAsACAAXAAiAE4ARQBcACIALAAgAFwAIgBOAEcAQQBGACAAMgAwADIANQA6ACAAVABhAGIAbABlACAAOQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAGEAcgBzACAAYQBuAGQAIABsAGkAZwBoAHQAIABjAG8AbQBtAGUAcgBjAGkAYQBsACAAdgBlAGgAaQBjAGwAZQBzAFwAIgAsACAAXAAiAFIAZQBuAGUAdwBhAGIAbABlACAAZABpAGUAcwBlAGwAXAAiACwAIAAzADgALgA2ACwAIABcACIAawBsAFwAIgAsACAAMAAuADAALAAgADAALgAwADEALAAgADAALgA1ACwAIAAwAC4ANQAxACwAIABcACIATgBFAFwAIgAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAYQByAHMAIABhAG4AZAAgAGwAaQBnAGgAdAAgAGMAbwBtAG0AZQByAGMAaQBhAGwAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIATwB0AGgAZQByACAAYgBpAG8AZgB1AGUAbABzAFwAIgAsACAAMgAzAC4ANAAsACAAXAAiAGsAbABcACIALAAgADAALgAwACwAIAAwAC4AOAAsACAAMQAuADcALAAgADIALgA1ACwAIABcACIATgBFAFwAIgAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEwAaQBnAGgAdAAgAGQAdQB0AHkAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIAQwBvAG0AcAByAGUAcwBzAGUAZAAgAG4AYQB0AHUAcgBhAGwAIABnAGEAcwBcACIALAAgADAALgAwADMAOQAzACwAIABcACIAbQAzAFwAIgAsACAANQAxAC4ANAAsACAANwAuADMALAAgADAALgAzACwAIAA1ADkALgAwACwAIAAxADgALgAwACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIATABpAGcAaAB0ACAAZAB1AHQAeQAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBMAGkAcQB1AGUAZgBpAGUAZAAgAG4AYQB0AHUAcgBhAGwAIABnAGEAcwBcACIALAAgADIANQAuADMALAAgAFwAIgBrAGwAXAAiACwAIAA1ADEALgA0ACwAIAA3AC4AMwAsACAAMAAuADMALAAgADUAOQAuADAALAAgADEAOAAuADAALAAgAFwAIgBOAEcAQQBGACAAMgAwADIANQA6ACAAVABhAGIAbABlACAAOQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAGUAYQB2AHkAIABkAHUAdAB5ACAAdgBlAGgAaQBjAGwAZQBzAFwAIgAsACAAXAAiAEMAbwBtAHAAcgBlAHMAcwBlAGQAIABuAGEAdAB1AHIAYQBsACAAZwBhAHMAXAAiACwAIAAwAC4AMAAzADkAMwAsACAAXAAiAG0AMwBcACIALAAgADUAMQAuADQALAAgADIALgA4ACwAIAAwAC4AMwAsACAANQA0AC4ANQAsACAAMQA4AC4AMAAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAZQBhAHYAeQAgAGQAdQB0AHkAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIATABpAHEAdQBlAGYAaQBlAGQAIABuAGEAdAB1AHIAYQBsACAAZwBhAHMAXAAiACwAIAAyADUALgAzACwAIABcACIAawBsAFwAIgAsACAANQAxAC4ANAAsACAAMgAuADgALAAgADAALgAzACwAIAA1ADQALgA1ACwAIAAxADgALgAwACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABlAGEAdgB5ACAAZAB1AHQAeQAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBEAGkAZQBzAGUAbAAgAG8AaQBsACAALQAgAEUAdQByAG8AIABpAHYAIABvAHIAIABoAGkAZwBoAGUAcgBcACIALAAgADMAOAAuADYALAAgAFwAIgBrAGwAXAAiACwAIAA2ADkALgA5ACwAIAAwAC4AMAA3ACwAIAAwAC4ANAAsACAANwAwAC4AMwA3ACwAIAAxADcALgAzACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABlAGEAdgB5ACAAZAB1AHQAeQAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBEAGkAZQBzAGUAbAAgAG8AaQBsACAALQAgAEUAdQByAG8AIABpAGkAaQBcACIALAAgADMAOAAuADYALAAgAFwAIgBrAGwAXAAiACwAIAA2ADkALgA5ACwAIAAwAC4AMQAsACAAMAAuADQALAAgADcAMAAuADQALAAgADEANwAuADMALAAgAFwAIgBOAEcAQQBGACAAMgAwADIANQA6ACAAVABhAGIAbABlACAAOQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAGUAYQB2AHkAIABkAHUAdAB5ACAAdgBlAGgAaQBjAGwAZQBzAFwAIgAsACAAXAAiAEQAaQBlAHMAZQBsACAAbwBpAGwAIAAtACAARQB1AHIAbwAgAGkAXAAiACwAIAAzADgALgA2ACwAIABcACIAawBsAFwAIgAsACAANgA5AC4AOQAsACAAMAAuADIALAAgADAALgA0ACwAIAA3ADAALgA1ACwAIAAxADcALgAzACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABlAGEAdgB5ACAAZAB1AHQAeQAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBSAGUAbgBlAHcAYQBiAGwAZQAgAGQAaQBlAHMAZQBsACAAEyAgAEUAdQByAG8AIABpAHYAIABvAHIAIABoAGkAZwBoAGUAcgBcACIALAAgADMAOAAuADYALAAgAFwAIgBrAGwAXAAiACwAIAAwAC4AMAAsACAAMAAuADAANwAsACAAMAAuADQALAAgADAALgA0ADcALAAgAFwAIgBOAEUAXAAiACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABlAGEAdgB5ACAAZAB1AHQAeQAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBSAGUAbgBlAHcAYQBiAGwAZQAgAGQAaQBlAHMAZQBsACAAEyAgAEUAdQByAG8AIABpAGkAaQBcACIALAAgADMAOAAuADYALAAgAFwAIgBrAGwAXAAiACwAIAAwAC4AMAAsACAAMAAuADEALAAgADAALgA0ACwAIAAwAC4ANQAsACAAXAAiAE4ARQBcACIALAAgAFwAIgBOAEcAQQBGACAAMgAwADIANQA6ACAAVABhAGIAbABlACAAOQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAGUAYQB2AHkAIABkAHUAdAB5ACAAdgBlAGgAaQBjAGwAZQBzAFwAIgAsACAAXAAiAFIAZQBuAGUAdwBhAGIAbABlACAAZABpAGUAcwBlAGwAIAATICAARQB1AHIAbwAgAGkAXAAiACwAIAAzADgALgA2ACwAIABcACIAawBsAFwAIgAsACAAMAAuADAALAAgADAALgAyACwAIAAwAC4ANAAsACAAMAAuADYALAAgAFwAIgBOAEUAXAAiACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQQB2AGkAYQB0AGkAbwBuAFwAIgAsACAAXAAiAEcAYQBzAG8AbABpAG4AZQAgAGYAbwByACAAdQBzAGUAIABhAHMAIABmAHUAZQBsACAAaQBuACAAYQBuACAAYQBpAHIAYwByAGEAZgB0AFwAIgAsACAAMwAzAC4AMQAsACAAXAAiAGsAbABcACIALAAgADYANwAuADAALAAgADAALgAwADYALAAgADAALgA2ACwAIAA2ADcALgA2ADYALAAgADEAOAAuADAALAAgAFwAIgBOAEcAQQBGACAAMgAwADIANQA6ACAAVABhAGIAbABlACAAOQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAHYAaQBhAHQAaQBvAG4AXAAiACwAIABcACIASwBlAHIAbwBzAGUAbgBlACAAZgBvAHIAIAB1AHMAZQAgAGEAcwAgAGYAdQBlAGwAIABpAG4AIABhAG4AIABhAGkAcgBjAHIAYQBmAHQAXAAiACwAIAAzADYALgA4ACwAIABcACIAawBsAFwAIgAsACAANgA5AC4ANgAsACAAMAAuADAAMQAsACAAMAAuADYALAAgADcAMAAuADIAMQAsACAAMQA4AC4AMAAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEEAdgBpAGEAdABpAG8AbgBcACIALAAgAFwAIgBSAGUAbgBlAHcAYQBiAGwAZQAgAGEAdgBpAGEAdABpAG8AbgAgAGsAZQByAG8AcwBlAG4AZQBcACIALAAgADMANgAuADgALAAgAFwAIgBrAGwAXAAiACwAIAAwAC4AMAAsACAAMAAuADAAMQAsACAAMAAuADYALAAgADAALgA2ADEALAAgAFwAIgBOAEUAXAAiACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVgBlAHMAcwBlAGwAcwBcACIALAAgAFwAIgBHAGEAcwBvAGwAaQBuAGUAXAAiACwAIAAzADQALgAyACwAIABcACIAawBMAFwAIgAsACAANgA3AC4ANAAsACAAMQAwAC4AMQAsACAAMAAuADMALAAgAFwAIgBcACIALAAgADEANwAuADIALAAgAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4ANAAuADIALgAxAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFYAZQBzAHMAZQBsAHMAXAAiACwAIABcACIARABpAGUAcwBlAGwAIABvAGkAbABcACIALAAgADMAOAAuADYALAAgAFwAIgBrAEwAXAAiACwAIAA2ADkALgA5ACwAIAAwAC4AMgAsACAAMAAuADUALAAgAFwAIgBcACIALAAgADEANwAuADMALAAgAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4ANAAuADIALgAxAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFYAZQBzAHMAZQBsAHMAXAAiACwAIABcACIARgB1AGUAbAAgAE8AaQBsAFwAIgAsACAAMwA5AC4ANwAsACAAXAAiAGsATABcACIALAAgADcAMwAuADYALAAgADAALgAyACwAIAAwAC4ANQAsACAAXAAiAFwAIgAsACAAMQA4AC4AMAAsACAAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgA0AC4AMgAuADEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwBmAGYALQByAG8AYQBkACAAQQBnAHIAaQBjAHUAbAB0AHUAcgBlACAAYQBuAGQAIABmAG8AcgBlAHMAdAByAHkAIABlAHEAdQBpAHAAbQBlAG4AdABcACIALAAgAFwAIgBEAGkAZQBzAGUAbAAgAG8AaQBsAFwAIgAsACAAMwA4AC4ANgAsACAAXAAiAGsATABcACIALAAgADYAOQAuADkALAAgADAALgAzACwAIAAwAC4ANQAsACAAXAAiAFwAIgAsACAAMQA3AC4AMwAsACAAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgA0AC4AMgAuADEAXAAiAFwAbgAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACkAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAVAByAGEAbgBzAHAAbwByAHQAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAXAB1ADAAMAAyADcATgBFAFwAdQAwADAAMgA3ACAAdgBhAGwAdQBlAHMAIAByAGUAdAB1AHIAbgBlAGQAIABhAHMAIAB6AGUAcgBvACAAZgBvAHIAIABjAGEAbABjAHUAbABhAHQAaQBvAG4AcwAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBGAHUAZQBsACAAcwBjAG8AcABlACAAMQAgAGEAbgBkACAAMwAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIAAtACAATwBmAGYALQByAGEAZAAgAGUAcQB1AGkAcABtAGUAbgB0ACAAYQBuAGQAIAB2AGUAcwBzAGUAbABzAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAVAByAGEAbgBzAHAAbwByAHQATwBmAGYAUgBvAGEAZABfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEYAdQBlAGwAIABzAGMAbwBwAGUAIAAxACAAYQBuAGQAIAAzACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAC0AIABPAGYAZgAtAHIAbwBhAGQAIABlAHEAdQBpAHAAbQBlAG4AdAAgAGEAbgBkACAAdgBlAHMAcwBlAGwAcwBcACIAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAVAByAGEAbgBzAHAAbwByAHQATwBmAGYAUgBvAGEAZABfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEQAaQByAGUAYwB0ACAAKABzAGMAbwBwAGUAIAAxACkAIABhAG4AZAAgAGkAbgBkAGkAcgBlAGMAdAAgACgAcwBjAG8AcABlACAAMwApACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAdABoAGUAIABjAG8AbgBzAHUAbQBwAHQAaQBvAG4AIABvAGYAIABmAHUAZQBsAHMAIABpAG4AIABvAGYAZgAtAHIAbwBhAGQAIABlAHEAdQBpAHAAbQBlAG4AdAAgAGEAbgBkACAAdgBlAHMAcwBlAGwAcwBcACIAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAVAByAGEAbgBzAHAAbwByAHQATwBmAGYAUgBvAGEAZABfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADQALgAyAC4AMQBcACIAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAVAByAGEAbgBzAHAAbwByAHQATwBmAGYAUgBvAGEAZABfAEQAYQB0AGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAANwAsAFwAbgAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAYQBuAHMAcABvAHIAdAAgAHQAeQBwAGUAIAB0AFwAIgAsACAAXAAiAEYAdQBlAGwAIAB0AHkAcABlACAAcQBcACIALAAgAFwAIgBFAEMAVAByAGEAbgBzACwAcQAgACgARwBKAC8AawBMACkAXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAEMATwAyACAARQBGAFQAcgBhAG4ALAAxACwAdABxAGcAIAAoAGsAZwAgAEMATwAyAC0AZQAvAEcASgApAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAIABDAEgANAAgAEUARgBUAHIAYQBuACwAMQAsAHQAZwBnACAAKABrAGcAIABDAE8AMgAtAGUALwBHAEoAKQBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAxACAATgAyAE8AIABFAEYAVAByAGEAbgAsADEALAB0AGcAZwAgACgAawBnACAAQwBPADIALQBlAC8ARwBKACkAXAAiACwAIABcACIAUwBjAG8AcABlACAAMwAgAEUARgBUAHIAYQBuAHMALAAzACwAcQAgACgAawBnACAAQwBPADIALQBlAC8ARwBKACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVgBlAHMAcwBlAGwAXAAiACwAIABcACIAUABlAHQAcgBvAGwAXAAiACwAIAAzADQALgAyACwAIAA2ADcALgA0ACwAIAAxADAALgAxACwAIAAwAC4AMwAsACAAMQA3AC4AMgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFYAZQBzAHMAZQBsAFwAIgAsACAAXAAiAEQAaQBlAHMAZQBsAFwAIgAsACAAMwA4AC4ANgAsACAANgA5AC4AOQAsACAAMAAuADIALAAgADAALgA1ACwAIAAxADcALgAzADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVgBlAHMAcwBlAGwAXAAiACwAIABcACIARgB1AGUAbAAgAE8AaQBsAFwAIgAsACAAMwA5AC4ANwAsACAANwAzAC4ANgAsACAAMAAuADIALAAgADAALgA1ACwAIAAxADgALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwBmAGYALQByAG8AYQBkACAAQQBnAHIAaQBjAHUAbAB0AHUAcgBlACAAYQBuAGQAIABmAG8AcgBlAHMAdAByAHkAIABlAHEAdQBpAHAAbQBlAG4AdABcACIALAAgAFwAIgBEAGkAZQBzAGUAbABcACIALAAgADMAOAAuADYALAAgADYAOQAuADkALAAgADAALgAzACwAIAAwAC4ANQAsACAAMQA3AC4AMwBcAG4AIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgApACkAKQA7AFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEYAdQBlAGwAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBGAHUAZQBsAF8ARwBlAHQAVAByAGEAbgBzAHAAbwByAHQARgB1AGUAbABTAHQAcgBpAG4AZwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEMAZQBsAGwALABcAG4AIAAgACAAIABMAEUARgBUACgAQwBlAGwAbAAsACAARgBJAE4ARAAoAFwAIgAsACAAXAAiACwAQwBlAGwAbAApACAALQAxACkAXABuACkAOwBcAG4AXABuAEYAdQBlAGwAXwBHAGUAdABTAHQAYQB0AGkAbwBuAGEAcgB5AEYAdQBlAGwAUwB0AHIAaQBuAGcAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABDAGUAbABsACwAXABuACAAIAAgACAAUgBJAEcASABUACgAQwBlAGwAbAAsAEwARQBOACgAQwBlAGwAbAApAC0ARgBJAE4ARAAoAFwAIgAsACAAXAAiACwAQwBlAGwAbAApACkAXABuACkAOwBcAG4AXABuAEYAdQBlAGwAXwBUAG8AdABhAGwAQwBvAG4AcwB1AG0AcAB0AGkAbwBuAFwAbgA9ACAATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABGAHUAZQBsAEMAbwBuAHMAdQBtAHAAdABpAG8AbgBBAHIAcgBhAHkALAAgAEYAdQBlAGwAVQBzAGUAQQByAHIAYQB5ACwAIABGAHUAZQBsAFUAcwBlACwAIABGAHUAZQBsAFQAeQBwAGUAQQByAHIAYQB5ACwAIABGAHUAZQBsAFQAeQBwAGUALABcAG4AIAAgACAAIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAUwBVAE0AKABcAG4AIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABcAG4AIAAgACAAIAAgACAAIAAgAEYAdQBlAGwAQwBvAG4AcwB1AG0AcAB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgACAAIAAgACAAKABGAHUAZQBsAFQAeQBwAGUAQQByAHIAYQB5ACAAPQAgAEYAdQBlAGwAVAB5AHAAZQApACAAKgAgAFwAbgAgACAAIAAgACAAIAAgACAAKABGAHUAZQBsAFUAcwBlAEEAcgByAGEAeQAgAD0AIABGAHUAZQBsAFUAcwBlACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQAsAFwAbgAgACAAIAAgADAAXABuACAAIAApAFwAbgApADsAIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AOAA6ACAARgB1AGUAbAAgAFUAcwBlAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADgALgAxACAARgB1AGUAbAAgAFUAcwBlACAALQAgAFQAcgBhAG4AcwBwAG8AcgB0ACAAZgB1AGUAbABcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBcAG4AVgBFAEUAUgBHAF8AOABfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABRACwAIABFAEMALAAgAEUARgAsAFwAbgAgACAAIAAgACgAUQAgACoAIABFAEMAIAAqACAARQBGACkAIAAqACAAMQAwACAAXgAgAC0AIAAzAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADgAXwAxAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AVAByAGEAbgBzAHAAbwByAHQAXABuAEUAbQBpAHMAcwBpAG8AbgBzACAAZgBvAHIAIABlAGEAYwBoACAARwBIAEcAIABmAHIAbwBtACAAdABoAGUAIABjAG8AbQBiAHUAcwB0AGkAbwBuACAAbwBmACAAZgB1AGUAbABzACAAZgBvAHIAIAB0AHIAYQBuAHMAcABvAHIAdAAgAGUAbgBlAHIAZwB5ACAAcAB1AHIAcABvAHMAZQBzAFwAbgBRACAAOgAgAEEAbQBvAHUAbgB0ACAAbwBmACAAZgB1AGUAbAAgAHQAeQBwAGUAIABxACAAYwBvAG0AYgB1AHMAdABlAGQAIABmAG8AcgAgAHQAcgBhAG4AcwBwAG8AcgB0ACAAZQBuAGUAcgBnAHkAIABwAHUAcgBwAG8AcwBlAHMAIAA6ACAAawBMAFwAbgBFAEMAIAA6ACAAZQBuAGUAcgBnAHkAIABjAG8AbgB0AGUAbgB0ACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHQAcgBhAG4AcwBwAG8AcgB0ACAAZQBuAGUAcgBnAHkAIABwAHUAcgBwAG8AcwBlAHMAIAA6ACAARwBKAC8AawBMAFwAbgBFAEYAIAA6ACAAUwBjAG8AcABlACAAMQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AHIAYQBuAHMAcABvAHIAdAAgAGUAbgBlAHIAZwB5ACAAcAB1AHIAcABvAHMAZQBzACAAZgBvAHIAIABlAGEAYwBoACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzACAAOgAgAGsAZwAgAEMATwAyAGUAIAAvACAARwBKAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFwAbgBWAEUARQBSAEcAXwA4AF8AMQBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFQAcgBhAG4AcwBwAG8AcgB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFEAXwBUAHIAYQBuAHMAdABxACwAIABFAEMAXwBUAHIAYQBuAHMAcQAsACAARQBGAF8AVAByAGEAbgBzADEAdABxAGcALABcAG4AIAAgACAAIABWAEUARQBSAEcAXwA4AF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuACgAUQBfAFQAcgBhAG4AcwB0AHEALAAgAEUAQwBfAFQAcgBhAG4AcwBxACwAIABFAEYAXwBUAHIAYQBuAHMAMQB0AHEAZwApAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAFYARQBFAFIARwBfADgAXwAxAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AVAByAGEAbgBzAHAAbwByAHQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgBzACAAZgBvAHIAIABlAGEAYwBoACAARwBIAEcAIABmAHIAbwBtACAAdABoAGUAIABjAG8AbQBiAHUAcwB0AGkAbwBuACAAbwBmACAAZgB1AGUAbABzACAAZgBvAHIAIAB0AHIAYQBuAHMAcABvAHIAdAAgAGUAbgBlAHIAZwB5ACAAcAB1AHIAcABvAHMAZQBzAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA4AF8AMQBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFQAcgBhAG4AcwBwAG8AcgB0AF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AZwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOABfADEAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBUAHIAYQBuAHMAcABvAHIAdABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgAtAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADgAXwAxAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AVAByAGEAbgBzAHAAbwByAHQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAOAAuADEALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADgAXwAxAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AVAByAGEAbgBzAHAAbwByAHQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAE4AYQB0AGkAbwBuAGEAbAAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABBAGMAYwBvAHUAbgB0AHMAIABGAGEAYwB0AG8AcgBzACAAMgAwADIANQAgAC0AIAAyAC4AMwAgAEUAcwB0AGkAbQBhAHQAaQBuAGcAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIAB0AHIAYQBuAHMAcABvAHIAdAAgAGYAdQBlAGwAcwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOABfADEAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBUAHIAYQBuAHMAcABvAHIAdABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwBnAD0AXABcAHMAdQBtAFwAXABuAG8AbABpAG0AaQB0AHMAXwB0ACAAXABcAHMAdQBtAFwAXABuAG8AbABpAG0AaQB0AHMAXwBxAFwAXABsAGUAZgB0ACgAUQBfAHsAVAByAGEAbgBzACwAdABxAH0AXABcAHQAaQBtAGUAcwAgAEUAQwBfAHsAVAByAGEAbgBzACwAcQB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AFQAcgBhAG4AcwAsADEALAB0AHEAZwB9AFwAXAByAGkAZwBoAHQAKQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOABfADEAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBUAHIAYQBuAHMAcABvAHIAdABfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANwAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQBfAFQAcgBhAG4AcwB0AHEAXAAiACwAIABcACIAQQBtAG8AdQBuAHQAIABvAGYAIABmAHUAZQBsACAAdAB5AHAAZQAgAHEAIABjAG8AbQBiAHUAcwB0AGUAZAAgAGYAbwByACAAdAByAGEAbgBzAHAAbwByAHQAIABlAG4AZQByAGcAeQAgAHAAdQByAHAAbwBzAGUAcwBcACIALAAgAFwAIgBWAGEAcgBpAGUAcwAgAGIAYQBzAGUAZAAgAG8AbgAgAGYAdQBlAGwAIAB0AHkAcABlADoAIABrAEwALAAgAG0AMwAsACAARwBKAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAF8AVAByAGEAbgBzAHEAXAAiACwAIABcACIARQBuAGUAcgBnAHkAIABjAG8AbgB0AGUAbgB0ACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHQAcgBhAG4AcwBwAG8AcgB0ACAAZQBuAGUAcgBnAHkAIABwAHUAcgBwAG8AcwBlAHMAXAAiACwAIABcACIARwBKACAALwAgAHUAbgBpAHQAIABvAGYAIABmAHUAZQBsAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8AVAByAGEAbgBzADEAdABxAGcAXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AHIAYQBuAHMAcABvAHIAdAAgAGUAbgBlAHIAZwB5ACAAcAB1AHIAcABvAHMAZQBzACAAZgBvAHIAIABlAGEAYwBoACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAFwAIgAsACAAXAAiAGsAZwAgAEMATwAyAGUAIAAvACAARwBKAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAcQBcACIALAAgAFwAIgBGAHUAZQBsACAAdAB5AHAAZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBhAG4AcwBcACIALAAgAFwAIgBUAHIAYQBuAHMAcABvAHIAdAAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AXAAiACwAIABcACIAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBnAFwAIgAsACAAXAAiAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBcACIALAAgAFwAIgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEAXAAiACwAIABcACIAUwBjAG8AcABlACAAMQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA4AF8AMgBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFMAdABhAHQAaQBvAG4AYQByAHkAXABuAEUAbQBpAHMAcwBpAG8AbgBzACAAZgBvAHIAIABlAGEAYwBoACAARwBIAEcAIABmAHIAbwBtACAAdABoAGUAIABzAHQAYQB0AGkAbwBuAGEAcgB5ACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgAG8AZgAgAGYAdQBlAGwAcwBcAG4AUQAgADoAIABBAG0AbwB1AG4AdAAgAG8AZgAgAGYAdQBlAGwAIAB0AHkAcABlACAAcQAgAHUAcwBlAGQAIABmAG8AcgAgAHMAdABhAHQAaQBvAG4AYQByAHkAIABjAG8AbQBiAHUAcwB0AGkAbwBuACAAbwBwAGUAcgBhAHQAaQBvAG4AcwAgADoAIABrAEwAXABuAEUAQwAgADoAIABFAG4AZQByAGcAeQAgAGMAbwBuAHQAZQBuAHQAIABmAGEAYwB0AG8AcgAgAGYAbwByACAAcwB0AGEAdABpAG8AbgBhAHIAeQAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AIABvAHAAZQByAGEAdABpAG8AbgBzACAAOgAgAEcASgAvAGsATABcAG4ARQBGACAAOgAgAFMAYwBvAHAAZQAgADEAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAcwB0AGEAdABpAG8AbgBhAHIAeQAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AIABmAG8AcgAgAGUAYQBjAGgAIABnAHIAZQBlAG4AaABvAHUAcwBlACAAZwBhAHMAIAA6ACAAawBnACAAQwBPADIAZQAgAC8AIABHAEoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAFYARQBFAFIARwBfADgAXwAyAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AUwB0AGEAdABpAG8AbgBhAHIAeQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABRAF8AUwBDAHEALAAgAEUAQwBfAFMAQwBxACwAIABFAEYAXwBTAEMAMQBxAGcALABcAG4AIAAgACAAIABWAEUARQBSAEcAXwA4AF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuACgAUQBfAFMAQwBxACwAIABFAEMAXwBTAEMAcQAsACAARQBGAF8AUwBDADEAcQBnACkAXABuACAAIAApAFwAbgA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOABfADIAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBTAHQAYQB0AGkAbwBuAGEAcgB5AF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAGYAbwByACAAZQBhAGMAaAAgAEcASABHACAAZgByAG8AbQAgAHQAaABlACAAcwB0AGEAdABpAG8AbgBhAHIAeQAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AIABvAGYAIABmAHUAZQBsAHMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADgAXwAyAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AUwB0AGEAdABpAG8AbgBhAHIAeQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAGcAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADgAXwAyAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AUwB0AGEAdABpAG8AbgBhAHIAeQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgAtAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADgAXwAyAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AUwB0AGEAdABpAG8AbgBhAHIAeQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA4AC4AMgAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOABfADIAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBTAHQAYQB0AGkAbwBuAGEAcgB5AF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABOAGEAdABpAG8AbgBhAGwAIABHAHIAZQBlAG4AaABvAHUAcwBlACAAQQBjAGMAbwB1AG4AdABzACAARgBhAGMAdABvAHIAcwAgADIAMAAyADUAIAAtACAAMgAuADIAIABFAHMAdABpAG0AYQB0AGkAbgBnACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAcwB0AGEAdABpAG8AbgBhAHIAeQAgAGUAbgBlAHIAZwB5ACAAcwBvAHUAcgBjAGUAcwAgAC0AIABDAGEAbABjAHUAbABhAHQAaQBuAGcAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABzAHQAYQB0AGkAbwBuAGEAcgB5ACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgAG8AZgAgAGwAaQBxAHUAaQBkACAAZgB1AGUAbABzAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA4AF8AMgBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFMAdABhAHQAaQBvAG4AYQByAHkAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AZwA9AFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AdAAgAFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AcQBcAFwAbABlAGYAdAAoAFEAXwB7AFMAQwAsAHEAfQBcAFwAdABpAG0AZQBzACAARQBDAF8AewBTAEMALABxAH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAUwBDACwAMQAsAHEAZwB9AFwAXAByAGkAZwBoAHQAKQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOABfADIAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBTAHQAYQB0AGkAbwBuAGEAcgB5AF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA3ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBRAF8AUwBDAHEAXAAiACwAIABcACIAQQBtAG8AdQBuAHQAIABvAGYAIABmAHUAZQBsACAAdAB5AHAAZQAgAHEAIAB1AHMAZQBkACAAZgBvAHIAIABzAHQAYQB0AGkAbwBuAGEAcgB5ACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgAG8AcABlAHIAYQB0AGkAbwBuAHMAXAAiACwAIABcACIAVgBhAHIAaQBlAHMAIABiAGEAcwBlAGQAIABvAG4AIABmAHUAZQBsACAAdAB5AHAAZQA6ACAAawBMACwAIABtADMALAAgAEcASgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAQwBfAFMAQwBxAFwAIgAsACAAXAAiAEUAbgBlAHIAZwB5ACAAYwBvAG4AdABlAG4AdAAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABzAHQAYQB0AGkAbwBuAGEAcgB5ACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgAG8AcABlAHIAYQB0AGkAbwBuAHMAXAAiACwAIABcACIARwBKACAALwAgAHUAbgBpAHQAIABvAGYAIABmAHUAZQBsAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8AUwBDADEAcQBnAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAcwB0AGEAdABpAG8AbgBhAHIAeQAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AIABmAG8AcgAgAGUAYQBjAGgAIABnAHIAZQBlAG4AaABvAHUAcwBlACAAZwBhAHMAXAAiACwAIABcACIAawBnACAAQwBPADIAZQAgAC8AIABHAEoAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBxAFwAIgAsACAAXAAiAEYAdQBlAGwAIAB0AHkAcABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBDAFwAIgAsACAAXAAiAFMAdABhAHQAaQBvAG4AYQByAHkAIABjAG8AbQBiAHUAcwB0AGkAbwBuAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAZwBcACIALAAgAFwAIgBHAHIAZQBlAG4AaABvAHUAcwBlACAAZwBhAHMAXAAiACwAIABcACIAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAXAAiACwAIABcACIAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADkAOgAgAFIAZQBmAHIAaQBnAGUAcgBhAG4AdAAgAFUAcwBlAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADkALgAxACAAUgBlAGYAcgBpAGcAZQByAGEAbgB0ACAAVQBzAGUAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAXABuAFQAaABlACAAdABvAHQAYQBsACAAZQBtAGkAcwBzAGkAbwBuAHMAIABvAGYAIAByAGUAZgByAGkAZwBlAHIAYQBuAHQAIABsAGUAYQBrAGkAbgBnACAAZAB1AHIAaQBuAGcAIABvAHAAZQByAGEAdABpAG8AbgAgACgAbgBvAHQAIABkAHUAcgBpAG4AZwAgAGkAbgBzAHQAYQBsAGwAYQB0AGkAbwBuACAAbwByACAAZABpAHMAcABvAHMAYQBsACkAXABuAEcAVwBQAFIAIAA6ACAARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABvAGYAIAByAGUAZgByAGkAZwBlAHIAYQBuAHQAIABSACAAOgAgAEQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXABuAGMAaABhAHIAZwBlAF8AUgBhACAAOgAgAEEAbQBvAHUAbgB0ACAAbwBmACAAcgBlAGYAcgBpAGcAZQByAGEAbgB0ACAAUgAgAGMAbwBuAHQAYQBpAG4AZQBkACAAaQBuACAAYQBwAHAAbABpAGEAbgBjAGUAIABhACAAOgAgAGsAZwBcAG4AbABlAGEAawBhAGcAZQByAGEAdABlAF8AYQAgADoAIABQAHIAYwBlAG4AdABhAGcAZQAgAG8AZgAgAHQAbwB0AGEAbAAgAGMAaABhAHIAZwBlACAAbABlAGEAawBlAGQAIABmAHIAbwBtACAAYQBwAHAAbABpAGEAbgBjAGUAIABhACAAZQBhAGMAaAAgAHkAZQBhAHIAIAA6ACAAUABlAHIAYwBlAG4AdABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYwBoAGEAcgBnAGUAXwBSAGEALAAgAGwAZQBhAGsAYQBnAGUAcgBhAHQAZQBfAGEALABcAG4AIAAgACAAIAAoAGMAaABhAHIAZwBlAF8AUgBhACAAKgAgACgAbABlAGEAawBhAGcAZQByAGEAdABlAF8AYQAvADEAMAAwACkAKQAgACoAIAAxADAAIABeACAALQAgADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBHAFcAUABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8AUgAsACAARwBXAFAAXwBSACwAXABuACAAIAAgACAAKAAoAEUAXwBSACAAKgAgADEAMABeADMAKQAgACoAIABHAFcAUABfAFIAKQAgACoAIAAxADAAXgAtADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVABoAGUAIAB0AG8AdABhAGwAIABlAG0AaQBzAHMAaQBvAG4AcwAgAG8AZgAgAHIAZQBmAHIAaQBnAGUAcgBhAG4AdAAgAGwAZQBhAGsAaQBuAGcAIABkAHUAcgBpAG4AZwAgAG8AcABlAHIAYQB0AGkAbwBuACAAKABuAG8AdAAgAGQAdQByAGkAbgBnACAAaQBuAHMAdABhAGwAbABhAHQAaQBvAG4AIABvAHIAIABkAGkAcwBwAG8AcwBhAGwAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcARwBXAFAAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdAAgAGwAZQBhAGsAYQBnAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGMAbwBuAHYAZQByAHQAZQBkACAAdABvACAAQwBPADIALQBlAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAFIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAAcgBlAGYAcgBpAGcAZQByAGEAbgB0ACAAZwBhAHMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAEcAVwBQAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAC0AZQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAOQAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAE4AYQB0AGkAbwBuAGEAbAAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABBAGMAYwBvAHUAbgB0AHMAIABGAGEAYwB0AG8AcgBzACAAMgAwADIANQAgAC0AIAAzAC4AMQAgAEUAcwB0AGkAbQBhAHQAaQBuAGcAIABpAG4AZAB1AHMAdAByAGkAYQBsACAAcAByAG8AYwBlAHMAcwBlAHMAIABlAG0AaQBzAHMAaQBvAG4AcwAgAC0AIABSAGUAZgByAGkAZwBlAHIAYQBuAHQAIABsAGUAYQBrAGEAZwBlAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBfAFIAZQBhAGQAYQBiAGwAZQBFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGMAaABhAHIAZwBlAF8AUgBhACAAKgAgACgAbABlAGEAawBhAGcAZQByAGEAdABlAF8AYQAvADEAMAAwACkAIAAqACAAMQAwACAAXgAgAC0AIAAzAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwBSACAAPQAgAFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AYQAgAFwAXABsAGUAZgB0ACgAIABjAGgAYQByAGcAZQBfAHsAUgBhAH0AIABcAFwAdABpAG0AZQBzACAAXABcAGYAcgBhAGMAewBsAGUAYQBrAGEAZwBlAFwAXAAsAHIAYQB0AGUAXwBhAH0AewAxADAAMAB9ACAAXABcAHIAaQBnAGgAdAApACAAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAEcAVwBQAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAEMATwAyAGUAIAA9ACAAXABcAGwAZQBmAHQAKABFAF8AUgAgAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7ADMAfQAgAFwAXAByAGkAZwBoAHQAKQAgAFwAXAB0AGkAbQBlAHMAIABHAFcAUABfAFIAIABcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGMAaABhAHIAZwBlAF8AUgBhAFwAIgAsACAAXAAiAEEAbQBvAHUAbgB0ACAAbwBmACAAcgBlAGYAcgBpAGcAZQByAGEAbgB0ACAAUgAgAGMAbwBuAHQAYQBpAG4AZQBkACAAaQBuACAAYQBwAHAAbABpAGEAbgBjAGUAIABhAFwAIgAsACAAXAAiAGsAZwBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGwAZQBhAGsAYQBnAGUAcgBhAHQAZQBfAGEAXAAiACwAIABcACIAUAByAGMAZQBuAHQAYQBnAGUAIABvAGYAIAB0AG8AdABhAGwAIABjAGgAYQByAGcAZQAgAGwAZQBhAGsAZQBkACAAZgByAG8AbQAgAGEAcABwAGwAaQBhAG4AYwBlACAAYQAgAGUAYQBjAGgAIAB5AGUAYQByAFwAIgAsACAAXAAiAFAAZQByAGMAZQBuAHQAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBhAFwAIgAsACAAXAAiAEEAcABwAGwAaQBhAG4AYwBlACAAdAB5AHAAZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAXAAiACwAIABcACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAEcAVwBQAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAF8AUgBcACIALAAgAFwAIgBUAG8AdABhAGwAIABlAG0AaQBzAHMAaQBvAG4AcwAgAG8AZgAgAHIAZQBmAHIAaQBnAGUAcgBhAG4AdAAgAFIAXAAiACwAIABcACIAdAAgAHIAZQBmAHIAaQBnAGUAcgBhAG4AdAAgAGcAYQBzAFwAIgAsACAAXAAiAEMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAAOQAuADEALgAxACAAKAAxACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAF8AUgBcACIALAAgAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAG8AZgAgAHIAZQBmAHIAaQBnAGUAcgBhAG4AdAAgAFIAXAAiACwAIABcACIARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ATgAgAFMATwBVAFIAQwBFADoAIABBAGQAZABlAGQAIABlAHEAdQBhAHQAaQBvAG4AIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAcgBlAGYAcgBpAGcAZQByAGEAbgB0ACAAUgAgAHQAbwAgAEMATwAyAC0AZQAgAHUAcwBpAG4AZwAgAHQAaABlACAAcgBlAGYAcgBpAGcAZQByAGEAbgB0AFwAdQAwADAAMgA3AHMAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgACgARwBXAFAAKQAuAFwAIgApADsAIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAEEAcABwAGUAbgBkAGkAeAAgADIAIABHAGwAbwBiAGEAbAAgAFcAYQByAG0AaQBuAGcAIABQAG8AdABlAG4AdABpAGEAbABzADoAIABUAGEAYgBsAGUAIAAyADMAIABHAGwAbwBiAGEAbAAgAFcAYQByAG0AaQBuAGcAIABQAG8AdABlAG4AdABpAGEAbABzAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABHAFcAUABfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEcAbABvAGIAYQBsACAAVwBhAHIAbQBpAG4AZwAgAFAAbwB0AGUAbgB0AGkAYQBsAHMAXAAiACkAKQA7AFwAbgBcAG4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBDAGgAZQBtAGkAYwBhAGwARwBXAFAAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABHAFcAUABfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAE4AYQB0AGkAbwBuAGEAbAAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABBAGMAYwBvAHUAbgB0AHMAIABGAGEAYwB0AG8AcgBzACAAMgAwADIANQAgAC0AIABBAHAAcABlAG4AZABpAHgAIAAyACAALQAgAFQAYQBiAGwAZQAgADIAMwBcACIAKQApADsAXABuAFwAbgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABHAFcAUABfAEQAYQB0AGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwA5ACwAIAA1ACwAXABuACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEcAYQBzAFwAIgAsACAAXAAiAEMAaABlAG0AaQBjAGEAbAAgAGYAbwByAG0AdQBsAGEAXAAiACwAIABcACIARwBsAG8AYgBhAGwAIABXAGEAcgBtAGkAbgBnACAAUABvAHQAZQBuAHQAaQBhAGwAIAAoAEEAUgA1ACkAXAAiACwAIABcACIARwBhAHMAIAAtACAARgBDACAAbgBhAG0AZQBcACIALAAgAFwAIgBBAGQAaQB0AGkAbwBuAGEAbAAgAGQAYQB0AGEAIABzAG8AdQByAGMAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAXAAiACwAIABcACIAQwBPADIAXAAiACwAIAAxACwAIABcACIAQwBPADIAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIATQBlAHQAaABhAG4AZQBcACIALAAgAFwAIgBDAEgANABcACIALAAgADIAOAAsACAAXAAiAEMASAA0AFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAXAAiACwAIABcACIATgAyAE8AXAAiACwAIAAyADYANQAsACAAXAAiAE4AMgBPAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFMAdQBsAHAAaAB1AHIAIABoAGUAeABhAGYAbAB1AG8AcgBpAGQAZQBcACIALAAgAFwAIgBTAEYANgBcACIALAAgADIAMwA1ADAAMAAsACAAXAAiAFMARgA2AFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgARgBDAC0AMgAzACAAKABSAC0AMgAzACkAXAAiACwAIABcACIAQwBIAEYAMwBcACIALAAgACAAMQAyADQAMAAwACwAIABcACIASABGAEMALQAyADMAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABGAEMALQAzADIAIAAoAFIALQAzADIAKQBcACIALAAgAFwAIgBDAEgAMgBGADIAXAAiACwAIAA2ADcANwAsACAAXAAiAEgARgBDAC0AMwAyAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgARgBDAC0ANAAxACAAKABSAC0ANAAxACkAXAAiACwAIABcACIAQwBIADMARgBcACIALAAgACAAMQAxADYALAAgAFwAIgBIAEYAQwAtADQAMQBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAEYAQwAtADQAMwAtADEAMABtAGUAZQAgACgAUgAtADQAMwAxADAAbQBlAGUAKQBcACIALAAgAFwAIgBDADUASAAyAEYAMQAwAFwAIgAsACAAMQA2ADUAMAAsACAAXAAiAEgARgBDAC0ANAAzAC0AMQAwAG0AZQBlAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgARgBDAC0AMQAyADUAIAAoAFIALQAxADIANQApAFwAIgAsACAAXAAiAEMAMgBIAEYANQBcACIALAAgACAAMwAxADcAMAAsACAAXAAiAEgARgBDAC0AMQAyADUAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABGAEMALQAxADMANAAgACgAUgAtADEAMwA0ACkAXAAiACwAIABcACIAQwAyAEgAMgBGADQAIAAoAEMASABGADIAQwBIAEYAMgApAFwAIgAsACAAIAAxADEAMgAwACwAIABcACIASABGAEMALQAxADMANABcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAEYAQwAtADEAMwA0AGEAIAAoAFIALQAxADMANABhACkAXAAiACwAIABcACIAQwAyAEgAMgBGADQAIAAoAEMASAAyAEYAQwBGADMAKQBcACIALAAgADEAMwAwADAALAAgAFwAIgBIAEYAQwAtADEAMwA0AGEAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABGAEMALQAxADQAMwAgACgAUgAtADEANAAzACkAXAAiACwAIABcACIAQwAyAEgAMwBGADMAIAAoAEMASABGADIAQwBIADIARgApAFwAIgAsACAAMwAyADgALAAgAFwAIgBIAEYAQwAtADEANAAzAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgARgBDAC0AMQA0ADMAYQAgACgAUgAtADEANAAzAGEAKQBcACIALAAgAFwAIgBDADIASAAzAEYAMwAgACgAQwBGADMAQwBIADMAKQBcACIALAAgADQAOAAwADAALAAgAFwAIgBIAEYAQwAtADEANAAzAGEAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABGAEMALQAxADUAMgBhACAAKABSAC0AMQA1ADIAYQApAFwAIgAsACAAXAAiAEMAMgBIADQARgAyACAAKABDAEgAMwBDAEgARgAyACkAXAAiACwAIAAxADMAOAAsACAAXAAiAEgARgBDAC0AMQA1ADIAYQBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAEYAQwAtADIAMgA3AGUAYQAgACgAUgAtADIAMgA3AGUAYQApAFwAIgAsACAAXAAiAEMAMwBIAEYANwBcACIALAAgADMAMwA1ADAALAAgAFwAIgBIAEYAQwAtADIAMgA3AGUAYQBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAEYAQwAtADIAMwA2AGYAYQAgACgAUgAtADIAMwA2AGYAYQApAFwAIgAsACAAXAAiAEMAMwBIADIARgA2AFwAIgAsACAAOAAwADYAMAAsACAAXAAiAEgARgBDAC0AMgAzADYAZgBhAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgARgBDAC0AMgA0ADUAYwBhACAAKABSAC0AMgA0ADUAYwBhACkAXAAiACwAIABcACIAQwAzAEgAMwBGADUAXAAiACwAIAA3ADEANgAsACAAXAAiAEgARgBDAC0AMgA0ADUAYwBhAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgARgBDAC0AMgA0ADUAZgBhACAAKABSAC0AMgA0ADUAZgBhACkAXAAiACwAIABcACIAQwBIAEYAMgBDAEgAMgBDAEYAMwBcACIALAAgADgANQA4ACwAIABcACIASABGAEMALQAyADQANQBmAGEAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABGAEMALQAzADYANQBtAGYAYwAgACgAUgAtADMANgA1AG0AZgBjACkAXAAiACwAIABcACIAQwBIADMAQwBGADIAQwBIADIAQwBGADMAXAAiACwAIAA4ADAANAAsACAAXAAiAEgARgBDAC0AMwA2ADUAbQBmAGMAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABDAEYAQwAtADIAMgAgACgAUgAtADIAMgApAFwAIgAsACAAXAAiAEMASABDAGwARgAyAFwAIgAsACAAMQA3ADYAMAAsACAAXAAiAEgAQwBGAEMALQAyADIAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABDAEYAQwAtADEAMgAzACAAKABSAC0AMQAyADMAKQBcACIALAAgAFwAIgBDAEgAQwBsADIAMgBDAEYAMwBcACIALAAgADcAOQAsACAAXAAiAEgAQwBGAEMALQAxADIAMwBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAEMARgBDAC0AMQAyADQAIAAoAFIALQAxADIANAApAFwAIgAsACAAXAAiAEMASABDAGwARgBDAEYAMwBcACIALAAgADUAMgA3ACwAIABcACIASABDAEYAQwAtADEAMgA0AFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAQwBGAEMALQAxADQAMQBiACAAKABSAC0AMQA0ADEAYgApAFwAIgAsACAAXAAiAEMASAAzAEMAQwBsADIARgBcACIALAAgADcAOAAyACwAIABcACIASABDAEYAQwAtADEANAAxAGIAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABDAEYAQwAtADEANAAyAGIAIAAoAFIALQAxADQAMgBiACkAXAAiACwAIABcACIAQwBIADIAQwBDAGwARgAyAFwAIgAsACAAMQA5ADgAMAAsACAAXAAiAEgAQwBGAEMALQAxADQAMgBiAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAQwBGAEMALQAyADIANQBjAGEAIAAoAFIALQAyADIANQBjAGEAKQBcACIALAAgAFwAIgBDAEgAQwBsADIAQwBGADIAQwBGADMAXAAiACwAIAAxADIANwAsACAAXAAiAEgAQwBGAEMALQAyADIANQBjAGEAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABDAEYAQwAtADIAMgA1AGMAYgAgACgAUgAtADIAMgA1AGMAYgApAFwAIgAsACAAXAAiAEMASABDAGwARgBDAEYAMgBDAEMASQBGADIAXAAiACwAIAA1ADIANQAsACAAXAAiAEgAQwBGAEMALQAyADIANQBjAGIAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUABGAEMALQAxADQAIABQAGUAcgBmAGwAdQBvAHIAbwBtAGUAdABoAGEAbgBlACAAKAB0AGUAdAByAGEAZgBsAHUAbwByAG8AbQBlAHQAaABhAG4AZQApAFwAIgAsACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAAsACAAXAAiAFAARgBDAC0AMQA0AFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFAARgBDAC0AMQAxADYAIABQAGUAcgBmAGwAdQBvAHIAbwBlAHQAaABhAG4AZQAgACgAaABlAHgAYQBmAGwAdQBvAHIAbwBlAHQAaABhAG4AZQApAFwAIgAsACAAXAAiAEMAMgBGADYAXAAiACwAIAAxADEAMQAwADAALAAgAFwAIgBQAEYAQwAtADEAMQA2AFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFAARgBDAC0AMgAxADgAIABQAGUAcgBmAGwAdQBvAHIAbwBwAHIAbwBwAGEAbgBlAFwAIgAsACAAXAAiAEMAMwBGADgAXAAiACwAIAA4ADkAMAAwACwAIABcACIAUABGAEMALQAyADEAOABcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAEYAQwAtADMAMQAtADEAMAAgAFAAZQByAGYAbAB1AG8AcgBvAGIAdQB0AGEAbgBlAFwAIgAsACAAXAAiAEMANABGADEAMABcACIALAAgADkAMgAwADAALAAgAFwAIgBQAEYAQwAtADMAMQAtADEAMABcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAEYAQwAtADMAMQA4ACAAUABlAHIAZgBsAHUAbwByAG8AYwB5AGMAbABvAGIAdQB0AGEAbgBlAFwAIgAsACAAXAAiAGMALQBDADQARgA4AFwAIgAsACAAOQA1ADQAMAAsACAAXAAiAFAARgBDAC0AMwAxADgAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUABGAEMALQA0ADEALQAxADIAIABQAGUAcgBmAGwAdQBvAHIAbwBwAGUAbgB0AGEAbgBlAFwAIgAsACAAXAAiAEMANQBGADEAMgBcACIALAAgADgANQA1ADAALAAgAFwAIgBQAEYAQwAtADQAMQAtADEAMgBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAEYAQwAtADUAMQAtADEANAAgAFAAZQByAGYAbAB1AG8AcgBvAGgAZQB4AGEAbgBlAFwAIgAsACAAXAAiAEMANgBGADEANABcACIALAAgADcAOQAxADAALAAgAFwAIgBQAEYAQwAtADUAMQAtADEANABcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAEYAQwAtADkAMQAtADEAOAAgAFAAZQByAGYAbAB1AG4AYQBmAGUAbgBlAFwAIgAsACAAXAAiAEMAMQAwAEYAMQA4AFwAIgAsACAANwAxADkAMAAsACAAXAAiAFAARgBDAC0AOQAxAC0AMQA4AFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMARgBDAC0AMQAyAFwAIgAsACAAXAAiAEMAQwBsADIARgAyAFwAIgAsACAAMQAwADIAMAAwACwAIABcACIAQwBGAEMALQAxADIAXAAiACwAIABcACIASQBQAEMAQwAgAEcAbABvAGIAYQBsACAAVwBhAHIAbQBpAG4AZwAgAFAAbwB0AGUAbgB0AGkAYQBsACAAVgBhAGwAdQBlAHMAIAB2ADIALgAwACAALQAgACgAQQBSADUAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAEYAQwAtADEAMwBcACIALAAgAFwAIgBDAEMAbABGADMAXAAiACwAIAAxADMAOQAwADAALAAgAFwAIgBDAEYAQwAtADEAMwBcACIALAAgAFwAIgBJAFAAQwBDACAARwBsAG8AYgBhAGwAIABXAGEAcgBtAGkAbgBnACAAUABvAHQAZQBuAHQAaQBhAGwAIABWAGEAbAB1AGUAcwAgAHYAMgAuADAAIAAtACAAKABBAFIANQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMARgBDAC0AMQAxADQAXAAiACwAIABcACIAQwBDAGwARgAyAEMAQwBsAEYAMgBcACIALAAgADgANQA5ADAALAAgAFwAIgBDAEYAQwAtADEAMQA0AFwAIgAsACAAXAAiAEkAUABDAEMAIABHAGwAbwBiAGEAbAAgAFcAYQByAG0AaQBuAGcAIABQAG8AdABlAG4AdABpAGEAbAAgAFYAYQBsAHUAZQBzACAAdgAyAC4AMAAgAC0AIAAoAEEAUgA1ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBGAEMALQAxADEANQBcACIALAAgAFwAIgBDAEMAbABGADIAQwBGADMAXAAiACwAIAA3ADYANwAwACwAIABcACIAQwBGAEMALQAxADEANQBcACIALAAgAFwAIgBJAFAAQwBDACAARwBsAG8AYgBhAGwAIABXAGEAcgBtAGkAbgBnACAAUABvAHQAZQBuAHQAaQBhAGwAIABWAGEAbAB1AGUAcwAgAHYAMgAuADAAIAAtACAAKABBAFIANQApAFwAIgBcAG4AIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgApACkAKQA7AFwAbgBcAG4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBDAGgAZQBtAGkAYwBhAGwARwBXAFAAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABcAHUAMAAwADIANwBHAEEAUwAgAC0AIABGAEMAIABuAGEAbQBlAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AIAB3AGkAdABoACAAdAByAHUAbgBjAGEAdABlAGQAIABnAGEAcwAgAG4AYQBtAGUAIAB0AG8AIABhAGwAbABvAHcAIABtAGEAdABjAGgAaQBuAGcAIAB3AGkAdABoACAAbwB0AGgAZQByACAAdABhAGIAbABlAHMALgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAGcAYQBzAGUAcwAgAGYAcgBvAG0AIABJAFAAQwBDACAARwBsAG8AYgBhAGwAIABXAGEAcgBtAGkAbgBnACAAUABvAHQAZQBuAHQAaQBhAGwAIABWAGEAbAB1AGUAcwAgAHYAMgAuADAAIAAtACAAKABBAFIANQApAC4AIABBAGQAZABlAGQAIABcAHUAMAAwADIANwBBAGQAZABpAHQAaQBvAG4AYQBsACAAZABhAHQAYQAgAHMAbwB1AHIAYwBlAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4ALgBcACIAKQApADsAXABuAFwAbgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAEEAcABwAGUAbgBkAGkAeAAgADIAIABHAGwAbwBiAGEAbAAgAFcAYQByAG0AaQBuAGcAIABQAG8AdABlAG4AdABpAGEAbABzADoAIABCAGwAZQBuAGQAZQBkACAAcgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AQwBoAGUAbQBpAGMAYQBsAEIAbABlAG4AZABzAF8AVABpAHQAbABlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAQgBsAGUAbgBkAGUAZAAgAHIAZQBmAHIAaQBnAGUAcgBhAG4AdABzACAAKABtAGEAbgB5ACAAYwBvAG4AdABhAGkAbgBpAG4AZwAgAEgARgBDAFMAIABhAG4AZAAvAG8AcgAgAFAARgBDAFMAKQBcACIAKQApADsAXABuAFwAbgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABCAGwAZQBuAGQAcwBfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AQwBoAGUAbQBpAGMAYQBsAEIAbABlAG4AZABzAF8AUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAEEAYwBjAG8AdQBuAHQAcwAgAEYAYQBjAHQAbwByAHMAIAAyADAAMgA1ACAALQAgAEEAcABwAGUAbgBkAGkAeAAgADIAIAAtACAAVABhAGIAbABlACAAMgA0AFwAIgApACkAOwBcAG4AXABuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AQwBoAGUAbQBpAGMAYQBsAEIAbABlAG4AZABzAF8ARABhAHQAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ADEALAAgADMALABcAG4AIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIABcACIAQgBsAGUAbgBkAFwAIgAsACAAXAAiAEMAbwBuAHMAdABpAHQAdQBlAG4AdABzAFwAIgAsACAAXAAiAEMAbwBtAHAAbwBzAGkAdABpAG8AbgAgACgAJQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADAAMABcACIALAAgAFwAIgBDAEYAQwAtADEAMgAvAEMARgBDAC0AMQAxADQAXAAiACwAIABcACIAUgAtADQAMAAwACAAYwBhAG4AIABoAGEAdgBlACAAdgBhAHIAaQBvAHUAcwAgAHAAcgBvAHAAbwByAHQAaQBvAG4AcwAgAG8AZgAgAEMARgBDAC0AMQAyACAAYQBuAGQAIABDAEYAQwAtADEAMQA0AC4AIABUAGgAZQAgAGUAeABhAGMAdAAgAGMAbwBtAHAAbwBzAGkAdABpAG8AbgAgAG4AZQBlAGQAcwAgAHQAbwAgAGIAZQAgAHMAcABlAGMAaQBmAGkAZQBkACwAIABlAC4AZwAuACwAIABSAC0ANAAwADAAIAAoADYAMAAvADQAMAApAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMAAxAEEAXAAiACwAIABcACIASABDAEYAQwAtADIAMgAvAEgARgBDAC0AMQA1ADIAYQAvAEgAQwBGAEMALQAxADIANABcACIALAAgAFwAIgAoADUAMwAuADAALwAxADMALgAwAC8AMwA0AC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADAAMQBCAFwAIgAsACAAXAAiAEgAQwBGAEMALQAyADIALwBIAEYAQwAtADEANQAyAGEALwBIAEMARgBDAC0AMQAyADQAXAAiACwAIABcACIAKAA2ADEALgAwAC8AMQAxAC4AMAAvADIAOAAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAwADEAQwBcACIALAAgAFwAIgBIAEMARgBDAC0AMgAyAC8ASABGAEMALQAxADUAMgBhAC8ASABDAEYAQwAtADEAMgA0AFwAIgAsACAAXAAiACgAMwAzAC4AMAAvADEANQAuADAALwA1ADIALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMAAyAEEAXAAiACwAIABcACIASABGAEMALQAxADIANQAvAEgAQwAtADIAOQAwAC8ASABDAEYAQwAtADIAMgBcACIALAAgAFwAIgAoADYAMAAuADAALwAyAC4AMAAvADMAOAAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAwADIAQgBcACIALAAgAFwAIgBIAEYAQwAtADEAMgA1AC8ASABDAC0AMgA5ADAALwBIAEMARgBDAC0AMgAyAFwAIgAsACAAXAAiACgAMwA4AC4AMAAvADIALgAwAC8ANgAwAC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADAAMwBBAFwAIgAsACAAXAAiAEgAQwAtADIAOQAwAC8ASABDAEYAQwAtADIAMgAvAFAARgBDAC0AMgAxADgAXAAiACwAIABcACIAKAA1AC4AMAAvADcANQAuADAALwAyADAALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMAAzAEIAXAAiACwAIABcACIASABDAC0AMgA5ADAALwBIAEMARgBDAC0AMgAyAC8AUABGAEMALQAyADEAOABcACIALAAgAFwAIgAoADUALgAwAC8ANQA2AC4AMAAvADMAOQAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAwADQAQQBcACIALAAgAFwAIgBIAEYAQwAtADEAMgA1AC8ASABGAEMALQAxADQAMwBhAC8ASABGAEMALQAxADMANABhAFwAIgAsACAAXAAiACgANAA0AC4AMAAvADUAMgAuADAALwA0AC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADAANQBBAFwAIgAsACAAXAAiAEgAQwBGAEMALQAyADIALwAgAEgARgBDAC0AMQA1ADIAYQAvAEgAQwBGAEMALQAxADQAMgBiAC8AUABGAEMALQAzADEAOABcACIALAAgAFwAIgAoADQANQAuADAALwA3AC4AMAAvADUALgA1AC8ANAAyAC4ANQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADAANgBBAFwAIgAsACAAXAAiAEgAQwBGAEMALQAyADIALwBIAEMALQA2ADAAMABhAC8ASABDAEYAQwAtADEANAAyAGIAXAAiACwAIABcACIAKAA1ADUALgAwAC8AMQA0AC4AMAAvADQAMQAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAwADcAQQBcACIALAAgAFwAIgBIAEYAQwAtADMAMgAvAEgARgBDAC0AMQAyADUALwBIAEYAQwAtADEAMwA0AGEAXAAiACwAIABcACIAKAAyADAALgAwAC8ANAAwAC4AMAAvADQAMAAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAwADcAQgBcACIALAAgAFwAIgBIAEYAQwAtADMAMgAvAEgARgBDAC0AMQAyADUALwBIAEYAQwAtADEAMwA0AGEAXAAiACwAIABcACIAKAAxADAALgAwAC8ANwAwAC4AMAAvADIAMAAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAwADcAQwBcACIALAAgAFwAIgBIAEYAQwAtADMAMgAvAEgARgBDAC0AMQAyADUALwBIAEYAQwAtADEAMwA0AGEAXAAiACwAIABcACIAKAAyADMALgAwAC8AMgA1AC4AMAAvADUAMgAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAwADcARABcACIALAAgAFwAIgBIAEYAQwAtADMAMgAvAEgARgBDAC0AMQAyADUALwBIAEYAQwAtADEAMwA0AGEAXAAiACwAIABcACIAKAAxADUALgAwAC8AMQA1AC4AMAAvADcAMAAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAwADcARQBcACIALAAgAFwAIgBIAEYAQwAtADMAMgAvAEgARgBDAC0AMQAyADUALwBIAEYAQwAtADEAMwA0AGEAXAAiACwAIABcACIAKAAyADUALgAwAC8AMQA1AC4AMAAvADYAMAAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAwADgAQQBcACIALAAgAFwAIgBIAEYAQwAtADEAMgA1AC8ASABGAEMALQAxADQAMwBhAC8ASABDAEYAQwAtADIAMgBcACIALAAgAFwAIgAoADcALgAwAC8ANAA2AC4AMAAvADQANwAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAwADkAQQBcACIALAAgAFwAIgBIAEMARgBDAC0AMgAyAC8ASABDAEYAQwAtADEAMgA0AC8ASABDAEYAQwAtADEANAAyAGIAXAAiACwAIABcACIAKAA2ADAALgAwAC8AMgA1AC4AMAAvADEANQAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAwADkAQgBcACIALAAgAFwAIgBIAEMARgBDAC0AMgAyAC8ASABDAEYAQwAtADEAMgA0AC8ASABDAEYAQwAtADEANAAyAGIAXAAiACwAIABcACIAKAA2ADUALgAwAC8AMgA1AC4AMAAvADEAMAAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAxADAAQQBcACIALAAgAFwAIgBIAEYAQwAtADMAMgAvAEgARgBDAC0AMQAyADUAXAAiACwAIABcACIAKAA1ADAALgAwAC8ANQAwAC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADEAMABCAFwAIgAsACAAXAAiAEgARgBDAC0AMwAyAC8ASABGAEMALQAxADIANQBcACIALAAgAFwAIgAoADQANQAuADAALwA1ADUALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMQAxAEEAXAAiACwAIABcACIASABDAC0AMQAyADcAMAAvAEgAQwBGAEMALQAyADIALwBIAEYAQwAtADEANQAyAGEAXAAiACwAIABcACIAKAAxAC4ANQAvADgANwAuADUALwAxADEALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMQAxAEIAXAAiACwAIABcACIASABDAC0AMQAyADcAMAAvAEgAQwBGAEMALQAyADIALwBIAEYAQwAtADEANQAyAGEAXAAiACwAIABcACIAKAAzAC4AMAAvADkANAAuADAALwAzAC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADEAMQBDAFwAIgAsACAAXAAiAEgAQwAtADEAMgA3ADAALwBIAEMARgBDAC0AMgAyAC8ASABGAEMALQAxADUAMgBhAFwAIgAsACAAXAAiACgAMwAuADAALwA5ADUALgA1AC8AMQAuADUAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAxADIAQQBcACIALAAgAFwAIgBIAEMARgBDAC0AMgAyAC8AUABGAEMALQAyADEAOAAvAEgAQwBGAEMALQAxADQAMgBiAFwAIgAsACAAXAAiACgANwAwAC4AMAAvADUALgAwAC8AMgA1AC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADEAMwBBAFwAIgAsACAAXAAiAFAARgBDAC0AMgAxADgALwBIAEYAQwAtADEAMwA0AGEALwBIAEMALQA2ADAAMABhAFwAIgAsACAAXAAiACgAOQAuADAALwA4ADgALgAwAC8AMwAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAxADQAQQBcACIALAAgAFwAIgBIAEMARgBDAC0AMgAyAC8ASABDAEYAQwAtADEAMgA0AC8ASABDAC0ANgAwADAAYQAvAEgAQwBGAEMALQAxADQAMgBiAFwAIgAsACAAXAAiACgANQAxAC4AMAAvADIAOAAuADUALwA0AC4AMAAvADEANgAuADUAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAxADQAQgBcACIALAAgAFwAIgBIAEMARgBDAC0AMgAyAC8ASABDAEYAQwAtADEAMgA0AC8ASABDAC0ANgAwADAAYQAvAEgAQwBGAEMALQAxADQAMgBiAFwAIgAsACAAXAAiACgANQAwAC4AMAAvADMAOQAuADAALwAxAC4ANQAvADkALgA1ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMQA1AEEAXAAiACwAIABcACIASABDAEYAQwAtADIAMgAvAEgARgBDAC0AMQA1ADIAYQBcACIALAAgAFwAIgAoADgAMgAuADAALwAxADgALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMQA1AEIAXAAiACwAIABcACIASABDAEYAQwAtADIAMgAvAEgARgBDAC0AMQA1ADIAYQBcACIALAAgAFwAIgAoADIANQAuADAALwA3ADUALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMQA2AEEAXAAiACwAIABcACIASABGAEMALQAxADMANABhAC8ASABDAEYAQwAtADEAMgA0AC8ASABDAC0ANgAwADAAXAAiACwAIABcACIAKAA1ADkALgAwAC8AMwA5AC4ANQAvADEALgA1ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMQA3AEEAXAAiACwAIABcACIASABGAEMALQAxADIANQAvAEgARgBDAC0AMQAzADQAYQAvAEgAQwAtADYAMAAwAFwAIgAsACAAXAAiACgANAA2AC4ANgAvADUAMAAuADAALwAzAC4ANAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADEAOABBAFwAIgAsACAAXAAiAEgAQwAtADIAOQAwAC8ASABDAEYAQwAtADIAMgAvAEgARgBDAC0AMQA1ADIAYQBcACIALAAgAFwAIgAoADEALgA1AC8AOQA2AC4AMAAvADIALgA1ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMQA5AEEAXAAiACwAIABcACIASABGAEMALQAxADIANQAvAEgARgBDAC0AMQAzADQAYQAvAEgARQAtAEUAMQA3ADAAXAAiACwAIABcACIAKAA3ADcALgAwAC8AMQA5AC4AMAAvADQALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMgAwAEEAXAAiACwAIABcACIASABGAEMALQAxADMANABhAC8ASABDAEYAQwAtADEANAAyAGIAXAAiACwAIABcACIAKAA4ADgALgAwAC8AMQAyAC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADIAMQBBAFwAIgAsACAAXAAiAEgARgBDAC0AMQAyADUALwBIAEYAQwAtADEAMwA0AGEAXAAiACwAIABcACIAKAA1ADgALgAwAC8ANAAyAC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADIAMgBBAFwAIgAsACAAXAAiAEgARgBDAC0AMQAyADUALwBIAEYAQwAtADEAMwA0AGEALwBIAEMALQA2ADAAMABhAFwAIgAsACAAXAAiACgAOAA1AC4AMQAvADEAMQAuADUALwAzAC4ANAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADIAMgBCAFwAIgAsACAAXAAiAEgARgBDAC0AMQAyADUALwBIAEYAQwAtADEAMwA0AGEALwBIAEMALQA2ADAAMABhAFwAIgAsACAAXAAiACgANQA1AC4AMAAvADQAMgAuADAALwAzAC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADIAMgBDAFwAIgAsACAAXAAiAEgARgBDAC0AMQAyADUALwBIAEYAQwAtADEAMwA0AGEALwBIAEMALQA2ADAAMABhAFwAIgAsACAAXAAiACgAOAAyAC4AMAAvADEANQAuADAALwAzAC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA1ADAAMABcACIALAAgAFwAIgBDAEYAQwAtADEAMgAvAEgARgBDAC0AMQA1ADIAYQBcACIALAAgAFwAIgAoADcAMwAuADgALwAyADYALgAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADUAMAAxAFwAIgAsACAAXAAiAEgAQwBGAEMALQAyADIALwBDAEYAQwAtADEAMgBcACIALAAgAFwAIgAoADcANQAuADAALwAyADUALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADUAMAAyAFwAIgAsACAAXAAiAEgAQwBGAEMALQAyADIALwBDAEYAQwAtADEAMQA1AFwAIgAsACAAXAAiACgANAA4AC4AOAAvADUAMQAuADIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANQAwADMAXAAiACwAIABcACIASABGAEMALQAyADMALwBDAEYAQwAtADEAMwBcACIALAAgAFwAIgAoADQAMAAuADEALwA1ADkALgA5ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADUAMAA0AFwAIgAsACAAXAAiAEgARgBDAC0AMwAyAC8AQwBGAEMALQAxADEANQBcACIALAAgAFwAIgAoADQAOAAuADIALwA1ADEALgA4ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADUAMAA1AFwAIgAsACAAXAAiAEMARgBDAC0AMQAyAC8ASABDAEYAQwAtADMAMQBcACIALAAgAFwAIgAoADcAOAAuADAALwAyADIALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADUAMAA2AFwAIgAsACAAXAAiAEMARgBDAC0AMwAxAC8AQwBGAEMALQAxADEANABcACIALAAgAFwAIgAoADUANQAuADEALwA0ADQALgA5ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADUAMAA3AEEAXAAiACwAIABcACIASABGAEMALQAxADIANQAvAEgARgBDAC0AMQA0ADMAYQBcACIALAAgAFwAIgAoADUAMAAuADAALwA1ADAALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADUAMAA4AEEAXAAiACwAIABcACIASABGAEMALQAyADMALwBQAEYAQwAtADEAMQA2AFwAIgAsACAAXAAiACgAMwA5AC4AMAAvADYAMQAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANQAwADgAQgBcACIALAAgAFwAIgBIAEYAQwAtADIAMwAvAFAARgBDAC0AMQAxADYAXAAiACwAIABcACIAKAA0ADYALgAwAC8ANQA0AC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA1ADAAOQBBAFwAIgAsACAAXAAiAEgAQwBGAEMALQAyADIALwBQAEYAQwAtADIAMQA4AFwAIgAsACAAXAAiACgANAA0AC4AMAAvADUANgAuADAAKQBcACIAXABuACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AKQApACkAOwBcAG4AXABuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AQwBoAGUAbQBpAGMAYQBsAEIAbABlAG4AZABzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAARgBpAHgAZQBkACAAdAB5AHAAbwAgAC0AIABjAGgAYQBuAGcAZQBkACAASABDADYAMAAwAGEAIAB0AG8AIABIAEMALQA2ADAAMABhACAAZgBvAHIAIABiAGwAZQBuAGQAIABSAC0ANAAxADQAQgAuACAARgBpAHgAZQBkACAAdAB5AHAAbwAgAGYAbwByACAAYgBsAGUAbgBkACAAUgAtADQAMAA1AEEAIAAtACAAQwBoAGEAbgBnAGUAZAAgAEgAQwBGAEMAMQA0ADIAYgAgAHQAbwAgAEgAQwBGAEMALQAxADQAMgBiAC4AXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ATABlAGEAawBhAGcAZQAgAHIAYQB0AGUAcwAgAGYAbwByACAAYwBvAG0AbQBvAG4AIAByAGUAZgByAGkAZwBlAHIAYQB0AGkAbwBuACAAYQBuAGQAIABhAGkAcgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBMAGUAYQBrAGEAZwBlAFIAYQB0AGUAcwBfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEkAbgBkAGkAYwBhAHQAaQB2AGUAIABsAGUAYQBrAGEAZwBlACAAcgBhAHQAZQBzACAAZgBvAHIAIABjAG8AbQBtAG8AbgAgAHIAZQBmAHIAaQBnAGUAcgBhAHQAaQBvAG4AIABhAG4AZAAgAGEAaQByACAALQAgAGMAbwBuAGQAaQB0AGkAbwBuAGkAbgBnACAAZQBxAHUAaQBwAG0AZQBuAHQAXAAiACkAKQA7AFwAbgBcAG4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBMAGUAYQBrAGEAZwBlAFIAYQB0AGUAcwBfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ATABlAGEAawBhAGcAZQBSAGEAdABlAHMAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABOAGEAdABpAG8AbgBhAGwAIABHAHIAZQBlAG4AaABvAHUAcwBlACAAQQBjAGMAbwB1AG4AdABzACAARgBhAGMAdABvAHIAcwAgADIAMAAyADUAIAAtACAAVABhAGIAbABlACAAMQAwAFwAIgApACkAOwBcAG4AXABuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ATABlAGEAawBhAGcAZQBSAGEAdABlAHMAXwBEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADgAMQAsACAAMgAsAFwAbgAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwBkAHUAYwB0AFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAbABlAGEAawBhAGcAZQAgAHIAYQB0AGUAIAAoACUAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBEAG8AbQBlAHMAdABpAGMAIAByAGUAZgByAGkAZwBlAHIAYQB0AG8AcgBzAFwAIgAsACAAMQAuADcAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAYQBuAHMAcABvAHIAdAAgAHIAZQBmAHIAaQBnAGUAcgBhAHQAaQBvAG4AXAAiACwAIAAxADUALgA3ADsAXABuACAAIAAgACAAIAAgACAAIABcACIARABvAG0AZQBzAHQAaQBjACAAQQAvAEMAIABwAG8AcgB0AGEAYgBsAGUAXAAiACwAIAAyAC4ANQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEQAbwBtAGUAcwB0AGkAYwAgAEEALwBDACAAcwBwAGwAaQB0AFwAIgAsACAAMwAuADUAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBEAG8AbQBlAHMAdABpAGMAIABBAC8AQwAgAHAAYQBjAGsAYQBnAGUAZABcACIALAAgADIALgA1ADsAXABuACAAIAAgACAAIAAgACAAIABcACIATABpAGcAaAB0ACAAdgBlAGgAaQBjAGwAZQAgAEEALwBDAFwAIgAsACAANgAuADcAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAGUAYQB2AHkAIAB2AGUAaABpAGMAbABlACAAQQAvAEMAXAAiACwAIAAxADAALgA4AFwAbgAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACkAKQApADsAXABuAFwAbgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEwAZQBhAGsAYQBnAGUAUgBhAHQAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBDAGEAbABjAHUAbABhAHQAZQBCAGwAZQBuAGQARwBXAFAAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAEMAbwBuAHMAdABpAHQAdQBlAG4AdABGAGEAYwB0AGkAbwBuADEALAAgAEMAbwBuAHMAdABpAHQAdQBlAG4AdABHAFcAUAAxACwAIABcAG4AIAAgAEMAbwBuAHMAdABpAHQAdQBlAG4AdABGAGEAYwB0AGkAbwBuADIALAAgAEMAbwBuAHMAdABpAHQAdQBlAG4AdABHAFcAUAAyACwAIABcAG4AIAAgAEMAbwBuAHMAdABpAHQAdQBlAG4AdABGAGEAYwB0AGkAbwBuADMALAAgAEMAbwBuAHMAdABpAHQAdQBlAG4AdABHAFcAUAAzACwAIABcAG4AIAAgAEMAbwBuAHMAdABpAHQAdQBlAG4AdABGAGEAYwB0AGkAbwBuADQALAAgAEMAbwBuAHMAdABpAHQAdQBlAG4AdABHAFcAUAA0ACwAXABuACAAIAAoAEMAbwBuAHMAdABpAHQAdQBlAG4AdABGAGEAYwB0AGkAbwBuADEAIAAqACAAQwBvAG4AcwB0AGkAdAB1AGUAbgB0AEcAVwBQADEAKQAgACsAXABuACAAIAAoAEMAbwBuAHMAdABpAHQAdQBlAG4AdABGAGEAYwB0AGkAbwBuADIAIAAqACAAQwBvAG4AcwB0AGkAdAB1AGUAbgB0AEcAVwBQADIAKQAgACsAXABuACAAIAAoAEMAbwBuAHMAdABpAHQAdQBlAG4AdABGAGEAYwB0AGkAbwBuADMAIAAqACAAQwBvAG4AcwB0AGkAdAB1AGUAbgB0AEcAVwBQADMAKQAgACsAXABuACAAIAAoAEMAbwBuAHMAdABpAHQAdQBlAG4AdABGAGEAYwB0AGkAbwBuADQAIAAqACAAQwBvAG4AcwB0AGkAdAB1AGUAbgB0AEcAVwBQADQAKQBcAG4AKQA7ACIAfQBdACwAIgBwAHIAbwBqAGUAYwB0AE4AYQBtAGUAcwAiADoAWwAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATwBuAGUAQwBvAGwAdQBtAG4AQQBuAGQASABlAGEAZABlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABOADIATwBFAEYARgByAG8AbQBQAHIAbwBkAEkAcgByAGkAZwBhAHQAaQBvAG4AUgBhAGkAbgBmAGEAbABsACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBDAG8AbgB2AGUAcgB0AFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAFQAbwBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBUAGkAdABsAGUAIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADEARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8ARABlAHMAYwByAGkAcAB0AGkAbwBuACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAEQAYQB0AGEAIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADEARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8AVABpAHQAbABlACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBTAG8AdQByAGMAZQAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBEAGEAdABhACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBMAGkAcQB1AGkAZABfAFQAaQB0AGwAZQAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEwAaQBxAHUAaQBkAF8ARABlAHMAYwByAGkAcAB0AGkAbwBuACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkATABpAHEAdQBpAGQAXwBTAG8AdQByAGMAZQAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEwAaQBxAHUAaQBkAF8ARABhAHQAYQAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEwAaQBxAHUAaQBkAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAVAByAGEAbgBzAHAAbwByAHQAXwBUAGkAdABsAGUAIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAVAByAGEAbgBzAHAAbwByAHQAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAVAByAGEAbgBzAHAAbwByAHQAXwBTAG8AdQByAGMAZQAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBUAHIAYQBuAHMAcABvAHIAdABfAEQAYQB0AGEAIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAVAByAGEAbgBzAHAAbwByAHQAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBUAHIAYQBuAHMAcABvAHIAdABPAGYAZgBSAG8AYQBkAF8AVABpAHQAbABlACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AE8AZgBmAFIAbwBhAGQAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAVAByAGEAbgBzAHAAbwByAHQATwBmAGYAUgBvAGEAZABfAFMAbwB1AHIAYwBlACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AE8AZgBmAFIAbwBhAGQAXwBEAGEAdABhACIALAAiAEYAdQBlAGwAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBGAHUAZQBsAF8ARwBlAHQAVAByAGEAbgBzAHAAbwByAHQARgB1AGUAbABTAHQAcgBpAG4AZwAiACwAIgBGAHUAZQBsAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4ARgB1AGUAbABfAEcAZQB0AFMAdABhAHQAaQBvAG4AYQByAHkARgB1AGUAbABTAHQAcgBpAG4AZwAiACwAIgBGAHUAZQBsAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4ARgB1AGUAbABfAFQAbwB0AGEAbABDAG8AbgBzAHUAbQBwAHQAaQBvAG4AIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AMQBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFQAcgBhAG4AcwBwAG8AcgB0ACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwAxAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AVAByAGEAbgBzAHAAbwByAHQAXwBUAGkAdABsAGUAIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfADEAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBUAHIAYQBuAHMAcABvAHIAdABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AMQBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFQAcgBhAG4AcwBwAG8AcgB0AF8AVQBuAGkAdAAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AMQBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFQAcgBhAG4AcwBwAG8AcgB0AF8AUwBvAHUAcgBjAGUAIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfADEAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBUAHIAYQBuAHMAcABvAHIAdABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwAxAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AVAByAGEAbgBzAHAAbwByAHQAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwAxAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AVAByAGEAbgBzAHAAbwByAHQAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AMgBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFMAdABhAHQAaQBvAG4AYQByAHkAIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfADIAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBTAHQAYQB0AGkAbwBuAGEAcgB5AF8AVABpAHQAbABlACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwAyAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AUwB0AGEAdABpAG8AbgBhAHIAeQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AMgBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFMAdABhAHQAaQBvAG4AYQByAHkAXwBVAG4AaQB0ACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwAyAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AUwB0AGEAdABpAG8AbgBhAHIAeQBfAFMAbwB1AHIAYwBlACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwAyAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AUwB0AGEAdABpAG8AbgBhAHIAeQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwAyAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AUwB0AGEAdABpAG8AbgBhAHIAeQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfADIAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBTAHQAYQB0AGkAbwBuAGEAcgB5AF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfAFgAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4ARwBlAG4AZQByAGkAYwAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AWABfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBHAGUAbgBlAHIAaQBjAF8AVABpAHQAbABlACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwBYAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAEcAZQBuAGUAcgBpAGMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfAFgAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4ARwBlAG4AZQByAGkAYwBfAFUAbgBpAHQAIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfAFgAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4ARwBlAG4AZQByAGkAYwBfAFMAbwB1AHIAYwBlACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwBYAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAEcAZQBuAGUAcgBpAGMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AWABfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBHAGUAbgBlAHIAaQBjAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AWABfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBHAGUAbgBlAHIAaQBjAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfAFgAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4ARwBlAG4AZQByAGkAYwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcARwBXAFAAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAF8AVABpAHQAbABlACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBHAFcAUABfAFQAaQB0AGwAZQAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBfAFUAbgBpAHQAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAEcAVwBQAF8AVQBuAGkAdAAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAXwBTAG8AdQByAGMAZQAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcARwBXAFAAXwBTAG8AdQByAGMAZQAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAXwBSAGUAYQBkAGEAYgBsAGUARQBxAHUAYQB0AGkAbwBuACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAEcAVwBQAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcARwBXAFAAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABHAFcAUABfAFQAaQB0AGwAZQAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABHAFcAUABfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABHAFcAUABfAFMAbwB1AHIAYwBlACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AQwBoAGUAbQBpAGMAYQBsAEcAVwBQAF8ARABhAHQAYQAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABHAFcAUABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AQwBoAGUAbQBpAGMAYQBsAEIAbABlAG4AZABzAF8AVABpAHQAbABlACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AQwBoAGUAbQBpAGMAYQBsAEIAbABlAG4AZABzAF8ARABlAHMAYwByAGkAcAB0AGkAbwBuACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AQwBoAGUAbQBpAGMAYQBsAEIAbABlAG4AZABzAF8AUwBvAHUAcgBjAGUAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBDAGgAZQBtAGkAYwBhAGwAQgBsAGUAbgBkAHMAXwBEAGEAdABhACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AQwBoAGUAbQBpAGMAYQBsAEIAbABlAG4AZABzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBMAGUAYQBrAGEAZwBlAFIAYQB0AGUAcwBfAFQAaQB0AGwAZQAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEwAZQBhAGsAYQBnAGUAUgBhAHQAZQBzAF8ARABlAHMAYwByAGkAcAB0AGkAbwBuACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ATABlAGEAawBhAGcAZQBSAGEAdABlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEwAZQBhAGsAYQBnAGUAUgBhAHQAZQBzAF8ARABhAHQAYQAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEwAZQBhAGsAYQBnAGUAUgBhAHQAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAYQBsAGMAdQBsAGEAdABlAEIAbABlAG4AZABHAFcAUAAiAF0ALAAiAGwAbwBjAGEAbABlACIAOgB7ACIAbABpAHMAdABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHIAbwB3AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAYwBvAGwAdQBtAG4AUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHQAaABvAHUAcwBhAG4AZABzAFAAbwBzAGkAdABpAG8AbgBzACIAOgBbADMAXQAsACIAZABlAGMAaQBtAGEAbABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAuACIALAAiAGQAYQB0AGUATwByAGQAZQByACIAOgAiAEQATQBZACIALAAiAGMAdQByAHIAZQBuAGMAeQBTAHkAbQBiAG8AbAAiADoAIgAkACIALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwATABlAGEAZAAiADoAdAByAHUAZQAsACIAaQBzAEMAdQByAHIAZQBuAGMAeQBTAGUAcABCAHkAUwBwAGEAYwBlACIAOgBmAGEAbABzAGUALAAiAHIAbwB3AEwAZQB0AHQAZQByACIAOgAiAFIAIgAsACIAYwBvAGwAdQBtAG4ATABlAHQAdABlAHIAIgA6ACIAQwAiACwAIgByAGMATABlAGYAdABCAHIAYQBjAGsAZQB0ACIAOgAiAFsAIgAsACIAcgBjAFIAaQBnAGgAdABCAHIAYQBjAGsAZQB0ACIAOgAiAF0AIgAsACIAcwB0AGEAdABlAG0AZQBuAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIAOwAiACwAIgBsAG8AYwBhAGwAZQBOAGEAbQBlACIAOgAiAGUAbgAtAHUAcwAiAH0AfQA=</AFEJSONBlob>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
@@ -19339,9 +19367,12 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="09eef6d6-daa8-4301-8f9f-b1ec38079286"/>
+    <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -19355,12 +19386,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="09eef6d6-daa8-4301-8f9f-b1ec38079286"/>
-    <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
